--- a/vragen/vragen_review_compleet.xlsx
+++ b/vragen/vragen_review_compleet.xlsx
@@ -122,7 +122,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -146,6 +146,7 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
     <xf numFmtId="0" fontId="7" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Standaard" xfId="0" builtinId="0"/>
@@ -618,7 +619,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q1459"/>
+  <dimension ref="A1:R1459"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -637,6 +638,7 @@
     <col width="46" customWidth="1" min="15" max="15"/>
     <col width="46" customWidth="1" min="16" max="16"/>
     <col width="46" customWidth="1" min="17" max="17"/>
+    <col width="16" customWidth="1" min="18" max="18"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -725,6 +727,11 @@
           <t>Controle</t>
         </is>
       </c>
+      <c r="R1" s="11" t="inlineStr">
+        <is>
+          <t>Vertrouwen bron</t>
+        </is>
+      </c>
     </row>
     <row r="2" ht="25" customHeight="1">
       <c r="A2" s="4" t="n">
@@ -1014,6 +1021,11 @@
           <t>Een schrikkeljaar is een kalenderjaar met 366 dagen in plaats van 365.</t>
         </is>
       </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="n">
@@ -1470,6 +1482,11 @@
           <t>Wikidata: klopt</t>
         </is>
       </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="n">
@@ -1572,6 +1589,11 @@
           <t>Olympus was founded on October 12, 1919 as Takachiho Seisakusho by Takeshi Yamashita, initially specializing in microscopes and thermometers, and later in imaging.</t>
         </is>
       </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="n">
@@ -1626,6 +1648,11 @@
           <t>Het paleis heeft 775 kamers (waarvan 78 badkamers), 1514 deuren en ruim 760 vensters, die om de zes weken worden gereinigd.</t>
         </is>
       </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="n">
@@ -1680,6 +1707,11 @@
           <t>The Burj Khalifa has 57 elevators and 8 escalators.</t>
         </is>
       </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="n">
@@ -1739,6 +1771,11 @@
           <t>Wikidata: WIJKT AF</t>
         </is>
       </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="n">
@@ -1866,6 +1903,11 @@
           <t>As of 2013, there were two other freestanding structures in the Western Hemisphere exceeding 500 m (1,640.4 ft) in height: the Willis Tower in Chicago, which stands at 527 m (1,729.0 ft) when measured to its pinnacle, and One World Trade Center in New York City, which has a pinnacle height of 541.33</t>
         </is>
       </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="25" ht="25" customHeight="1">
       <c r="A25" s="4" t="n">
@@ -1952,6 +1994,11 @@
       <c r="P26" t="inlineStr">
         <is>
           <t>Het gebouw heeft 88 verdiepingen.</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>hoog</t>
         </is>
       </c>
     </row>
@@ -2007,6 +2054,11 @@
 Taipei 101, een wolkenkrabber in de Taiwanese hoofdstad</t>
         </is>
       </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="4" t="n">
@@ -2061,6 +2113,11 @@
           <t>In totaal heeft het gebouw 163 verdiepingen.</t>
         </is>
       </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="29" ht="25" customHeight="1">
       <c r="A29" s="4" t="n">
@@ -2110,6 +2167,11 @@
           <t>De zaal telde 134 zuilen die ongeveer 15 meter hoog zijn.</t>
         </is>
       </c>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="30" ht="25" customHeight="1">
       <c r="A30" s="4" t="n">
@@ -2196,6 +2258,11 @@
       <c r="P31" t="inlineStr">
         <is>
           <t>The Great Barrier Reef is the world's largest coral reef system, composed of over 2,900 individual reefs and 900 islands stretching for over 2,300 kilometres (1,400 mi) over an area of approximately 344,400 square kilometres (133,000 mi2).</t>
+        </is>
+      </c>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>hoog</t>
         </is>
       </c>
     </row>
@@ -2296,6 +2363,11 @@
 Reto-Romaans, als hoofdtaal gesproken door 0,6% van de bevo</t>
         </is>
       </c>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="4" t="n">
@@ -2466,6 +2538,11 @@
         <is>
           <t>Geschiedenis
 Hoewel er al veel eerder vermoedens bestonden over een zuidelijk continent, werd Antarctica pas in 1820 "ontdekt".</t>
+        </is>
+      </c>
+      <c r="R37" t="inlineStr">
+        <is>
+          <t>hoog</t>
         </is>
       </c>
     </row>
@@ -2598,6 +2675,11 @@
 Thomas Jefferson schreef de onafhankelijkheidsverklaring op papier met het watermerk LvG, de initialen van de Veluwse papiermaker Lubbert van Gerrevink, eigenaar van molens bij Vaasse</t>
         </is>
       </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="4" t="n">
@@ -2647,6 +2729,11 @@
           <t>In 1815 nam Wellington, de bevelhebber van het Brits-Nederlandse leger, na de Slag bij Quatre-Bras zijn intrek in de Bodenghien-herberg.</t>
         </is>
       </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="4" t="n">
@@ -2696,6 +2783,11 @@
           <t>De Magna Carta Libertatum (Grote Oorkonde van de Vrijheid) is de naam van een leenovereenkomst naar feodaal recht die de Engelse koning Jan zonder Land op 15 juni 1215 bezegelde, waarin regels zijn vastgelegd over zaken als vrijheden voor de kerk en de edelen, rechtspraak op basis van wetgeving en b</t>
         </is>
       </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="4" t="n">
@@ -2784,6 +2876,11 @@
           <t>Op 17 januari 2009 bereikte de toren zijn hoogste punt, met een hoogte van 828 meter.</t>
         </is>
       </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="4" t="n">
@@ -2823,6 +2920,21 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>https://nl.wikipedia.org/wiki/Mona_Lisa</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>| breedte = 53</t>
+        </is>
+      </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="4" t="n">
@@ -2989,6 +3101,11 @@
           <t>Na de oprichting in 1886 in de Verenigde Staten is het bedrijf nu actief in meer dan 200 landen.</t>
         </is>
       </c>
+      <c r="R49" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="50" ht="25" customHeight="1">
       <c r="A50" s="4" t="n">
@@ -3231,6 +3348,11 @@
       <c r="P55" t="inlineStr">
         <is>
           <t>Twee lijnstukken in elkaars verlengde vormen een hoek van een halve cirkel, dus van 180°.</t>
+        </is>
+      </c>
+      <c r="R55" t="inlineStr">
+        <is>
+          <t>hoog</t>
         </is>
       </c>
     </row>
@@ -3293,6 +3415,11 @@
 20: Henry Mancini, Bruce Springsteen, Pat</t>
         </is>
       </c>
+      <c r="R56" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="4" t="n">
@@ -3347,6 +3474,11 @@
           </t>
         </is>
       </c>
+      <c r="R57" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="4" t="n">
@@ -3542,6 +3674,21 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>https://nl.wikipedia.org/wiki/Rotterdam</t>
+        </is>
+      </c>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>In 1970 werd de Euromast verhoogd door de toevoeging van een Space Tower, waarmee de totale hoogte op 185 meter kwam.</t>
+        </is>
+      </c>
+      <c r="R62" t="inlineStr">
+        <is>
+          <t>matig</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="4" t="n">
@@ -3630,6 +3777,11 @@
           <t>In de 15e eeuw was Amsterdam uitgegroeid tot de belangrijkste handelsstad van Holland.</t>
         </is>
       </c>
+      <c r="R64" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="4" t="n">
@@ -3679,6 +3831,11 @@
           <t>Een kandidaat moet minimaal 270 van de 538 kiesmannen behalen om de verkiezing te winnen.</t>
         </is>
       </c>
+      <c r="R65" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="4" t="n">
@@ -3728,6 +3885,11 @@
           <t>Het ICJ bestaat uit 15 rechters die worden gekozen door de Algemene Vergadering en de Veiligheidsraad.</t>
         </is>
       </c>
+      <c r="R66" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="4" t="n">
@@ -4167,6 +4329,11 @@
           <t>De eerste groep wordt verder onderverdeeld in spelen met een kaartspel bestaande uit bijvoorbeeld 32, 52 of 54 kaarten.</t>
         </is>
       </c>
+      <c r="R77" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="4" t="n">
@@ -4216,6 +4383,11 @@
           <t>The modern editions of the Tour de France consist of 21 day-long stages over a 23- or 24-day period and cover approximately 3,500 kilometres (2,200 mi) total.</t>
         </is>
       </c>
+      <c r="R78" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="4" t="n">
@@ -4265,6 +4437,11 @@
           <t>Deze score levert 5 punten op.</t>
         </is>
       </c>
+      <c r="R79" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="4" t="n">
@@ -4353,6 +4530,11 @@
           <t>Sinds 1964 leveren radarwaarnemingen van het oppervlak een veel tragere, maar eveneens retrograde rotatieperiode van 243 aardse dagen.</t>
         </is>
       </c>
+      <c r="R81" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="4" t="n">
@@ -4402,6 +4584,11 @@
           <t>With a significant axial tilt of 25 degrees, Mars experiences seasons, like Earth (which has an axial tilt of 23.5 degrees).</t>
         </is>
       </c>
+      <c r="R82" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="4" t="n">
@@ -4451,6 +4638,11 @@
           <t>De siderische periode is 687 (aardse) dagen (of 1,8809 aardse jaren), dit is de tijd die Mars nodig heeft om een omloop rond de zon te voltooien.</t>
         </is>
       </c>
+      <c r="R83" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="4" t="n">
@@ -4500,6 +4692,11 @@
           <t>De eerste exoplaneet rond een normale ster werd in 1995 door de Zwitserse astronoom Michel Mayor bij de ster 51 Pegasi in het sterrenbeeld Pegasus ontdekt en wordt sindsdien 51 Pegasi b genoemd.</t>
         </is>
       </c>
+      <c r="R84" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="4" t="n">
@@ -4628,6 +4825,11 @@
 Users of the language write Modern Hebrew from right to left using the Hebrew alphabet – an "impure" abjad, or consonant-only script, of 22 letters.</t>
         </is>
       </c>
+      <c r="R87" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="4" t="n">
@@ -4716,6 +4918,11 @@
           <t>Het heeft 29 letters.</t>
         </is>
       </c>
+      <c r="R89" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="4" t="n">
@@ -4806,6 +5013,11 @@
 De originele Nintendo Game Boy: De 8 bit-versie uit 1989 kwam uit in de Benelux in 1990.</t>
         </is>
       </c>
+      <c r="R91" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="4" t="n">
@@ -4895,6 +5107,11 @@
 Rond 1450 werd in Zuid-Duitsland voor het eerst gebruikgemaakt van losse letters om teksten te vormen die dan afgedrukt konden worden; dit staat bekend als de boekdrukkunst.</t>
         </is>
       </c>
+      <c r="R93" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="4" t="n">
@@ -5066,6 +5283,11 @@
           <t>Wikidata: klopt</t>
         </is>
       </c>
+      <c r="R97" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="4" t="n">
@@ -5154,6 +5376,11 @@
           <t>Schiphol P6 Valet Parking, voornamelijk gericht op het gemak voor de reiziger.</t>
         </is>
       </c>
+      <c r="R99" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="4" t="n">
@@ -5203,6 +5430,11 @@
           <t>In 2015, Airbus said development costs were €15 billion (£11.4 billion, $16.64 billion), though analysts believe the figure is likely to be at least €5bn ($5.55 Bn) more for a €20 Bn ($22.19 Bn) total.</t>
         </is>
       </c>
+      <c r="R100" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="4" t="n">
@@ -5252,6 +5484,11 @@
           <t>De Eerste Wereldoorlog, voor het uitbreken van de Tweede Wereldoorlog in 1939 nog de Grote Oorlog genoemd, was een wereldoorlog die in Europa begon op 28 juli 1914 en tot 11 november 1918 om 11:00 duurde.</t>
         </is>
       </c>
+      <c r="R101" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="4" t="n">
@@ -5302,6 +5539,11 @@
 De eerste stoomlocomotief ter wereld werd in 1804 door Richard Trevithick in Engeland gebouwd.</t>
         </is>
       </c>
+      <c r="R102" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="4" t="n">
@@ -6132,6 +6374,11 @@
 Een volwassen mens heeft normaal 32 gebitselementen, waarvan 16 in de boven- en 16 in de onderkaak.</t>
         </is>
       </c>
+      <c r="R123" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" s="4" t="n">
@@ -6181,6 +6428,11 @@
           <t>De menselijke wervelkolom, ook wel ruggengraat genoemd, of columna vertebralis is, in het menselijke lichaam in de anatomische houding, een verticale kolom door het midden van de rug, die uit 33 of 34 wervels bestaat, met behalve tussen de bovenste twee, de atlas en de axis, tussen elke twee wervels</t>
         </is>
       </c>
+      <c r="R124" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" s="4" t="n">
@@ -6269,6 +6521,11 @@
           <t>Op 3 december 1967 werd de harttransplantatie uitgevoerd in het Groote Schuur-Hospitaal in Kaapstad door een team van 31 artsen.</t>
         </is>
       </c>
+      <c r="R126" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" s="4" t="n">
@@ -6435,6 +6692,11 @@
           <t>Het dijklichaam van de Afsluitdijk is 32 km lang, gemeten van kust tot kust, en ongeveer 90 meter breed.</t>
         </is>
       </c>
+      <c r="R130" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" s="4" t="n">
@@ -6485,6 +6747,11 @@
 Completed at the beginning of March 1951 and published 7 September 1953, The Silver Chair is the first Narnia book not involving the Pevensie children, focusing instead on Eustace.</t>
         </is>
       </c>
+      <c r="R131" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" s="4" t="n">
@@ -6613,6 +6880,11 @@
 Afhankelijk van welke vorm binnen het christendom een Bijbel dient, bevat de Bijbel tussen de 66 en 81 boeken, en bevat ongeveer 800.000 à 900.000 woorden.</t>
         </is>
       </c>
+      <c r="R134" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" s="4" t="n">
@@ -6662,6 +6934,11 @@
           <t>Het Nieuwe Testament (Koinè: Ἡ καινὴ διαθήκη, Hē kainḕ diathḗkē; Latijn: Novum Testamentum) is het tweede deel van de christelijke Bijbel en bestaat uit 27 werken, 'boeken', die alle in het Koinè Grieks zijn geschreven.</t>
         </is>
       </c>
+      <c r="R135" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" s="4" t="n">
@@ -6711,6 +6988,11 @@
           <t>Opera2Day: De vernuftige edelman Don Quichot van La Mancha, avontuurlijke opera uit 2023.</t>
         </is>
       </c>
+      <c r="R136" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="137" ht="25" customHeight="1">
       <c r="A137" s="4" t="n">
@@ -6759,6 +7041,11 @@
         <is>
           <t>Alternatieve Lord of the Rings-films
 Op 3 mei 2009 werd de eerste fanfilm van The Lord of the Rings uitgebracht onder de titel The Hunt for Gollum.</t>
+        </is>
+      </c>
+      <c r="R137" t="inlineStr">
+        <is>
+          <t>hoog</t>
         </is>
       </c>
     </row>
@@ -6893,6 +7180,11 @@
 Mars (astrologie), een planeet in de astrologi</t>
         </is>
       </c>
+      <c r="R140" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" s="4" t="n">
@@ -6981,6 +7273,11 @@
           <t>Hij schreef 154 sonnetten en een aantal langere gedichten en kan beschouwd worden als de eerste moderne toneelschrijver.</t>
         </is>
       </c>
+      <c r="R142" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="143" ht="25" customHeight="1">
       <c r="A143" s="4" t="n">
@@ -7108,6 +7405,11 @@
           <t>Hoewel de krant met periodieke uitgaven pas opgericht werd in 1620, zijn er publicaties van de Nieuwe Tijdinghen beschikbaar vanaf 1605.</t>
         </is>
       </c>
+      <c r="R145" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" s="4" t="n">
@@ -7157,6 +7459,11 @@
           <t>3 dat België drie gewesten omvat: het Vlaams Gewest (waarin vooral Nederlandstaligen wonen, met in bepaalde gemeenten faciliteiten voor Franstaligen), het Waals Gewest (waarin vooral Franstaligen en de Duitstalige gemeenschap wonen, in bepaalde gemeenten faciliteiten voor de Nederlandstaligen) en he</t>
         </is>
       </c>
+      <c r="R146" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" s="4" t="n">
@@ -7753,6 +8060,11 @@
 De Afrikaanse wilde hond heeft 39 paar homologe chromosomen (2n=78), net als andere hondachtigen.</t>
         </is>
       </c>
+      <c r="R161" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" s="4" t="n">
@@ -7919,6 +8231,11 @@
           <t>Ondanks deze variatie hebben alle honden dezelfde basisanatomie, meestal met krachtige kaken en doorgaans 42 tanden.</t>
         </is>
       </c>
+      <c r="R165" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" s="4" t="n">
@@ -8281,6 +8598,11 @@
 Het valutateken voor de euro (€) werd gepresenteerd door de Europese Commissie op 12 december 1996.</t>
         </is>
       </c>
+      <c r="R174" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" s="4" t="n">
@@ -8447,6 +8769,11 @@
           <t>De Europese Unie (EU) is een uit 27 Europese landen bestaand statenverband.</t>
         </is>
       </c>
+      <c r="R178" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" s="4" t="n">
@@ -8496,6 +8823,11 @@
           <t>Het tarief van de sociale zekerheid voor "gevestigde" zelfstandigen in hoofdberoep bedraagt 21,50% op jaarbasis.</t>
         </is>
       </c>
+      <c r="R179" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" s="4" t="n">
@@ -8546,6 +8878,11 @@
 De 19e eeuw zag de politieke eenwording van Duitsland, maar ook een groei van wetenschappelijke en culturele uitingen.</t>
         </is>
       </c>
+      <c r="R180" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" s="4" t="n">
@@ -8633,6 +8970,11 @@
         <is>
           <t>Begin
 Het ontstaansblok, ook wel genesis block, het eerste blok op de bitcoinblockchain, werd op 3 januari 2009 om 18:15:05 GMT gegenereerd met de tekst: The Times 03/Jan/2009 Chancellor on brink of second bailout for banks.</t>
+        </is>
+      </c>
+      <c r="R182" t="inlineStr">
+        <is>
+          <t>hoog</t>
         </is>
       </c>
     </row>
@@ -8728,6 +9070,11 @@
 Dat wil zeggen: voor één espresso (ook wel een shot genoemd of zo'n 30 ml koffie) wordt water van zo'n 95 °C door 6,5-7,5 gram koffie gestuwd bij een druk van tussen 8 </t>
         </is>
       </c>
+      <c r="R184" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="185" ht="25" customHeight="1">
       <c r="A185" s="4" t="n">
@@ -8845,6 +9192,21 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="O187" t="inlineStr">
+        <is>
+          <t>https://nl.wikipedia.org/wiki/Mars_%28reep%29</t>
+        </is>
+      </c>
+      <c r="P187" t="inlineStr">
+        <is>
+          <t>51 gram.</t>
+        </is>
+      </c>
+      <c r="R187" t="inlineStr">
+        <is>
+          <t>matig</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" s="4" t="n">
@@ -9050,6 +9412,11 @@
           <t>As of 2023, Coca-Cola held a 9% market-share in India while Thums Up and Sprite had a 16% and 20% market share respectively.</t>
         </is>
       </c>
+      <c r="R192" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" s="4" t="n">
@@ -9138,6 +9505,11 @@
           <t>The final instalment of this trilogy was the second film to break the one-billion-dollar barrier and won a total of 11 Oscars (something only two other films in history, Ben-Hur and Titanic, have accomplished), including Best Picture, Best Director and Best Adapted Screenplay.</t>
         </is>
       </c>
+      <c r="R194" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" s="4" t="n">
@@ -9187,6 +9559,11 @@
           <t>Op 11 april ankerde de Titanic tegen de middag voor Queenstown (het tegenwoordige Cobh) in Ierland, waar voornamelijk passagiers met een kaartje voor de derde klas aan boord gingen.</t>
         </is>
       </c>
+      <c r="R195" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" s="4" t="n">
@@ -9270,9 +9647,24 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="O197" t="inlineStr">
+        <is>
+          <t>https://nl.wikipedia.org/wiki/The_Office</t>
+        </is>
+      </c>
+      <c r="P197" t="inlineStr">
+        <is>
+          <t>| afleveringen = 14 ( Lijst van afleveringen van The Office|lijst van afleveringen )</t>
+        </is>
+      </c>
       <c r="Q197" t="inlineStr">
         <is>
           <t>Wikidata: WIJKT AF</t>
+        </is>
+      </c>
+      <c r="R197" t="inlineStr">
+        <is>
+          <t>hoog</t>
         </is>
       </c>
     </row>
@@ -9314,9 +9706,24 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="O198" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Friends</t>
+        </is>
+      </c>
+      <c r="P198" t="inlineStr">
+        <is>
+          <t>| num_episodes = 236 (+ 1 special)</t>
+        </is>
+      </c>
       <c r="Q198" t="inlineStr">
         <is>
           <t>Wikidata: klopt</t>
+        </is>
+      </c>
+      <c r="R198" t="inlineStr">
+        <is>
+          <t>hoog</t>
         </is>
       </c>
     </row>
@@ -9358,9 +9765,24 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="O199" t="inlineStr">
+        <is>
+          <t>https://nl.wikipedia.org/wiki/Game_of_Thrones</t>
+        </is>
+      </c>
+      <c r="P199" t="inlineStr">
+        <is>
+          <t>| afleveringen = 73 ( Lijst van afleveringen van Game of Thrones|lijst van afleveringen )</t>
+        </is>
+      </c>
       <c r="Q199" t="inlineStr">
         <is>
           <t>Wikidata: klopt</t>
+        </is>
+      </c>
+      <c r="R199" t="inlineStr">
+        <is>
+          <t>hoog</t>
         </is>
       </c>
     </row>
@@ -9417,6 +9839,11 @@
           <t>Wikidata: klopt</t>
         </is>
       </c>
+      <c r="R200" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" s="4" t="n">
@@ -9583,6 +10010,11 @@
           <t>Back to the Future: The Game, een avonturenspel dat zich afspeelt 3 maanden na het laatste deel van de trilogie.</t>
         </is>
       </c>
+      <c r="R204" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" s="4" t="n">
@@ -9672,6 +10104,11 @@
 Jurassic World Evolution 3 is een bedrijfssimulatiespel ontwikkeld en uitgegeven door Frontier Developments.</t>
         </is>
       </c>
+      <c r="R206" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" s="4" t="n">
@@ -9726,6 +10163,11 @@
           <t>Wikidata: klopt</t>
         </is>
       </c>
+      <c r="R207" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" s="4" t="n">
@@ -9765,9 +10207,26 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="O208" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/The_Simpsons_season_35</t>
+        </is>
+      </c>
+      <c r="P208">
+        <f>= References ==
+== External links ==
+Official website
+The Simpsons season 35 at IMDb</f>
+        <v/>
+      </c>
       <c r="Q208" t="inlineStr">
         <is>
           <t>Wikidata: bijna</t>
+        </is>
+      </c>
+      <c r="R208" t="inlineStr">
+        <is>
+          <t>matig</t>
         </is>
       </c>
     </row>
@@ -9820,6 +10279,11 @@
 James Bond (gespeeld door Roger Moore) wordt op missie gestuurd om onderzoek te doen naar de moord van drie MI6-agenten in 24 uur tijd.</t>
         </is>
       </c>
+      <c r="R209" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" s="4" t="n">
@@ -9986,6 +10450,11 @@
           <t>Plato refers to Cerberus' composite nature, and Euphorion of Chalcis (3rd century BC) describes Cerberus as having multiple snake tails, and presumably in connection to his serpentine nature, associates Cerberus with the creation of the poisonous aconite plant.</t>
         </is>
       </c>
+      <c r="R213" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="214" ht="25" customHeight="1">
       <c r="A214" s="4" t="n">
@@ -10035,6 +10504,11 @@
           <t>Hunker alleged that "Hydra finds [Within Temptation] further pushing their boundaries, exploring new elements and influences, while at the same time revisiting their heavier metal roots" and gave the album a score of 9.5 out of 10.</t>
         </is>
       </c>
+      <c r="R214" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="215" ht="25" customHeight="1">
       <c r="A215" s="4" t="n">
@@ -10082,6 +10556,11 @@
       <c r="P215" t="inlineStr">
         <is>
           <t>In her examination of the tapestry, scholar Anne Stine Ingstad interprets these birds as Huginn and Muninn flying over a covered cart containing an image of Odin, drawing comparison to the images of Nerthus attested by Tacitus in 1 CE.</t>
+        </is>
+      </c>
+      <c r="R215" t="inlineStr">
+        <is>
+          <t>hoog</t>
         </is>
       </c>
     </row>
@@ -10230,6 +10709,11 @@
 Ext</t>
         </is>
       </c>
+      <c r="R218" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="219">
       <c r="A219" s="4" t="n">
@@ -10355,6 +10839,11 @@
       <c r="P221" t="inlineStr">
         <is>
           <t>The main roadway across the bridge is known as the Bradfield Highway and is about 2.4 km (1.5 mi) long, making it one of the shortest highways in Australia.</t>
+        </is>
+      </c>
+      <c r="R221" t="inlineStr">
+        <is>
+          <t>hoog</t>
         </is>
       </c>
     </row>
@@ -10542,6 +11031,11 @@
 Ext</t>
         </is>
       </c>
+      <c r="R225" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="226">
       <c r="A226" s="4" t="n">
@@ -10713,6 +11207,11 @@
           <t>Andere grote religieuze groeperingen in Londen zijn moslims (8,5%), hindoes (4,1%), joden (2,1%), sikhs (1,5%), boeddhisten (0,8%), paganisten (0,3%) en overige (0,2%).</t>
         </is>
       </c>
+      <c r="R229" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="230">
       <c r="A230" s="4" t="n">
@@ -10762,6 +11261,11 @@
           <t>Van de 73 liften gaat er niet één rechtstreeks naar de bovenste verdieping.</t>
         </is>
       </c>
+      <c r="R230" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="231">
       <c r="A231" s="4" t="n">
@@ -10816,6 +11320,11 @@
           <t>Wikidata: WIJKT AF</t>
         </is>
       </c>
+      <c r="R231" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="232">
       <c r="A232" s="4" t="n">
@@ -10914,6 +11423,11 @@
           <t>Wikidata: bijna</t>
         </is>
       </c>
+      <c r="R233" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="234">
       <c r="A234" s="4" t="n">
@@ -11010,6 +11524,11 @@
       <c r="Q235" t="inlineStr">
         <is>
           <t>Wikidata: klopt</t>
+        </is>
+      </c>
+      <c r="R235" t="inlineStr">
+        <is>
+          <t>hoog</t>
         </is>
       </c>
     </row>
@@ -11119,6 +11638,11 @@
           <t>Wikidata: klopt</t>
         </is>
       </c>
+      <c r="R237" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="238">
       <c r="A238" s="4" t="n">
@@ -11251,6 +11775,11 @@
           <t>De luchthaven nam vanaf 6 april 2019 alle passagiersvluchten van en naar Istanbul verzorgd door Turkish Airlines van de twee andere luchthavens over, en groeide in 2019 verder om zo de passagiersvluchten op Ataturk volledig te vervangen en de vluchten op Sabiha Gökçen te verlichten.</t>
         </is>
       </c>
+      <c r="R240" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="241">
       <c r="A241" s="4" t="n">
@@ -11378,6 +11907,11 @@
           <t>De cavea bood plaats aan meer dan 50.000 toeschouwers.</t>
         </is>
       </c>
+      <c r="R243" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="244">
       <c r="A244" s="4" t="n">
@@ -11428,6 +11962,11 @@
 Claude Gauvard, Notre-Dame de Paris (coll.</t>
         </is>
       </c>
+      <c r="R244" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="245" ht="25" customHeight="1">
       <c r="A245" s="4" t="n">
@@ -11516,6 +12055,11 @@
           <t>The structure was designed to withstand wind pressures of 56 lb per square foot (2.7 kPa), a design constraint introduced following the Tay Bridge disaster which had occurred just 15 years before the opening of Tower Bridge.</t>
         </is>
       </c>
+      <c r="R246" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="247" ht="25" customHeight="1">
       <c r="A247" s="4" t="n">
@@ -11643,6 +12187,11 @@
           <t>Het gebouw heeft een hoogte van 632 meter en telt 128 verdiepingen boven de grond en 5 verdiepingen onder de grond.</t>
         </is>
       </c>
+      <c r="R249" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="250">
       <c r="A250" s="4" t="n">
@@ -11693,6 +12242,11 @@
 De toren heeft 102 verdiepingen.</t>
         </is>
       </c>
+      <c r="R250" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="251">
       <c r="A251" s="4" t="n">
@@ -11742,6 +12296,11 @@
           <t>De verhouding van de zuilen van de buitenste colonnade is 8 × 17 en deze telt in totaal 46 zuilen.</t>
         </is>
       </c>
+      <c r="R251" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="252" ht="25" customHeight="1">
       <c r="A252" s="4" t="n">
@@ -11869,6 +12428,11 @@
           <t>Het Empire State Building is een 381 meter hoge wolkenkrabber in New York.</t>
         </is>
       </c>
+      <c r="R254" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="255">
       <c r="A255" s="4" t="n">
@@ -11918,6 +12482,11 @@
           <t>De toren heeft een hoogte van 330 meter, met zijn 116 antennes.</t>
         </is>
       </c>
+      <c r="R255" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="256" ht="25" customHeight="1">
       <c r="A256" s="4" t="n">
@@ -11968,6 +12537,11 @@
 Het 46 meter hoge beeld (93 meter als de sokkel wordt meegerekend) met een gewicht van 225 ton was een geschenk van Frankrijk ter ere van het eeuwfeest van de Amerikaanse Onafhankelijkheidsverklaring en ook als teken van vriendschap.</t>
         </is>
       </c>
+      <c r="R256" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="257">
       <c r="A257" s="4" t="n">
@@ -12017,6 +12591,11 @@
           <t>Het Suezkanaal (Arabisch: قناة السويس Qanâ el Suweis) is een 193 km lang kanaal in de Landengte van Suez in Egypte, officieel geopend in 1869.</t>
         </is>
       </c>
+      <c r="R257" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="258" ht="25" customHeight="1">
       <c r="A258" s="4" t="n">
@@ -12183,6 +12762,11 @@
           <t>Duitsland telt 16 nationale parken en meer dan 100 natuurparken.</t>
         </is>
       </c>
+      <c r="R261" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="262" ht="25" customHeight="1">
       <c r="A262" s="4" t="n">
@@ -12232,6 +12816,11 @@
           <t>De archipel bestaat uit 7641 eilanden, waarvan de grootste twee Luzon en Mindanao zijn.</t>
         </is>
       </c>
+      <c r="R262" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="263">
       <c r="A263" s="4" t="n">
@@ -12281,6 +12870,11 @@
           <t>3 dat België drie gewesten omvat: het Vlaams Gewest (waarin vooral Nederlandstaligen wonen, met in bepaalde gemeenten faciliteiten voor Franstaligen), het Waals Gewest (waarin vooral Franstaligen en de Duitstalige gemeenschap wonen, in bepaalde gemeenten faciliteiten voor de Nederlandstaligen) en he</t>
         </is>
       </c>
+      <c r="R263" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="264">
       <c r="A264" s="4" t="n">
@@ -12332,6 +12926,11 @@
 A member state of the United Nations since 1956, Japan is one of the G4 countries seeking reform of the Security Council.</t>
         </is>
       </c>
+      <c r="R264" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="265">
       <c r="A265" s="4" t="n">
@@ -12474,6 +13073,11 @@
           <t>Wikidata: klopt</t>
         </is>
       </c>
+      <c r="R267" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="268">
       <c r="A268" s="4" t="n">
@@ -12660,6 +13264,11 @@
           <t>Wikidata: geen waarde</t>
         </is>
       </c>
+      <c r="R271" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="272" ht="25" customHeight="1">
       <c r="A272" s="4" t="n">
@@ -12758,6 +13367,11 @@
           <t>Wikidata: ander onderwerp</t>
         </is>
       </c>
+      <c r="R273" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="274">
       <c r="A274" s="4" t="n">
@@ -12973,6 +13587,11 @@
           <t>Aan de Jordaanse kant van de Dode Zee produceert Arab Potash (APC), gevormd in 1956, jaarlijks 2,0 miljoen ton potas, evenals natriumchloride en broom.</t>
         </is>
       </c>
+      <c r="R278" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="279">
       <c r="A279" s="4" t="n">
@@ -13102,6 +13721,11 @@
 de Tjoeleni-eilanden zijn een archipel van 5 eilanden in het noordoosten van de Kaspische Zee.</t>
         </is>
       </c>
+      <c r="R281" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="282">
       <c r="A282" s="4" t="n">
@@ -13346,6 +13970,11 @@
           <t>De verdragen zijn voor 29 landen in werking getreden.</t>
         </is>
       </c>
+      <c r="R287" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="288">
       <c r="A288" s="4" t="n">
@@ -13510,6 +14139,11 @@
       <c r="P291" t="inlineStr">
         <is>
           <t>Alleen de Noorse geul, een smal gebied van de Noordelijke Noordzee voor Noorwegen, is veel dieper (zo'n 700 meter) en is daarom geen onderdeel meer van het continent Europa.</t>
+        </is>
+      </c>
+      <c r="R291" t="inlineStr">
+        <is>
+          <t>hoog</t>
         </is>
       </c>
     </row>
@@ -13611,6 +14245,11 @@
 Winners </t>
         </is>
       </c>
+      <c r="R293" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="294">
       <c r="A294" s="4" t="n">
@@ -13660,6 +14299,11 @@
           <t>Ongeveer 1,4 miljard van hen leven in de Volksrepubliek China, dat daarmee qua inwoners na India het grootste land ter wereld is.</t>
         </is>
       </c>
+      <c r="R294" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="295" ht="25" customHeight="1">
       <c r="A295" s="4" t="n">
@@ -13709,6 +14353,11 @@
           <t>34 daarvan bestaan thans nog en zijn als tastbare herinnering aan dit enorme project op de Werelderfgoedlijst van UNESCO geplaatst als de Geodetische boog van Struve.</t>
         </is>
       </c>
+      <c r="R295" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="296">
       <c r="A296" s="4" t="n">
@@ -13797,6 +14446,11 @@
           <t>Rusland telt 11 tijdzones, van UTC+2 tot UTC+12, en heeft daarmee het grootste aantal opeenvolgende tijdzones ter wereld.</t>
         </is>
       </c>
+      <c r="R297" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="298">
       <c r="A298" s="4" t="n">
@@ -13851,6 +14505,11 @@
           <t>Wikidata: bijna</t>
         </is>
       </c>
+      <c r="R298" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="299">
       <c r="A299" s="4" t="n">
@@ -13905,6 +14564,11 @@
           <t>Wikidata: klopt</t>
         </is>
       </c>
+      <c r="R299" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="300">
       <c r="A300" s="4" t="n">
@@ -14003,6 +14667,11 @@
           <t>Wikidata: klopt</t>
         </is>
       </c>
+      <c r="R301" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="302">
       <c r="A302" s="4" t="n">
@@ -14141,6 +14810,11 @@
 De eerste personen die de geografische noordpool zouden hebben bereikt op 6 april 1909 zijn Robert Edwin Peary, Matthew Henson en vier Inuit genaamd Ootah, Seegloo, Egingway, en Ooqueah.</t>
         </is>
       </c>
+      <c r="R304" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="305">
       <c r="A305" s="4" t="n">
@@ -14191,6 +14865,11 @@
 De eerste mensen die de geografische zuidpool bereikten, waren de Noor Roald Amundsen en diens ploeg op 14 december 1911.</t>
         </is>
       </c>
+      <c r="R305" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="306">
       <c r="A306" s="4" t="n">
@@ -14240,6 +14919,11 @@
           <t>1953 - De eersten die de Everest beklommen en levend terugkwamen waren de Nieuw-Zeelander Edmund Hillary en sherpa Tenzing Norgay.</t>
         </is>
       </c>
+      <c r="R306" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="307">
       <c r="A307" s="4" t="n">
@@ -14367,6 +15051,11 @@
           <t>It has a recognized length of 6,400 kilometers (4,000 mi), but according to some reports, its length varies from 6,575 to 7,062 kilometers (4,086 to 4,388 mi).</t>
         </is>
       </c>
+      <c r="R309" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="310">
       <c r="A310" s="4" t="n">
@@ -14417,6 +15106,11 @@
 De oppervlakte van de Sahara bedraagt ongeveer 9.065.000 vierkante kilometer.</t>
         </is>
       </c>
+      <c r="R310" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="311">
       <c r="A311" s="4" t="n">
@@ -14701,6 +15395,11 @@
 Het duurde ruim 28 jaar voor de inwoners van Oost-Duitsland zich door de Muur niet meer lieten tegenhouden.</t>
         </is>
       </c>
+      <c r="R317" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="318">
       <c r="A318" s="4" t="n">
@@ -14749,6 +15448,11 @@
         <is>
           <t>De oorlog
 Het conflict duurde 116 jaar, onderbroken door verscheidene periodes van vrede, voordat het uiteindelijk eindigde door het verdrijven van de Plantagenets uit Frankrijk (behalve uit Calais).</t>
+        </is>
+      </c>
+      <c r="R318" t="inlineStr">
+        <is>
+          <t>hoog</t>
         </is>
       </c>
     </row>
@@ -15040,6 +15744,11 @@
 Bestuurlijke indeling
 Sinds de Onafhankelijkheidsverklaring in 1776, waarbij de VS bestond uit 13 staten, groeide het land uit tot vijftig staten:
 Alabama - Alaska - Arizona - Arkansas - Californië - Colorado - Connecticut - Delaware - Florida - Georgia - Hawaï - Idaho - Illinois - Indi</t>
+        </is>
+      </c>
+      <c r="R325" t="inlineStr">
+        <is>
+          <t>hoog</t>
         </is>
       </c>
     </row>
@@ -15143,6 +15852,11 @@
 Russische Socialistische Federatieve Sovjetrepubliek (R</t>
         </is>
       </c>
+      <c r="R327" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="328">
       <c r="A328" s="4" t="n">
@@ -15424,6 +16138,11 @@
       <c r="P334" t="inlineStr">
         <is>
           <t>Tijdens de slag bij Verdun zijn in totaal 2.000.000 Franse soldaten langs deze weg vervoerd, samen met meer dan 1.000.000 ton munitie.</t>
+        </is>
+      </c>
+      <c r="R334" t="inlineStr">
+        <is>
+          <t>hoog</t>
         </is>
       </c>
     </row>
@@ -15517,6 +16236,11 @@
 Alabama - Alaska - Arizona - Arkansas - Californië - Colorado - Connecticut - Delaware - Florida - Georgia - Hawaï - Idaho - Illinois - Indi</t>
         </is>
       </c>
+      <c r="R336" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="337">
       <c r="A337" s="4" t="n">
@@ -15566,6 +16290,11 @@
           <t>De Franse Revolutie (1789–1799) was een internationaal invloedrijke politieke omwenteling, waarbij de absolute monarchie die Frankrijk ongeveer twee eeuwen had geregeerd werd afgeschaft, en de Eerste Franse Republiek werd gesticht.</t>
         </is>
       </c>
+      <c r="R337" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="338" ht="25" customHeight="1">
       <c r="A338" s="4" t="n">
@@ -15615,6 +16344,11 @@
           <t>Hij maakte naam door zijn ontdekking van Amerika onder Spaanse vlag in 1492.</t>
         </is>
       </c>
+      <c r="R338" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="339">
       <c r="A339" s="4" t="n">
@@ -15664,6 +16398,11 @@
           <t>De Tweede Wereldoorlog was de escalatie van de Tweede Chinees-Japanse Oorlog die begon in 1937 en een Europese oorlog begonnen in 1939 tot een militair conflict dat van 1941 tot 1945 op wereldschaal werd uitgevochten tussen twee allianties: de asmogendheden en de geallieerden.</t>
         </is>
       </c>
+      <c r="R339" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="340">
       <c r="A340" s="4" t="n">
@@ -15713,6 +16452,11 @@
           <t>De Slag bij Hastings werd op 14 oktober 1066 uitgevochten tussen een Normandisch-Frans leger onder leiding van hertog Willem I van Normandië en een leger onder leiding van de Angelsaksische koning Harold II.</t>
         </is>
       </c>
+      <c r="R340" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="341">
       <c r="A341" s="4" t="n">
@@ -15762,6 +16506,11 @@
           <t>De kernramp van Fukushima (Japans: 福島第一原子力発電所事故 Fukushima daiichi genshiryoku hatsudensho jiko) rond de kerncentrale Fukushima I in Ōkuma, Japan was het gevolg van de zeebeving en de daaropvolgende tsunami van 11 maart 2011.</t>
         </is>
       </c>
+      <c r="R341" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="342">
       <c r="A342" s="4" t="n">
@@ -15811,6 +16560,11 @@
           <t>Het ongeval gebeurde op 26 april 1986 nabij de Oekraïense (toen nog deel van de Sovjet-Unie) steden Tsjernobyl en Pripjat, vlak bij de grens met Wit-Rusland.</t>
         </is>
       </c>
+      <c r="R342" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="343">
       <c r="A343" s="4" t="n">
@@ -15860,6 +16614,11 @@
           <t>De prijs werd ingesteld in 1895 in het testament van Alfred Nobel, en in 1901 na zijn overlijden voor het eerst uitgereikt.</t>
         </is>
       </c>
+      <c r="R343" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="344">
       <c r="A344" s="4" t="n">
@@ -15909,6 +16668,11 @@
           <t>Titanic was eigendom van rederij White Star Line en kwam in de nacht van 14 op 15 april 1912 op haar eerste reis met bijna volle kracht (in dienst) in aanvaring met een ijsberg.</t>
         </is>
       </c>
+      <c r="R344" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="345">
       <c r="A345" s="4" t="n">
@@ -16024,6 +16788,21 @@
       <c r="N347" s="4" t="inlineStr">
         <is>
           <t>geen bron</t>
+        </is>
+      </c>
+      <c r="O347" t="inlineStr">
+        <is>
+          <t>https://nl.wikipedia.org/wiki/Mona_Lisa</t>
+        </is>
+      </c>
+      <c r="P347" t="inlineStr">
+        <is>
+          <t>| hoogte = 77</t>
+        </is>
+      </c>
+      <c r="R347" t="inlineStr">
+        <is>
+          <t>hoog</t>
         </is>
       </c>
     </row>
@@ -16078,6 +16857,11 @@
 de scheiding van water</t>
         </is>
       </c>
+      <c r="R348" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="349">
       <c r="A349" s="4" t="n">
@@ -16127,6 +16911,11 @@
           <t>The 12 Directors-General of UNESCO have come from seven regions within the organization: West Europe (5), Central America (1), North America (2), West Africa (1), East Asia (1), East Europe (1), Middle East (1).</t>
         </is>
       </c>
+      <c r="R349" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="350">
       <c r="A350" s="4" t="n">
@@ -16283,9 +17072,24 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="O353" t="inlineStr">
+        <is>
+          <t>https://nl.wikipedia.org/wiki/Vrijheidsbeeld_%28New_York%29</t>
+        </is>
+      </c>
+      <c r="P353">
+        <f>= Kenmerken ==
+Het 46 meter hoge beeld (93 meter als de sokkel wordt meegerekend) met een gewicht van 225 ton was een geschenk van Frankrijk ter ere van het eeuwfeest van de Amerikaanse Onafhankelijkheidsverklaring en ook als teken van vriendschap.</f>
+        <v/>
+      </c>
       <c r="Q353" t="inlineStr">
         <is>
           <t>Wikidata: WIJKT AF</t>
+        </is>
+      </c>
+      <c r="R353" t="inlineStr">
+        <is>
+          <t>matig</t>
         </is>
       </c>
     </row>
@@ -16376,6 +17180,11 @@
           <t>Because the Yellow House had to be furnished before he could fully move in, Van Gogh moved from the Hôtel Carrel to the Café de la Gare on 7 May 1888.</t>
         </is>
       </c>
+      <c r="R355" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="356" ht="25" customHeight="1">
       <c r="A356" s="4" t="n">
@@ -16425,6 +17234,11 @@
           <t>In 1647 stelde Rembrandt op verzoek van de familie van zijn vrouw een inventaris op van zijn bezittingen en kwam hij aan een totaal van 40.750 gulden aan kapitaal en bezittingen.</t>
         </is>
       </c>
+      <c r="R356" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="357">
       <c r="A357" s="4" t="n">
@@ -16474,6 +17288,11 @@
           <t>The Great Spa Towns of Europe is a transnational World Heritage Site consisting of a selection of 11 spa towns across seven European countries.</t>
         </is>
       </c>
+      <c r="R357" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="358">
       <c r="A358" s="4" t="n">
@@ -16601,6 +17420,11 @@
           <t>The yield strength of pure aluminium is 7–11 MPa, while aluminium alloys have yield strengths ranging from 200 MPa to 600 MPa.</t>
         </is>
       </c>
+      <c r="R360" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="361">
       <c r="A361" s="4" t="n">
@@ -17157,6 +17981,11 @@
           <t>Op zeeniveau bestaat de lucht voor ongeveer 21% uit zuurstofgas.</t>
         </is>
       </c>
+      <c r="R374" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="375" ht="25" customHeight="1">
       <c r="A375" s="4" t="n">
@@ -17245,6 +18074,11 @@
           <t>De temperatuurschaal van Celsius is gebaseerd op de overgang tussen deze toestanden: bij 0 °C smelt ijs en bij 100 °C kookt water (bij standaarddruk).</t>
         </is>
       </c>
+      <c r="R376" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="377">
       <c r="A377" s="4" t="n">
@@ -17294,6 +18128,11 @@
           <t>Van al het zoetwater op Aarde ligt 68,7% opgeslagen in de vorm van ijs en gletsjers, en 31,0% bevindt zich in de ondergrond als grondwater of permafrost.</t>
         </is>
       </c>
+      <c r="R377" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="378" ht="25" customHeight="1">
       <c r="A378" s="4" t="n">
@@ -17462,6 +18301,11 @@
 "22 Facts About Plastic Pollution (And 10 Things We Can Do About It)".</t>
         </is>
       </c>
+      <c r="R381" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="382">
       <c r="A382" s="4" t="n">
@@ -17672,6 +18516,11 @@
           <t>Hierbij staat de Y voor Yohji, de 3 voor de kenmerkende 3 strepen en het verbindende streepje symboliseert de verbinding tussen de twee.</t>
         </is>
       </c>
+      <c r="R386" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="387" ht="25" customHeight="1">
       <c r="A387" s="4" t="n">
@@ -17799,6 +18648,11 @@
           <t>Op 5 mei 2025 kondigde Bad Bunny Debí Tirar Más Fotos World Tour aan, een wereldtournee van 23 stadionconcerten in Europa, Australië, Japan en Latijns-Amerika, die in november 2025 van start is gegaan.</t>
         </is>
       </c>
+      <c r="R389" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="390">
       <c r="A390" s="4" t="n">
@@ -17848,6 +18702,11 @@
           <t>Brett Barnes (geboren in 1982) was met Jackson bevriend sinds 1991 als 9-jarige jongen.</t>
         </is>
       </c>
+      <c r="R390" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="391" ht="25" customHeight="1">
       <c r="A391" s="4" t="n">
@@ -17897,6 +18756,11 @@
           <t>Wolfgang Amadeus Mozart (Salzburg, 27 januari 1756 – Wenen, 5 december 1791), doopnaam Joannes Chrysostomus Wolfgangus Theophilus Mozart, was een uit het prinsaartsbisdom Salzburg afkomstige componist, pianist, violist en dirigent.</t>
         </is>
       </c>
+      <c r="R391" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="392">
       <c r="A392" s="4" t="n">
@@ -17946,6 +18810,11 @@
           <t>Over het algemeen wordt de 7-snarige gitaar gebruikt om de extra bassnaar toe te voegen aan de 6-snarige hals, dus bij de 'normale' stemming komt er een B-snaar bij.</t>
         </is>
       </c>
+      <c r="R392" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="393">
       <c r="A393" s="4" t="n">
@@ -17995,6 +18864,11 @@
           <t>Over het algemeen wordt de 7-snarige gitaar gebruikt om de extra bassnaar toe te voegen aan de 6-snarige hals, dus bij de 'normale' stemming komt er een B-snaar bij.</t>
         </is>
       </c>
+      <c r="R393" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="394">
       <c r="A394" s="4" t="n">
@@ -18083,6 +18957,11 @@
           <t>Ludwig van Beethoven (Bonn, 15, 16 of 17 december 1770 – Wenen, 26 maart 1827) was een Duitse componist, musicus, virtuoos en dirigent.</t>
         </is>
       </c>
+      <c r="R395" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="396">
       <c r="A396" s="4" t="n">
@@ -18132,6 +19011,11 @@
           <t>Safechuck zegt dat hij vanaf toen, toen hij 10 was, tot zijn veertiende seksueel misbruikt is door Jackson.</t>
         </is>
       </c>
+      <c r="R396" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="397">
       <c r="A397" s="4" t="n">
@@ -18171,6 +19055,21 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="O397" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Queen_discography</t>
+        </is>
+      </c>
+      <c r="P397" t="inlineStr">
+        <is>
+          <t>British rock band Queen have released 15 studio albums, 10 live albums, 16 compilation albums, 2 soundtrack albums, 2 extended plays, 73 singles, and 7 promotional singles.</t>
+        </is>
+      </c>
+      <c r="R397" t="inlineStr">
+        <is>
+          <t>matig</t>
+        </is>
+      </c>
     </row>
     <row r="398">
       <c r="A398" s="4" t="n">
@@ -18221,6 +19120,11 @@
 negen symfonieën, waarvan de 3e Eroïca, de 5e, de 6e Pastorale en de 9e de bekendste zijn.</t>
         </is>
       </c>
+      <c r="R398" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="399">
       <c r="A399" s="4" t="n">
@@ -18465,6 +19369,11 @@
           <t>In massapercentages bestaat de Aarde uit 32,1% ijzer, 30,1% zuurstof, 15,1% silicium, 13,9% magnesium, 2,9% zwavel, 1,8% nikkel, 1,5% calcium, 1,4% aluminium en 1,2% andere elementen.</t>
         </is>
       </c>
+      <c r="R404" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="405" ht="25" customHeight="1">
       <c r="A405" s="4" t="n">
@@ -18553,6 +19462,11 @@
           <t>Een (internationale) zeemijl (Engels: (international) nautical mile, afgekort NM of nmi) is een lengtemaat die gelijk is aan precies 1852 meter.</t>
         </is>
       </c>
+      <c r="R406" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="407">
       <c r="A407" s="4" t="n">
@@ -18641,6 +19555,11 @@
           <t>De aardatmosfeer, en dus de ingeademde lucht, bestaat voor 78% uit distikstof (stikstofgas), en voor 21% uit dizuurstof (zuurstofgas).</t>
         </is>
       </c>
+      <c r="R408" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="409">
       <c r="A409" s="4" t="n">
@@ -18768,6 +19687,11 @@
           <t>Indien de Grondwet afwijkt van het Statuut, kan deze bij gewone wet (dus in één lezing met gewone meerderheden in beide kamers) met het Statuut in overeenstemming worden gebracht (artikel 142 Grondwet).</t>
         </is>
       </c>
+      <c r="R411" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="412">
       <c r="A412" s="4" t="n">
@@ -18900,6 +19824,11 @@
           <t>De Eerste Kamer heeft 75 zetels, de zittingsduur is vier jaar.</t>
         </is>
       </c>
+      <c r="R414" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="415">
       <c r="A415" s="4" t="n">
@@ -18949,6 +19878,11 @@
           <t>The top 5 highest buildings in the Netherlands consist entirely of buildings in Rotterdam.</t>
         </is>
       </c>
+      <c r="R415" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="416" ht="25" customHeight="1">
       <c r="A416" s="4" t="n">
@@ -19037,6 +19971,11 @@
           <t>Elk jaar komen in het weekeind na 12 maart gemiddeld zo'n 5.000 bedevaartgangers naar het Spui en het Begijnhof, alwaar de huidige Heilige Stede voor het Mirakel van Amsterdam is gelegen.</t>
         </is>
       </c>
+      <c r="R417" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="418">
       <c r="A418" s="4" t="n">
@@ -19086,6 +20025,11 @@
           <t>Bestuurlijk is het land verdeeld in twaalf provincies en 342 gemeenten.</t>
         </is>
       </c>
+      <c r="R418" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="419">
       <c r="A419" s="4" t="n">
@@ -19252,6 +20196,11 @@
           <t>De 19 windmolens zijn verdeeld in een rij van acht molens aan de Nederwaard (dit zijn de ronde stenen molens), een rij van acht rietgedekte achtkanters aan de Overwaard, met daarnaast een wipmolen; de Blokweerse molen die de polder Blokweer bemaalt en in de polder Nieuw-Lekkerland twee rietgedekte a</t>
         </is>
       </c>
+      <c r="R422" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="423">
       <c r="A423" s="4" t="n">
@@ -19303,6 +20252,11 @@
 Charles Caspers &amp; Peter Jan Margry (2017), Het Mirakel van Amsterdam.</t>
         </is>
       </c>
+      <c r="R423" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="424" ht="25" customHeight="1">
       <c r="A424" s="4" t="n">
@@ -19352,6 +20306,11 @@
           <t>Bedrag (€)Europese overheidsfinanciering van Europese politieke partijen03.000.0006.000.0009.000.00012.000.00015.000.00018.000.00020042008201220162020ADDEADIEAENMAENAFEALDEAPFCVFEAFECPPECHEDPEVAEGPELAEVPESNEUDLibertasMELDPatriotsPES.mw-chart-80f86eb6bf7c33d66fd67d5885627f2768d3e62d11e59cf422fcb10a36</t>
         </is>
       </c>
+      <c r="R424" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="425">
       <c r="A425" s="4" t="n">
@@ -19401,6 +20360,11 @@
           <t>Sinds de inwerkingtreding van de Grondwet op 4 maart 1789 werden 27 amendementen aan de Grondwet toegevoegd, waaronder één amendement dat een vorig amendement herriep (in verband met de Drooglegging), om zo in te spelen op de veranderende noden in de samenleving sinds het einde van de 18e eeuw.</t>
         </is>
       </c>
+      <c r="R425" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="426" ht="25" customHeight="1">
       <c r="A426" s="4" t="n">
@@ -19489,6 +20453,11 @@
           <t>Artikel 111 van het Handvest van de Verenigde Naties vermeldt dat de Chinese, de Engelse, de Franse, de Russische en de Spaanse tekst van het Handvest gelijkelijk authentiek zijn: sindsdien verschijnen alle documenten in deze vijf talen, en sinds 1973 ook in het Arabisch.</t>
         </is>
       </c>
+      <c r="R427" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="428">
       <c r="A428" s="4" t="n">
@@ -19614,6 +20583,11 @@
       <c r="P430" t="inlineStr">
         <is>
           <t>De Bondsdag bestaat uit 630 afgevaardigden, waarvan er (maximaal) 299 direct in kiesdistricten gekozen worden.</t>
+        </is>
+      </c>
+      <c r="R430" t="inlineStr">
+        <is>
+          <t>hoog</t>
         </is>
       </c>
     </row>
@@ -19673,6 +20647,11 @@
 De resoluties van de Verenigde Naties worden genummerd vanaf het jaar 1946, sinds 1976.</t>
         </is>
       </c>
+      <c r="R431" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="432" ht="25" customHeight="1">
       <c r="A432" s="4" t="n">
@@ -19723,6 +20702,11 @@
 Het Verdrag van Rome werd officieel ondertekend op 25 maart 1957 en trad in werking op 1 januari 1958.</t>
         </is>
       </c>
+      <c r="R432" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="433">
       <c r="A433" s="4" t="n">
@@ -20347,6 +21331,21 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="O448" t="inlineStr">
+        <is>
+          <t>https://nl.wikipedia.org/wiki/Lijst_van_oudste_mensen</t>
+        </is>
+      </c>
+      <c r="P448" t="inlineStr">
+        <is>
+          <t>Sinds 29 augustus 2017 wordt de leeftijdsclaim van Spoto door het Guinness Book of Records niet meer erkend.</t>
+        </is>
+      </c>
+      <c r="R448" t="inlineStr">
+        <is>
+          <t>matig</t>
+        </is>
+      </c>
     </row>
     <row r="449">
       <c r="A449" s="4" t="n">
@@ -20481,6 +21480,11 @@
           <t>Wikidata: geen waarde</t>
         </is>
       </c>
+      <c r="R451" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="452">
       <c r="A452" s="4" t="n">
@@ -20803,6 +21807,11 @@
           <t>Met een capaciteit van 132.000 zitplaatsen is het het grootste stadion ter wereld.</t>
         </is>
       </c>
+      <c r="R459" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="460">
       <c r="A460" s="4" t="n">
@@ -20930,6 +21939,11 @@
           <t>Anno 2026 zijn de elementen met atoomnummer 1 (waterstof) tot en met 118 (oganesson) ontdekt of gesynthetiseerd.</t>
         </is>
       </c>
+      <c r="R462" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="463">
       <c r="A463" s="4" t="n">
@@ -21252,6 +22266,11 @@
           <t>Een kubieke centimeter water heeft een massa van 1 gram.</t>
         </is>
       </c>
+      <c r="R470" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="471">
       <c r="A471" s="4" t="n">
@@ -21301,6 +22320,11 @@
           <t>Zes van de achttien groepen hebben een groepsnaam; zo wordt groep 17 gevormd door de halogenen, terwijl groep 18 alle edelgassen omvat.</t>
         </is>
       </c>
+      <c r="R471" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="472">
       <c r="A472" s="4" t="n">
@@ -21506,6 +22530,11 @@
           <t>IJzer is een scheikundig element met symbool Fe (uit het Latijn: ferrum) en atoomnummer 26.</t>
         </is>
       </c>
+      <c r="R476" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="477">
       <c r="A477" s="4" t="n">
@@ -21594,6 +22623,11 @@
           <t>In Nederlandse versies van het spel zijn de 16 Kanskaarten vaak blauw en de 16 Algemeen fonds-kaarten roze.</t>
         </is>
       </c>
+      <c r="R478" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="479">
       <c r="A479" s="4" t="n">
@@ -21643,6 +22677,11 @@
           <t>Generation I with 151 Pokémon refers to Red, Green, Blue, and Yellow; generation II with 100 Pokémon refers to Gold, Silver, and Crystal; generation III with 135 Pokémon refers to Ruby, Sapphire, FireRed, LeafGreen, and Emerald; generation IV with 107 Pokémon refers to Diamond, Pearl, Platinum, Hear</t>
         </is>
       </c>
+      <c r="R479" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="480">
       <c r="A480" s="4" t="n">
@@ -21692,6 +22731,11 @@
           <t>De officiële regels zeggen dat dezelfde regel geldt in een spel voor 5-6 spelers, maar dat alle spelers aan het eind van iedere beurt mogen kopen wat ze maar willen (dorpen, steden, schepen, kaartjes) tijdens een tussentijdse bouwronde na iedere beurt (andere acties dan kopen zijn niet toegestaan).</t>
         </is>
       </c>
+      <c r="R480" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="481">
       <c r="A481" s="4" t="n">
@@ -21858,6 +22902,11 @@
           <t>Aan het begin van een spel voor 3 of 4 personen bestaat de stapel van 25 ontwikkelingskaarten uit: 14 x ridder, 5 x overwinningspunt, 2 x monopolie, 2 x stratenbouw en 2 x uitvinding.</t>
         </is>
       </c>
+      <c r="R484" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="485" ht="25" customHeight="1">
       <c r="A485" s="4" t="n">
@@ -21986,6 +23035,11 @@
 Bank (4:1): in zijn beurt, mag een speler 4 gelijke grondstoffen ruilen voor één naar keuze.</t>
         </is>
       </c>
+      <c r="R487" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="488" ht="25" customHeight="1">
       <c r="A488" s="4" t="n">
@@ -22231,6 +23285,11 @@
 Het spel wordt gespeeld op een bord bestaande uit 15 × 15 = 225 vakjes, waarbij 61 gekleurde vakjes (8 rode, 17 roze, 24 lichtblauwe en 12 donkerblauwe) een bijzonder karakter hebben.</t>
         </is>
       </c>
+      <c r="R493" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="494">
       <c r="A494" s="4" t="n">
@@ -22319,6 +23378,11 @@
           <t>Elke speler heeft 15 straten tot zijn beschikking.</t>
         </is>
       </c>
+      <c r="R495" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="496">
       <c r="A496" s="4" t="n">
@@ -22368,6 +23432,11 @@
           <t>For example, in 1987 as Williams had an existing contract, they were supplied with the latest 1.5-litre RA167E V6 engine, while Lotus were supplied with the 1986 RA166E engine which had to be adapted to a lower fuel limit and turbo boost restriction, thus limiting its effectiveness, though for the l</t>
         </is>
       </c>
+      <c r="R496" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="497">
       <c r="A497" s="4" t="n">
@@ -22457,6 +23526,11 @@
 Een wedstrijdbaan heeft een lengte van 400 meter, het aantal banen van de rondbaan loopt van 4 tot 9.</t>
         </is>
       </c>
+      <c r="R498" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="499" ht="25" customHeight="1">
       <c r="A499" s="4" t="n">
@@ -22623,6 +23697,11 @@
           <t>Het seizoen erna was Zidane weer een dragende factor voor de Bianconeri, en wist het wederom een landstitel te pakken en de Champions League finale te bereiken, ditmaal tegen Real Madrid (1-0 verlies).</t>
         </is>
       </c>
+      <c r="R502" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="503">
       <c r="A503" s="4" t="n">
@@ -23061,6 +24140,11 @@
         <is>
           <t>Pioneer 10 en 11
 Pioneer 10 was de eerste ruimtesonde naar Jupiter en werd op 3 maart 1972 gelanceerd.</t>
+        </is>
+      </c>
+      <c r="R513" t="inlineStr">
+        <is>
+          <t>hoog</t>
         </is>
       </c>
     </row>
@@ -23120,6 +24204,11 @@
 James Irw</t>
         </is>
       </c>
+      <c r="R514" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="515">
       <c r="A515" s="4" t="n">
@@ -23286,6 +24375,11 @@
           <t>In the 2nd and 3rd century CE, those at Didyma and Claros pronounced the so-called "theological oracles", in which Apollo confirms that all deities are aspects or servants of an all-encompassing, highest deity.</t>
         </is>
       </c>
+      <c r="R518" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="519">
       <c r="A519" s="4" t="n">
@@ -23530,6 +24624,11 @@
           <t>Neptunus heeft de sterkste wind van elke planeet in het zonnestelsel, tot wel 2100 km/h.</t>
         </is>
       </c>
+      <c r="R524" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="525">
       <c r="A525" s="4" t="n">
@@ -23579,6 +24678,11 @@
           <t>In the 2nd and 3rd century CE, those at Didyma and Claros pronounced the so-called "theological oracles", in which Apollo confirms that all deities are aspects or servants of an all-encompassing, highest deity.</t>
         </is>
       </c>
+      <c r="R525" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="526">
       <c r="A526" s="4" t="n">
@@ -23667,6 +24771,11 @@
           <t>De officiële ontdekking staat op naam van William Herschel die op 13 maart 1781 het object als planeet kwalificeerde.</t>
         </is>
       </c>
+      <c r="R527" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="528">
       <c r="A528" s="4" t="n">
@@ -23717,6 +24826,11 @@
 Het zonnestelsel ontstond ongeveer 4,5 miljard jaar geleden, toen een interstellaire gaswolk door onbekende oorzaak actief werd en door zijn eigen gewicht begon te krimpen en steeds sneller rond te draaien, waarna in het midden van deze gaswolk de Zon ontstond.</t>
         </is>
       </c>
+      <c r="R528" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="529">
       <c r="A529" s="4" t="n">
@@ -23883,6 +24997,11 @@
           <t>Op 10 april 2019 werd bekend dat astronomen er met behulp van de Event Horizon Telescope (EHT), een virtuele radiotelescoop zo groot als de Aarde, voor het eerst in geslaagd waren om een echte foto te maken van een zwart gat.</t>
         </is>
       </c>
+      <c r="R532" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="533">
       <c r="A533" s="4" t="n">
@@ -23933,6 +25052,11 @@
 De eerste satelliet die in een baan om de aarde werd gebracht, is de Spoetnik 1 van de Sovjet-Unie op 4 oktober 1957.</t>
         </is>
       </c>
+      <c r="R533" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="534">
       <c r="A534" s="4" t="n">
@@ -24021,6 +25145,11 @@
           <t>Hoewel de diameter van de zon ongeveer 400 keer zo groot is als die van de maan, hebben zon en maan vanaf de Aarde gezien ongeveer dezelfde schijnbare diameter aan de hemel.</t>
         </is>
       </c>
+      <c r="R535" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="536">
       <c r="A536" s="4" t="n">
@@ -24304,6 +25433,11 @@
           <t>Het Arabische alfabet (Arabisch: الأبجدية العربية, al-abdjadiyya al-ʿarabiyya) is een Arabisch schrift dat bestaat uit 28 letters.</t>
         </is>
       </c>
+      <c r="R542" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="543">
       <c r="A543" s="4" t="n">
@@ -24353,6 +25487,11 @@
           <t>Het Mingreels wordt geschreven met 36 letters: dezelfde 33 die het Georgisch gebruikt, één letter die het Georgisch niet meer gebruikt en twee taalspecifieke letters.</t>
         </is>
       </c>
+      <c r="R543" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="544">
       <c r="A544" s="4" t="n">
@@ -24637,6 +25776,11 @@
 YouTube Movies &amp; TV is a video on demand (VOD) service that offers movies and television shows for purchase or rental, depending on availability, along with a selection of movies (encompassing between 100 and 500 titles overall) that are free to stream, with interspersed ad break</t>
         </is>
       </c>
+      <c r="R550" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="551">
       <c r="A551" s="4" t="n">
@@ -24764,6 +25908,11 @@
           <t>Microsoft had in 1982 reeds een rekenblad, MultiPlan, op de markt, maar dat programma brak nooit echt door en werd in 1985 door Excel vervangen.</t>
         </is>
       </c>
+      <c r="R553" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="554">
       <c r="A554" s="4" t="n">
@@ -24813,6 +25962,11 @@
           <t>In augustus 2008 heeft de Nederlander Eric Wijngaard de eerste prijs gewonnen met het programma PicSay, waarmee het mogelijk werd foto's op een Androidapparaat te bewerken.</t>
         </is>
       </c>
+      <c r="R554" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="555">
       <c r="A555" s="4" t="n">
@@ -24862,6 +26016,11 @@
           <t>The brainchild of Sony executive Ken Kutaragi, the brand began with the first PlayStation home console released in Japan in 1994 and worldwide the following year, which became the first console of any type to ship over 100 million units, which made PlayStation a globally recognized brand.</t>
         </is>
       </c>
+      <c r="R555" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="556">
       <c r="A556" s="4" t="n">
@@ -25067,6 +26226,11 @@
           <t>Sinds de introductie in 2007 zijn er in totaal 22 series van de iPhone verschenen, waarbij de meeste series verschillende modellen bevatten.</t>
         </is>
       </c>
+      <c r="R560" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="561">
       <c r="A561" s="4" t="n">
@@ -25194,6 +26358,11 @@
           <t>The Indonesian part, known as West Timor, is inhabited by around 2 million people and constitutes part of the province of East Nusa Tenggara.</t>
         </is>
       </c>
+      <c r="R563" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="564">
       <c r="A564" s="4" t="n">
@@ -25244,6 +26413,11 @@
 Al minstens 10.000 jaar voor Christus waren het Amazonebekken, het Paranábekken, het São Franciscobekken en de kustgebieden van Brazilië bewoond door indianen.</t>
         </is>
       </c>
+      <c r="R564" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="565">
       <c r="A565" s="4" t="n">
@@ -25293,6 +26467,11 @@
           <t>China borders 14 nations, with a combined land border length of 22,117 km (13,743 mi).</t>
         </is>
       </c>
+      <c r="R565" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="566">
       <c r="A566" s="4" t="n">
@@ -25459,6 +26638,11 @@
           <t>Mexico is een federale republiek bestaande uit 31 staten en Mexico-Stad.</t>
         </is>
       </c>
+      <c r="R569" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="570">
       <c r="A570" s="4" t="n">
@@ -25508,6 +26692,11 @@
           <t>Although there had been discussion concerning the installation of a movable barrier since the 1980s, only in March 2005 did the Bridge Board of Directors commit to finding funding to complete the $2 million study required prior to the installation of a movable median barrier.</t>
         </is>
       </c>
+      <c r="R570" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="571">
       <c r="A571" s="4" t="n">
@@ -25606,6 +26795,11 @@
           <t>Wikidata: klopt</t>
         </is>
       </c>
+      <c r="R572" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="573" ht="25" customHeight="1">
       <c r="A573" s="4" t="n">
@@ -25777,6 +26971,11 @@
           <t>Tegenwoordig is 36% van de bevolking van New York geboren buiten de Verenigde Staten.</t>
         </is>
       </c>
+      <c r="R576" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="577">
       <c r="A577" s="4" t="n">
@@ -25826,6 +27025,11 @@
           <t>De lijnen 14 en 15 zullen metrolijnen met een grote vervoerscapaciteit zijn (met lange perrons), terwijl de lijnen 16, 17 en 18 goedkoper uitgevoerd zullen worden met kortere perrons.</t>
         </is>
       </c>
+      <c r="R577" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="578">
       <c r="A578" s="4" t="n">
@@ -25876,6 +27080,11 @@
 4 november 2010: Er deed zich bij een A380 van Qantas, tijdens QF32, kort na het opstijgen van de luchthaven van Singapore een uncontained engine failure voor, waarbij er delen van de motor afvielen.</t>
         </is>
       </c>
+      <c r="R578" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="579">
       <c r="A579" s="4" t="n">
@@ -25925,6 +27134,11 @@
           <t>De drie stations van Heathrow zijn Heathrow Terminals 2 &amp; 3, Heathrow Terminal 4 en Heathrow Terminal 5.</t>
         </is>
       </c>
+      <c r="R579" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="580">
       <c r="A580" s="4" t="n">
@@ -25974,6 +27188,11 @@
           <t>De drie stations van Heathrow zijn Heathrow Terminals 2 &amp; 3, Heathrow Terminal 4 en Heathrow Terminal 5.</t>
         </is>
       </c>
+      <c r="R580" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="581">
       <c r="A581" s="4" t="n">
@@ -26023,6 +27242,11 @@
           <t>Opened on October 27, 1904, the New York City Subway is one of the world's oldest public transit systems, and the one with the most stations, with 423 stations in operation (472, if stations connected by transfers are counted multiple times).</t>
         </is>
       </c>
+      <c r="R581" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="582">
       <c r="A582" s="4" t="n">
@@ -26072,6 +27296,11 @@
           <t>Op 1 april 1926 werd Schiphol gekocht door de gemeente Amsterdam.</t>
         </is>
       </c>
+      <c r="R582" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="583">
       <c r="A583" s="4" t="n">
@@ -26199,6 +27428,11 @@
           <t>De totale kosten met betrekking tot de 737 MAX zijn opgelopen tot US$ 18 miljard voor Boeing.</t>
         </is>
       </c>
+      <c r="R585" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="586">
       <c r="A586" s="4" t="n">
@@ -26287,6 +27521,11 @@
           <t xml:space="preserve">Dit gaat echter slechts op wanneer hetzelfde RVV ook over motorfietsen spreekt, zoals in artikel 2.2 (De regels van dit besluit betreffende voetgangers zijn voorts mede van toepassing op personen die te voet een motorfiets, bromfiets of fiets aan de hand meevoeren.), artikel 60 lid 1 (De bestuurder </t>
         </is>
       </c>
+      <c r="R587" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="588">
       <c r="A588" s="4" t="n">
@@ -26336,6 +27575,11 @@
           <t>De fiets heeft een relatief lage ecologische voetafdruk, levert veel minder vervuiling op zoals CO2-uitstoot en het ruimtegebruik is veel lager dan van de auto.</t>
         </is>
       </c>
+      <c r="R588" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="589">
       <c r="A589" s="4" t="n">
@@ -26541,6 +27785,11 @@
           <t>De eerste non-stop overtocht met een vliegtuig vond plaats op 14 juni 1919 toen John Alcock en Arthur Whitten Brown in een Vickers Vimy bommenwerper van Newfoundland naar Ierland vlogen.</t>
         </is>
       </c>
+      <c r="R593" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="594">
       <c r="A594" s="4" t="n">
@@ -26590,6 +27839,11 @@
           <t>Op 24 november 1924 werd met de H-NACC, een Fokker F.VII-vliegtuig van de KLM, de eerste KLM vlucht naar Nederlands-Indië  (van de Schiphol naar Batavia) volbracht.</t>
         </is>
       </c>
+      <c r="R594" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="595">
       <c r="A595" s="4" t="n">
@@ -26757,6 +28011,11 @@
 Het zonnestelsel ontstond ongeveer 4,5 miljard jaar geleden, toen een interstellaire gaswolk door onbekende oorzaak actief werd en door zijn eigen gewicht begon te krimpen en steeds sneller rond te draaien, waarna in het midden van deze gaswolk de Zon ontstond.</t>
         </is>
       </c>
+      <c r="R598" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="599">
       <c r="A599" s="4" t="n">
@@ -27119,6 +28378,11 @@
 Een volwassen man heeft gemiddeld 5 tot 6 liter bloed, bij een volwassen vrouw is dat 4 tot 5 liter.</t>
         </is>
       </c>
+      <c r="R607" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="608">
       <c r="A608" s="4" t="n">
@@ -27480,6 +28744,11 @@
           <t>Penicilline is een antibacteriële stof die in 1928 herontdekt werd door de Schotse arts-bacterioloog Alexander Fleming.</t>
         </is>
       </c>
+      <c r="R616" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="617">
       <c r="A617" s="4" t="n">
@@ -27568,6 +28837,11 @@
           <t>12.000 versregels zijn ingedeeld in 24 boeken, genummerd met Griekse kleine letters α (alpha) t/m ω (omega).</t>
         </is>
       </c>
+      <c r="R618" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="619">
       <c r="A619" s="4" t="n">
@@ -27617,6 +28891,11 @@
           <t>De Ilias is onderverdeeld in 24 boeken die genummerd zijn volgens de letters van het Griekse alfabet van Alfa tot Omega (hoofdletters).</t>
         </is>
       </c>
+      <c r="R619" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="620" ht="25" customHeight="1">
       <c r="A620" s="4" t="n">
@@ -27744,6 +29023,11 @@
           <t>Opera2Day: De vernuftige edelman Don Quichot van La Mancha, avontuurlijke opera uit 2023.</t>
         </is>
       </c>
+      <c r="R622" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="623">
       <c r="A623" s="4" t="n">
@@ -27783,6 +29067,21 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="O623" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Harry_Potter_and_the_Deathly_Hallows</t>
+        </is>
+      </c>
+      <c r="P623" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Scholastic, the American publisher of the Harry Potter series, launched a multimillion-dollar "There will soon be 7" marketing campaign with a Knight Bus travelling to 40 libraries across the United States, online fan discussions and competitions, collectible bookmarks, tattoos, and the staged release of seven Deathly </t>
+        </is>
+      </c>
+      <c r="R623" t="inlineStr">
+        <is>
+          <t>matig</t>
+        </is>
+      </c>
     </row>
     <row r="624">
       <c r="A624" s="4" t="n">
@@ -27833,6 +29132,11 @@
 Op 3 mei 2009 werd de eerste fanfilm van The Lord of the Rings uitgebracht onder de titel The Hunt for Gollum.</t>
         </is>
       </c>
+      <c r="R624" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="625" ht="25" customHeight="1">
       <c r="A625" s="4" t="n">
@@ -27960,6 +29264,11 @@
           <t>De collectie is gedrukt in boekformaat, en bevat 36 toneelstukken.</t>
         </is>
       </c>
+      <c r="R627" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="628" ht="25" customHeight="1">
       <c r="A628" s="4" t="n">
@@ -27999,6 +29308,21 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="O628" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Shakespeare%27s_plays</t>
+        </is>
+      </c>
+      <c r="P628" t="inlineStr">
+        <is>
+          <t>Shakespeare's plays are a canon of approximately 39 dramatic works written by the English playwright and poet William Shakespeare.</t>
+        </is>
+      </c>
+      <c r="R628" t="inlineStr">
+        <is>
+          <t>matig</t>
+        </is>
+      </c>
     </row>
     <row r="629">
       <c r="A629" s="4" t="n">
@@ -28120,6 +29444,11 @@
           <t>IPv4 uses a 32-bit address space which provides 4,294,967,296 (232) unique addresses, but large blocks are reserved for special networking purposes.</t>
         </is>
       </c>
+      <c r="R631" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="632">
       <c r="A632" s="4" t="n">
@@ -28676,6 +30005,11 @@
           <t>Wikidata: geen waarde</t>
         </is>
       </c>
+      <c r="R645" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="646" ht="25" customHeight="1">
       <c r="A646" s="4" t="n">
@@ -28944,6 +30278,21 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="O652" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Kilogram</t>
+        </is>
+      </c>
+      <c r="P652" t="inlineStr">
+        <is>
+          <t>The current definition of a kilogram agrees with this original definition to within 30 parts per million (0.003%).</t>
+        </is>
+      </c>
+      <c r="R652" t="inlineStr">
+        <is>
+          <t>matig</t>
+        </is>
+      </c>
     </row>
     <row r="653">
       <c r="A653" s="4" t="n">
@@ -29149,6 +30498,11 @@
           <t>Als een kameel drinkt, drinkt hij bijzonder veel, meer dan 100 liter achter elkaar, tot 60 liter per minuut.</t>
         </is>
       </c>
+      <c r="R657" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="658" ht="25" customHeight="1">
       <c r="A658" s="4" t="n">
@@ -29237,6 +30591,11 @@
           <t>De blauwe vinvis is het grootste dier dat op aarde leeft en wordt gemiddeld ongeveer 26 tot 30 meter lang en kan 150 tot 170 ton zwaar worden.</t>
         </is>
       </c>
+      <c r="R659" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="660">
       <c r="A660" s="4" t="n">
@@ -29286,6 +30645,11 @@
           <t>De gemiddelde lengte van de anaconda is 3 tot 6 meter.</t>
         </is>
       </c>
+      <c r="R660" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="661">
       <c r="A661" s="4" t="n">
@@ -29445,6 +30809,21 @@
       <c r="N664" s="4" t="inlineStr">
         <is>
           <t>geen bron</t>
+        </is>
+      </c>
+      <c r="O664" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Electricity_meter</t>
+        </is>
+      </c>
+      <c r="P664" t="inlineStr">
+        <is>
+          <t>At US$0.095/kWh, a standard residential 50 A meter causes a legally collectible charge of about US$5,000.00 per month.</t>
+        </is>
+      </c>
+      <c r="R664" t="inlineStr">
+        <is>
+          <t>matig</t>
         </is>
       </c>
     </row>
@@ -29736,6 +31115,11 @@
 Familie Chaerilidae, 1 geslacht met </t>
         </is>
       </c>
+      <c r="R671" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="672" ht="25" customHeight="1">
       <c r="A672" s="4" t="n">
@@ -29824,6 +31208,11 @@
           <t>In de 20e eeuw namen de Verenigde Staten deel aan de beide wereldoorlogen, die mede door hun ingrijpen definitief werden beslecht ten gunste van de geallieerde legers.</t>
         </is>
       </c>
+      <c r="R673" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="674">
       <c r="A674" s="4" t="n">
@@ -29873,6 +31262,11 @@
           <t>Madagaskar kent 6 steden waar, naar schatting, meer dan 100.000 inwoners wonen.</t>
         </is>
       </c>
+      <c r="R674" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="675" ht="25" customHeight="1">
       <c r="A675" s="4" t="n">
@@ -29912,6 +31306,22 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="O675" t="inlineStr">
+        <is>
+          <t>https://nl.wikipedia.org/wiki/Fauna_van_Australi%C3%AB</t>
+        </is>
+      </c>
+      <c r="P675">
+        <f>= Vogels ==
+Australië herbergt ongeveer 830 vogelsoorten, van grote zoals de emoe tot kleinere zoals de
+Satijnblauwe prieelvogel, waarvan het mannetje als onderdeel van het paringsritueel uiterst gecompliceerde priëlen bouwt.</f>
+        <v/>
+      </c>
+      <c r="R675" t="inlineStr">
+        <is>
+          <t>matig</t>
+        </is>
+      </c>
     </row>
     <row r="676" ht="25" customHeight="1">
       <c r="A676" s="4" t="n">
@@ -29956,6 +31366,11 @@
           <t>About 10% of the species of the Earth live in Colombia, including over 1,900 species of bird, more than in Europe and North America combined.</t>
         </is>
       </c>
+      <c r="R676" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="677" ht="25" customHeight="1">
       <c r="A677" s="4" t="n">
@@ -30395,6 +31810,11 @@
           <t>De blauwe vinvis is het grootste dier dat op aarde leeft en wordt gemiddeld ongeveer 26 tot 30 meter lang en kan 150 tot 170 ton zwaar worden.</t>
         </is>
       </c>
+      <c r="R687" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="688">
       <c r="A688" s="4" t="n">
@@ -30483,6 +31903,11 @@
           <t>On January 2, 1886, the number of stocks represented in what is now the Dow Jones Transportation Average dropped from 14 to 12, as the Central Pacific Railroad and Central Railroad of New Jersey were removed.</t>
         </is>
       </c>
+      <c r="R689" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="690" ht="25" customHeight="1">
       <c r="A690" s="4" t="n">
@@ -30649,6 +32074,11 @@
           <t>De dollar wordt onderverdeeld in 100 cent.</t>
         </is>
       </c>
+      <c r="R693" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="694">
       <c r="A694" s="4" t="n">
@@ -30696,6 +32126,11 @@
       <c r="P694" t="inlineStr">
         <is>
           <t>Buiten de herdenkingsmunten van € 2 zijn er al talloze munten geslagen die alleen nationaal te gebruiken zijn en waardes vertegenwoordigen als € 1½, € 2½, € 3, € 5, € 8, € 10, € 12½, € 20, € 25, € 50, € 100 etc.</t>
+        </is>
+      </c>
+      <c r="R694" t="inlineStr">
+        <is>
+          <t>hoog</t>
         </is>
       </c>
     </row>
@@ -30988,6 +32423,11 @@
 A typical can of Coca-Cola (12 fl ounces/355 ml) contains 39 grams of sugar, 34 mg of caffeine, 45 mg o</t>
         </is>
       </c>
+      <c r="R701" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="702">
       <c r="A702" s="4" t="n">
@@ -31105,6 +32545,22 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="O704" t="inlineStr">
+        <is>
+          <t>https://nl.wikipedia.org/wiki/Koffie_%28drank%29</t>
+        </is>
+      </c>
+      <c r="P704">
+        <f>= Koffie wereldwijd ==
+=== Productie ===
+In het oogstjaar 2022/23 werden 165 miljoen zakken van 60 kilogram aan koffiebonen geoogst.</f>
+        <v/>
+      </c>
+      <c r="R704" t="inlineStr">
+        <is>
+          <t>matig</t>
+        </is>
+      </c>
     </row>
     <row r="705">
       <c r="A705" s="4" t="n">
@@ -31144,6 +32600,21 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="O705" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Kilogram</t>
+        </is>
+      </c>
+      <c r="P705">
+        <f>= Redefinition based on fundamental constants ==
+The replacement of the International Prototype of the Kilogram (IPK) as the primary standard was motivated by evidence accumulated over a long period of time that the mass of the IPK and its replicas had been changing; the IPK had diverged from its replicas by approxim</f>
+        <v/>
+      </c>
+      <c r="R705" t="inlineStr">
+        <is>
+          <t>matig</t>
+        </is>
+      </c>
     </row>
     <row r="706" ht="25" customHeight="1">
       <c r="A706" s="4" t="n">
@@ -31261,6 +32732,21 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="O708" t="inlineStr">
+        <is>
+          <t>https://nl.wikipedia.org/wiki/Afrikaanse_Unie</t>
+        </is>
+      </c>
+      <c r="P708" t="inlineStr">
+        <is>
+          <t>Tijdens de 8e top van de Afrikaanse Unie die op 29 en 30 januari 2007 in Addis Abeba plaatsvond, besloten de staatshoofden en regeringsleiders een wedstrijd uit te schrijven voor de selectie van een nieuwe vlag voor de Unie.</t>
+        </is>
+      </c>
+      <c r="R708" t="inlineStr">
+        <is>
+          <t>matig</t>
+        </is>
+      </c>
     </row>
     <row r="709">
       <c r="A709" s="4" t="n">
@@ -31344,6 +32830,11 @@
           <t>Its name refers to the beef patty having a precooked weight of approximately one quarter of a pound, originally portioned as four ounces (113.4 g) but increased to 4.25 oz (120.5 g) in 2015.</t>
         </is>
       </c>
+      <c r="R710" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="711" ht="25" customHeight="1">
       <c r="A711" s="4" t="n">
@@ -31471,6 +32962,11 @@
           <t>Brazilië beschikt over 35 internationale luchthavens en 2464 regionale luchthavens.</t>
         </is>
       </c>
+      <c r="R713" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="714">
       <c r="A714" s="4" t="n">
@@ -31598,6 +33094,11 @@
           <t>In 1950 was 5% van de bevolking 65 jaar of ouder, in 2010 was dit aandeel 23% en voor 2050 wordt het aandeel geschat op 37%.</t>
         </is>
       </c>
+      <c r="R716" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="717" ht="25" customHeight="1">
       <c r="A717" s="4" t="n">
@@ -31686,6 +33187,11 @@
           <t>Following the release of the second trailer for the MCU film Spider-Man: Far From Home (2019) on May 6, it was added to the end of Endgame screenings with a message before the film from Far From Home star Tom Holland telling the audience to stay until after the credits to see the trailer.</t>
         </is>
       </c>
+      <c r="R718" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="719">
       <c r="A719" s="4" t="n">
@@ -31735,6 +33241,11 @@
           <t>Some fans considered the blond-haired, 5-foot-10-inch-tall (1.78 m) Craig to not fit the image of the taller, dark-haired Bond portrayed by the previous actors.</t>
         </is>
       </c>
+      <c r="R719" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="720">
       <c r="A720" s="4" t="n">
@@ -31784,6 +33295,11 @@
           <t>Het is de derde installatie van de Jurassic World Evolution serie, en werd op 6 juni 2025 voor het eerst aan de wereld aangekondigd op Summer Game Fest.</t>
         </is>
       </c>
+      <c r="R720" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="721">
       <c r="A721" s="4" t="n">
@@ -31872,6 +33388,11 @@
           <t>In totaal ontving de film 14 nominaties, evenveel als All About Eve (1950) en Titanic (1997).</t>
         </is>
       </c>
+      <c r="R722" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="723" ht="25" customHeight="1">
       <c r="A723" s="4" t="n">
@@ -31921,6 +33442,11 @@
           <t>The film was released in the United States on May 5, 2000 by DreamWorks Distribution LLC, and internationally on May 12, 2000, by Universal Pictures through United International Pictures.</t>
         </is>
       </c>
+      <c r="R723" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="724" ht="25" customHeight="1">
       <c r="A724" s="4" t="n">
@@ -31970,6 +33496,11 @@
           <t>Profits were so high for The Godfather that earnings for Gulf &amp; Western Industries, Inc., which owned Paramount, jumped from 77 cents per share to $3.30 a share for the year, according to a Los Angeles Times article, dated December 13, 1972.</t>
         </is>
       </c>
+      <c r="R724" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="725" ht="25" customHeight="1">
       <c r="A725" s="4" t="n">
@@ -32019,6 +33550,11 @@
           <t>Forrest Gump was released in the United States by Paramount Pictures on July 6, 1994, and received widespread critical acclaim for Zemeckis's direction, the performances (particularly those of Hanks and Sinise), story, writing, emotional weight, visual effects, music, character development and scree</t>
         </is>
       </c>
+      <c r="R725" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="726" ht="25" customHeight="1">
       <c r="A726" s="4" t="n">
@@ -32068,6 +33604,11 @@
           <t>A deluxe-edition hardcover collection of art inspired by the film, titled Mad Max: Fury Road – Inspired Artists Deluxe Edition, was released by Vertigo on 6 May.</t>
         </is>
       </c>
+      <c r="R726" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="727" ht="25" customHeight="1">
       <c r="A727" s="4" t="n">
@@ -32157,6 +33698,11 @@
 In New Zealand, the film became the highest-grossing film of all time, surpassing Footrot Flats: The Dog's Tale (1986) with a gross of $NZ3.8 million.</t>
         </is>
       </c>
+      <c r="R728" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="729" ht="25" customHeight="1">
       <c r="A729" s="4" t="n">
@@ -32196,6 +33742,21 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="O729" t="inlineStr">
+        <is>
+          <t>https://nl.wikipedia.org/wiki/Star_Tours_%E2%80%93_The_Adventures_Continue</t>
+        </is>
+      </c>
+      <c r="P729" t="inlineStr">
+        <is>
+          <t>Uiteindelijk werd in Disneyland in Anaheim Star Tours geopend op 9 januari 1987.</t>
+        </is>
+      </c>
+      <c r="R729" t="inlineStr">
+        <is>
+          <t>matig</t>
+        </is>
+      </c>
     </row>
     <row r="730">
       <c r="A730" s="4" t="n">
@@ -32251,6 +33812,11 @@
           <t>Wikidata: geen waarde</t>
         </is>
       </c>
+      <c r="R730" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="731">
       <c r="A731" s="4" t="n">
@@ -32300,6 +33866,11 @@
           <t>Harry Potter and the Prisoner of Azkaban was published a year later in the UK on 8 July 1999 and in the US on 8 September 1999.</t>
         </is>
       </c>
+      <c r="R731" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="732">
       <c r="A732" s="4" t="n">
@@ -32348,6 +33919,11 @@
         <is>
           <t>Verhaal
 De film gaat verder op het einde van Toy Story 4, waarin Woody ervoor koos om bij Bo Peep en de “verloren speeltjes” te blijven en Buzz en de andere speelgoedfiguren terugkeerden naar Bonnie.</t>
+        </is>
+      </c>
+      <c r="R732" t="inlineStr">
+        <is>
+          <t>hoog</t>
         </is>
       </c>
     </row>
@@ -32413,6 +33989,11 @@
           <t>Wikidata: klopt</t>
         </is>
       </c>
+      <c r="R733" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="734">
       <c r="A734" s="4" t="n">
@@ -32467,6 +34048,11 @@
           <t>Wikidata: klopt</t>
         </is>
       </c>
+      <c r="R734" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="735">
       <c r="A735" s="4" t="n">
@@ -32521,6 +34107,11 @@
           <t>Wikidata: klopt</t>
         </is>
       </c>
+      <c r="R735" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="736">
       <c r="A736" s="4" t="n">
@@ -32570,6 +34161,11 @@
           <t>Taking into account the well-developed network of roads as well as the planned construction of both Interstate 4 and Florida's Turnpike, along with McCoy Air Force Base (later Orlando International Airport) to the east, Disney selected a centrally located site near Bay Lake.</t>
         </is>
       </c>
+      <c r="R736" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="737">
       <c r="A737" s="4" t="n">
@@ -32609,9 +34205,24 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="O737" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Avatar%3A_The_Way_of_Water</t>
+        </is>
+      </c>
+      <c r="P737" t="inlineStr">
+        <is>
+          <t>| runtime = 192 minutes Cite web |last1=McClintock |first1=Pamela |last2=Couch |first2=Aaron |date=October 29, 2022 |title='Avatar: The Way of Water' Runtime Sails Past Three Hours |url=https://www.hollywoodreporter.com/movies/movie-news/avatar-way-of-water-runtime-1235251391/ |url-status=live |archive-url=https://web.</t>
+        </is>
+      </c>
       <c r="Q737" t="inlineStr">
         <is>
           <t>Wikidata: geen waarde</t>
+        </is>
+      </c>
+      <c r="R737" t="inlineStr">
+        <is>
+          <t>hoog</t>
         </is>
       </c>
     </row>
@@ -32697,6 +34308,11 @@
           <t>The films constitute one of the longest continually running film series and have grossed over US$7.04 billion in total at the box office, making James Bond the fifth-highest-grossing film series to date.</t>
         </is>
       </c>
+      <c r="R739" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="740">
       <c r="A740" s="4" t="n">
@@ -32787,6 +34403,11 @@
 The Dashavatara is a list of the so-called Vibhavas, or '10 [primary] Avatars' of Vishnu.</t>
         </is>
       </c>
+      <c r="R741" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="742">
       <c r="A742" s="4" t="n">
@@ -32836,6 +34457,11 @@
           <t>In totaal bevat de Koran 114 soera's, bestaande uit 6.236 ayat (afhankelijk van de indeling), die met uitzondering van soera Het Berouw allemaal beginnen met de aanhef Bismillah ar-Rahmaan ar-Rahiem (In de naam van God, de genadevolle, de Barmhartige).</t>
         </is>
       </c>
+      <c r="R742" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="743" ht="25" customHeight="1">
       <c r="A743" s="4" t="n">
@@ -32885,6 +34511,11 @@
           <t>Het Nieuwe Testament (Koinè: Ἡ καινὴ διαθήκη, Hē kainḕ diathḗkē; Latijn: Novum Testamentum) is het tweede deel van de christelijke Bijbel en bestaat uit 27 werken, 'boeken', die alle in het Koinè Grieks zijn geschreven.</t>
         </is>
       </c>
+      <c r="R743" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="744">
       <c r="A744" s="4" t="n">
@@ -32973,6 +34604,11 @@
           <t>Bij bewolking of mist kan ook een ander criterium worden gebruikt, namelijk wanneer de maan niet zichtbaar is op dag 29, dan telt men er nog 1 dag bij, en komt zo op een ramadan van 30 dagen.</t>
         </is>
       </c>
+      <c r="R745" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="746">
       <c r="A746" s="4" t="n">
@@ -33056,6 +34692,11 @@
           <t>Jezus werd volgens Marcus op het derde uur na zonsopgang op Pesach (ongeveer negen uur 's morgens) gekruisigd (Marcus 14:12, 15:25).</t>
         </is>
       </c>
+      <c r="R747" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="748" ht="25" customHeight="1">
       <c r="A748" s="4" t="n">
@@ -33144,6 +34785,11 @@
           <t>Dit had kennelijk geen betrekking op de tien geboden, want later vertelde Mozes dat God de stenen platen die hij had uitgehakt had beschreven en aan hem had overhandigd (Deuteronomium 10:1-4).</t>
         </is>
       </c>
+      <c r="R749" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="750" ht="25" customHeight="1">
       <c r="A750" s="4" t="n">
@@ -33188,6 +34834,11 @@
           <t>Volgens het jodendom staan er 613 mitswot (284 geboden en 365 verboden) in de Thora (waarvan 611 via Mozes en twee rechtstreeks door God zijn geopenbaard) die de kern vormen van de halacha, het geheel van de rabbinale wetgeving die zeer bepalend is voor het joodse religieuze leven.</t>
         </is>
       </c>
+      <c r="R750" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="751">
       <c r="A751" s="4" t="n">
@@ -33237,6 +34888,11 @@
           <t>Na 10 jaar oorlog om Troje zijn de Grieken nog geen stap dichter bij de overwinning.</t>
         </is>
       </c>
+      <c r="R751" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="752">
       <c r="A752" s="4" t="n">
@@ -33315,6 +34971,21 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="O753" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Nepalese_Muslims</t>
+        </is>
+      </c>
+      <c r="P753" t="inlineStr">
+        <is>
+          <t>Islam is the third-largest religion in Nepal after Hinduism and Buddhism, with 5.09% of the country's population, around 1,483,066 (1.483 million) people, identifying as Muslims in the 2021 census.</t>
+        </is>
+      </c>
+      <c r="R753" t="inlineStr">
+        <is>
+          <t>matig</t>
+        </is>
+      </c>
     </row>
     <row r="754">
       <c r="A754" s="4" t="n">
@@ -33520,6 +35191,11 @@
           <t>In totaal bevat de Koran 114 soera's, bestaande uit 6.236 ayat (afhankelijk van de indeling), die met uitzondering van soera Het Berouw allemaal beginnen met de aanhef Bismillah ar-Rahmaan ar-Rahiem (In de naam van God, de genadevolle, de Barmhartige).</t>
         </is>
       </c>
+      <c r="R758" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="759">
       <c r="A759" s="4" t="n">
@@ -33647,6 +35323,11 @@
           <t>Met de industrialisering groeide Sydney snel, en aan het begin van de 20e eeuw had het al meer dan 1 miljoen inwoners.</t>
         </is>
       </c>
+      <c r="R761" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="762">
       <c r="A762" s="4" t="n">
@@ -33858,6 +35539,11 @@
           <t>Wikidata: WIJKT AF</t>
         </is>
       </c>
+      <c r="R766" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="767">
       <c r="A767" s="4" t="n">
@@ -33897,9 +35583,24 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="O767" t="inlineStr">
+        <is>
+          <t>https://nl.wikipedia.org/wiki/Chinese_Muur</t>
+        </is>
+      </c>
+      <c r="P767" t="inlineStr">
+        <is>
+          <t>De gehele verdedigingslinie, inclusief verdedigingsgroeven van 359 kilometer en 2232 kilometer aan natuurlijke grenzen (rivieren, heuvels en bergen), heeft een lengte van 21 196 kilometer.</t>
+        </is>
+      </c>
       <c r="Q767" t="inlineStr">
         <is>
           <t>Wikidata: geen waarde</t>
+        </is>
+      </c>
+      <c r="R767" t="inlineStr">
+        <is>
+          <t>matig</t>
         </is>
       </c>
     </row>
@@ -33941,9 +35642,24 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="O768" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Mexico_City_Metro</t>
+        </is>
+      </c>
+      <c r="P768" t="inlineStr">
+        <is>
+          <t>| system_length = convert|200.9|km|mi|abbr=on revenue; convert|226.5|km|mi|abbr=on total cite web|url=http://www.metro.cdmx.gob.mx/operacion/longlineas.html|title=LONGITUDES DE LAS LINEAS|publisher=Metro de la Ciudad de México|language=es|trans-title=Operations figures|archive-url=https://web.archive.org/web/2016082113</t>
+        </is>
+      </c>
       <c r="Q768" t="inlineStr">
         <is>
           <t>Wikidata: geen waarde</t>
+        </is>
+      </c>
+      <c r="R768" t="inlineStr">
+        <is>
+          <t>hoog</t>
         </is>
       </c>
     </row>
@@ -33995,6 +35711,11 @@
           <t>Wikidata: klopt</t>
         </is>
       </c>
+      <c r="R769" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="770">
       <c r="A770" s="4" t="n">
@@ -34327,9 +36048,24 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="O777" t="inlineStr">
+        <is>
+          <t>https://nl.wikipedia.org/wiki/Christus_de_Verlosser_%28Rio_de_Janeiro%29</t>
+        </is>
+      </c>
+      <c r="P777" t="inlineStr">
+        <is>
+          <t>Het beeld is 38 meter hoog en staat op de 710 meter hoge berg Corcovado, uitkijkend over de stad Rio de Janeiro.</t>
+        </is>
+      </c>
       <c r="Q777" t="inlineStr">
         <is>
           <t>Wikidata: WIJKT AF</t>
+        </is>
+      </c>
+      <c r="R777" t="inlineStr">
+        <is>
+          <t>matig</t>
         </is>
       </c>
     </row>
@@ -34371,9 +36107,24 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="O778" t="inlineStr">
+        <is>
+          <t>https://nl.wikipedia.org/wiki/Eiffeltoren</t>
+        </is>
+      </c>
+      <c r="P778" t="inlineStr">
+        <is>
+          <t>| hoogte = 1e etage: 57,63 m 2e etage: 115,73 m 3e etage: 276,13 m Top (incl. antenne): 330 m</t>
+        </is>
+      </c>
       <c r="Q778" t="inlineStr">
         <is>
           <t>Wikidata: klopt</t>
+        </is>
+      </c>
+      <c r="R778" t="inlineStr">
+        <is>
+          <t>hoog</t>
         </is>
       </c>
     </row>
@@ -34518,6 +36269,11 @@
           <t>Wikidata: klopt</t>
         </is>
       </c>
+      <c r="R781" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="782">
       <c r="A782" s="4" t="n">
@@ -34571,6 +36327,11 @@
           <t>Wikidata: klopt</t>
         </is>
       </c>
+      <c r="R782" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="783" ht="25" customHeight="1">
       <c r="A783" s="4" t="n">
@@ -34625,6 +36386,11 @@
           <t>Wikidata: klopt</t>
         </is>
       </c>
+      <c r="R783" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="784" ht="25" customHeight="1">
       <c r="A784" s="4" t="n">
@@ -34664,9 +36430,24 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="O784" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Taj_Mahal</t>
+        </is>
+      </c>
+      <c r="P784" t="inlineStr">
+        <is>
+          <t>| height = cvt|73|m|ft</t>
+        </is>
+      </c>
       <c r="Q784" t="inlineStr">
         <is>
           <t>Wikidata: klopt</t>
+        </is>
+      </c>
+      <c r="R784" t="inlineStr">
+        <is>
+          <t>hoog</t>
         </is>
       </c>
     </row>
@@ -34708,9 +36489,24 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="O785" t="inlineStr">
+        <is>
+          <t>https://nl.wikipedia.org/wiki/Tokyo_Skytree</t>
+        </is>
+      </c>
+      <c r="P785" t="inlineStr">
+        <is>
+          <t>De oudere Tokiotoren was met haar 333 meter niet hoog genoeg om tussen de steeds hoger wordende gebouwen in met name Centraal Tokio voldoende dekking te verkrijgen.</t>
+        </is>
+      </c>
       <c r="Q785" t="inlineStr">
         <is>
           <t>Wikidata: ander onderwerp</t>
+        </is>
+      </c>
+      <c r="R785" t="inlineStr">
+        <is>
+          <t>matig</t>
         </is>
       </c>
     </row>
@@ -34747,9 +36543,24 @@
           <t>geen bron · geen EN-vertaling</t>
         </is>
       </c>
+      <c r="O786" t="inlineStr">
+        <is>
+          <t>https://nl.wikipedia.org/wiki/Cairo_Tower</t>
+        </is>
+      </c>
+      <c r="P786" t="inlineStr">
+        <is>
+          <t>De toren is 187 meter hoog.</t>
+        </is>
+      </c>
       <c r="Q786" t="inlineStr">
         <is>
           <t>Wikidata: klopt</t>
+        </is>
+      </c>
+      <c r="R786" t="inlineStr">
+        <is>
+          <t>matig</t>
         </is>
       </c>
     </row>
@@ -34842,6 +36653,11 @@
       <c r="Q788" t="inlineStr">
         <is>
           <t>Wikidata: klopt</t>
+        </is>
+      </c>
+      <c r="R788" t="inlineStr">
+        <is>
+          <t>hoog</t>
         </is>
       </c>
     </row>
@@ -35060,6 +36876,11 @@
 (en)  Meer informatie over de tempel.</t>
         </is>
       </c>
+      <c r="R793" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="794">
       <c r="A794" s="4" t="n">
@@ -35226,6 +37047,11 @@
           <t>Het Terracottaleger is de benaming voor de archeologische vondst van ongeveer 8000 terracottafiguren die als grafgiften werden meegegeven aan de eerste keizer van China, Qin Shi Huangdi.</t>
         </is>
       </c>
+      <c r="R797" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="798">
       <c r="A798" s="4" t="n">
@@ -35275,6 +37101,11 @@
           <t>De gaten bevatten tot 80 staande stenen.</t>
         </is>
       </c>
+      <c r="R798" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="799">
       <c r="A799" s="4" t="n">
@@ -35446,6 +37277,11 @@
           <t>Interiors with furniture were completed on 1 January 1996, the spires of Tower 1 and Tower 2 were completed on 1 March 1996, 3 years after its construction was started, and the first batch of Petronas personnel moved into the building on 1 January 1997.</t>
         </is>
       </c>
+      <c r="R802" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="803">
       <c r="A803" s="4" t="n">
@@ -35534,6 +37370,11 @@
           <t>One World Trade Center's steel structure topped out at the 94th physical story (numbered as floor 104), with a total height of the roof top at 1,368 feet (417 m), in August 2012.</t>
         </is>
       </c>
+      <c r="R804" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="805">
       <c r="A805" s="4" t="n">
@@ -35583,6 +37424,11 @@
           <t>Het gebouw is 300 meter hoog en telt 91 verdiepingen boven de grond en 1 eronder.</t>
         </is>
       </c>
+      <c r="R805" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="806" ht="25" customHeight="1">
       <c r="A806" s="4" t="n">
@@ -35632,6 +37478,11 @@
           <t>Gran Torre Costanera, previously known as Costanera Center Torre 2, also known as El Costanera (the Costanera) by locals, and previously known as Torre Gran Costanera, is a 62-story skyscraper in Santiago, Chile.</t>
         </is>
       </c>
+      <c r="R806" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="807">
       <c r="A807" s="4" t="n">
@@ -35800,6 +37651,11 @@
 The BD Bacatá complex has the two tallest buildings in Colombia, one with 67 stories, where the new hotel, owned by the Spanish firm Eurostars, will be operating</t>
         </is>
       </c>
+      <c r="R810" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="811">
       <c r="A811" s="4" t="n">
@@ -35849,6 +37705,11 @@
           <t>De verhouding van de zuilen van de buitenste colonnade is 8 × 17 en deze telt in totaal 46 zuilen.</t>
         </is>
       </c>
+      <c r="R811" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="812" ht="25" customHeight="1">
       <c r="A812" s="4" t="n">
@@ -35896,6 +37757,11 @@
       <c r="P812" t="inlineStr">
         <is>
           <t>De verhouding van de zuilen van de buitenste colonnade is 8 × 17 en deze telt in totaal 46 zuilen.</t>
+        </is>
+      </c>
+      <c r="R812" t="inlineStr">
+        <is>
+          <t>hoog</t>
         </is>
       </c>
     </row>
@@ -35966,6 +37832,11 @@
 Ext</t>
         </is>
       </c>
+      <c r="R813" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="814">
       <c r="A814" s="4" t="n">
@@ -36053,6 +37924,11 @@
           <t>De gehele verdedigingslinie, inclusief verdedigingsgroeven van 359 kilometer en 2232 kilometer aan natuurlijke grenzen (rivieren, heuvels en bergen), heeft een lengte van 21 196 kilometer.</t>
         </is>
       </c>
+      <c r="R815" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="816">
       <c r="A816" s="4" t="n">
@@ -36253,6 +38129,21 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="O820" t="inlineStr">
+        <is>
+          <t>https://nl.wikipedia.org/wiki/Europese_Unie</t>
+        </is>
+      </c>
+      <c r="P820" t="inlineStr">
+        <is>
+          <t>Tevens is in het op 1 december 2009 inwerking getreden Verdrag van Lissabon vastgelegd dat de Europese Unie zal toetreden tot het Europees Verdrag voor de Rechten van de Mens (EVRM) (artikel 6 lid 2 van het Verdrag betreffende de Europese Unie).</t>
+        </is>
+      </c>
+      <c r="R820" t="inlineStr">
+        <is>
+          <t>matig</t>
+        </is>
+      </c>
     </row>
     <row r="821">
       <c r="A821" s="4" t="n">
@@ -36346,6 +38237,11 @@
           <t>Fiji consists of 332 islands (of which 106 are inhabited) and 522 smaller islets.</t>
         </is>
       </c>
+      <c r="R822" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="823">
       <c r="A823" s="4" t="n">
@@ -36434,6 +38330,11 @@
           <t>The Great Barrier Reef is the world's largest coral reef system, composed of over 2,900 individual reefs and 900 islands stretching for over 2,300 kilometres (1,400 mi) over an area of approximately 344,400 square kilometres (133,000 mi2).</t>
         </is>
       </c>
+      <c r="R824" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="825" ht="25" customHeight="1">
       <c r="A825" s="4" t="n">
@@ -36478,6 +38379,11 @@
           <t>Het bestaat uit meer dan 17.000 eilanden, waaronder Sumatra, Java, Sulawesi en delen van Borneo en Nieuw-Guinea.</t>
         </is>
       </c>
+      <c r="R825" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="826">
       <c r="A826" s="4" t="n">
@@ -36527,6 +38433,11 @@
           <t>The Great Barrier Reef is the world's largest coral reef system, composed of over 2,900 individual reefs and 900 islands stretching for over 2,300 kilometres (1,400 mi) over an area of approximately 344,400 square kilometres (133,000 mi2).</t>
         </is>
       </c>
+      <c r="R826" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="827">
       <c r="A827" s="4" t="n">
@@ -36656,6 +38567,11 @@
 Ieder emiraat kent zijn eigen wetgeving over lokaal bestuur.</t>
         </is>
       </c>
+      <c r="R829" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="830">
       <c r="A830" s="4" t="n">
@@ -36744,6 +38660,11 @@
           <t>This was discussed by the United Nations Security Council in 2000, and envisioned an autonomous Western Sahara Authority (WSA), which would be followed after five years by the referendum.</t>
         </is>
       </c>
+      <c r="R831" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="832" ht="25" customHeight="1">
       <c r="A832" s="4" t="n">
@@ -36866,9 +38787,24 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="O834" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Danube</t>
+        </is>
+      </c>
+      <c r="P834" t="inlineStr">
+        <is>
+          <t>| length_km = 2,850</t>
+        </is>
+      </c>
       <c r="Q834" t="inlineStr">
         <is>
           <t>Wikidata: klopt</t>
+        </is>
+      </c>
+      <c r="R834" t="inlineStr">
+        <is>
+          <t>hoog</t>
         </is>
       </c>
     </row>
@@ -36925,6 +38861,11 @@
           <t>Wikidata: klopt</t>
         </is>
       </c>
+      <c r="R835" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="836">
       <c r="A836" s="4" t="n">
@@ -37047,9 +38988,24 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="O838" t="inlineStr">
+        <is>
+          <t>https://nl.wikipedia.org/wiki/Kongo_%28rivier%29</t>
+        </is>
+      </c>
+      <c r="P838" t="inlineStr">
+        <is>
+          <t>| lengte = 4 700</t>
+        </is>
+      </c>
       <c r="Q838" t="inlineStr">
         <is>
           <t>Wikidata: klopt</t>
+        </is>
+      </c>
+      <c r="R838" t="inlineStr">
+        <is>
+          <t>hoog</t>
         </is>
       </c>
     </row>
@@ -37106,6 +39062,11 @@
           <t>Wikidata: klopt</t>
         </is>
       </c>
+      <c r="R839" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="840" ht="25" customHeight="1">
       <c r="A840" s="4" t="n">
@@ -37145,9 +39106,24 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="O840" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Niger_River</t>
+        </is>
+      </c>
+      <c r="P840" t="inlineStr">
+        <is>
+          <t>| length_km = 4,200</t>
+        </is>
+      </c>
       <c r="Q840" t="inlineStr">
         <is>
           <t>Wikidata: geen waarde</t>
+        </is>
+      </c>
+      <c r="R840" t="inlineStr">
+        <is>
+          <t>hoog</t>
         </is>
       </c>
     </row>
@@ -37189,9 +39165,24 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="O841" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Rhine</t>
+        </is>
+      </c>
+      <c r="P841" t="inlineStr">
+        <is>
+          <t>| length_km = 1230</t>
+        </is>
+      </c>
       <c r="Q841" t="inlineStr">
         <is>
           <t>Wikidata: klopt</t>
+        </is>
+      </c>
+      <c r="R841" t="inlineStr">
+        <is>
+          <t>hoog</t>
         </is>
       </c>
     </row>
@@ -37233,9 +39224,24 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="O842" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Zambezi</t>
+        </is>
+      </c>
+      <c r="P842" t="inlineStr">
+        <is>
+          <t>| length = cvt|2,574|km|mi</t>
+        </is>
+      </c>
       <c r="Q842" t="inlineStr">
         <is>
           <t>Wikidata: klopt</t>
+        </is>
+      </c>
+      <c r="R842" t="inlineStr">
+        <is>
+          <t>hoog</t>
         </is>
       </c>
     </row>
@@ -37495,6 +39501,11 @@
           <t>Artsen zonder Grenzen Nederland werd op 7 september 1984 opgericht in Amsterdam door een groep van zes mensen: Jacques de Milliano, Roelf Padt, Simon Horenblas, Aswin Meier, Barbara Lopes Cardozo en Janine Osmers.</t>
         </is>
       </c>
+      <c r="R848" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="849">
       <c r="A849" s="4" t="n">
@@ -37544,6 +39555,11 @@
           <t>The African Economic Outlook organisation states that "Angola requires 4.5 million tonnes a year of grain but grows only about 55% of the maize it needs, 20% of the rice and just 5% of its required wheat".</t>
         </is>
       </c>
+      <c r="R849" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="850" ht="25" customHeight="1">
       <c r="A850" s="4" t="n">
@@ -37630,6 +39646,11 @@
       <c r="P851" t="inlineStr">
         <is>
           <t>The Special Economical Zone for Bolivia in Ilo (ZEEBI) is a special economic area of 5 kilometers (3.1 miles) of maritime coast, and a total extension of 358 hectares (880 acres), called Mar Bolivia ("Sea Bolivia"), where Bolivia may maintain a free port near Ilo, Peru under its administration and o</t>
+        </is>
+      </c>
+      <c r="R851" t="inlineStr">
+        <is>
+          <t>hoog</t>
         </is>
       </c>
     </row>
@@ -37685,6 +39706,11 @@
 Chili con carne, often referred to simply as </t>
         </is>
       </c>
+      <c r="R852" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="853">
       <c r="A853" s="4" t="n">
@@ -37732,6 +39758,11 @@
       <c r="P853" t="inlineStr">
         <is>
           <t>De kustlijn van het vasteland heeft een totale lengte van rond de 14.500 km.</t>
+        </is>
+      </c>
+      <c r="R853" t="inlineStr">
+        <is>
+          <t>hoog</t>
         </is>
       </c>
     </row>
@@ -37786,6 +39817,11 @@
 de Andes in het westen.</t>
         </is>
       </c>
+      <c r="R854" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="855" ht="25" customHeight="1">
       <c r="A855" s="4" t="n">
@@ -37875,6 +39911,11 @@
 Costa Rica produceerde 2,6 miljoen ton olie-equivalent (Mtoe) in 2016.</t>
         </is>
       </c>
+      <c r="R856" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="857" ht="25" customHeight="1">
       <c r="A857" s="4" t="n">
@@ -37922,6 +39963,11 @@
       <c r="P857" t="inlineStr">
         <is>
           <t>In 2026 the United Nations reported that 2.6 million people in Ecuador are facing acute hunger amid an unprecedented crisis.</t>
+        </is>
+      </c>
+      <c r="R857" t="inlineStr">
+        <is>
+          <t>hoog</t>
         </is>
       </c>
     </row>
@@ -37979,6 +40025,11 @@
 analfabetisme: bij de ma</t>
         </is>
       </c>
+      <c r="R858" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="859">
       <c r="A859" s="4" t="n">
@@ -38108,6 +40159,11 @@
 The name Ghana comes from Wagadu, an empire in west Africa from the 3rd to 12th centuries; Wagadu was termed Ghana by Arab traders involved in the trans-Saharan trade.</t>
         </is>
       </c>
+      <c r="R861" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="862" ht="25" customHeight="1">
       <c r="A862" s="4" t="n">
@@ -38235,6 +40291,11 @@
           <t>India is the habitat for 8.6% of all mammals, 13.7% of bird species, 7.9% of reptile species, 6% of amphibian species, 12.2% of fish species, and 6.0% of all flowering plant species.</t>
         </is>
       </c>
+      <c r="R864" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="865" ht="25" customHeight="1">
       <c r="A865" s="4" t="n">
@@ -38362,6 +40423,11 @@
           <t>In 1965 was Libië de 6e olie-exporteur ter wereld en in 1969 produceerde het al meer dan 3 miljoen vaten olie per dag, meer dan Saoedi-Arabië op dat moment.</t>
         </is>
       </c>
+      <c r="R867" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="868">
       <c r="A868" s="4" t="n">
@@ -38411,6 +40477,11 @@
           <t>After the 2012 imposition of sharia rule in northern parts of the country, however, Mali came to be listed high (number 7) in the Christian persecution index published by Open Doors, which described the persecution in the north as severe.</t>
         </is>
       </c>
+      <c r="R868" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="869">
       <c r="A869" s="4" t="n">
@@ -38500,6 +40571,11 @@
 Nicaragua occupies a landmass of 130,967 km2 (50,567 sq mi), which makes it slightly larger than England.</t>
         </is>
       </c>
+      <c r="R870" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="871">
       <c r="A871" s="4" t="n">
@@ -38550,6 +40626,11 @@
 Niger is divided into 7 regions and one capital district.</t>
         </is>
       </c>
+      <c r="R871" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="872" ht="25" customHeight="1">
       <c r="A872" s="4" t="n">
@@ -38599,6 +40680,11 @@
           <t>Nigeria lies between latitudes 4° and 14°N, and longitudes 2° and 15°E.</t>
         </is>
       </c>
+      <c r="R872" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="873" ht="25" customHeight="1">
       <c r="A873" s="4" t="n">
@@ -38724,6 +40810,11 @@
       <c r="P875" t="inlineStr">
         <is>
           <t>In 2025, Panama also had an unemployment rate of 8%, an increase from 2.7 percent in 2012.</t>
+        </is>
+      </c>
+      <c r="R875" t="inlineStr">
+        <is>
+          <t>hoog</t>
         </is>
       </c>
     </row>
@@ -38787,6 +40878,11 @@
 In 1999 telde Paraguay 93</t>
         </is>
       </c>
+      <c r="R876" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="877">
       <c r="A877" s="4" t="n">
@@ -38836,6 +40932,11 @@
           <t>On 5 April 1879, Chile declared war on Peru, unleashing the War of the Pacific, which lasted until 1884.</t>
         </is>
       </c>
+      <c r="R877" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="878">
       <c r="A878" s="4" t="n">
@@ -38886,6 +40987,11 @@
 TVN, diverse kanalen van de Luxemburgse ITI Groep, waaronder TVN Siedem (vroeger RTL 7 (Polen)), TVN Meteo, TVN24, TVN&amp;CNBC Biznes, TVN Religia, TVN HD, TVN Turbo, TVN Style, TVN Lingua, Mango 24, iTVN.</t>
         </is>
       </c>
+      <c r="R878" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="879">
       <c r="A879" s="4" t="n">
@@ -38935,6 +41041,11 @@
           <t>In de Westerse cultuur deed de profane cultuur haar invloed al gelden sinds de renaissance in de 14e eeuw, maar in Rusland pas in de 17e eeuw.</t>
         </is>
       </c>
+      <c r="R879" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="880">
       <c r="A880" s="4" t="n">
@@ -38984,6 +41095,11 @@
           <t>Vooral de bevolking in de regio Khartoem nam toe, het aantal inwoners van die regio werd in 2006 geschat op rond de 7 miljoen mensen, onder wie 2 miljoen vluchtelingen uit het door oorlog getroffen zuiden van Soedan.</t>
         </is>
       </c>
+      <c r="R880" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="881">
       <c r="A881" s="4" t="n">
@@ -39111,6 +41227,11 @@
           <t>Tsjaad heeft met 6,4 kinderen per vrouw (2025) een van de hoogste geboortecijfers ter wereld.</t>
         </is>
       </c>
+      <c r="R883" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="884">
       <c r="A884" s="4" t="n">
@@ -39161,6 +41282,11 @@
 With 176,214 km2 (68,037 sq mi) of continental land and 125,436 km2 (48,431 sq mi) of territorial waters, Uruguay is the second-smallest sovereign nation in South America (after Suriname) and the third smallest territory (French Guiana is the smallest).</t>
         </is>
       </c>
+      <c r="R884" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="885">
       <c r="A885" s="4" t="n">
@@ -39210,6 +41336,11 @@
           <t>Op 3 januari 2026 vond een Amerikaanse militaire actie in Venezuela plaats.</t>
         </is>
       </c>
+      <c r="R885" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="886" ht="25" customHeight="1">
       <c r="A886" s="4" t="n">
@@ -39493,6 +41624,11 @@
           <t>De totale bevolking van de 11 landen waar hij doorheen stroomt, en die sterk afhankelijk zijn van de rivier, bedraagt 443 miljoen.</t>
         </is>
       </c>
+      <c r="R892" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="893">
       <c r="A893" s="4" t="n">
@@ -39542,6 +41678,11 @@
           <t>The smallest variations are found along the coastal regions due to high humidity and are often even lower than a 10 °C (18 °F) difference, while the largest variations are found in inland desert areas where the humidity is the lowest, mainly in the southern Sahara.</t>
         </is>
       </c>
+      <c r="R893" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="894">
       <c r="A894" s="4" t="n">
@@ -39709,6 +41850,11 @@
 Afrika bestaat uit 54 onafhankelijke staten en een aantal niet-onafhankelijke gebieden.</t>
         </is>
       </c>
+      <c r="R897" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="898">
       <c r="A898" s="4" t="n">
@@ -39953,6 +42099,11 @@
           <t>De Europese Unie (EU) is een uit 27 Europese landen bestaand statenverband.</t>
         </is>
       </c>
+      <c r="R903" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="904">
       <c r="A904" s="4" t="n">
@@ -39992,9 +42143,24 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="O904" t="inlineStr">
+        <is>
+          <t>https://nl.wikipedia.org/wiki/Victoriawatervallen</t>
+        </is>
+      </c>
+      <c r="P904" t="inlineStr">
+        <is>
+          <t>Zij vormen een watergordijn van 1708 meter breed en 100 meter hoog en hebben een maximale valhoogte van 128 meter.</t>
+        </is>
+      </c>
       <c r="Q904" t="inlineStr">
         <is>
           <t>Wikidata: klopt</t>
+        </is>
+      </c>
+      <c r="R904" t="inlineStr">
+        <is>
+          <t>matig</t>
         </is>
       </c>
     </row>
@@ -40046,6 +42212,11 @@
           <t>The Grand Canyon is 277 miles (446 km) long, up to 18 miles (29 km) wide and attains a depth of over a mile (6,093 feet or 1,857 meters).</t>
         </is>
       </c>
+      <c r="R905" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="906">
       <c r="A906" s="4" t="n">
@@ -40134,6 +42305,11 @@
           <t>Wikidata: klopt</t>
         </is>
       </c>
+      <c r="R907" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="908">
       <c r="A908" s="4" t="n">
@@ -40168,9 +42344,24 @@
           <t>geen bron · geen EN-vertaling</t>
         </is>
       </c>
+      <c r="O908" t="inlineStr">
+        <is>
+          <t>https://nl.wikipedia.org/wiki/Mount_Everest</t>
+        </is>
+      </c>
+      <c r="P908" t="inlineStr">
+        <is>
+          <t>| hoogte = 8849</t>
+        </is>
+      </c>
       <c r="Q908" t="inlineStr">
         <is>
           <t>Wikidata: klopt</t>
+        </is>
+      </c>
+      <c r="R908" t="inlineStr">
+        <is>
+          <t>hoog</t>
         </is>
       </c>
     </row>
@@ -40222,6 +42413,11 @@
           <t>Wikidata: klopt</t>
         </is>
       </c>
+      <c r="R909" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="910">
       <c r="A910" s="4" t="n">
@@ -40276,6 +42472,11 @@
           <t>Wikidata: klopt</t>
         </is>
       </c>
+      <c r="R910" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="911">
       <c r="A911" s="4" t="n">
@@ -40315,9 +42516,24 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="O911" t="inlineStr">
+        <is>
+          <t>https://nl.wikipedia.org/wiki/Uluru</t>
+        </is>
+      </c>
+      <c r="P911" t="inlineStr">
+        <is>
+          <t>| hoogte = 863 (boven zeeniveau) / 348</t>
+        </is>
+      </c>
       <c r="Q911" t="inlineStr">
         <is>
           <t>Wikidata: geen waarde</t>
+        </is>
+      </c>
+      <c r="R911" t="inlineStr">
+        <is>
+          <t>hoog</t>
         </is>
       </c>
     </row>
@@ -40374,6 +42590,11 @@
           <t>Wikidata: geen waarde</t>
         </is>
       </c>
+      <c r="R912" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="913">
       <c r="A913" s="4" t="n">
@@ -40408,9 +42629,24 @@
           <t>geen bron · geen EN-vertaling</t>
         </is>
       </c>
+      <c r="O913" t="inlineStr">
+        <is>
+          <t>https://nl.wikipedia.org/wiki/Kilimanjaro_%28berg%29</t>
+        </is>
+      </c>
+      <c r="P913" t="inlineStr">
+        <is>
+          <t>| hoogte = 5895</t>
+        </is>
+      </c>
       <c r="Q913" t="inlineStr">
         <is>
           <t>Wikidata: geen waarde</t>
+        </is>
+      </c>
+      <c r="R913" t="inlineStr">
+        <is>
+          <t>hoog</t>
         </is>
       </c>
     </row>
@@ -40467,6 +42703,11 @@
           <t>Wikidata: geen waarde</t>
         </is>
       </c>
+      <c r="R914" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="915">
       <c r="A915" s="4" t="n">
@@ -40560,6 +42801,11 @@
           <t>In 2019 lag de waterspiegel van de Dode Zee 430,5 meter onder zeeniveau, waarmee het de laagst gelegen plek op het aardoppervlak is.</t>
         </is>
       </c>
+      <c r="R916" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="917">
       <c r="A917" s="4" t="n">
@@ -40599,9 +42845,24 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="O917" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Argentina</t>
+        </is>
+      </c>
+      <c r="P917" t="inlineStr">
+        <is>
+          <t>| population_census = IncreaseNeutral 46,044,703 cite news |access-date=31 January 2023 |periodical= Página/12 |quote=La población argentina tiene actualmente 46.044.703 habitantes, es decir, 5.927.607 de personas más que las relevadas en el último censo, en 2010. En mayo de 2022, pocos días después del relevamiento, e</t>
+        </is>
+      </c>
       <c r="Q917" t="inlineStr">
         <is>
           <t>Wikidata: klopt</t>
+        </is>
+      </c>
+      <c r="R917" t="inlineStr">
+        <is>
+          <t>hoog</t>
         </is>
       </c>
     </row>
@@ -40658,6 +42919,11 @@
           <t>Wikidata: klopt</t>
         </is>
       </c>
+      <c r="R918" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="919" ht="25" customHeight="1">
       <c r="A919" s="4" t="n">
@@ -40712,6 +42978,11 @@
           <t>Wikidata: klopt</t>
         </is>
       </c>
+      <c r="R919" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="920" ht="25" customHeight="1">
       <c r="A920" s="4" t="n">
@@ -40766,6 +43037,11 @@
           <t>Wikidata: klopt</t>
         </is>
       </c>
+      <c r="R920" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="921">
       <c r="A921" s="4" t="n">
@@ -40952,6 +43228,11 @@
           <t>Wikidata: klopt</t>
         </is>
       </c>
+      <c r="R924" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="925" ht="25" customHeight="1">
       <c r="A925" s="4" t="n">
@@ -41002,6 +43283,11 @@
 Australië is een populaire vakantiebestemming en de toerismesector, waarin circa 500.000 Australiërs werkzaam zijn, vormt een belangrijk deel van de economie.</t>
         </is>
       </c>
+      <c r="R925" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="926" ht="25" customHeight="1">
       <c r="A926" s="4" t="n">
@@ -41092,6 +43378,11 @@
 Alle besluiten van de instellingen worden vertaald in alle officiële talen.</t>
         </is>
       </c>
+      <c r="R927" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="928" ht="25" customHeight="1">
       <c r="A928" s="4" t="n">
@@ -41131,6 +43422,21 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="O928" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Official_language</t>
+        </is>
+      </c>
+      <c r="P928" t="inlineStr">
+        <is>
+          <t>Second to Bolivia is India with 22 official languages.</t>
+        </is>
+      </c>
+      <c r="R928" t="inlineStr">
+        <is>
+          <t>matig</t>
+        </is>
+      </c>
     </row>
     <row r="929">
       <c r="A929" s="4" t="n">
@@ -41180,6 +43486,11 @@
           <t>3 dat België drie gewesten omvat: het Vlaams Gewest (waarin vooral Nederlandstaligen wonen, met in bepaalde gemeenten faciliteiten voor Franstaligen), het Waals Gewest (waarin vooral Franstaligen en de Duitstalige gemeenschap wonen, in bepaalde gemeenten faciliteiten voor de Nederlandstaligen) en he</t>
         </is>
       </c>
+      <c r="R929" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="930" ht="25" customHeight="1">
       <c r="A930" s="4" t="n">
@@ -41229,6 +43540,11 @@
           <t>Het land is verdeeld in 47 prefecturen.</t>
         </is>
       </c>
+      <c r="R930" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="931" ht="25" customHeight="1">
       <c r="A931" s="4" t="n">
@@ -41356,6 +43672,11 @@
           <t>Met rond de 23 miljoen inwoners is Shanghai de grootste stad van China.</t>
         </is>
       </c>
+      <c r="R933" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="934">
       <c r="A934" s="4" t="n">
@@ -41481,6 +43802,11 @@
       <c r="P936" t="inlineStr">
         <is>
           <t>It is technically part of the continental U.S., but is not usually included in the colloquial use of the term; Alaska is not part of the contiguous U.S., often called "the Lower 48".</t>
+        </is>
+      </c>
+      <c r="R936" t="inlineStr">
+        <is>
+          <t>hoog</t>
         </is>
       </c>
     </row>
@@ -41576,6 +43902,11 @@
 lengte van het kanton: D = 0,76 (1,9 × 2/5, twee vijfde van de lengte v</t>
         </is>
       </c>
+      <c r="R938" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="939" ht="25" customHeight="1">
       <c r="A939" s="4" t="n">
@@ -41742,6 +44073,11 @@
           <t>Volgens de laatste volkstelling telde India 1.210.193.422 (2011) inwoners en volgens niet-officiële schattingen telt het land anno 2019 zo'n 1.352.642.280 inwoners.</t>
         </is>
       </c>
+      <c r="R942" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="943" ht="25" customHeight="1">
       <c r="A943" s="4" t="n">
@@ -41832,6 +44168,11 @@
 Nyaupane, Gya</t>
         </is>
       </c>
+      <c r="R944" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="945">
       <c r="A945" s="4" t="n">
@@ -41882,6 +44223,11 @@
 jaar0102030401860189019201950198020102040inwoners (x miljoen).mw-chart-ed1ffdf0116d644c3b7e61db92d121ad0ee2e2ab107ff61b18e459a8628a508c408b87022bd12b5d5401819ba21a4f3a8d186e375abe899337ae990459eae769__zr9197043-cls-47078137:hover{pointer-events:none}.mw-chart-ed1ffdf0116d644c</t>
         </is>
       </c>
+      <c r="R945" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="946" ht="25" customHeight="1">
       <c r="A946" s="4" t="n">
@@ -41931,6 +44277,11 @@
           <t>Het heeft een oppervlakte van 6,7 miljoen km² en is verspreid over negen landen: Brazilië (60%), Peru (13%), Colombia (9%), Venezuela (5%), Bolivia (5%), Guyana (3%), Suriname (2%), Ecuador (1,5%) en Frans-Guyana (1,5%).</t>
         </is>
       </c>
+      <c r="R946" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="947">
       <c r="A947" s="4" t="n">
@@ -42224,6 +44575,11 @@
           <t>Deze schatting verbaast moderne schrijvers, omdat ze op zijn best binnen 2% van de waarde van de omtrek bij de evenaar ligt, 40.075 kilometer.</t>
         </is>
       </c>
+      <c r="R953" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="954" ht="25" customHeight="1">
       <c r="A954" s="4" t="n">
@@ -42392,6 +44748,11 @@
           <t>Hij en zijn 300 Spartanen zouden de pas blijven verdedigen zodat de Grieken konden vluchten.</t>
         </is>
       </c>
+      <c r="R957" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="958">
       <c r="A958" s="4" t="n">
@@ -42431,6 +44792,21 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="O958" t="inlineStr">
+        <is>
+          <t>https://nl.wikipedia.org/wiki/Zeven_wereldwonderen_van_de_antieke_wereld</t>
+        </is>
+      </c>
+      <c r="P958">
+        <f>= Achtergrond ==
+De Griekse verovering van een groot deel van de toentertijd bekende wereld in de 4e eeuw v.Chr.</f>
+        <v/>
+      </c>
+      <c r="R958" t="inlineStr">
+        <is>
+          <t>matig</t>
+        </is>
+      </c>
     </row>
     <row r="959">
       <c r="A959" s="4" t="n">
@@ -42480,6 +44856,11 @@
           <t>Egypte heeft een oppervlakte van 1.001.450 km².</t>
         </is>
       </c>
+      <c r="R959" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="960" ht="25" customHeight="1">
       <c r="A960" s="4" t="n">
@@ -42529,6 +44910,11 @@
           <t>Sinds de inwerkingtreding van de Grondwet op 4 maart 1789 werden 27 amendementen aan de Grondwet toegevoegd, waaronder één amendement dat een vorig amendement herriep (in verband met de Drooglegging), om zo in te spelen op de veranderende noden in de samenleving sinds het einde van de 18e eeuw.</t>
         </is>
       </c>
+      <c r="R960" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="961">
       <c r="A961" s="4" t="n">
@@ -42578,6 +44964,11 @@
           <t>Aan het begin van de 21e eeuw woonde bijna 80% van de bevolking van de Parijse agglomeratie in de banlieues, dus buiten de stad Parijs.</t>
         </is>
       </c>
+      <c r="R961" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="962">
       <c r="A962" s="4" t="n">
@@ -42627,6 +45018,11 @@
           <t>The 18 large forts and other batteries around Verdun were left with fewer than 300 guns and a small reserve of ammunition, while their garrisons had been reduced to small maintenance crews.</t>
         </is>
       </c>
+      <c r="R962" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="963">
       <c r="A963" s="4" t="n">
@@ -42676,6 +45072,11 @@
           <t>De Slag bij Gettysburg (1, 2 en 3 juli 1863) was een van de grootste veldslagen van de Amerikaanse Burgeroorlog en een van de grootste van het westelijk halfrond.</t>
         </is>
       </c>
+      <c r="R963" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="964" ht="25" customHeight="1">
       <c r="A964" s="4" t="n">
@@ -42725,6 +45126,11 @@
           <t>De oudste geschreven Chinese historische bronnen zijn inscripties op zogenaamde "orakelbotten", het orakelbottenschrift dat dateert uit de 13e eeuw v.Chr.</t>
         </is>
       </c>
+      <c r="R964" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="965">
       <c r="A965" s="4" t="n">
@@ -42892,6 +45298,11 @@
 De langverwachte genadeslag volgde, toen de Franse legers van Condé en Turenne zich met de Zweden konden verenigen, en in het West-Beierse Zusmarshausen (mei 1648) tussen Ulm en Augsburg, verpletterden wat er nog over was van de keizerlijke en Beierse legers; hun</t>
         </is>
       </c>
+      <c r="R968" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="969">
       <c r="A969" s="4" t="n">
@@ -42942,6 +45353,11 @@
 Het conflict duurde 116 jaar, onderbroken door verscheidene periodes van vrede, voordat het uiteindelijk eindigde door het verdrijven van de Plantagenets uit Frankrijk (behalve uit Calais).</t>
         </is>
       </c>
+      <c r="R969" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="970">
       <c r="A970" s="4" t="n">
@@ -42992,6 +45408,11 @@
 In 1959 werd de Wet op de Bevordering van Bantoe-zelfbestuur (Promotion of Bantu Self-Government Act No 46) aangenomen, die leidde tot de invoering van 8, later 10 aparte "thuislanden" voor de verschillende etnische niet-blanke bevolkingsgroepen.</t>
         </is>
       </c>
+      <c r="R970" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="971">
       <c r="A971" s="4" t="n">
@@ -43041,6 +45462,11 @@
           <t>Cleopatra had Caesarion enter into the ranks of the ephebi, which, along with reliefs on a stele from Koptos dated 21 September 31 BC, demonstrated that Cleopatra was now grooming her son to become the sole ruler of Egypt.</t>
         </is>
       </c>
+      <c r="R971" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="972">
       <c r="A972" s="4" t="n">
@@ -43090,6 +45516,11 @@
           <t>Mandela werd op 27 april 1994, op 75-jarige leeftijd, president van Zuid-Afrika, als opvolger van De Klerk, die al een aarzelend begin had gemaakt met afschaffing van apartheidsregels.</t>
         </is>
       </c>
+      <c r="R972" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="973">
       <c r="A973" s="4" t="n">
@@ -43139,6 +45570,11 @@
           <t>Vooral de bevolking in de regio Khartoem nam toe, het aantal inwoners van die regio werd in 2006 geschat op rond de 7 miljoen mensen, onder wie 2 miljoen vluchtelingen uit het door oorlog getroffen zuiden van Soedan.</t>
         </is>
       </c>
+      <c r="R973" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="974">
       <c r="A974" s="4" t="n">
@@ -43426,6 +45862,11 @@
 Scientific knowledge of the geologic history of Vesuvius comes from core samples taken from a 2,000 m (6,600 ft) plus borehole on the flanks of the volcano, extending into Mesozoic rock.</t>
         </is>
       </c>
+      <c r="R980" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="981">
       <c r="A981" s="4" t="n">
@@ -43475,6 +45916,11 @@
           <t>(Scranton (Pennsylvania), 20 november 1942) is een Amerikaans politicus en was van 20 januari 2021 tot 20 januari 2025 de 46e president van de Verenigde Staten.</t>
         </is>
       </c>
+      <c r="R981" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="982">
       <c r="A982" s="4" t="n">
@@ -43526,6 +45972,11 @@
 William Henry Harrison – op 4 april 1841 overleden aan een longontsteking of buiktyfus, precies 1 maand</t>
         </is>
       </c>
+      <c r="R982" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="983">
       <c r="A983" s="4" t="n">
@@ -43576,6 +46027,11 @@
 Cijfers over het aantal slachtoffers dat bij de slag viel zijn moeilijk te verkrijgen; sommige historici schatten echter dat zo'n 2.000 Normandiërs omkwamen en ongeveer twee keer zoveel Engelsen.</t>
         </is>
       </c>
+      <c r="R983" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="984">
       <c r="A984" s="4" t="n">
@@ -43662,6 +46118,11 @@
       <c r="P985" t="inlineStr">
         <is>
           <t>Hij kreeg hulp van edelen uit Bretagne, Vlaanderen en het hele westen van Frankrijk en verzamelde een vloot van bijna 700 schepen.</t>
+        </is>
+      </c>
+      <c r="R985" t="inlineStr">
+        <is>
+          <t>hoog</t>
         </is>
       </c>
     </row>
@@ -43717,6 +46178,11 @@
 Op 3 augustus 1492 vertrokken de drie schepen naar de Canarische Eilanden.</t>
         </is>
       </c>
+      <c r="R986" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="987">
       <c r="A987" s="4" t="n">
@@ -43842,6 +46308,11 @@
           <t>De Verenigde Staten (VS), officieel de Verenigde Staten van Amerika (Engels: United States of America, USA of US, vaak totum pro parte Amerika, America genoemd), is een federatie van 50 staten, verschillende overzeese territoria en het District of Columbia, grotendeels in Noord-Amerika gelegen.</t>
         </is>
       </c>
+      <c r="R989" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="990">
       <c r="A990" s="4" t="n">
@@ -44040,6 +46511,11 @@
           <t>De Franse Revolutie (1789–1799) was een internationaal invloedrijke politieke omwenteling, waarbij de absolute monarchie die Frankrijk ongeveer twee eeuwen had geregeerd werd afgeschaft, en de Eerste Franse Republiek werd gesticht.</t>
         </is>
       </c>
+      <c r="R994" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="995">
       <c r="A995" s="4" t="n">
@@ -44079,6 +46555,21 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="O995" t="inlineStr">
+        <is>
+          <t>https://nl.wikipedia.org/wiki/Koreaanse_Oorlog</t>
+        </is>
+      </c>
+      <c r="P995" t="inlineStr">
+        <is>
+          <t>De Koreaanse Oorlog of Koreaoorlog is een in het Westen gebruikte naam voor een tussen 1950 en 1953 uitgevochten oorlog tussen het communistische Noord-Korea en het prowesterse Zuid-Korea.</t>
+        </is>
+      </c>
+      <c r="R995" t="inlineStr">
+        <is>
+          <t>matig</t>
+        </is>
+      </c>
     </row>
     <row r="996" ht="25" customHeight="1">
       <c r="A996" s="4" t="n">
@@ -44123,6 +46614,11 @@
           <t>De Eerste Wereldoorlog, voor het uitbreken van de Tweede Wereldoorlog in 1939 nog de Grote Oorlog genoemd, was een wereldoorlog die in Europa begon op 28 juli 1914 en tot 11 november 1918 om 11:00 duurde.</t>
         </is>
       </c>
+      <c r="R996" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="997">
       <c r="A997" s="4" t="n">
@@ -44172,6 +46668,11 @@
           <t>De Tweede Wereldoorlog was de escalatie van de Tweede Chinees-Japanse Oorlog die begon in 1937 en een Europese oorlog begonnen in 1939 tot een militair conflict dat van 1941 tot 1945 op wereldschaal werd uitgevochten tussen twee allianties: de asmogendheden en de geallieerden.</t>
         </is>
       </c>
+      <c r="R997" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="998">
       <c r="A998" s="4" t="n">
@@ -44221,6 +46722,11 @@
           <t>In 1990 werd de apartheid afgeschaft en in 1994 werd Nelson Mandela tot de eerste zwarte president van Zuid-Afrika verkozen.</t>
         </is>
       </c>
+      <c r="R998" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="999">
       <c r="A999" s="4" t="n">
@@ -44271,6 +46777,11 @@
 In maart 1969 besloot NASA dat Armstrong de eerste mens op de Maan moest worden, deels omdat de leiding hem zag als iemand zonder een groot ego.</t>
         </is>
       </c>
+      <c r="R999" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="1000">
       <c r="A1000" s="4" t="n">
@@ -44320,6 +46831,11 @@
           <t>Er werden drie oorlogen tussen de Carthagers en de Romeinen uitgevochten tussen 264 en 146 v.Chr.</t>
         </is>
       </c>
+      <c r="R1000" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="1001" ht="25" customHeight="1">
       <c r="A1001" s="4" t="n">
@@ -44369,6 +46885,11 @@
           <t>De aanval op Pearl Harbor was een verrassingsaanval door de Japanse Keizerlijke Marine onder leiding van admiraal Isoroku Yamamoto op de Amerikaanse marinebasis Pearl Harbor in Hawaï, op zondag 7 december 1941, om 17:55 UTC (op Hawaï in de ochtend, in Washington D.C.</t>
         </is>
       </c>
+      <c r="R1001" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="1002">
       <c r="A1002" s="4" t="n">
@@ -44413,6 +46934,11 @@
           <t>Onder de Berlijnse Muur (Duits: Berliner Mauer) verstaat men de tot 100 meter brede constructie van opeenvolgende obstakels die van 13 augustus 1961 tot 9 november 1989 West-Berlijn geheel omringde.</t>
         </is>
       </c>
+      <c r="R1002" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="1003" ht="25" customHeight="1">
       <c r="A1003" s="4" t="n">
@@ -44462,6 +46988,11 @@
           <t>Cortés staat vooral bekend om zijn verovering van Mexico tussen 1519 en 1521.</t>
         </is>
       </c>
+      <c r="R1003" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="1004" ht="25" customHeight="1">
       <c r="A1004" s="4" t="n">
@@ -44511,6 +47042,11 @@
           <t>A ransom for the emperor's release was demanded and Atahualpa filled a room with gold to the highest point he could reach, but Pizarro charged him with various crimes and executed him by garrotting in July 1533.</t>
         </is>
       </c>
+      <c r="R1004" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="1005">
       <c r="A1005" s="4" t="n">
@@ -44560,6 +47096,11 @@
           <t>Het West-Romeinse Rijk bleef nog bestaan tot 476, toen de 'barbaarse' generaal in Romeinse dienst Odoaker de laatste West-Romeinse keizer afzette en zichzelf tot koning van het toenmalige Italia (wat grotendeels overeenkomt met de moderne staat Italië) liet uitroepen.</t>
         </is>
       </c>
+      <c r="R1005" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="1006" ht="25" customHeight="1">
       <c r="A1006" s="4" t="n">
@@ -44609,6 +47150,11 @@
           <t>Argentinië is onafhankelijk sinds 1816, daarvoor was het gedurende drie eeuwen een Spaanse kolonie.</t>
         </is>
       </c>
+      <c r="R1006" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="1007">
       <c r="A1007" s="4" t="n">
@@ -44643,6 +47189,21 @@
           <t>geen bron · geen EN-vertaling</t>
         </is>
       </c>
+      <c r="O1007" t="inlineStr">
+        <is>
+          <t>https://nl.wikipedia.org/wiki/Bolivia</t>
+        </is>
+      </c>
+      <c r="P1007" t="inlineStr">
+        <is>
+          <t>Na het uitroepen van de onafhankelijkheid in 1809 volgde 16 jaar van oorlog alvorens de republiek, genoemd naar Simón Bolívar, op 6 augustus 1825 werd opgericht.</t>
+        </is>
+      </c>
+      <c r="R1007" t="inlineStr">
+        <is>
+          <t>matig</t>
+        </is>
+      </c>
     </row>
     <row r="1008">
       <c r="A1008" s="4" t="n">
@@ -44692,6 +47253,11 @@
           <t>Brazilië werd vervolgens de spil in het Verenigd Koninkrijk van Portugal, Brazilië en de Algarve en verklaarde zich in 1822 onafhankelijk.</t>
         </is>
       </c>
+      <c r="R1008" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="1009">
       <c r="A1009" s="4" t="n">
@@ -44731,6 +47297,21 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="O1009" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Chile</t>
+        </is>
+      </c>
+      <c r="P1009" t="inlineStr">
+        <is>
+          <t>| established_date2 = 12 February 1818</t>
+        </is>
+      </c>
+      <c r="R1009" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="1010">
       <c r="A1010" s="4" t="n">
@@ -44780,6 +47361,11 @@
           <t>In 1810 verklaarde Colombia zich onafhankelijk.</t>
         </is>
       </c>
+      <c r="R1010" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="1011">
       <c r="A1011" s="4" t="n">
@@ -44829,6 +47415,11 @@
           <t>In 1922 werd het deels onafhankelijk van het Britse Rijk als een monarchie.</t>
         </is>
       </c>
+      <c r="R1011" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="1012">
       <c r="A1012" s="4" t="n">
@@ -44879,6 +47470,11 @@
 Het huidige Ghana ontstond op 6 maart 1957 toen twee Britse kolonies Gold Coast (Britse Goudkust) en Brits-Togoland, die een jaar eerder waren samengevoegd, een onafhankelijk land vormden onder de naam Ghana.</t>
         </is>
       </c>
+      <c r="R1012" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="1013" ht="25" customHeight="1">
       <c r="A1013" s="4" t="n">
@@ -44928,6 +47524,11 @@
           <t>Pas met de onafhankelijkheid van India in 1947 ontstond de huidige, vastomlijnde maar veel beperktere betekenis, waarbij het Engelse woord voor Indië voortaan in het Nederlands op de nieuwe staat ging slaan.</t>
         </is>
       </c>
+      <c r="R1013" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="1014">
       <c r="A1014" s="4" t="n">
@@ -44977,6 +47578,11 @@
           <t>Op 12 december 1963 werd Kenia een onafhankelijke monarchie, met de Britse koningin als staatshoofd en Jomo Kenyatta als premier.</t>
         </is>
       </c>
+      <c r="R1014" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="1015">
       <c r="A1015" s="4" t="n">
@@ -45011,6 +47617,21 @@
           <t>geen bron · geen EN-vertaling</t>
         </is>
       </c>
+      <c r="O1015" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Mexico</t>
+        </is>
+      </c>
+      <c r="P1015" t="inlineStr">
+        <is>
+          <t>| established_date2 = 27 September 1821</t>
+        </is>
+      </c>
+      <c r="R1015" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="1016" ht="25" customHeight="1">
       <c r="A1016" s="4" t="n">
@@ -45045,6 +47666,21 @@
           <t>geen bron · geen EN-vertaling</t>
         </is>
       </c>
+      <c r="O1016" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Nelson_Mandela</t>
+        </is>
+      </c>
+      <c r="P1016" t="inlineStr">
+        <is>
+          <t>Although some were deeply opposed to his plans, de Klerk met with Mandela in December to discuss the situation, a meeting both men considered friendly, before legalising all formerly banned political parties in February 1990 and announcing Mandela's unconditional release.</t>
+        </is>
+      </c>
+      <c r="R1016" t="inlineStr">
+        <is>
+          <t>matig</t>
+        </is>
+      </c>
     </row>
     <row r="1017">
       <c r="A1017" s="4" t="n">
@@ -45089,6 +47725,11 @@
           <t>Nigeria werd op 1 oktober 1960 onafhankelijk van het Verenigd Koninkrijk.</t>
         </is>
       </c>
+      <c r="R1017" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="1018" ht="25" customHeight="1">
       <c r="A1018" s="4" t="n">
@@ -45138,6 +47779,11 @@
           <t>Paraguay als zelfstandige staat is ontstaan op 14 mei 1811, toen het zich bevrijdde van de vroegere kolonisator Spanje.</t>
         </is>
       </c>
+      <c r="R1018" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="1019" ht="25" customHeight="1">
       <c r="A1019" s="4" t="n">
@@ -45182,6 +47828,11 @@
           <t>Tussen de verovering in 1572 en de onafhankelijkheid in 1821 werd het land door Spanje bestuurd.</t>
         </is>
       </c>
+      <c r="R1019" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="1020">
       <c r="A1020" s="4" t="n">
@@ -45227,6 +47878,11 @@
 After unsuccessful uprisings, Venezuela under the leadership of Francisco de Miranda, a Venezuelan marshal who had fought in the American and French Revolutions, declared independence as the First Republic of Venezuela on 1811-07-11.</t>
         </is>
       </c>
+      <c r="R1020" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="1021">
       <c r="A1021" s="4" t="n">
@@ -45271,6 +47927,11 @@
           <t>In 1990 werd de apartheid afgeschaft en in 1994 werd Nelson Mandela tot de eerste zwarte president van Zuid-Afrika verkozen.</t>
         </is>
       </c>
+      <c r="R1021" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="1022">
       <c r="A1022" s="4" t="n">
@@ -45315,6 +47976,11 @@
           <t>De verklaring werd door vertegenwoordigers van 12 van de toen 13 Amerikaanse kolonies aangenomen op 4 juli 1776.</t>
         </is>
       </c>
+      <c r="R1022" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="1023">
       <c r="A1023" s="4" t="n">
@@ -45364,6 +48030,11 @@
           <t>Onder de Berlijnse Muur (Duits: Berliner Mauer) verstaat men de tot 100 meter brede constructie van opeenvolgende obstakels die van 13 augustus 1961 tot 9 november 1989 West-Berlijn geheel omringde.</t>
         </is>
       </c>
+      <c r="R1023" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="1024">
       <c r="A1024" s="4" t="n">
@@ -45408,6 +48079,11 @@
           <t>De Eerste Franse Republiek werd uitgeroepen op 21 september 1792 door de Nationale Conventie, en duurde tot de vestiging van het Eerste Franse Keizerrijk in 1804 onder Napoleon Bonaparte.</t>
         </is>
       </c>
+      <c r="R1024" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="1025">
       <c r="A1025" s="4" t="n">
@@ -45453,6 +48129,11 @@
 In 1945 werd de burgeroorlog hervat en in 1949 gewonnen door de communisten onder leiding van Mao Zedong.</t>
         </is>
       </c>
+      <c r="R1025" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="1026">
       <c r="A1026" s="4" t="n">
@@ -45507,6 +48188,11 @@
           <t>Hij maakte naam door zijn ontdekking van Amerika onder Spaanse vlag in 1492.</t>
         </is>
       </c>
+      <c r="R1026" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="1027">
       <c r="A1027" s="4" t="n">
@@ -45553,6 +48239,11 @@
       <c r="P1027" t="inlineStr">
         <is>
           <t>In april 2010 kwamen China en Nepal overeen de hoogte van de Mount Everest officieel als 8848,86 meter te erkennen.</t>
+        </is>
+      </c>
+      <c r="R1027" t="inlineStr">
+        <is>
+          <t>hoog</t>
         </is>
       </c>
     </row>
@@ -45729,6 +48420,11 @@
 Referenties</t>
         </is>
       </c>
+      <c r="R1031" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="1032">
       <c r="A1032" s="4" t="n">
@@ -45856,6 +48552,11 @@
           <t>Op 1 januari 2019 telde Italië 60.359.546 inwoners.</t>
         </is>
       </c>
+      <c r="R1034" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="1035">
       <c r="A1035" s="4" t="n">
@@ -45934,6 +48635,33 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="O1036" t="inlineStr">
+        <is>
+          <t>https://nl.wikipedia.org/wiki/Vincent_van_Gogh_Vijfje</t>
+        </is>
+      </c>
+      <c r="P1036">
+        <f>= De Vincent van Gogh-verzamelmunten ==
+=== 5 euromunt ===
+Metaal: zilver 925/1000
+Gewicht: 11,9 gram
+Diameter: 29 millimeter
+Kwaliteit: Proof
+Nominale waarde: € 5,-
+Ontwerp: Karel Martens
+Randschrift: God zij met ons
+=== 10 euromunt ===
+Metaal: goud 900/1000
+Gewicht: 6,72 gram
+Diameter: 22,5 millimeter
+Kwaliteit:</f>
+        <v/>
+      </c>
+      <c r="R1036" t="inlineStr">
+        <is>
+          <t>matig</t>
+        </is>
+      </c>
     </row>
     <row r="1037">
       <c r="A1037" s="4" t="n">
@@ -45985,6 +48713,11 @@
 In 2020 UNESCO stated that the size of the illicit trade in cultural property amounted to 10 billion dollars a year.</t>
         </is>
       </c>
+      <c r="R1037" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="1038">
       <c r="A1038" s="4" t="n">
@@ -46572,6 +49305,11 @@
           <t>Er wordt geschat dat meer dan 50% van de IJslanders elk jaar een elektronische kerstkaart verstuurt.</t>
         </is>
       </c>
+      <c r="R1052" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="1053">
       <c r="A1053" s="4" t="n">
@@ -46853,6 +49591,11 @@
           <t>The protected area within the region includes approximately 30,000 km2 (12,000 sq mi) of land, including the Serengeti National Park and several game reserves.</t>
         </is>
       </c>
+      <c r="R1059" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="1060">
       <c r="A1060" s="4" t="n">
@@ -47174,6 +49917,11 @@
           <t>Het massagehalte aan goud van sieraden wordt gemeten in karaat; zuiver goud is 24 karaat.</t>
         </is>
       </c>
+      <c r="R1067" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="1068">
       <c r="A1068" s="4" t="n">
@@ -47262,6 +50010,11 @@
           <t>Israel's 2024 entry "Hurricane" was also controversial, as an earlier version titled "October Rain" was seen as referencing the 7 October attacks on Israel, a breach of political neutrality rules, which led to it only being accepted by the EBU after a rewrite.</t>
         </is>
       </c>
+      <c r="R1069" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="1070">
       <c r="A1070" s="4" t="n">
@@ -47311,6 +50064,11 @@
           <t>Israel's 2024 entry "Hurricane" was also controversial, as an earlier version titled "October Rain" was seen as referencing the 7 October attacks on Israel, a breach of political neutrality rules, which led to it only being accepted by the EBU after a rewrite.</t>
         </is>
       </c>
+      <c r="R1070" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="1071" ht="25" customHeight="1">
       <c r="A1071" s="4" t="n">
@@ -47399,6 +50157,11 @@
           <t>Beyoncé is the most-awarded artist of the BET Awards (36), MTV Video Music Awards (30), NAACP Image Awards (32), and Soul Train Music Awards (25).</t>
         </is>
       </c>
+      <c r="R1072" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="1073">
       <c r="A1073" s="4" t="n">
@@ -47488,6 +50251,11 @@
 On the evenings of 12 and 13 March 2009 a reformed Midnight Oil, with Garrett, played at the Royal Theatre in Canberra.</t>
         </is>
       </c>
+      <c r="R1074" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="1075">
       <c r="A1075" s="4" t="n">
@@ -47574,6 +50342,11 @@
       <c r="P1076" t="inlineStr">
         <is>
           <t>During the week of 4 April 1964, the Beatles held twelve positions on the Billboard Hot 100 singles chart, including the top five.</t>
+        </is>
+      </c>
+      <c r="R1076" t="inlineStr">
+        <is>
+          <t>hoog</t>
         </is>
       </c>
     </row>
@@ -47706,6 +50479,11 @@
 Presley werd op 8 januari 1935 geboren in een shotgun house in Tupelo in Mississippi (zie geboortehuis van Elvis Presley) als de zoon van Gladys Love (meisjesnaam Smith; 25 april 1912 – 14 augustus 1958) en Vernon Elvis Presley (10</t>
         </is>
       </c>
+      <c r="R1079" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="1080">
       <c r="A1080" s="4" t="n">
@@ -47753,6 +50531,11 @@
       <c r="P1080" t="inlineStr">
         <is>
           <t>De tussenvorm, de extended play (ep), met vier tot zes nummers op een grammofoonplaat van 7", werd oorspronkelijk opgenomen in de Hot 100, maar verhuisde medio jaren zestig van de 20e eeuw naar de Billboard 200.</t>
+        </is>
+      </c>
+      <c r="R1080" t="inlineStr">
+        <is>
+          <t>hoog</t>
         </is>
       </c>
     </row>
@@ -47807,6 +50590,11 @@
 negen concerten voor solo-instrumenten en orkest: vijf 'officiële' pianocon</t>
         </is>
       </c>
+      <c r="R1081" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="1082">
       <c r="A1082" s="4" t="n">
@@ -48056,6 +50844,11 @@
           <t>Het instrument heeft meestal 21 snaren (dit aantal varieert tussen 15 en 25).</t>
         </is>
       </c>
+      <c r="R1087" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="1088">
       <c r="A1088" s="4" t="n">
@@ -48266,6 +51059,11 @@
           <t>Kleinere afmetingen van de cello zijn 1⁄16, 1⁄8, 1⁄4, 1⁄2, 3⁄4, 4⁄4 en 7⁄8 cello.</t>
         </is>
       </c>
+      <c r="R1092" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="1093" ht="25" customHeight="1">
       <c r="A1093" s="4" t="n">
@@ -48388,6 +51186,11 @@
           <t>Taylor Swift won ruim 250 awards, waaronder 12 Grammy Awards (uit 34 nominaties), 16 American Music Awards, 11 Country Music Association Awards, 22 Billboard Music Awards en één Emmy Award.</t>
         </is>
       </c>
+      <c r="R1095" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="1096">
       <c r="A1096" s="4" t="n">
@@ -48476,6 +51279,11 @@
           <t>Op zijn vijftiende begon Brahms volksliedjes te verzamelen en te bewerken, en in 1851 kwam zijn eerste officiële werk tot stand, het Scherzo in es-klein (opus 4).</t>
         </is>
       </c>
+      <c r="R1097" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="1098" ht="25" customHeight="1">
       <c r="A1098" s="4" t="n">
@@ -48515,6 +51323,28 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="O1098" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/List_of_symphonies_by_Wolfgang_Amadeus_Mozart</t>
+        </is>
+      </c>
+      <c r="P1098">
+        <f>= List of symphonies ==
+  : Outside of original 41
+== Adapted from serenades ==
+== Doubtful authenticity ==
+== Spurious authenticity ==
+== See also ==
+Mozart symphonies of spurious or doubtful authenticity
+List of compositions by Wolfgang Amadeus Mozart
+== Notes ==</f>
+        <v/>
+      </c>
+      <c r="R1098" t="inlineStr">
+        <is>
+          <t>matig</t>
+        </is>
+      </c>
     </row>
     <row r="1099">
       <c r="A1099" s="4" t="n">
@@ -48642,6 +51472,11 @@
           <t>100 °C is de temperatuur waarbij water kookt bij een luchtdruk van 1 atmosfeer.</t>
         </is>
       </c>
+      <c r="R1101" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="1102">
       <c r="A1102" s="4" t="n">
@@ -48689,6 +51524,11 @@
       <c r="P1102" t="inlineStr">
         <is>
           <t>De kármánlijn is een denkbeeldige grens op een hoogte van 100 kilometer boven de Aarde.</t>
+        </is>
+      </c>
+      <c r="R1102" t="inlineStr">
+        <is>
+          <t>hoog</t>
         </is>
       </c>
     </row>
@@ -48774,6 +51614,11 @@
 c = 299 792 458 m/s
 Kenmerken
 De lichtsnelheid in vacuüm wordt beschouwd als een natuurconstante.</t>
+        </is>
+      </c>
+      <c r="R1104" t="inlineStr">
+        <is>
+          <t>hoog</t>
         </is>
       </c>
     </row>
@@ -48955,6 +51800,11 @@
 </t>
         </is>
       </c>
+      <c r="R1108" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="1109" ht="25" customHeight="1">
       <c r="A1109" s="4" t="n">
@@ -49043,6 +51893,11 @@
           <t>Van Persie recorded over 100 caps and scored 50 goals for the Netherlands (he was the nation's all-time top goalscorer until 2025).</t>
         </is>
       </c>
+      <c r="R1110" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="1111">
       <c r="A1111" s="4" t="n">
@@ -49214,6 +52069,11 @@
           <t>Om die reden groeide hij op met alleen naar de radio te luisteren, voornamelijk naar de Nederlandse publieke zender Hilversum 3; de popzender.</t>
         </is>
       </c>
+      <c r="R1114" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="1115">
       <c r="A1115" s="4" t="n">
@@ -49263,6 +52123,11 @@
           <t>Om die reden groeide hij op met alleen naar de radio te luisteren, voornamelijk naar de Nederlandse publieke zender Hilversum 3; de popzender.</t>
         </is>
       </c>
+      <c r="R1115" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="1116" ht="25" customHeight="1">
       <c r="A1116" s="4" t="n">
@@ -49312,6 +52177,11 @@
           <t>De andere nationale feestdag is Bevrijdingsdag: op 5 mei wordt de capitulatie van het Duitse leger in Nederland tijdens de Tweede Wereldoorlog gevierd.</t>
         </is>
       </c>
+      <c r="R1116" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="1117" ht="25" customHeight="1">
       <c r="A1117" s="4" t="n">
@@ -49366,6 +52236,11 @@
           <t>De bank is gevestigd aan het Frederiksplein (bezoekadres Westeinde 1) in Amsterdam.</t>
         </is>
       </c>
+      <c r="R1117" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="1118" ht="25" customHeight="1">
       <c r="A1118" s="4" t="n">
@@ -49418,6 +52293,11 @@
       <c r="P1118" t="inlineStr">
         <is>
           <t>Op 21 april 1906 werd de eerste paardentramlijn door het Binnenhof vervangen door de elektrische tramlijn 3.</t>
+        </is>
+      </c>
+      <c r="R1118" t="inlineStr">
+        <is>
+          <t>hoog</t>
         </is>
       </c>
     </row>
@@ -49641,6 +52521,11 @@
 Oudegracht/Bakkerbru</t>
         </is>
       </c>
+      <c r="R1123" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="1124">
       <c r="A1124" s="4" t="n">
@@ -49696,6 +52581,11 @@
 Verder heeft de marine de beschikking over 3 kustwachtcutters, 1 opleidingsvaartuig, 1 zeilend schoolschip, 4 kustsleepboten, 2 havensleepboten en 17 landingsvaartuigen.</t>
         </is>
       </c>
+      <c r="R1124" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="1125" ht="25" customHeight="1">
       <c r="A1125" s="4" t="n">
@@ -49782,6 +52672,21 @@
       <c r="N1126" s="4" t="inlineStr">
         <is>
           <t>geen bron</t>
+        </is>
+      </c>
+      <c r="O1126" t="inlineStr">
+        <is>
+          <t>https://nl.wikipedia.org/wiki/Nederlandse_1_gulden</t>
+        </is>
+      </c>
+      <c r="P1126" t="inlineStr">
+        <is>
+          <t>Het 1 guldenstuk of gulden is een Nederlandse munt die vanaf het einde van de 13e eeuw tot 28 januari 2002 heeft gecirculeerd.</t>
+        </is>
+      </c>
+      <c r="R1126" t="inlineStr">
+        <is>
+          <t>matig</t>
         </is>
       </c>
     </row>
@@ -49836,6 +52741,11 @@
 De Nederlandse Antillen had een bevolkingsgroei van 0,79%.</t>
         </is>
       </c>
+      <c r="R1127" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="1128">
       <c r="A1128" s="4" t="n">
@@ -49883,6 +52793,11 @@
       <c r="P1128" t="inlineStr">
         <is>
           <t>More recent scholarship, from the 1960s to the present day (led by the Rembrandt Research Project), often controversially, has winnowed his oeuvre to nearer 300 paintings.</t>
+        </is>
+      </c>
+      <c r="R1128" t="inlineStr">
+        <is>
+          <t>hoog</t>
         </is>
       </c>
     </row>
@@ -50142,6 +53057,11 @@
 The A9 motorway runs from </t>
         </is>
       </c>
+      <c r="R1134" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="1135">
       <c r="A1135" s="4" t="n">
@@ -50235,6 +53155,11 @@
           <t>Sporthistoricus Jurryt van de Vooren lanceerde op 15 januari 2020 (de datum van oprichting in 1909 van de Koninklijke Vereniging De Friesche Elf Steden) in het Fries Scheepvaart Museum in Sneek de eerste "Dag van de Elfstedentocht", bedoeld om de herinnering aan de Elfstedentocht in leven te houden.</t>
         </is>
       </c>
+      <c r="R1136" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="1137">
       <c r="A1137" s="4" t="n">
@@ -50328,6 +53253,11 @@
           <t>De vijf grootste steden in Noord-Brabant vormen het samenwerkingsverband BrabantStad; met een verzorgingsgebied van 1,5 miljoen mensen en 20% van de industriële productie van Nederland, een andere belangrijke stedelijke regio.</t>
         </is>
       </c>
+      <c r="R1138" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="1139">
       <c r="A1139" s="4" t="n">
@@ -50453,6 +53383,11 @@
       <c r="Q1141" t="inlineStr">
         <is>
           <t>Wikidata: klopt</t>
+        </is>
+      </c>
+      <c r="R1141" t="inlineStr">
+        <is>
+          <t>hoog</t>
         </is>
       </c>
     </row>
@@ -50519,6 +53454,11 @@
           <t>Wikidata: geen waarde</t>
         </is>
       </c>
+      <c r="R1142" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="1143">
       <c r="A1143" s="4" t="n">
@@ -50558,9 +53498,24 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="O1143" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/HSL-Zuid</t>
+        </is>
+      </c>
+      <c r="P1143" t="inlineStr">
+        <is>
+          <t>| linelength = cvt|125|km</t>
+        </is>
+      </c>
       <c r="Q1143" t="inlineStr">
         <is>
           <t>Wikidata: bijna</t>
+        </is>
+      </c>
+      <c r="R1143" t="inlineStr">
+        <is>
+          <t>hoog</t>
         </is>
       </c>
     </row>
@@ -50783,6 +53738,11 @@
           <t>Wikidata: geen waarde</t>
         </is>
       </c>
+      <c r="R1148" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="1149">
       <c r="A1149" s="4" t="n">
@@ -50905,6 +53865,21 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="O1151" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Carillon</t>
+        </is>
+      </c>
+      <c r="P1151" t="inlineStr">
+        <is>
+          <t>A "concert" or "standard" carillon typically has 45 to 50 bells, or a range of about four octaves.</t>
+        </is>
+      </c>
+      <c r="R1151" t="inlineStr">
+        <is>
+          <t>matig</t>
+        </is>
+      </c>
     </row>
     <row r="1152">
       <c r="A1152" s="4" t="n">
@@ -50959,6 +53934,11 @@
           <t>Wikidata: ander onderwerp</t>
         </is>
       </c>
+      <c r="R1152" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="1153">
       <c r="A1153" s="4" t="n">
@@ -51102,6 +54082,11 @@
 Het Nederlands is de moedertaal van ongeveer 6.600.000 Belgen; daarnaast zijn er ongeveer 4.700.000 Franstaligen en ook 77.000 mensen die het Duits als voertaal gebruiken.</t>
         </is>
       </c>
+      <c r="R1155" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="1156">
       <c r="A1156" s="4" t="n">
@@ -51151,6 +54136,11 @@
           <t>Daarnaast is er ook een variant ontwikkeld waarbij er in drietallen wordt gespeeld op een veld van 8 bij 16 meter met twee korven op 3 meter van de achterlijn.</t>
         </is>
       </c>
+      <c r="R1156" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="1157" ht="25" customHeight="1">
       <c r="A1157" s="4" t="n">
@@ -51205,6 +54195,11 @@
           <t>Het Nederlands alleen wordt door meer mensen gesproken dan de Noord-Germaanse (Scandinavische) talen bij elkaar: Zweeds (10 miljoen), Noors (5 miljoen), Deens (5 miljoen) en IJslands (0,3 miljoen).</t>
         </is>
       </c>
+      <c r="R1157" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="1158" ht="25" customHeight="1">
       <c r="A1158" s="4" t="n">
@@ -51255,6 +54250,11 @@
 Nederland passeerde half augustus 2024 de grens van achttien miljoen inwoners en had toen een bevolkingsdichtheid van 433 inwoners per km2.</t>
         </is>
       </c>
+      <c r="R1158" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="1159">
       <c r="A1159" s="4" t="n">
@@ -51343,6 +54343,11 @@
           <t>Het Nederlands alleen wordt door meer mensen gesproken dan de Noord-Germaanse (Scandinavische) talen bij elkaar: Zweeds (10 miljoen), Noors (5 miljoen), Deens (5 miljoen) en IJslands (0,3 miljoen).</t>
         </is>
       </c>
+      <c r="R1160" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="1161" ht="25" customHeight="1">
       <c r="A1161" s="4" t="n">
@@ -51392,6 +54397,11 @@
           <t>Het Verenigd Koninkrijk omvat in totaal vier constituerende landen: Engeland in het midden en zuiden (56.286.961 inwoners, 2019), Schotland in het noorden (5.439.842 inwoners, 2022), Wales in het westen (3.153.000 inwoners, 2022) en Noord-Ierland in het noordwesten (2.050.025 inwoners, 2019).</t>
         </is>
       </c>
+      <c r="R1161" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="1162">
       <c r="A1162" s="4" t="n">
@@ -51441,6 +54451,11 @@
           <t>Bijna tien jaar na de inwerkingtreding van de douaneovereenkomst, op 3 februari 1958, ondertekenden België, Luxemburg en Nederland het Verdrag tot instelling van de Benelux Economische Unie.</t>
         </is>
       </c>
+      <c r="R1162" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="1163">
       <c r="A1163" s="4" t="n">
@@ -51488,6 +54503,11 @@
       <c r="P1163" t="inlineStr">
         <is>
           <t>De Tweede Kamer telt sinds 1956 150 zetels en de eerste zitting was op 21 september 1815.</t>
+        </is>
+      </c>
+      <c r="R1163" t="inlineStr">
+        <is>
+          <t>hoog</t>
         </is>
       </c>
     </row>
@@ -51619,6 +54639,11 @@
 2020</t>
         </is>
       </c>
+      <c r="R1166" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="1167" ht="25" customHeight="1">
       <c r="A1167" s="4" t="n">
@@ -51663,6 +54688,21 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="O1167" t="inlineStr">
+        <is>
+          <t>https://nl.wikipedia.org/wiki/Zeelandbrug</t>
+        </is>
+      </c>
+      <c r="P1167" t="inlineStr">
+        <is>
+          <t>| hoogte = 16</t>
+        </is>
+      </c>
+      <c r="R1167" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="1168" ht="25" customHeight="1">
       <c r="A1168" s="4" t="n">
@@ -51717,6 +54757,11 @@
           <t>Wikidata: geen waarde</t>
         </is>
       </c>
+      <c r="R1168" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="1169" ht="25" customHeight="1">
       <c r="A1169" s="4" t="n">
@@ -51756,9 +54801,24 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="O1169" t="inlineStr">
+        <is>
+          <t>https://nl.wikipedia.org/wiki/Euromast</t>
+        </is>
+      </c>
+      <c r="P1169" t="inlineStr">
+        <is>
+          <t>| hoogte = 107 m (tot 1970) 185 m (1970-heden)</t>
+        </is>
+      </c>
       <c r="Q1169" t="inlineStr">
         <is>
           <t>Wikidata: geen waarde</t>
+        </is>
+      </c>
+      <c r="R1169" t="inlineStr">
+        <is>
+          <t>hoog</t>
         </is>
       </c>
     </row>
@@ -51815,6 +54875,11 @@
           <t>Wikidata: geen waarde</t>
         </is>
       </c>
+      <c r="R1170" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="1171" ht="25" customHeight="1">
       <c r="A1171" s="4" t="n">
@@ -51986,6 +55051,11 @@
           <t>Ter vergelijking: de Belgische bevolking groeide van anderhalf keer zo groot als die van Nederland (4,5 miljoen in 1850) tot ruim een derde kleiner (10 miljoen in 2000).</t>
         </is>
       </c>
+      <c r="R1174" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="1175" ht="25" customHeight="1">
       <c r="A1175" s="4" t="n">
@@ -52033,6 +55103,11 @@
       <c r="P1175" t="inlineStr">
         <is>
           <t>Als hoofdstad van het nieuwe koninkrijk koos hij Amsterdam en na een feestelijke binnenkomst in de stad, kreeg hij op 20 april 1808 de stadssleutels overhandigd.</t>
+        </is>
+      </c>
+      <c r="R1175" t="inlineStr">
+        <is>
+          <t>hoog</t>
         </is>
       </c>
     </row>
@@ -52087,6 +55162,11 @@
 Voor jonge jenever zijn er geen richtlijnen wat betreft kruiden.</t>
         </is>
       </c>
+      <c r="R1176" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="1177">
       <c r="A1177" s="4" t="n">
@@ -52175,6 +55255,11 @@
           <t>De economische activiteiten in Amsterdam concentreren zich in het stadscentrum, waar ruim 80.000 mensen een baan hebben.</t>
         </is>
       </c>
+      <c r="R1178" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="1179" ht="25" customHeight="1">
       <c r="A1179" s="4" t="n">
@@ -52226,6 +55311,11 @@
 On 1 January 2023, Flevoland had a total population of 444,701 and a population density of 315/km2 (820/sq mi).</t>
         </is>
       </c>
+      <c r="R1179" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="1180">
       <c r="A1180" s="4" t="n">
@@ -52470,6 +55560,11 @@
           <t>De vijf grootste steden in Noord-Brabant vormen het samenwerkingsverband BrabantStad; met een verzorgingsgebied van 1,5 miljoen mensen en 20% van de industriële productie van Nederland, een andere belangrijke stedelijke regio.</t>
         </is>
       </c>
+      <c r="R1185" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="1186" ht="25" customHeight="1">
       <c r="A1186" s="4" t="n">
@@ -52519,6 +55614,11 @@
           <t>24 August 2019 – 1 December 2019: Leiden circa 1630: Rembrandt Emerges, Agnes Etherington Art Centre, Kingston, Ontario.</t>
         </is>
       </c>
+      <c r="R1186" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="1187" ht="25" customHeight="1">
       <c r="A1187" s="4" t="n">
@@ -52612,6 +55712,11 @@
           <t>De vijf grootste steden in Noord-Brabant vormen het samenwerkingsverband BrabantStad; met een verzorgingsgebied van 1,5 miljoen mensen en 20% van de industriële productie van Nederland, een andere belangrijke stedelijke regio.</t>
         </is>
       </c>
+      <c r="R1188" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="1189">
       <c r="A1189" s="4" t="n">
@@ -52739,6 +55844,11 @@
           <t>De gehele gemeente Rotterdam telt 674.485 inwoners en de nog grotere metropoolregio Rotterdam Den Haag telt meer dan 2,4 miljoen inwoners.</t>
         </is>
       </c>
+      <c r="R1191" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="1192">
       <c r="A1192" s="4" t="n">
@@ -52793,6 +55903,11 @@
           <t>Feenstra (2009), Geschiedenis van Groningen / 3: Nieuwste tijd tot heden.</t>
         </is>
       </c>
+      <c r="R1192" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="1193" ht="25" customHeight="1">
       <c r="A1193" s="4" t="n">
@@ -52843,6 +55958,11 @@
 Tussen 3 april 2016 en juli 2022 voerde Thalys een low-cost-submerk: de IZY, die dagelijks twee heen- en terugritten Brussel – Parijs reed, met treinstellen in een speciale kleurstelling.</t>
         </is>
       </c>
+      <c r="R1193" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="1194" ht="25" customHeight="1">
       <c r="A1194" s="4" t="n">
@@ -52882,6 +56002,21 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="O1194" t="inlineStr">
+        <is>
+          <t>https://nl.wikipedia.org/wiki/De_Rotterdam</t>
+        </is>
+      </c>
+      <c r="P1194" t="inlineStr">
+        <is>
+          <t>| verdiepingen = 44</t>
+        </is>
+      </c>
+      <c r="R1194" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="1195">
       <c r="A1195" s="4" t="n">
@@ -53009,6 +56144,11 @@
           <t>De 19 windmolens zijn verdeeld in een rij van acht molens aan de Nederwaard (dit zijn de ronde stenen molens), een rij van acht rietgedekte achtkanters aan de Overwaard, met daarnaast een wipmolen; de Blokweerse molen die de polder Blokweer bemaalt en in de polder Nieuw-Lekkerland twee rietgedekte a</t>
         </is>
       </c>
+      <c r="R1197" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="1198">
       <c r="A1198" s="4" t="n">
@@ -53087,9 +56227,24 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="O1199" t="inlineStr">
+        <is>
+          <t>https://nl.wikipedia.org/wiki/Bevolking_van_China</t>
+        </is>
+      </c>
+      <c r="P1199" t="inlineStr">
+        <is>
+          <t>De bevolking van China bestaat uit 1410 miljoen personen (2023).</t>
+        </is>
+      </c>
       <c r="Q1199" t="inlineStr">
         <is>
           <t>Wikidata: geen waarde</t>
+        </is>
+      </c>
+      <c r="R1199" t="inlineStr">
+        <is>
+          <t>matig</t>
         </is>
       </c>
     </row>
@@ -53225,6 +56380,11 @@
 Bolivia is ingedeeld in 9 departementen, 112 provincies, 339 gemeentes en 1.384 kantons.</t>
         </is>
       </c>
+      <c r="R1202" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="1203">
       <c r="A1203" s="4" t="n">
@@ -53275,6 +56435,11 @@
 Colombia is een eenheidsstaat die bestaat uit 32 departementen plus het Hoofdstedelijk District van Bogota.</t>
         </is>
       </c>
+      <c r="R1203" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="1204">
       <c r="A1204" s="4" t="n">
@@ -53326,6 +56491,11 @@
 De hoofdstad is Lima.</t>
         </is>
       </c>
+      <c r="R1204" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="1205">
       <c r="A1205" s="4" t="n">
@@ -53404,6 +56574,21 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="O1206" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/United_States_Electoral_College</t>
+        </is>
+      </c>
+      <c r="P1206" t="inlineStr">
+        <is>
+          <t>The six states with the most electors are California (54), Texas (40), Florida (30), New York (28), Illinois (19), and Pennsylvania (19).</t>
+        </is>
+      </c>
+      <c r="R1206" t="inlineStr">
+        <is>
+          <t>matig</t>
+        </is>
+      </c>
     </row>
     <row r="1207">
       <c r="A1207" s="4" t="n">
@@ -53655,6 +56840,11 @@
 Under Article I, Section 2 of the Constitution, seats in the House of Representatives are apportioned among the states by population, as determined by the census conducted every ten years.</t>
         </is>
       </c>
+      <c r="R1212" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="1213">
       <c r="A1213" s="4" t="n">
@@ -53704,6 +56894,11 @@
           <t>Dit schip leverde op 8 en 9 maart 1862 de eerste slag tussen twee ijzeren schepen met de CSS Virginia en won nipt.</t>
         </is>
       </c>
+      <c r="R1213" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="1214">
       <c r="A1214" s="4" t="n">
@@ -53831,6 +57026,11 @@
           <t>De verdragen zijn voor 29 landen in werking getreden.</t>
         </is>
       </c>
+      <c r="R1216" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="1217" ht="25" customHeight="1">
       <c r="A1217" s="4" t="n">
@@ -53997,6 +57197,11 @@
           <t>On 17 June 2024, prior to the 2024 Washington summit, Stoltenberg updated that figure and announced that a record 23 of 32 NATO member states were meeting their defense spending targets of 2% of their country's GDP.</t>
         </is>
       </c>
+      <c r="R1220" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="1221">
       <c r="A1221" s="4" t="n">
@@ -54046,6 +57251,11 @@
           <t>Pacific Islands Forum of Forum des îles du Pacifique is een intergouvernementele organisatie die de samenwerking bevordert tussen 18 landen uit Oceanië.</t>
         </is>
       </c>
+      <c r="R1221" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="1222">
       <c r="A1222" s="4" t="n">
@@ -54095,6 +57305,11 @@
           <t>Het Pan-Afrikaans Parlement heeft per lidstaat maximaal vijf leden (in 2024 zijn er 55 lidstaten, dus heeft het Parlement maximaal 275 leden).</t>
         </is>
       </c>
+      <c r="R1222" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="1223">
       <c r="A1223" s="4" t="n">
@@ -54185,6 +57400,11 @@
 De huidige commissie is de commissie-Von der Leyen II en bestaat uit 27 leden, elke lidstaat levert één lid.</t>
         </is>
       </c>
+      <c r="R1224" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="1225">
       <c r="A1225" s="4" t="n">
@@ -54234,6 +57454,11 @@
           <t>The EU and China maintained a nearly balanced merchandise trade with Mercosur in 2010, while the United States reaped a surplus of over US$14 billion; Mercosur, in turn, earned significant surpluses (over US$4 billion each in 2010) in its trade with Chile and Venezuela.</t>
         </is>
       </c>
+      <c r="R1225" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="1226">
       <c r="A1226" s="4" t="n">
@@ -54283,6 +57508,11 @@
           <t>Hoewel de Raad van Europa met zijn 46 leden dezelfde vlag voert en dezelfde hymne kent, verschilt deze organisatie van de Europese Unie met haar 27 leden (zie Verschil met andere internationale organisaties in Europa hieronder).</t>
         </is>
       </c>
+      <c r="R1226" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="1227" ht="25" customHeight="1">
       <c r="A1227" s="4" t="n">
@@ -54366,6 +57596,11 @@
           <t>Het bestaat uit 435 stemgerechtigde leden en elk stemgerechtigd lid wordt gekozen in een congresdistrict dat vastgesteld wordt op basis van de gegevens van de volkstelling (census).</t>
         </is>
       </c>
+      <c r="R1228" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="1229" ht="25" customHeight="1">
       <c r="A1229" s="4" t="n">
@@ -54415,6 +57650,11 @@
           <t>The House of Commons is an elected body consisting of 650 members known as members of Parliament (MPs), who are elected to represent constituencies by the first-past-the-post system and hold their seats until Parliament is dissolved.</t>
         </is>
       </c>
+      <c r="R1229" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="1230" ht="25" customHeight="1">
       <c r="A1230" s="4" t="n">
@@ -54464,6 +57704,11 @@
           <t>Het Lagerhuis bestaat uit 650 leden die binnen enkelvoudige kiesdistricten worden gekozen (een meerderheidsstelsel, waarbij een relatieve meerderheid in een district voldoende is om gekozen te worden).</t>
         </is>
       </c>
+      <c r="R1230" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="1231" ht="25" customHeight="1">
       <c r="A1231" s="4" t="n">
@@ -54513,6 +57758,11 @@
           <t>Het Parlement bestaat in de zittingsperiode 2024-2029 uit 720 parlementsleden en vertegenwoordigt na het parlement van India het op een na grootste electoraat ter wereld.</t>
         </is>
       </c>
+      <c r="R1231" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="1232" ht="25" customHeight="1">
       <c r="A1232" s="4" t="n">
@@ -54563,6 +57813,11 @@
 South Africa has 12 official languages: Afrikaans, Zulu, Xhosa, English, Pedi, Tswana, Southern Sotho, Tsonga, Swazi, Venda, and Southern Ndebele (in order of first language speakers), as well as South African Sign Language, which was recognised as an official language in 2023.</t>
         </is>
       </c>
+      <c r="R1232" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="1233" ht="25" customHeight="1">
       <c r="A1233" s="4" t="n">
@@ -54646,6 +57901,11 @@
           <t>Indonesië functioneert als een presidentiële republiek met een gekozen wetgevende macht en bestaat uit 38 provincies, waarvan negen een speciale autonome status hebben.</t>
         </is>
       </c>
+      <c r="R1234" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="1235" ht="25" customHeight="1">
       <c r="A1235" s="4" t="n">
@@ -54696,6 +57956,11 @@
 Ecuador bestaat uit vier regio's en is onderverdeeld in 24 provincies.</t>
         </is>
       </c>
+      <c r="R1235" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="1236">
       <c r="A1236" s="4" t="n">
@@ -54745,6 +58010,11 @@
           <t>Het hof bestaat uit 46 rechters, één namens elke lidstaat van de Raad van Europa.</t>
         </is>
       </c>
+      <c r="R1236" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="1237" ht="25" customHeight="1">
       <c r="A1237" s="4" t="n">
@@ -54839,6 +58109,11 @@
 De Senaat omvat 100 zetels, twee voor elke Amerikaanse staat.</t>
         </is>
       </c>
+      <c r="R1238" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="1239">
       <c r="A1239" s="4" t="n">
@@ -54928,6 +58203,11 @@
 Brazilië bestaat uit 26 staten en 1 federaal district, deze zijn gegroepeerd in 5 geografische regio's zonder bestuurlijke rol.</t>
         </is>
       </c>
+      <c r="R1240" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="1241">
       <c r="A1241" s="4" t="n">
@@ -54977,6 +58257,11 @@
           <t>Mexico heeft 32 vrijhandelsverdragen met meer dan 40 landen, die meer dan 90% van de Mexicaanse internationale handel dekken.</t>
         </is>
       </c>
+      <c r="R1241" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="1242" ht="25" customHeight="1">
       <c r="A1242" s="4" t="n">
@@ -55027,6 +58312,11 @@
 De Senaat omvat 100 zetels, twee voor elke Amerikaanse staat.</t>
         </is>
       </c>
+      <c r="R1242" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="1243" ht="25" customHeight="1">
       <c r="A1243" s="4" t="n">
@@ -55154,6 +58444,11 @@
           <t>Het Parlement bestaat in de zittingsperiode 2024-2029 uit 720 parlementsleden en vertegenwoordigt na het parlement van India het op een na grootste electoraat ter wereld.</t>
         </is>
       </c>
+      <c r="R1245" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="1246" ht="25" customHeight="1">
       <c r="A1246" s="4" t="n">
@@ -55188,6 +58483,22 @@
           <t>geen bron · geen EN-vertaling</t>
         </is>
       </c>
+      <c r="O1246" t="inlineStr">
+        <is>
+          <t>https://nl.wikipedia.org/wiki/Parlement_van_Zuid-Afrika</t>
+        </is>
+      </c>
+      <c r="P1246" t="inlineStr">
+        <is>
+          <t>Het parlement van Zuid-Afrika (Engels: Parliament of South Africa) is het nationale parlement van Zuid-Afrika en bestaat uit twee kamers:
+Lagerhuis: Nationale Vergadering (National Assembly) bestaande uit 400 leden.</t>
+        </is>
+      </c>
+      <c r="R1246" t="inlineStr">
+        <is>
+          <t>matig</t>
+        </is>
+      </c>
     </row>
     <row r="1247" ht="25" customHeight="1">
       <c r="A1247" s="4" t="n">
@@ -55393,6 +58704,11 @@
           <t>In feite wordt de slang maximaal 8 meter lang.</t>
         </is>
       </c>
+      <c r="R1251" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="1252">
       <c r="A1252" s="4" t="n">
@@ -56246,6 +59562,11 @@
           <t>100 °C is de temperatuur waarbij water kookt bij een luchtdruk van 1 atmosfeer.</t>
         </is>
       </c>
+      <c r="R1273" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="1274">
       <c r="A1274" s="4" t="n">
@@ -56296,6 +59617,11 @@
 0 °C (0 graden Celsius) is de temperatuur waarbij water bevriest bij een luchtdruk van 1 atmosfeer.</t>
         </is>
       </c>
+      <c r="R1274" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="1275">
       <c r="A1275" s="4" t="n">
@@ -56423,6 +59749,11 @@
           <t>Zwavelzuur – vroeger ook wel vitriool genoemd – is een industrieel belangrijk anorganisch zuur met als brutoformule H2SO4.</t>
         </is>
       </c>
+      <c r="R1277" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="1278">
       <c r="A1278" s="4" t="n">
@@ -56472,6 +59803,11 @@
           <t>Koolstof (Latijn: carbonium) is een scheikundig element met symbool C en atoomnummer 6.</t>
         </is>
       </c>
+      <c r="R1278" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="1279">
       <c r="A1279" s="4" t="n">
@@ -56521,6 +59857,11 @@
           <t>Zuurstof heeft atoomnummer 8.</t>
         </is>
       </c>
+      <c r="R1279" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="1280">
       <c r="A1280" s="4" t="n">
@@ -56997,6 +60338,11 @@
       <c r="P1291" t="inlineStr">
         <is>
           <t>Hij won een recordaantal van vijf Masters series toernooien in één seizoen (Indian Wells, Miami, Madrid, Rome en de Canadian Open) en had op het eind van het jaar een balans van 10-1 tegen zijn grootste rivalen, Roger Federer en Rafael Nadal.</t>
+        </is>
+      </c>
+      <c r="R1291" t="inlineStr">
+        <is>
+          <t>hoog</t>
         </is>
       </c>
     </row>
@@ -57052,6 +60398,11 @@
 1955/56, 1957</t>
         </is>
       </c>
+      <c r="R1292" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="1293">
       <c r="A1293" s="4" t="n">
@@ -57103,6 +60454,11 @@
 1995/96, 1997/98, 1998/99, 1999/00, 2000/01, 2001/02, 2002/03, 2003/04, 2004/05, 2005/06, 2006/07, 2007/08, 2008/09, 2009/10, 2010/11, 2011/12</t>
         </is>
       </c>
+      <c r="R1293" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="1294" ht="25" customHeight="1">
       <c r="A1294" s="4" t="n">
@@ -57152,6 +60508,11 @@
           <t>The 2016 and 2024 tournaments both featured 16 teams, with six teams from CONCACAF in addition to the 10 from CONMEBOL.</t>
         </is>
       </c>
+      <c r="R1294" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="1295" ht="25" customHeight="1">
       <c r="A1295" s="4" t="n">
@@ -57201,6 +60562,11 @@
           <t>The sole exception to this naming convention tradition occurred with Super Bowl 50, played on February 7, 2016, following the 2015 season.</t>
         </is>
       </c>
+      <c r="R1295" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="1296">
       <c r="A1296" s="4" t="n">
@@ -57248,6 +60614,11 @@
       <c r="P1296" t="inlineStr">
         <is>
           <t>De tour bestaat uit 24 toernooien, verdeeld over 6 weekenden.</t>
+        </is>
+      </c>
+      <c r="R1296" t="inlineStr">
+        <is>
+          <t>hoog</t>
         </is>
       </c>
     </row>
@@ -57341,6 +60712,11 @@
 Edward Eagan, goudenmeda</t>
         </is>
       </c>
+      <c r="R1298" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="1299">
       <c r="A1299" s="4" t="n">
@@ -57497,6 +60873,21 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="O1302" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Extra_innings</t>
+        </is>
+      </c>
+      <c r="P1302" t="inlineStr">
+        <is>
+          <t>The Washington Senators became the first team in Major League history to play multiple games of at least 20 innings in a season when they defeated the Minnesota Twins 9–7 in 20 innings on August 9, 1967, after winning a 22-inning game over the Chicago White Sox on June 12 of that year.</t>
+        </is>
+      </c>
+      <c r="R1302" t="inlineStr">
+        <is>
+          <t>matig</t>
+        </is>
+      </c>
     </row>
     <row r="1303">
       <c r="A1303" s="4" t="n">
@@ -57663,6 +61054,11 @@
           <t>In 2019 was Brazilië 's werelds grootste producent van: suikerriet, sojabonen, koffie en sinaasappelen, de 2e producent van papaja, de 3e producent van mais, tabak en ananas, de 4e producent van katoen en cassave, de 5e producent van kokos en citroen, de zesde producent van cacao en avocado, 9e prod</t>
         </is>
       </c>
+      <c r="R1306" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="1307">
       <c r="A1307" s="4" t="n">
@@ -57712,6 +61108,11 @@
           <t>The viewership of the 2018 World Cup was estimated to be 3.57 billion, close to half of the global population, while the engagement with the 2022 World Cup was estimated to be 5 billion, with about 1.5 billion people watching the final match.</t>
         </is>
       </c>
+      <c r="R1307" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="1308">
       <c r="A1308" s="4" t="n">
@@ -57762,6 +61163,11 @@
 The Men's Rugby World Cup is a rugby union tournament contested every four years between the top international teams, the winners of which are recognized as the world champions of the </t>
         </is>
       </c>
+      <c r="R1308" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="1309">
       <c r="A1309" s="4" t="n">
@@ -57801,6 +61207,21 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="O1309" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/2026_FIFA_World_Cup_Group_J</t>
+        </is>
+      </c>
+      <c r="P1309" t="inlineStr">
+        <is>
+          <t>On June 22, Lionel Messi scored his 17th World Cup goal in Argentina's win against Austria, surpassing Miroslav Klose (16) as the FIFA World Cup's all-time top goalscorer.</t>
+        </is>
+      </c>
+      <c r="R1309" t="inlineStr">
+        <is>
+          <t>matig</t>
+        </is>
+      </c>
     </row>
     <row r="1310">
       <c r="A1310" s="4" t="n">
@@ -57850,6 +61271,11 @@
           <t>The viewership of the 2018 World Cup was estimated to be 3.57 billion, close to half of the global population, while the engagement with the 2022 World Cup was estimated to be 5 billion, with about 1.5 billion people watching the final match.</t>
         </is>
       </c>
+      <c r="R1310" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="1311">
       <c r="A1311" s="4" t="n">
@@ -57899,6 +61325,11 @@
           <t>During the 2014 end-of-year rugby union internationals, Japan lost their series with the Māori All Blacks 2–0, but went on to secure an 18–13 win over Romania.</t>
         </is>
       </c>
+      <c r="R1311" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="1312">
       <c r="A1312" s="4" t="n">
@@ -57948,6 +61379,11 @@
           <t>The Copa América trophy is a 9 kg (20 lb) weight and 77 cm (30 in) tall silver ornament, with a 3-level wooden base which contains several plaques.</t>
         </is>
       </c>
+      <c r="R1312" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="1313">
       <c r="A1313" s="4" t="n">
@@ -57997,6 +61433,11 @@
           <t>The viewership of the 2018 World Cup was estimated to be 3.57 billion, close to half of the global population, while the engagement with the 2022 World Cup was estimated to be 5 billion, with about 1.5 billion people watching the final match.</t>
         </is>
       </c>
+      <c r="R1313" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="1314">
       <c r="A1314" s="4" t="n">
@@ -58046,6 +61487,11 @@
           <t>Those were also the first two open world championships, as 1924 was the start of FIFA's professional era, and is the reason why Uruguay is allowed to wear 4 stars.</t>
         </is>
       </c>
+      <c r="R1314" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="1315">
       <c r="A1315" s="4" t="n">
@@ -58095,6 +61541,11 @@
           <t>The viewership of the 2018 World Cup was estimated to be 3.57 billion, close to half of the global population, while the engagement with the 2022 World Cup was estimated to be 5 billion, with about 1.5 billion people watching the final match.</t>
         </is>
       </c>
+      <c r="R1315" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="1316">
       <c r="A1316" s="4" t="n">
@@ -58144,6 +61595,11 @@
           <t>The sportswriters were correctly beginning to fear that Hinault was going to run away with his 4th Tour victory as 2nd place Knetemann was not considered an overall threat to the yellow jersey and aside from Anderson in 3rd the only other rider remotely close to Hinault was the now 7th placed Zoetem</t>
         </is>
       </c>
+      <c r="R1316" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="1317">
       <c r="A1317" s="4" t="n">
@@ -58193,6 +61649,11 @@
           <t>Those were also the first two open world championships, as 1924 was the start of FIFA's professional era, and is the reason why Uruguay is allowed to wear 4 stars.</t>
         </is>
       </c>
+      <c r="R1317" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="1318" ht="25" customHeight="1">
       <c r="A1318" s="4" t="n">
@@ -58243,6 +61704,11 @@
 The Men's Rugby World Cup is a rugby union tournament contested every four years between the top international teams, the winners of which are recognized as the world champions of the </t>
         </is>
       </c>
+      <c r="R1318" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="1319">
       <c r="A1319" s="4" t="n">
@@ -58292,6 +61758,11 @@
           <t>The viewership of the 2018 World Cup was estimated to be 3.57 billion, close to half of the global population, while the engagement with the 2022 World Cup was estimated to be 5 billion, with about 1.5 billion people watching the final match.</t>
         </is>
       </c>
+      <c r="R1319" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="1320" ht="25" customHeight="1">
       <c r="A1320" s="4" t="n">
@@ -58342,6 +61813,11 @@
 With 176,214 km2 (68,037 sq mi) of continental land and 125,436 km2 (48,431 sq mi) of territorial waters, Uruguay is the second-smallest sovereign nation in South America (after Suriname) and the third smallest territory (French Guiana is the smallest).</t>
         </is>
       </c>
+      <c r="R1320" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="1321">
       <c r="A1321" s="4" t="n">
@@ -58391,6 +61867,11 @@
           <t>Uruguay then took a 2–1 lead.</t>
         </is>
       </c>
+      <c r="R1321" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="1322">
       <c r="A1322" s="4" t="n">
@@ -58440,6 +61921,11 @@
           <t>Een halve marathon is een atletiekwedstrijd over 21,0975 km (21,1 km), de helft van de gewone marathon.Kenianen zijn op deze afstand dominant: 12 van de 15 snelste lopers ooit zijn afkomstig uit Kenia.</t>
         </is>
       </c>
+      <c r="R1322" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="1323">
       <c r="A1323" s="4" t="n">
@@ -58479,6 +61965,21 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="O1323" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Marathon</t>
+        </is>
+      </c>
+      <c r="P1323" t="inlineStr">
+        <is>
+          <t>The marathon is a long-distance foot race with a distance of 42.195 kilometres (c.</t>
+        </is>
+      </c>
+      <c r="R1323" t="inlineStr">
+        <is>
+          <t>matig</t>
+        </is>
+      </c>
     </row>
     <row r="1324" ht="25" customHeight="1">
       <c r="A1324" s="4" t="n">
@@ -58572,6 +62073,11 @@
           <t>He said: "[The World Cup is] not based on the quality of the teams because you don't have the best 32 at the World Cup ...</t>
         </is>
       </c>
+      <c r="R1325" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="1326">
       <c r="A1326" s="4" t="n">
@@ -58621,6 +62127,11 @@
           <t>In the tournament phase, 48 teams (as of the 2026 World Cup) compete for the title at venues within the host nation(s) over the course of about a month, initially in groups and then in a series of knockout rounds that culminate in the final to determine the overall winner.</t>
         </is>
       </c>
+      <c r="R1326" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="1327">
       <c r="A1327" s="4" t="n">
@@ -58742,6 +62253,11 @@
           <t>De marathon is een hardloopwedstrijd vanaf 1896, die sinds 1908 gelopen wordt over een afstand van 42,195 km.</t>
         </is>
       </c>
+      <c r="R1329" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="1330">
       <c r="A1330" s="4" t="n">
@@ -58791,6 +62307,11 @@
           <t>In Nederland worden dergelijke baden eenvoudigweg 50 meterbaden genoemd, terwijl ze in Frankrijk het voorvoegsel Olympisch krijgen.</t>
         </is>
       </c>
+      <c r="R1330" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="1331">
       <c r="A1331" s="4" t="n">
@@ -59381,6 +62902,11 @@
           <t>Als dit lukt scoort het team 3 punten, en als het niet lukt krijgt de tegenstander de bal op de plaats waar de poging werd ondernomen.</t>
         </is>
       </c>
+      <c r="R1345" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="1346">
       <c r="A1346" s="4" t="n">
@@ -59420,6 +62946,22 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="O1346" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/American_Idol_season_7</t>
+        </is>
+      </c>
+      <c r="P1346">
+        <f>= Releases ==
+=== iTunes ===
+During season 7, American Idol partnered with iTunes to make available for sale exclusive performance videos, live performance singles of the semifinalists, and full-length studio recordings of the songs that contestants performed on the show.</f>
+        <v/>
+      </c>
+      <c r="R1346" t="inlineStr">
+        <is>
+          <t>matig</t>
+        </is>
+      </c>
     </row>
     <row r="1347">
       <c r="A1347" s="4" t="n">
@@ -59469,6 +63011,11 @@
           <t>Een touchdown levert 6 punten op.</t>
         </is>
       </c>
+      <c r="R1347" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="1348">
       <c r="A1348" s="4" t="n">
@@ -59518,6 +63065,11 @@
           <t>Artikel 8: Het symbool van de Olympische Spelen bestaat uit 5 met elkaar verbonden ringen in de kleuren (van links naar rechts) blauw, geel, zwart, groen en rood.</t>
         </is>
       </c>
+      <c r="R1348" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="1349">
       <c r="A1349" s="4" t="n">
@@ -59562,6 +63114,21 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="O1349" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/The_Lord_of_the_Rings</t>
+        </is>
+      </c>
+      <c r="P1349" t="inlineStr">
+        <is>
+          <t>1 "The Lord of the Rings".</t>
+        </is>
+      </c>
+      <c r="R1349" t="inlineStr">
+        <is>
+          <t>matig</t>
+        </is>
+      </c>
     </row>
     <row r="1350">
       <c r="A1350" s="4" t="n">
@@ -59679,6 +63246,26 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="O1352" t="inlineStr">
+        <is>
+          <t>https://nl.wikipedia.org/wiki/Nederlands_handbalteam_%28vrouwen%29</t>
+        </is>
+      </c>
+      <c r="P1352" t="inlineStr">
+        <is>
+          <t>​ Kampioenen  ​ Runners-up  ​ Derde plaats  ​ Vierde plaats
+=== Overige toernooien ===
+Zeslandentoernooi Spanje 2010: 4e plaats (tegenstanders: Spanje, Montenegro, Rusland, Brazilië)
+Holland Handbal Toernooi 2006: 5e plaats
+Carpathian Trophy 2004: 3e plaats
+E-Boks Challenge toernooi Denemarken 2001: 4e plaats (tegens</t>
+        </is>
+      </c>
+      <c r="R1352" t="inlineStr">
+        <is>
+          <t>matig</t>
+        </is>
+      </c>
     </row>
     <row r="1353">
       <c r="A1353" s="4" t="n">
@@ -59884,6 +63471,11 @@
           <t>On 11 October 1900, Beerschot AC honorary president Jorge Díaz announced that Antwerp would host a series of challenge matches between Europe's best football teams.</t>
         </is>
       </c>
+      <c r="R1357" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="1358">
       <c r="A1358" s="4" t="n">
@@ -60239,6 +63831,11 @@
           <t>Na de verbouwing kwam de capaciteit van Camp Nou naar 99.354 plaatsen.</t>
         </is>
       </c>
+      <c r="R1366" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="1367">
       <c r="A1367" s="4" t="n">
@@ -60327,6 +63924,11 @@
           <t>Three contractors will develop individual designs over 12 months for later evaluation by NASA and the US Department of Energy.</t>
         </is>
       </c>
+      <c r="R1368" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="1369" ht="25" customHeight="1">
       <c r="A1369" s="4" t="n">
@@ -60381,6 +63983,11 @@
           <t>Chios: An Ionic temple of Apollo Phanaios was built at the end of the 6th century BC.</t>
         </is>
       </c>
+      <c r="R1369" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="1370">
       <c r="A1370" s="4" t="n">
@@ -60430,6 +64037,11 @@
           <t>Mariner 5 was the first NASA spacecraft to fly by Mars, followed by Mariner 6 and Mariner 7.</t>
         </is>
       </c>
+      <c r="R1370" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="1371" ht="25" customHeight="1">
       <c r="A1371" s="4" t="n">
@@ -60557,6 +64169,11 @@
           <t>Daarbij viel op dat, zoals bij de eerdere maanmissies van Apollo 8 en Apollo 10, na het openen van het luik er een behoorlijk onfrisse lucht uit de capsule ontsnapte.</t>
         </is>
       </c>
+      <c r="R1373" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="1374">
       <c r="A1374" s="4" t="n">
@@ -60693,6 +64310,11 @@
           <t>Wikidata: geen waarde</t>
         </is>
       </c>
+      <c r="R1376" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="1377" ht="37.5" customHeight="1">
       <c r="A1377" s="4" t="n">
@@ -60818,6 +64440,11 @@
           <t>De foto’s werden geanalyseerd, waarna op 6 november 1960 de eerste atlas van de achterkant van de maan werd uitgebracht door de Russische Academie van Wetenschappen.</t>
         </is>
       </c>
+      <c r="R1379" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="1380">
       <c r="A1380" s="4" t="n">
@@ -60866,6 +64493,11 @@
           <t>Sinds september 2012 is de astronomische eenheid gedefinieerd als exact 149 597 870 700 meter.</t>
         </is>
       </c>
+      <c r="R1380" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="1381">
       <c r="A1381" s="4" t="n">
@@ -60954,6 +64586,11 @@
           <t>Alle objecten in een LEO bewegen zich voort met een snelheid van ongeveer 8 km/s, waardoor een volledige omgang rond de Aarde circa 90 minuten duurt.</t>
         </is>
       </c>
+      <c r="R1382" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="1383">
       <c r="A1383" s="4" t="n">
@@ -61002,6 +64639,11 @@
         <is>
           <t>Samenstelling
 De massa van de Aarde bedraagt 5,97×1024 kg.</t>
+        </is>
+      </c>
+      <c r="R1383" t="inlineStr">
+        <is>
+          <t>hoog</t>
         </is>
       </c>
     </row>
@@ -61097,6 +64739,11 @@
 Mars (astrologie), een planeet in de astrologi</t>
         </is>
       </c>
+      <c r="R1385" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="1386">
       <c r="A1386" s="4" t="n">
@@ -61305,6 +64952,11 @@
           <t>Wikidata: klopt</t>
         </is>
       </c>
+      <c r="R1390" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="1391">
       <c r="A1391" s="4" t="n">
@@ -61396,6 +65048,11 @@
           <t>De gemiddelde diameter van een referentie-ellipsoïde is 12 742 km.</t>
         </is>
       </c>
+      <c r="R1392" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="1393">
       <c r="A1393" s="4" t="n">
@@ -61445,6 +65102,11 @@
           <t>De afstand tot de zon bedraagt gemiddeld bijna 150 miljoen km en de snelheid waarmee de Aarde om de zon beweegt is 29,783 km/s.</t>
         </is>
       </c>
+      <c r="R1393" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="1394">
       <c r="A1394" s="4" t="n">
@@ -61572,6 +65234,11 @@
           <t>Dit alfabet is in de oudheid (rond de 9e eeuw v.Chr.) ontwikkeld uit het Fenicische alfabet en bestaat uit 24 letters.</t>
         </is>
       </c>
+      <c r="R1396" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="1397">
       <c r="A1397" s="4" t="n">
@@ -61611,6 +65278,31 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="O1397" t="inlineStr">
+        <is>
+          <t>https://nl.wikipedia.org/wiki/Algemene_Latijnse_vervoegingen_en_verbuigingen</t>
+        </is>
+      </c>
+      <c r="P1397" t="inlineStr">
+        <is>
+          <t>Daarnaast kent het Latijnse werkwoord:
+Drie genera:
+Activum (bedrijvende vorm)
+Passivum (lijdende vorm)
+Deponens (passieve actieve vorm)
+Zes tempora:
+Praesens (onvoltooid tegenwoordige tijd)
+Imperfectum (onvoltooid verleden tijd)
+Futurum (simplex) (onvoltooid toekomende tijd)
+Perfectum (voltooid tegenwoordige tijd)
+P</t>
+        </is>
+      </c>
+      <c r="R1397" t="inlineStr">
+        <is>
+          <t>matig</t>
+        </is>
+      </c>
     </row>
     <row r="1398" ht="25" customHeight="1">
       <c r="A1398" s="4" t="n">
@@ -61738,6 +65430,11 @@
           <t>Beide schriftsoorten hebben daarom tegenwoordig nog maar 46 basiskarakters, hoewel de benaming van deze tekensets nog steeds gojūon (50 klanken) luidt [hiragana no gojūon en katakana no gojūon].</t>
         </is>
       </c>
+      <c r="R1400" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="1401">
       <c r="A1401" s="4" t="n">
@@ -61826,6 +65523,11 @@
           <t>De de facto standaard is dat een byte uit 8 bits bestaat.</t>
         </is>
       </c>
+      <c r="R1402" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="1403">
       <c r="A1403" s="4" t="n">
@@ -61909,6 +65611,11 @@
           <t>The top operational commercial speed of the Shanghai maglev was 431 km/h (268 mph), making it the world's fastest train in regular commercial service from its opening in April 2004 until its speed reduction in May 2021.</t>
         </is>
       </c>
+      <c r="R1404" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="1405">
       <c r="A1405" s="4" t="n">
@@ -62112,6 +65819,11 @@
           <t>In 2007 heeft het bedrijf formeel zijn naam gewijzigd van Apple Computer, Inc.</t>
         </is>
       </c>
+      <c r="R1409" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="1410">
       <c r="A1410" s="4" t="n">
@@ -62151,6 +65863,21 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="O1410" t="inlineStr">
+        <is>
+          <t>https://nl.wikipedia.org/wiki/Shinkansen</t>
+        </is>
+      </c>
+      <c r="P1410" t="inlineStr">
+        <is>
+          <t>De eerste lijn, tussen Tokio, Nagoya en Osaka, die de Tōkaidō-express gedoopt werd, werd in gebruik genomen in hetzelfde jaar waarin de Olympische Zomerspelen in Tokio (1964) werden gehouden.</t>
+        </is>
+      </c>
+      <c r="R1410" t="inlineStr">
+        <is>
+          <t>matig</t>
+        </is>
+      </c>
     </row>
     <row r="1411">
       <c r="A1411" s="4" t="n">
@@ -62200,6 +65927,11 @@
           <t>Het werd in 1994 opgericht door Jeff Bezos en was een van de eerste grote bedrijven die goederen over het internet verkochten.</t>
         </is>
       </c>
+      <c r="R1411" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="1412">
       <c r="A1412" s="4" t="n">
@@ -62244,6 +65976,11 @@
           <t>is een Amerikaans technologiebedrijf dat op 1 april 1976 is opgericht (toen met de naam Apple Computer, Inc.) door Steve Jobs, Steve Wozniak en Ronald Wayne.</t>
         </is>
       </c>
+      <c r="R1412" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="1413">
       <c r="A1413" s="4" t="n">
@@ -62288,6 +66025,11 @@
           <t>Facebook ontstond daadwerkelijk op 4 februari 2004 als "The facebook".</t>
         </is>
       </c>
+      <c r="R1413" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="1414">
       <c r="A1414" s="4" t="n">
@@ -62337,6 +66079,11 @@
           <t>Op 4 september 1998 werd de naam Google Inc.</t>
         </is>
       </c>
+      <c r="R1414" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="1415">
       <c r="A1415" s="4" t="n">
@@ -62386,6 +66133,11 @@
           <t>It was first released on October 25, 1983, under the original name Multi-Tool Word for Xenix systems.</t>
         </is>
       </c>
+      <c r="R1415" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="1416" ht="25" customHeight="1">
       <c r="A1416" s="4" t="n">
@@ -62435,6 +66187,11 @@
           <t>Het bedrijf werd opgericht door Bill Gates en Paul Allen op 4 april 1975.</t>
         </is>
       </c>
+      <c r="R1416" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="1417">
       <c r="A1417" s="4" t="n">
@@ -62485,6 +66242,11 @@
 Het bedrijf is opgericht in 1993 door Jen-Hsun Huang, Chris Malachowsky en Curtis Priem, en is gevestigd in Santa Clara, Californië, in de Verenigde Staten.</t>
         </is>
       </c>
+      <c r="R1417" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="1418">
       <c r="A1418" s="4" t="n">
@@ -62534,6 +66296,11 @@
           <t>Founded in 1938 by Lee Byung-chul as a trading company, Samsung diversified into various sectors, including food processing, textiles, insurance, securities, and retail, over the next three decades.</t>
         </is>
       </c>
+      <c r="R1418" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="1419">
       <c r="A1419" s="4" t="n">
@@ -62568,6 +66335,21 @@
           <t>geen bron · geen EN-vertaling</t>
         </is>
       </c>
+      <c r="O1419" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Sony</t>
+        </is>
+      </c>
+      <c r="P1419" t="inlineStr">
+        <is>
+          <t>| founded = Start date and age|df=yes|1946|5|7 Nihonbashi , Chūō, Tokyo, Japan Cite web |title=Sony Corporate History |url=https://www.sony.com/en/SonyInfo/CorporateInfo/History/company/ |access-date=3 April 2021 |website=sony.com |language=en |archive-date=2021-04-13 |archive-url=https://web.archive.org/web/2021041319</t>
+        </is>
+      </c>
+      <c r="R1419" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="1420">
       <c r="A1420" s="4" t="n">
@@ -62612,6 +66394,11 @@
           <t>The newly formed word was trademarked and the company began trading on August 28, 1937, as the Toyota Motor Company Ltd.</t>
         </is>
       </c>
+      <c r="R1420" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="1421">
       <c r="A1421" s="4" t="n">
@@ -62739,6 +66526,11 @@
           <t>De Intel chip was de 4 bit Intel 4004, uitgebracht op 15 november 1971, ontwikkeld door Federico Faggin en Marcian Hoff.</t>
         </is>
       </c>
+      <c r="R1423" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="1424">
       <c r="A1424" s="4" t="n">
@@ -62827,6 +66619,11 @@
           <t>De eerste e-mail over een computernetwerk werd in 1971 door Ray Tomlinson verzonden.</t>
         </is>
       </c>
+      <c r="R1425" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="1426">
       <c r="A1426" s="4" t="n">
@@ -62993,6 +66790,11 @@
           <t>Gopher expansion stagnated, to the advantage of the World Wide Web, which released the WWW into the public domain in April 1993, which CERN maintained.</t>
         </is>
       </c>
+      <c r="R1429" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="1430">
       <c r="A1430" s="4" t="n">
@@ -63120,6 +66922,11 @@
           <t>Canada is een federale staat met 10 provincies en 3 territoria en een parlementaire constitutionele monarchie (een Commonwealth realm).</t>
         </is>
       </c>
+      <c r="R1432" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="1433">
       <c r="A1433" s="4" t="n">
@@ -63169,6 +66976,11 @@
           <t>In 2025, China recorded 5.6 births per 1000 people, the lowest recorded birthrate since at least 1949.</t>
         </is>
       </c>
+      <c r="R1433" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="1434">
       <c r="A1434" s="4" t="n">
@@ -63218,6 +67030,11 @@
           <t>De Verenigde Staten (VS), officieel de Verenigde Staten van Amerika (Engels: United States of America, USA of US, vaak totum pro parte Amerika, America genoemd), is een federatie van 50 staten, verschillende overzeese territoria en het District of Columbia, grotendeels in Noord-Amerika gelegen.</t>
         </is>
       </c>
+      <c r="R1434" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="1435">
       <c r="A1435" s="4" t="n">
@@ -63310,6 +67127,11 @@
           <t>Wikidata: klopt</t>
         </is>
       </c>
+      <c r="R1436" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="1437">
       <c r="A1437" s="4" t="n">
@@ -63398,6 +67220,11 @@
           <t>Het biedt plaats aan 853 passagiers, bij een gemiddelde configuratie passen er 555 personen in.</t>
         </is>
       </c>
+      <c r="R1438" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="1439">
       <c r="A1439" s="4" t="n">
@@ -63447,6 +67274,11 @@
           <t>Het vliegtuigmodel, dat tussen de 305 en 550 passagiers kan vervoeren, werd in 1995 in dienst genomen.</t>
         </is>
       </c>
+      <c r="R1439" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="1440">
       <c r="A1440" s="4" t="n">
@@ -63496,6 +67328,11 @@
           <t>Notably, on June 6, 2020, protestors occupied the bridge as part of a nationwide denunciation to police brutality in the wake of the George Floyd's murder, and in November 2021 two California Highway Patrol officers and three bridge employees were injured in a vehicular chain-reaction crash during a</t>
         </is>
       </c>
+      <c r="R1440" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="1441">
       <c r="A1441" s="4" t="n">
@@ -63584,6 +67421,11 @@
           <t>The system's 272 stations collectively accommodate up to 5 million passenger journeys a day.</t>
         </is>
       </c>
+      <c r="R1442" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="1443">
       <c r="A1443" s="4" t="n">
@@ -63908,6 +67750,11 @@
 De eerste voorlopers van elektrische auto's waren als schaalmodel gemaakt, onder andere door de Hongaar Ányos Jedlik (1828), de Amerikaan Thomas Davenport (1834), de Groninger Sibrandus Stratingh (1835).</t>
         </is>
       </c>
+      <c r="R1450" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="1451" ht="25" customHeight="1">
       <c r="A1451" s="4" t="n">
@@ -63995,6 +67842,11 @@
           <t>Deze transcontinentale spoorlijn is 9289 kilometer lang en strekt zich uit van Moskou dwars door Siberië naar Vladivostok.</t>
         </is>
       </c>
+      <c r="R1452" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="1453" ht="25" customHeight="1">
       <c r="A1453" s="4" t="n">
@@ -64037,6 +67889,11 @@
       <c r="P1453" t="inlineStr">
         <is>
           <t>On October 12, 2024, a user named Luke Durant from San Jose, California, found the current largest known Mersenne prime, 2136279841 − 1, having 41024320 digits.</t>
+        </is>
+      </c>
+      <c r="R1453" t="inlineStr">
+        <is>
+          <t>hoog</t>
         </is>
       </c>
     </row>
@@ -64098,6 +67955,11 @@
           </t>
         </is>
       </c>
+      <c r="R1454" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
     </row>
     <row r="1455">
       <c r="A1455" s="4" t="n">
@@ -64184,6 +68046,11 @@
       <c r="P1456" t="inlineStr">
         <is>
           <t>Een centimeter (cm) is een lengte van 0,01 meter = 10 mm.</t>
+        </is>
+      </c>
+      <c r="R1456" t="inlineStr">
+        <is>
+          <t>hoog</t>
         </is>
       </c>
     </row>

--- a/vragen/vragen_review_compleet.xlsx
+++ b/vragen/vragen_review_compleet.xlsx
@@ -3557,6 +3557,21 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>https://nl.wikipedia.org/wiki/Piano</t>
+        </is>
+      </c>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Een piano heeft 88 toetsen: 52 witte en 36 zwarte.</t>
+        </is>
+      </c>
+      <c r="R59" t="inlineStr">
+        <is>
+          <t>handmatig</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="4" t="n">
@@ -3596,6 +3611,21 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>https://nl.wikipedia.org/wiki/Geluidssnelheid</t>
+        </is>
+      </c>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Bij 15 °C op zeeniveau is de geluidssnelheid 340,3 m/s, oftewel 1225 km/u. Het opgegeven 1234 hoort bij 20 °C; verschil van minder dan één procent.</t>
+        </is>
+      </c>
+      <c r="R60" t="inlineStr">
+        <is>
+          <t>handmatig</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="4" t="n">
@@ -3968,6 +3998,21 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Stockport_County_F.C.</t>
+        </is>
+      </c>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Stockport County tegen Doncaster Rovers, 30 maart 1946: 203 minuten, afgebroken wegens duisternis.</t>
+        </is>
+      </c>
+      <c r="R68" t="inlineStr">
+        <is>
+          <t>handmatig</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="4" t="n">
@@ -4085,6 +4130,21 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t>https://www.guinnessworldrecords.com/world-records/largest-hamburger</t>
+        </is>
+      </c>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>De zwaarste hamburger woog 1164,2 kg (Pilsting, Duitsland, 9 juli 2017).</t>
+        </is>
+      </c>
+      <c r="R71" t="inlineStr">
+        <is>
+          <t>handmatig</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="4" t="n">
@@ -4124,6 +4184,21 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t>https://www.guinnessworldrecords.com/world-records/heaviest-pumpkin</t>
+        </is>
+      </c>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Sinds 6 oktober 2025 staat het record op 1278,8 kg. Het opgegeven 1247 was het record van 2023.</t>
+        </is>
+      </c>
+      <c r="R72" t="inlineStr">
+        <is>
+          <t>handmatig</t>
+        </is>
+      </c>
     </row>
     <row r="73" ht="25" customHeight="1">
       <c r="A73" s="4" t="n">
@@ -4278,6 +4353,21 @@
       <c r="N76" s="4" t="inlineStr">
         <is>
           <t>geen bron</t>
+        </is>
+      </c>
+      <c r="O76" t="inlineStr">
+        <is>
+          <t>https://nl.wikipedia.org/wiki/Dammen</t>
+        </is>
+      </c>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>Bij internationaal dammen op een bord van 10 bij 10 krijgt elke speler 20 stenen.</t>
+        </is>
+      </c>
+      <c r="R76" t="inlineStr">
+        <is>
+          <t>handmatig</t>
         </is>
       </c>
     </row>
@@ -7932,6 +8022,21 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="O158" t="inlineStr">
+        <is>
+          <t>https://nl.wikipedia.org/wiki/Noordse_stern</t>
+        </is>
+      </c>
+      <c r="P158" t="inlineStr">
+        <is>
+          <t>De noordse stern legt jaarlijks ongeveer 70.000 km af tussen de poolgebieden.</t>
+        </is>
+      </c>
+      <c r="R158" t="inlineStr">
+        <is>
+          <t>handmatig</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" s="4" t="n">
@@ -8679,6 +8784,21 @@
       <c r="N176" s="4" t="inlineStr">
         <is>
           <t>geen bron</t>
+        </is>
+      </c>
+      <c r="O176" t="inlineStr">
+        <is>
+          <t>https://www.g20.org/</t>
+        </is>
+      </c>
+      <c r="P176" t="inlineStr">
+        <is>
+          <t>De G20 telt 19 landen plus de Europese Unie en sinds 2023 de Afrikaanse Unie. Negentien klopt voor landen, maar de vraag moet dat expliciet zeggen.</t>
+        </is>
+      </c>
+      <c r="R176" t="inlineStr">
+        <is>
+          <t>handmatig</t>
         </is>
       </c>
     </row>
@@ -9246,6 +9366,21 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="O188" t="inlineStr">
+        <is>
+          <t>https://www.voedingscentrum.nl/encyclopedie/ei.aspx</t>
+        </is>
+      </c>
+      <c r="P188" t="inlineStr">
+        <is>
+          <t>Een middelgroot ei van ongeveer 58 gram levert circa 70 kcal.</t>
+        </is>
+      </c>
+      <c r="R188" t="inlineStr">
+        <is>
+          <t>handmatig</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" s="4" t="n">
@@ -9603,9 +9738,24 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="O196" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/The_Office_(American_TV_series)</t>
+        </is>
+      </c>
+      <c r="P196" t="inlineStr">
+        <is>
+          <t>De Amerikaanse versie telt 201 afleveringen over negen seizoenen.</t>
+        </is>
+      </c>
       <c r="Q196" t="inlineStr">
         <is>
           <t>Wikidata: geen waarde</t>
+        </is>
+      </c>
+      <c r="R196" t="inlineStr">
+        <is>
+          <t>handmatig</t>
         </is>
       </c>
     </row>
@@ -9883,6 +10033,21 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="O201" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/The_Hunger_Games</t>
+        </is>
+      </c>
+      <c r="P201" t="inlineStr">
+        <is>
+          <t>De oorspronkelijke trilogie bestaat uit drie boeken.</t>
+        </is>
+      </c>
+      <c r="R201" t="inlineStr">
+        <is>
+          <t>handmatig</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" s="4" t="n">
@@ -9922,6 +10087,21 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="O202" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/The_Godfather_(film_series)</t>
+        </is>
+      </c>
+      <c r="P202" t="inlineStr">
+        <is>
+          <t>De oorspronkelijke reeks telt drie films.</t>
+        </is>
+      </c>
+      <c r="R202" t="inlineStr">
+        <is>
+          <t>handmatig</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" s="4" t="n">
@@ -9961,6 +10141,21 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="O203" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Christopher_Nolan_filmography</t>
+        </is>
+      </c>
+      <c r="P203" t="inlineStr">
+        <is>
+          <t>Voor Oppenheimer (2023) regisseerde Nolan elf speelfilms.</t>
+        </is>
+      </c>
+      <c r="R203" t="inlineStr">
+        <is>
+          <t>handmatig</t>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204" s="4" t="n">
@@ -10052,6 +10247,21 @@
       <c r="N205" s="4" t="inlineStr">
         <is>
           <t>geen bron</t>
+        </is>
+      </c>
+      <c r="O205" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/The_Matrix_(franchise)</t>
+        </is>
+      </c>
+      <c r="P205" t="inlineStr">
+        <is>
+          <t>De oorspronkelijke trilogie telt drie films.</t>
+        </is>
+      </c>
+      <c r="R205" t="inlineStr">
+        <is>
+          <t>handmatig</t>
         </is>
       </c>
     </row>
@@ -12970,9 +13180,24 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="O265" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Monaco</t>
+        </is>
+      </c>
+      <c r="P265" t="inlineStr">
+        <is>
+          <t>Monaco heeft ongeveer 39.000 inwoners.</t>
+        </is>
+      </c>
       <c r="Q265" t="inlineStr">
         <is>
           <t>Wikidata: klopt</t>
+        </is>
+      </c>
+      <c r="R265" t="inlineStr">
+        <is>
+          <t>handmatig</t>
         </is>
       </c>
     </row>
@@ -14183,6 +14408,21 @@
       <c r="N292" s="4" t="inlineStr">
         <is>
           <t>geen bron</t>
+        </is>
+      </c>
+      <c r="O292" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Vatican_City</t>
+        </is>
+      </c>
+      <c r="P292" t="inlineStr">
+        <is>
+          <t>Vaticaanstad telt ongeveer 800 inwoners.</t>
+        </is>
+      </c>
+      <c r="R292" t="inlineStr">
+        <is>
+          <t>handmatig</t>
         </is>
       </c>
     </row>
@@ -15187,6 +15427,21 @@
       <c r="N312" s="4" t="inlineStr">
         <is>
           <t>geen bron</t>
+        </is>
+      </c>
+      <c r="O312" t="inlineStr">
+        <is>
+          <t>https://www.genome.gov/genetics-glossary/Chromosome</t>
+        </is>
+      </c>
+      <c r="P312" t="inlineStr">
+        <is>
+          <t>Een gezonde menselijke lichaamscel bevat 46 chromosomen, 23 paren.</t>
+        </is>
+      </c>
+      <c r="R312" t="inlineStr">
+        <is>
+          <t>handmatig</t>
         </is>
       </c>
     </row>
@@ -17131,6 +17386,21 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="O354" t="inlineStr">
+        <is>
+          <t>https://www.gov.za/documents/constitution-republic-south-africa-1996</t>
+        </is>
+      </c>
+      <c r="P354" t="inlineStr">
+        <is>
+          <t>Sinds de grondwetswijziging van 2023 erkent Zuid-Afrika twaalf talen; de Zuid-Afrikaanse gebarentaal is toegevoegd aan de oorspronkelijke elf.</t>
+        </is>
+      </c>
+      <c r="R354" t="inlineStr">
+        <is>
+          <t>handmatig</t>
+        </is>
+      </c>
     </row>
     <row r="355">
       <c r="A355" s="4" t="n">
@@ -18423,9 +18693,24 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="O384" t="inlineStr">
+        <is>
+          <t>https://www.guinnessworldrecords.com/world-records/longest-wedding-dress-train</t>
+        </is>
+      </c>
+      <c r="P384" t="inlineStr">
+        <is>
+          <t>De langste trouwjurksleep mat 8095 meter (Caroline Arts, Cyprus, 2021).</t>
+        </is>
+      </c>
       <c r="Q384" t="inlineStr">
         <is>
           <t>Wikidata: geen waarde</t>
+        </is>
+      </c>
+      <c r="R384" t="inlineStr">
+        <is>
+          <t>handmatig</t>
         </is>
       </c>
     </row>
@@ -18560,6 +18845,21 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="O387" t="inlineStr">
+        <is>
+          <t>https://www.grammy.com/artists/beyonce/13778</t>
+        </is>
+      </c>
+      <c r="P387" t="inlineStr">
+        <is>
+          <t>Het nominatietotaal groeit elk jaar. Zonder peildatum in de vraag verloopt het.</t>
+        </is>
+      </c>
+      <c r="R387" t="inlineStr">
+        <is>
+          <t>handmatig</t>
+        </is>
+      </c>
     </row>
     <row r="388" ht="25" customHeight="1">
       <c r="A388" s="4" t="n">
@@ -19242,6 +19542,21 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="O401" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Brilliant_(diamond_cut)</t>
+        </is>
+      </c>
+      <c r="P401" t="inlineStr">
+        <is>
+          <t>Een ronde briljant heeft 57 facetten, of 58 als je de culet meetelt. De vraag moet zeggen welke telling.</t>
+        </is>
+      </c>
+      <c r="R401" t="inlineStr">
+        <is>
+          <t>handmatig</t>
+        </is>
+      </c>
     </row>
     <row r="402">
       <c r="A402" s="4" t="n">
@@ -19281,6 +19596,21 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="O402" t="inlineStr">
+        <is>
+          <t>https://www.iso.org/standard/3601.html</t>
+        </is>
+      </c>
+      <c r="P402" t="inlineStr">
+        <is>
+          <t>De kamertoon a is genormeerd op 440 Hz in ISO 16.</t>
+        </is>
+      </c>
+      <c r="R402" t="inlineStr">
+        <is>
+          <t>handmatig</t>
+        </is>
+      </c>
     </row>
     <row r="403">
       <c r="A403" s="4" t="n">
@@ -20108,6 +20438,21 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="O420" t="inlineStr">
+        <is>
+          <t>https://nl.wikipedia.org/wiki/Netspanning</t>
+        </is>
+      </c>
+      <c r="P420" t="inlineStr">
+        <is>
+          <t>De Nederlandse netspanning is 230 volt.</t>
+        </is>
+      </c>
+      <c r="R420" t="inlineStr">
+        <is>
+          <t>handmatig</t>
+        </is>
+      </c>
     </row>
     <row r="421">
       <c r="A421" s="4" t="n">
@@ -20145,6 +20490,21 @@
       <c r="N421" s="4" t="inlineStr">
         <is>
           <t>geen bron</t>
+        </is>
+      </c>
+      <c r="O421" t="inlineStr">
+        <is>
+          <t>https://nl.wikipedia.org/wiki/Grondzeiler</t>
+        </is>
+      </c>
+      <c r="P421" t="inlineStr">
+        <is>
+          <t>Een grondzeiler heeft vier wieken.</t>
+        </is>
+      </c>
+      <c r="R421" t="inlineStr">
+        <is>
+          <t>handmatig</t>
         </is>
       </c>
     </row>
@@ -20824,6 +21184,21 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="O435" t="inlineStr">
+        <is>
+          <t>https://www.guinnessworldrecords.com/world-records/largest-pizza</t>
+        </is>
+      </c>
+      <c r="P435" t="inlineStr">
+        <is>
+          <t>De grootste pizza besloeg 1296,72 vierkante meter (Rome, 2012).</t>
+        </is>
+      </c>
+      <c r="R435" t="inlineStr">
+        <is>
+          <t>handmatig</t>
+        </is>
+      </c>
     </row>
     <row r="436">
       <c r="A436" s="4" t="n">
@@ -20863,6 +21238,21 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="O436" t="inlineStr">
+        <is>
+          <t>https://www.guinnessworldrecords.com/world-records/tallest-dog-ever</t>
+        </is>
+      </c>
+      <c r="P436" t="inlineStr">
+        <is>
+          <t>Zeus, een Duitse dog, mat 111,8 cm bij de schoft.</t>
+        </is>
+      </c>
+      <c r="R436" t="inlineStr">
+        <is>
+          <t>handmatig</t>
+        </is>
+      </c>
     </row>
     <row r="437">
       <c r="A437" s="4" t="n">
@@ -20902,6 +21292,21 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="O437" t="inlineStr">
+        <is>
+          <t>https://www.guinnessworldrecords.com/world-records/tallest-sandcastle</t>
+        </is>
+      </c>
+      <c r="P437" t="inlineStr">
+        <is>
+          <t>De hoogste zandsculptuur mat 21,16 meter (Denemarken, 2021).</t>
+        </is>
+      </c>
+      <c r="R437" t="inlineStr">
+        <is>
+          <t>handmatig</t>
+        </is>
+      </c>
     </row>
     <row r="438">
       <c r="A438" s="4" t="n">
@@ -20941,6 +21346,21 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="O438" t="inlineStr">
+        <is>
+          <t>https://www.guinnessworldrecords.com/world-records/tallest-horse-ever</t>
+        </is>
+      </c>
+      <c r="P438" t="inlineStr">
+        <is>
+          <t>Sampson, een shirepaard, mat 219,7 cm.</t>
+        </is>
+      </c>
+      <c r="R438" t="inlineStr">
+        <is>
+          <t>handmatig</t>
+        </is>
+      </c>
     </row>
     <row r="439">
       <c r="A439" s="4" t="n">
@@ -21019,6 +21439,21 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="O440" t="inlineStr">
+        <is>
+          <t>https://www.guinnessworldrecords.com/world-records/longest-time-in-an-abdominal-plank-position-male</t>
+        </is>
+      </c>
+      <c r="P440" t="inlineStr">
+        <is>
+          <t>Plankrecords worden vaak verbroken; 579 minuten is een momentopname.</t>
+        </is>
+      </c>
+      <c r="R440" t="inlineStr">
+        <is>
+          <t>handmatig</t>
+        </is>
+      </c>
     </row>
     <row r="441">
       <c r="A441" s="4" t="n">
@@ -21058,6 +21493,21 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="O441" t="inlineStr">
+        <is>
+          <t>https://www.guinnessworldrecords.com/world-records/tallest-man-living</t>
+        </is>
+      </c>
+      <c r="P441" t="inlineStr">
+        <is>
+          <t>Sultan Kösen meet 251 cm.</t>
+        </is>
+      </c>
+      <c r="R441" t="inlineStr">
+        <is>
+          <t>handmatig</t>
+        </is>
+      </c>
     </row>
     <row r="442">
       <c r="A442" s="4" t="n">
@@ -21097,6 +21547,21 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="O442" t="inlineStr">
+        <is>
+          <t>https://www.guinnessworldrecords.com/world-records/tallest-woman-living</t>
+        </is>
+      </c>
+      <c r="P442" t="inlineStr">
+        <is>
+          <t>Rumeysa Gelgi meet 215,16 cm.</t>
+        </is>
+      </c>
+      <c r="R442" t="inlineStr">
+        <is>
+          <t>handmatig</t>
+        </is>
+      </c>
     </row>
     <row r="443">
       <c r="A443" s="4" t="n">
@@ -21136,6 +21601,21 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="O443" t="inlineStr">
+        <is>
+          <t>https://www.guinnessworldrecords.com/world-records/longest-fingernails-on-a-pair-of-hands-ever-female</t>
+        </is>
+      </c>
+      <c r="P443" t="inlineStr">
+        <is>
+          <t>De langste nagels aan één hand maten samen ruim negen meter.</t>
+        </is>
+      </c>
+      <c r="R443" t="inlineStr">
+        <is>
+          <t>handmatig</t>
+        </is>
+      </c>
     </row>
     <row r="444">
       <c r="A444" s="4" t="n">
@@ -21175,6 +21655,21 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="O444" t="inlineStr">
+        <is>
+          <t>https://www.guinnessworldrecords.com/world-records/longest-dog-ever</t>
+        </is>
+      </c>
+      <c r="P444" t="inlineStr">
+        <is>
+          <t>Aicama Zorba, een Engelse mastiff, mat 250 cm van neus tot staart.</t>
+        </is>
+      </c>
+      <c r="R444" t="inlineStr">
+        <is>
+          <t>handmatig</t>
+        </is>
+      </c>
     </row>
     <row r="445">
       <c r="A445" s="4" t="n">
@@ -21214,6 +21709,21 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="O445" t="inlineStr">
+        <is>
+          <t>https://www.guinnessworldrecords.com/world-records/longest-hot-dog</t>
+        </is>
+      </c>
+      <c r="P445" t="inlineStr">
+        <is>
+          <t>De langste hotdog mat 203,8 meter.</t>
+        </is>
+      </c>
+      <c r="R445" t="inlineStr">
+        <is>
+          <t>handmatig</t>
+        </is>
+      </c>
     </row>
     <row r="446">
       <c r="A446" s="4" t="n">
@@ -21253,6 +21763,21 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="O446" t="inlineStr">
+        <is>
+          <t>https://www.guinnessworldrecords.com/world-records/longest-cat-ever</t>
+        </is>
+      </c>
+      <c r="P446" t="inlineStr">
+        <is>
+          <t>Mymains Stewart Gilligan mat 123 cm.</t>
+        </is>
+      </c>
+      <c r="R446" t="inlineStr">
+        <is>
+          <t>handmatig</t>
+        </is>
+      </c>
     </row>
     <row r="447">
       <c r="A447" s="4" t="n">
@@ -21385,6 +21910,21 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="O449" t="inlineStr">
+        <is>
+          <t>https://www.guinnessworldrecords.com/world-records/largest-cheese</t>
+        </is>
+      </c>
+      <c r="P449" t="inlineStr">
+        <is>
+          <t>De grootste kaas woog 26.090 kg (Wisconsin, 1988).</t>
+        </is>
+      </c>
+      <c r="R449" t="inlineStr">
+        <is>
+          <t>handmatig</t>
+        </is>
+      </c>
     </row>
     <row r="450">
       <c r="A450" s="4" t="n">
@@ -21424,6 +21964,21 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="O450" t="inlineStr">
+        <is>
+          <t>https://www.guinnessworldrecords.com/world-records/heaviest-dog</t>
+        </is>
+      </c>
+      <c r="P450" t="inlineStr">
+        <is>
+          <t>Zorba woog 155,58 kg.</t>
+        </is>
+      </c>
+      <c r="R450" t="inlineStr">
+        <is>
+          <t>handmatig</t>
+        </is>
+      </c>
     </row>
     <row r="451" ht="25" customHeight="1">
       <c r="A451" s="4" t="n">
@@ -21602,6 +22157,21 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="O454" t="inlineStr">
+        <is>
+          <t>https://www.guinnessworldrecords.com/world-records/largest-yoga-lesson</t>
+        </is>
+      </c>
+      <c r="P454" t="inlineStr">
+        <is>
+          <t>De grootste yogales telde 100.984 deelnemers (India, 2018).</t>
+        </is>
+      </c>
+      <c r="R454" t="inlineStr">
+        <is>
+          <t>handmatig</t>
+        </is>
+      </c>
     </row>
     <row r="455">
       <c r="A455" s="4" t="n">
@@ -21641,6 +22211,21 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="O455" t="inlineStr">
+        <is>
+          <t>https://www.guinnessworldrecords.com/world-records/most-body-piercings-in-a-single-count</t>
+        </is>
+      </c>
+      <c r="P455" t="inlineStr">
+        <is>
+          <t>Elaine Davidson had 462 piercings bij de laatste telling; 453 hoort bij een eerdere meting. Nakijken.</t>
+        </is>
+      </c>
+      <c r="R455" t="inlineStr">
+        <is>
+          <t>handmatig</t>
+        </is>
+      </c>
     </row>
     <row r="456">
       <c r="A456" s="4" t="n">
@@ -22775,6 +23360,21 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="O481" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Darts</t>
+        </is>
+      </c>
+      <c r="P481" t="inlineStr">
+        <is>
+          <t>Een dartbord heeft twintig genummerde vakken.</t>
+        </is>
+      </c>
+      <c r="R481" t="inlineStr">
+        <is>
+          <t>handmatig</t>
+        </is>
+      </c>
     </row>
     <row r="482">
       <c r="A482" s="4" t="n">
@@ -22814,6 +23414,21 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="O482" t="inlineStr">
+        <is>
+          <t>https://nl.wikipedia.org/wiki/Roulette</t>
+        </is>
+      </c>
+      <c r="P482" t="inlineStr">
+        <is>
+          <t>Een Europees roulettewiel heeft 37 vakjes, inclusief de nul.</t>
+        </is>
+      </c>
+      <c r="R482" t="inlineStr">
+        <is>
+          <t>handmatig</t>
+        </is>
+      </c>
     </row>
     <row r="483">
       <c r="A483" s="4" t="n">
@@ -22853,6 +23468,21 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="O483" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Uno_(card_game)</t>
+        </is>
+      </c>
+      <c r="P483" t="inlineStr">
+        <is>
+          <t>Een standaard UNO-spel bevat 112 kaarten.</t>
+        </is>
+      </c>
+      <c r="R483" t="inlineStr">
+        <is>
+          <t>handmatig</t>
+        </is>
+      </c>
     </row>
     <row r="484">
       <c r="A484" s="4" t="n">
@@ -22985,6 +23615,21 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="O486" t="inlineStr">
+        <is>
+          <t>https://nl.wikipedia.org/wiki/Mens_erger_je_niet</t>
+        </is>
+      </c>
+      <c r="P486" t="inlineStr">
+        <is>
+          <t>Elke speler heeft vier pionnen.</t>
+        </is>
+      </c>
+      <c r="R486" t="inlineStr">
+        <is>
+          <t>handmatig</t>
+        </is>
+      </c>
     </row>
     <row r="487">
       <c r="A487" s="4" t="n">
@@ -23079,6 +23724,21 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="O488" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Pac-Man</t>
+        </is>
+      </c>
+      <c r="P488" t="inlineStr">
+        <is>
+          <t>Een doolhof bevat 240 stippen plus vier power pellets, samen 244.</t>
+        </is>
+      </c>
+      <c r="R488" t="inlineStr">
+        <is>
+          <t>handmatig</t>
+        </is>
+      </c>
     </row>
     <row r="489">
       <c r="A489" s="4" t="n">
@@ -23157,6 +23817,21 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="O490" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Monopoly_(game)</t>
+        </is>
+      </c>
+      <c r="P490" t="inlineStr">
+        <is>
+          <t>Een klassiek bord heeft 22 straten, vier stations en twee nutsbedrijven: 28.</t>
+        </is>
+      </c>
+      <c r="R490" t="inlineStr">
+        <is>
+          <t>handmatig</t>
+        </is>
+      </c>
     </row>
     <row r="491">
       <c r="A491" s="4" t="n">
@@ -23329,6 +24004,21 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="O494" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Monopoly_(game)</t>
+        </is>
+      </c>
+      <c r="P494" t="inlineStr">
+        <is>
+          <t>Een Monopolybord telt veertig vakken.</t>
+        </is>
+      </c>
+      <c r="R494" t="inlineStr">
+        <is>
+          <t>handmatig</t>
+        </is>
+      </c>
     </row>
     <row r="495">
       <c r="A495" s="4" t="n">
@@ -23897,6 +24587,21 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="O507" t="inlineStr">
+        <is>
+          <t>https://www.lords.org/mcc/the-laws-of-cricket</t>
+        </is>
+      </c>
+      <c r="P507" t="inlineStr">
+        <is>
+          <t>Een cricketteam telt elf spelers.</t>
+        </is>
+      </c>
+      <c r="R507" t="inlineStr">
+        <is>
+          <t>handmatig</t>
+        </is>
+      </c>
     </row>
     <row r="508">
       <c r="A508" s="4" t="n">
@@ -23934,6 +24639,21 @@
       <c r="N508" s="4" t="inlineStr">
         <is>
           <t>geen bron</t>
+        </is>
+      </c>
+      <c r="O508" t="inlineStr">
+        <is>
+          <t>https://www.worldaquatics.com/rules</t>
+        </is>
+      </c>
+      <c r="P508" t="inlineStr">
+        <is>
+          <t>Een waterpoloteam heeft zeven spelers in het water, inclusief de keeper.</t>
+        </is>
+      </c>
+      <c r="R508" t="inlineStr">
+        <is>
+          <t>handmatig</t>
         </is>
       </c>
     </row>
@@ -25570,6 +26290,21 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="O545" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Hawaiian_alphabet</t>
+        </is>
+      </c>
+      <c r="P545" t="inlineStr">
+        <is>
+          <t>Het Hawaiiaanse alfabet telt dertien letters, de okina meegerekend.</t>
+        </is>
+      </c>
+      <c r="R545" t="inlineStr">
+        <is>
+          <t>handmatig</t>
+        </is>
+      </c>
     </row>
     <row r="546">
       <c r="A546" s="4" t="n">
@@ -25818,6 +26553,21 @@
       <c r="N551" s="4" t="inlineStr">
         <is>
           <t>geen bron</t>
+        </is>
+      </c>
+      <c r="O551" t="inlineStr">
+        <is>
+          <t>https://support.apple.com/en-us/HT202105</t>
+        </is>
+      </c>
+      <c r="P551" t="inlineStr">
+        <is>
+          <t>Apple levert adapters van 20 W, maar nieuwere modellen laden sneller. "Standaard" moet gedefinieerd worden.</t>
+        </is>
+      </c>
+      <c r="R551" t="inlineStr">
+        <is>
+          <t>handmatig</t>
         </is>
       </c>
     </row>

--- a/vragen/vragen_review_compleet.xlsx
+++ b/vragen/vragen_review_compleet.xlsx
@@ -619,7 +619,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R1459"/>
+  <dimension ref="A1:S1459"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -639,6 +639,7 @@
     <col width="46" customWidth="1" min="16" max="16"/>
     <col width="46" customWidth="1" min="17" max="17"/>
     <col width="16" customWidth="1" min="18" max="18"/>
+    <col width="30" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -732,6 +733,11 @@
           <t>Vertrouwen bron</t>
         </is>
       </c>
+      <c r="S1" s="10" t="inlineStr">
+        <is>
+          <t>Status oude bron</t>
+        </is>
+      </c>
     </row>
     <row r="2" ht="25" customHeight="1">
       <c r="A2" s="4" t="n">
@@ -786,6 +792,11 @@
         </is>
       </c>
       <c r="N2" s="4" t="n"/>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>geblokkeerd — niet te controleren</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="n">
@@ -835,6 +846,11 @@
         </is>
       </c>
       <c r="N3" s="4" t="n"/>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>getal staat niet op de pagina</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="25" customHeight="1">
       <c r="A4" s="4" t="n">
@@ -879,6 +895,11 @@
         </is>
       </c>
       <c r="N4" s="4" t="n"/>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>DODE LINK</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="n">
@@ -923,6 +944,11 @@
         </is>
       </c>
       <c r="N5" s="4" t="n"/>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>getal gezien op de pagina</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
@@ -967,6 +993,11 @@
         </is>
       </c>
       <c r="N6" s="4" t="n"/>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>geblokkeerd — niet te controleren</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="n">
@@ -1079,6 +1110,11 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>getal gezien op de pagina</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="n">
@@ -1123,6 +1159,11 @@
         </is>
       </c>
       <c r="N9" s="4" t="n"/>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>getal staat niet op de pagina</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="n">
@@ -1171,6 +1212,11 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>getal gezien op de pagina</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="n">
@@ -1220,6 +1266,11 @@
         </is>
       </c>
       <c r="N11" s="4" t="n"/>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>bevestigd</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="25" customHeight="1">
       <c r="A12" s="4" t="n">
@@ -1269,6 +1320,11 @@
         </is>
       </c>
       <c r="N12" s="4" t="n"/>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>onbereikbaar</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="n">
@@ -1317,6 +1373,11 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>getal gezien op de pagina</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="n">
@@ -1361,6 +1422,11 @@
         </is>
       </c>
       <c r="N14" s="4" t="n"/>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>onbereikbaar</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="n">
@@ -1419,6 +1485,11 @@
           <t>Wikidata: klopt</t>
         </is>
       </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>geen adres, alleen een omschrijving</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="n">
@@ -1531,6 +1602,11 @@
         </is>
       </c>
       <c r="N17" s="4" t="n"/>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>getal staat niet op de pagina</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="25" customHeight="1">
       <c r="A18" s="4" t="n">
@@ -1815,6 +1891,11 @@
         </is>
       </c>
       <c r="N22" s="4" t="n"/>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>DODE LINK</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="n">
@@ -1854,6 +1935,11 @@
         </is>
       </c>
       <c r="N23" s="4" t="n"/>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>geblokkeerd — niet te controleren</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="n">
@@ -1947,6 +2033,11 @@
         </is>
       </c>
       <c r="N25" s="4" t="n"/>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>getal gezien op de pagina</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="n">
@@ -2211,6 +2302,11 @@
         </is>
       </c>
       <c r="N30" s="4" t="n"/>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>getal staat niet op de pagina</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="n">
@@ -2307,6 +2403,11 @@
       <c r="Q32" t="inlineStr">
         <is>
           <t>Wikidata: klopt</t>
+        </is>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>geblokkeerd — niet te controleren</t>
         </is>
       </c>
     </row>
@@ -2407,6 +2508,11 @@
         </is>
       </c>
       <c r="N34" s="4" t="n"/>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>geblokkeerd — niet te controleren</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="4" t="n">
@@ -2451,6 +2557,11 @@
           <t>Wikidata: ander onderwerp</t>
         </is>
       </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>geblokkeerd — niet te controleren</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="4" t="n">
@@ -2490,6 +2601,11 @@
         </is>
       </c>
       <c r="N36" s="4" t="n"/>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>getal staat niet op de pagina</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="4" t="n">
@@ -2584,6 +2700,11 @@
         </is>
       </c>
       <c r="N38" s="4" t="n"/>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>geblokkeerd — niet te controleren</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="4" t="n">
@@ -2623,6 +2744,11 @@
         </is>
       </c>
       <c r="N39" s="4" t="n"/>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>getal gezien op de pagina</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="4" t="n">
@@ -2827,6 +2953,11 @@
         </is>
       </c>
       <c r="N43" s="4" t="n"/>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>getal staat niet op de pagina</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="4" t="n">
@@ -2974,6 +3105,11 @@
         </is>
       </c>
       <c r="N46" s="4" t="n"/>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>getal staat niet op de pagina</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="4" t="n">
@@ -3013,6 +3149,11 @@
         </is>
       </c>
       <c r="N47" s="4" t="n"/>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>getal staat niet op de pagina</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="4" t="n">
@@ -3052,6 +3193,11 @@
         </is>
       </c>
       <c r="N48" s="4" t="n"/>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>getal staat niet op de pagina</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="4" t="n">
@@ -3145,6 +3291,11 @@
         </is>
       </c>
       <c r="N50" s="4" t="n"/>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>geblokkeerd — niet te controleren</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="4" t="n">
@@ -3184,6 +3335,11 @@
         </is>
       </c>
       <c r="N51" s="4" t="n"/>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>onbereikbaar</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="4" t="n">
@@ -3223,6 +3379,11 @@
         </is>
       </c>
       <c r="N52" s="4" t="n"/>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>getal staat niet op de pagina</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="4" t="n">
@@ -3262,6 +3423,11 @@
         </is>
       </c>
       <c r="N53" s="4" t="n"/>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>getal staat niet op de pagina</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="4" t="n">
@@ -3301,6 +3467,11 @@
         </is>
       </c>
       <c r="N54" s="4" t="n"/>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>getal staat niet op de pagina</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="4" t="n">
@@ -3518,6 +3689,11 @@
         </is>
       </c>
       <c r="N58" s="4" t="n"/>
+      <c r="S58" t="inlineStr">
+        <is>
+          <t>getal staat niet op de pagina</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="4" t="n">
@@ -3665,6 +3841,11 @@
         </is>
       </c>
       <c r="N61" s="4" t="n"/>
+      <c r="S61" t="inlineStr">
+        <is>
+          <t>geblokkeerd — niet te controleren</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="4" t="n">
@@ -4277,6 +4458,11 @@
         </is>
       </c>
       <c r="N74" s="4" t="n"/>
+      <c r="S74" t="inlineStr">
+        <is>
+          <t>bevestigd</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="4" t="n">
@@ -4571,6 +4757,11 @@
         </is>
       </c>
       <c r="N80" s="4" t="n"/>
+      <c r="S80" t="inlineStr">
+        <is>
+          <t>DODE LINK</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="4" t="n">
@@ -4826,6 +5017,11 @@
         </is>
       </c>
       <c r="N85" s="4" t="n"/>
+      <c r="S85" t="inlineStr">
+        <is>
+          <t>getal staat niet op de pagina</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="4" t="n">
@@ -4865,6 +5061,11 @@
         </is>
       </c>
       <c r="N86" s="4" t="n"/>
+      <c r="S86" t="inlineStr">
+        <is>
+          <t>geblokkeerd — niet te controleren</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="4" t="n">
@@ -4959,6 +5160,11 @@
         </is>
       </c>
       <c r="N88" s="4" t="n"/>
+      <c r="S88" t="inlineStr">
+        <is>
+          <t>geblokkeerd — niet te controleren</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="4" t="n">
@@ -5052,6 +5258,11 @@
         </is>
       </c>
       <c r="N90" s="4" t="n"/>
+      <c r="S90" t="inlineStr">
+        <is>
+          <t>geblokkeerd — niet te controleren</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="4" t="n">
@@ -5147,6 +5358,11 @@
         </is>
       </c>
       <c r="N92" s="4" t="n"/>
+      <c r="S92" t="inlineStr">
+        <is>
+          <t>DODE LINK</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="4" t="n">
@@ -5241,6 +5457,11 @@
         </is>
       </c>
       <c r="N94" s="4" t="n"/>
+      <c r="S94" t="inlineStr">
+        <is>
+          <t>geblokkeerd — niet te controleren</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="4" t="n">
@@ -5280,6 +5501,11 @@
         </is>
       </c>
       <c r="N95" s="4" t="n"/>
+      <c r="S95" t="inlineStr">
+        <is>
+          <t>DODE LINK</t>
+        </is>
+      </c>
     </row>
     <row r="96" ht="25" customHeight="1">
       <c r="A96" s="4" t="n">
@@ -5417,6 +5643,11 @@
         </is>
       </c>
       <c r="N98" s="4" t="n"/>
+      <c r="S98" t="inlineStr">
+        <is>
+          <t>geblokkeerd — niet te controleren</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="4" t="n">
@@ -5673,6 +5904,11 @@
         </is>
       </c>
       <c r="N103" s="4" t="n"/>
+      <c r="S103" t="inlineStr">
+        <is>
+          <t>geen adres, alleen een omschrijving</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" s="4" t="n">
@@ -5712,6 +5948,11 @@
         </is>
       </c>
       <c r="N104" s="4" t="n"/>
+      <c r="S104" t="inlineStr">
+        <is>
+          <t>getal staat niet op de pagina</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" s="4" t="n">
@@ -5829,6 +6070,11 @@
         </is>
       </c>
       <c r="N107" s="4" t="n"/>
+      <c r="S107" t="inlineStr">
+        <is>
+          <t>bevestigd</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" s="4" t="n">
@@ -5868,6 +6114,11 @@
         </is>
       </c>
       <c r="N108" s="4" t="n"/>
+      <c r="S108" t="inlineStr">
+        <is>
+          <t>DODE LINK</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" s="4" t="n">
@@ -5907,6 +6158,11 @@
         </is>
       </c>
       <c r="N109" s="4" t="n"/>
+      <c r="S109" t="inlineStr">
+        <is>
+          <t>DODE LINK</t>
+        </is>
+      </c>
     </row>
     <row r="110" ht="25" customHeight="1">
       <c r="A110" s="4" t="n">
@@ -5946,6 +6202,11 @@
         </is>
       </c>
       <c r="N110" s="4" t="n"/>
+      <c r="S110" t="inlineStr">
+        <is>
+          <t>DODE LINK</t>
+        </is>
+      </c>
     </row>
     <row r="111" ht="25" customHeight="1">
       <c r="A111" s="4" t="n">
@@ -5985,6 +6246,11 @@
         </is>
       </c>
       <c r="N111" s="4" t="n"/>
+      <c r="S111" t="inlineStr">
+        <is>
+          <t>geblokkeerd — niet te controleren</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" s="4" t="n">
@@ -6024,6 +6290,11 @@
         </is>
       </c>
       <c r="N112" s="4" t="n"/>
+      <c r="S112" t="inlineStr">
+        <is>
+          <t>getal staat niet op de pagina</t>
+        </is>
+      </c>
     </row>
     <row r="113" ht="25" customHeight="1">
       <c r="A113" s="4" t="n">
@@ -6063,6 +6334,11 @@
         </is>
       </c>
       <c r="N113" s="4" t="n"/>
+      <c r="S113" t="inlineStr">
+        <is>
+          <t>geblokkeerd — niet te controleren</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" s="4" t="n">
@@ -6102,6 +6378,11 @@
         </is>
       </c>
       <c r="N114" s="4" t="n"/>
+      <c r="S114" t="inlineStr">
+        <is>
+          <t>getal staat niet op de pagina</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" s="4" t="n">
@@ -6141,6 +6422,11 @@
         </is>
       </c>
       <c r="N115" s="4" t="n"/>
+      <c r="S115" t="inlineStr">
+        <is>
+          <t>DODE LINK</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" s="4" t="n">
@@ -6180,6 +6466,11 @@
         </is>
       </c>
       <c r="N116" s="4" t="n"/>
+      <c r="S116" t="inlineStr">
+        <is>
+          <t>geblokkeerd — niet te controleren</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" s="4" t="n">
@@ -6219,6 +6510,11 @@
         </is>
       </c>
       <c r="N117" s="4" t="n"/>
+      <c r="S117" t="inlineStr">
+        <is>
+          <t>getal staat niet op de pagina</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" s="4" t="n">
@@ -6258,6 +6554,11 @@
         </is>
       </c>
       <c r="N118" s="4" t="n"/>
+      <c r="S118" t="inlineStr">
+        <is>
+          <t>bevestigd</t>
+        </is>
+      </c>
     </row>
     <row r="119" ht="25" customHeight="1">
       <c r="A119" s="4" t="n">
@@ -6297,6 +6598,11 @@
         </is>
       </c>
       <c r="N119" s="4" t="n"/>
+      <c r="S119" t="inlineStr">
+        <is>
+          <t>geblokkeerd — niet te controleren</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" s="4" t="n">
@@ -6336,6 +6642,11 @@
         </is>
       </c>
       <c r="N120" s="4" t="n"/>
+      <c r="S120" t="inlineStr">
+        <is>
+          <t>geblokkeerd — niet te controleren</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" s="4" t="n">
@@ -6375,6 +6686,11 @@
         </is>
       </c>
       <c r="N121" s="4" t="n"/>
+      <c r="S121" t="inlineStr">
+        <is>
+          <t>DODE LINK</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" s="4" t="n">
@@ -6414,6 +6730,11 @@
         </is>
       </c>
       <c r="N122" s="4" t="n"/>
+      <c r="S122" t="inlineStr">
+        <is>
+          <t>bevestigd</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" s="4" t="n">
@@ -6562,6 +6883,11 @@
         </is>
       </c>
       <c r="N125" s="4" t="n"/>
+      <c r="S125" t="inlineStr">
+        <is>
+          <t>DODE LINK</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" s="4" t="n">
@@ -6655,6 +6981,11 @@
         </is>
       </c>
       <c r="N127" s="4" t="n"/>
+      <c r="S127" t="inlineStr">
+        <is>
+          <t>DODE LINK</t>
+        </is>
+      </c>
     </row>
     <row r="128" ht="25" customHeight="1">
       <c r="A128" s="4" t="n">
@@ -6694,6 +7025,11 @@
         </is>
       </c>
       <c r="N128" s="4" t="n"/>
+      <c r="S128" t="inlineStr">
+        <is>
+          <t>getal gezien op de pagina</t>
+        </is>
+      </c>
     </row>
     <row r="129" ht="25" customHeight="1">
       <c r="A129" s="4" t="n">
@@ -6733,6 +7069,11 @@
         </is>
       </c>
       <c r="N129" s="4" t="n"/>
+      <c r="S129" t="inlineStr">
+        <is>
+          <t>geen adres, alleen een omschrijving</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" s="4" t="n">
@@ -6881,6 +7222,11 @@
         </is>
       </c>
       <c r="N132" s="4" t="n"/>
+      <c r="S132" t="inlineStr">
+        <is>
+          <t>geblokkeerd — niet te controleren</t>
+        </is>
+      </c>
     </row>
     <row r="133" ht="25" customHeight="1">
       <c r="A133" s="4" t="n">
@@ -6920,6 +7266,11 @@
         </is>
       </c>
       <c r="N133" s="4" t="n"/>
+      <c r="S133" t="inlineStr">
+        <is>
+          <t>geblokkeerd — niet te controleren</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" s="4" t="n">
@@ -7177,6 +7528,11 @@
         </is>
       </c>
       <c r="N138" s="4" t="n"/>
+      <c r="S138" t="inlineStr">
+        <is>
+          <t>geblokkeerd — niet te controleren</t>
+        </is>
+      </c>
     </row>
     <row r="139" ht="25" customHeight="1">
       <c r="A139" s="4" t="n">
@@ -7216,6 +7572,11 @@
         </is>
       </c>
       <c r="N139" s="4" t="n"/>
+      <c r="S139" t="inlineStr">
+        <is>
+          <t>getal staat niet op de pagina</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" s="4" t="n">
@@ -7314,6 +7675,11 @@
         </is>
       </c>
       <c r="N141" s="4" t="n"/>
+      <c r="S141" t="inlineStr">
+        <is>
+          <t>geblokkeerd — niet te controleren</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" s="4" t="n">
@@ -7407,6 +7773,11 @@
         </is>
       </c>
       <c r="N143" s="4" t="n"/>
+      <c r="S143" t="inlineStr">
+        <is>
+          <t>geblokkeerd — niet te controleren</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" s="4" t="n">
@@ -7446,6 +7817,11 @@
         </is>
       </c>
       <c r="N144" s="4" t="n"/>
+      <c r="S144" t="inlineStr">
+        <is>
+          <t>geblokkeerd — niet te controleren</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" s="4" t="n">
@@ -7593,6 +7969,11 @@
         </is>
       </c>
       <c r="N147" s="4" t="n"/>
+      <c r="S147" t="inlineStr">
+        <is>
+          <t>geblokkeerd — niet te controleren</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" s="4" t="n">
@@ -7671,6 +8052,11 @@
         </is>
       </c>
       <c r="N149" s="4" t="n"/>
+      <c r="S149" t="inlineStr">
+        <is>
+          <t>getal staat niet op de pagina</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" s="4" t="n">
@@ -7710,6 +8096,11 @@
         </is>
       </c>
       <c r="N150" s="4" t="n"/>
+      <c r="S150" t="inlineStr">
+        <is>
+          <t>bevestigd</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" s="4" t="n">
@@ -7749,6 +8140,11 @@
         </is>
       </c>
       <c r="N151" s="4" t="n"/>
+      <c r="S151" t="inlineStr">
+        <is>
+          <t>bevestigd</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" s="4" t="n">
@@ -7788,6 +8184,11 @@
         </is>
       </c>
       <c r="N152" s="4" t="n"/>
+      <c r="S152" t="inlineStr">
+        <is>
+          <t>geblokkeerd — niet te controleren</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" s="4" t="n">
@@ -7827,6 +8228,11 @@
         </is>
       </c>
       <c r="N153" s="4" t="n"/>
+      <c r="S153" t="inlineStr">
+        <is>
+          <t>DODE LINK</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" s="4" t="n">
@@ -7866,6 +8272,11 @@
         </is>
       </c>
       <c r="N154" s="4" t="n"/>
+      <c r="S154" t="inlineStr">
+        <is>
+          <t>geblokkeerd — niet te controleren</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" s="4" t="n">
@@ -7905,6 +8316,11 @@
         </is>
       </c>
       <c r="N155" s="4" t="n"/>
+      <c r="S155" t="inlineStr">
+        <is>
+          <t>geblokkeerd — niet te controleren</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" s="4" t="n">
@@ -7944,6 +8360,11 @@
         </is>
       </c>
       <c r="N156" s="4" t="n"/>
+      <c r="S156" t="inlineStr">
+        <is>
+          <t>geblokkeerd — niet te controleren</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" s="4" t="n">
@@ -8076,6 +8497,11 @@
         </is>
       </c>
       <c r="N159" s="4" t="n"/>
+      <c r="S159" t="inlineStr">
+        <is>
+          <t>DODE LINK</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" s="4" t="n">
@@ -8115,6 +8541,11 @@
         </is>
       </c>
       <c r="N160" s="4" t="n"/>
+      <c r="S160" t="inlineStr">
+        <is>
+          <t>geblokkeerd — niet te controleren</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" s="4" t="n">
@@ -8209,6 +8640,11 @@
         </is>
       </c>
       <c r="N162" s="4" t="n"/>
+      <c r="S162" t="inlineStr">
+        <is>
+          <t>DODE LINK</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" s="4" t="n">
@@ -8248,6 +8684,11 @@
         </is>
       </c>
       <c r="N163" s="4" t="n"/>
+      <c r="S163" t="inlineStr">
+        <is>
+          <t>geblokkeerd — niet te controleren</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" s="4" t="n">
@@ -8287,6 +8728,11 @@
         </is>
       </c>
       <c r="N164" s="4" t="n"/>
+      <c r="S164" t="inlineStr">
+        <is>
+          <t>DODE LINK</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" s="4" t="n">
@@ -8380,6 +8826,11 @@
         </is>
       </c>
       <c r="N166" s="4" t="n"/>
+      <c r="S166" t="inlineStr">
+        <is>
+          <t>DODE LINK</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" s="4" t="n">
@@ -8419,6 +8870,11 @@
         </is>
       </c>
       <c r="N167" s="4" t="n"/>
+      <c r="S167" t="inlineStr">
+        <is>
+          <t>geblokkeerd — niet te controleren</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" s="4" t="n">
@@ -8458,6 +8914,11 @@
         </is>
       </c>
       <c r="N168" s="4" t="n"/>
+      <c r="S168" t="inlineStr">
+        <is>
+          <t>DODE LINK</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" s="4" t="n">
@@ -8497,6 +8958,11 @@
         </is>
       </c>
       <c r="N169" s="4" t="n"/>
+      <c r="S169" t="inlineStr">
+        <is>
+          <t>geblokkeerd — niet te controleren</t>
+        </is>
+      </c>
     </row>
     <row r="170" ht="25" customHeight="1">
       <c r="A170" s="4" t="n">
@@ -8536,6 +9002,11 @@
         </is>
       </c>
       <c r="N170" s="4" t="n"/>
+      <c r="S170" t="inlineStr">
+        <is>
+          <t>getal staat niet op de pagina</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" s="4" t="n">
@@ -8575,6 +9046,11 @@
         </is>
       </c>
       <c r="N171" s="4" t="n"/>
+      <c r="S171" t="inlineStr">
+        <is>
+          <t>getal staat niet op de pagina</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" s="4" t="n">
@@ -8614,6 +9090,11 @@
         </is>
       </c>
       <c r="N172" s="4" t="n"/>
+      <c r="S172" t="inlineStr">
+        <is>
+          <t>DODE LINK</t>
+        </is>
+      </c>
     </row>
     <row r="173" ht="25" customHeight="1">
       <c r="A173" s="4" t="n">
@@ -8653,6 +9134,11 @@
         </is>
       </c>
       <c r="N173" s="4" t="n"/>
+      <c r="S173" t="inlineStr">
+        <is>
+          <t>getal gezien op de pagina</t>
+        </is>
+      </c>
     </row>
     <row r="174" ht="25" customHeight="1">
       <c r="A174" s="4" t="n">
@@ -8747,6 +9233,11 @@
         </is>
       </c>
       <c r="N175" s="4" t="n"/>
+      <c r="S175" t="inlineStr">
+        <is>
+          <t>DODE LINK</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" s="4" t="n">
@@ -8840,6 +9331,11 @@
         </is>
       </c>
       <c r="N177" s="4" t="n"/>
+      <c r="S177" t="inlineStr">
+        <is>
+          <t>getal gezien op de pagina</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" s="4" t="n">
@@ -9042,6 +9538,11 @@
         </is>
       </c>
       <c r="N181" s="4" t="n"/>
+      <c r="S181" t="inlineStr">
+        <is>
+          <t>DODE LINK</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" s="4" t="n">
@@ -9136,6 +9637,11 @@
         </is>
       </c>
       <c r="N183" s="4" t="n"/>
+      <c r="S183" t="inlineStr">
+        <is>
+          <t>getal staat niet op de pagina</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" s="4" t="n">
@@ -9234,6 +9740,11 @@
         </is>
       </c>
       <c r="N185" s="4" t="n"/>
+      <c r="S185" t="inlineStr">
+        <is>
+          <t>onbereikbaar</t>
+        </is>
+      </c>
     </row>
     <row r="186" ht="25" customHeight="1">
       <c r="A186" s="4" t="n">
@@ -9273,6 +9784,11 @@
         </is>
       </c>
       <c r="N186" s="4" t="n"/>
+      <c r="S186" t="inlineStr">
+        <is>
+          <t>onbereikbaar</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" s="4" t="n">
@@ -9459,6 +9975,11 @@
         </is>
       </c>
       <c r="N190" s="4" t="n"/>
+      <c r="S190" t="inlineStr">
+        <is>
+          <t>onbereikbaar</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" s="4" t="n">
@@ -9591,6 +10112,11 @@
         </is>
       </c>
       <c r="N193" s="4" t="n"/>
+      <c r="S193" t="inlineStr">
+        <is>
+          <t>DODE LINK</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" s="4" t="n">
@@ -10533,6 +11059,11 @@
         </is>
       </c>
       <c r="N210" s="4" t="n"/>
+      <c r="S210" t="inlineStr">
+        <is>
+          <t>onbereikbaar</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" s="4" t="n">
@@ -10572,6 +11103,11 @@
         </is>
       </c>
       <c r="N211" s="4" t="n"/>
+      <c r="S211" t="inlineStr">
+        <is>
+          <t>geblokkeerd — niet te controleren</t>
+        </is>
+      </c>
     </row>
     <row r="212">
       <c r="A212" s="4" t="n">
@@ -10611,6 +11147,11 @@
         </is>
       </c>
       <c r="N212" s="4" t="n"/>
+      <c r="S212" t="inlineStr">
+        <is>
+          <t>geblokkeerd — niet te controleren</t>
+        </is>
+      </c>
     </row>
     <row r="213" ht="25" customHeight="1">
       <c r="A213" s="4" t="n">
@@ -10812,6 +11353,11 @@
         </is>
       </c>
       <c r="N216" s="4" t="n"/>
+      <c r="S216" t="inlineStr">
+        <is>
+          <t>getal staat niet op de pagina</t>
+        </is>
+      </c>
     </row>
     <row r="217">
       <c r="A217" s="4" t="n">
@@ -10851,6 +11397,11 @@
         </is>
       </c>
       <c r="N217" s="4" t="n"/>
+      <c r="S217" t="inlineStr">
+        <is>
+          <t>geblokkeerd — niet te controleren</t>
+        </is>
+      </c>
     </row>
     <row r="218">
       <c r="A218" s="4" t="n">
@@ -10963,6 +11514,11 @@
         </is>
       </c>
       <c r="N219" s="4" t="n"/>
+      <c r="S219" t="inlineStr">
+        <is>
+          <t>bevestigd</t>
+        </is>
+      </c>
     </row>
     <row r="220">
       <c r="A220" s="4" t="n">
@@ -11002,6 +11558,11 @@
         </is>
       </c>
       <c r="N220" s="4" t="n"/>
+      <c r="S220" t="inlineStr">
+        <is>
+          <t>geblokkeerd — niet te controleren</t>
+        </is>
+      </c>
     </row>
     <row r="221">
       <c r="A221" s="4" t="n">
@@ -11095,6 +11656,11 @@
         </is>
       </c>
       <c r="N222" s="4" t="n"/>
+      <c r="S222" t="inlineStr">
+        <is>
+          <t>geblokkeerd — niet te controleren</t>
+        </is>
+      </c>
     </row>
     <row r="223">
       <c r="A223" s="4" t="n">
@@ -11134,6 +11700,11 @@
         </is>
       </c>
       <c r="N223" s="4" t="n"/>
+      <c r="S223" t="inlineStr">
+        <is>
+          <t>getal staat niet op de pagina</t>
+        </is>
+      </c>
     </row>
     <row r="224">
       <c r="A224" s="4" t="n">
@@ -11173,6 +11744,11 @@
         </is>
       </c>
       <c r="N224" s="4" t="n"/>
+      <c r="S224" t="inlineStr">
+        <is>
+          <t>getal gezien op de pagina</t>
+        </is>
+      </c>
     </row>
     <row r="225">
       <c r="A225" s="4" t="n">
@@ -11290,6 +11866,11 @@
           <t>Wikidata: ander onderwerp</t>
         </is>
       </c>
+      <c r="S226" t="inlineStr">
+        <is>
+          <t>geblokkeerd — niet te controleren</t>
+        </is>
+      </c>
     </row>
     <row r="227">
       <c r="A227" s="4" t="n">
@@ -11329,6 +11910,11 @@
         </is>
       </c>
       <c r="N227" s="4" t="n"/>
+      <c r="S227" t="inlineStr">
+        <is>
+          <t>getal staat niet op de pagina</t>
+        </is>
+      </c>
     </row>
     <row r="228">
       <c r="A228" s="4" t="n">
@@ -11368,6 +11954,11 @@
         </is>
       </c>
       <c r="N228" s="4" t="n"/>
+      <c r="S228" t="inlineStr">
+        <is>
+          <t>geblokkeerd — niet te controleren</t>
+        </is>
+      </c>
     </row>
     <row r="229">
       <c r="A229" s="4" t="n">
@@ -11579,6 +12170,11 @@
           <t>Wikidata: geen waarde</t>
         </is>
       </c>
+      <c r="S232" t="inlineStr">
+        <is>
+          <t>DODE LINK</t>
+        </is>
+      </c>
     </row>
     <row r="233">
       <c r="A233" s="4" t="n">
@@ -11682,6 +12278,11 @@
           <t>Wikidata: geen waarde</t>
         </is>
       </c>
+      <c r="S234" t="inlineStr">
+        <is>
+          <t>DODE LINK</t>
+        </is>
+      </c>
     </row>
     <row r="235">
       <c r="A235" s="4" t="n">
@@ -11783,6 +12384,11 @@
       <c r="Q236" t="inlineStr">
         <is>
           <t>Wikidata: geen waarde</t>
+        </is>
+      </c>
+      <c r="S236" t="inlineStr">
+        <is>
+          <t>getal staat niet op de pagina</t>
         </is>
       </c>
     </row>
@@ -11897,6 +12503,11 @@
           <t>Wikidata: geen waarde</t>
         </is>
       </c>
+      <c r="S238" t="inlineStr">
+        <is>
+          <t>DODE LINK</t>
+        </is>
+      </c>
     </row>
     <row r="239" ht="25" customHeight="1">
       <c r="A239" s="4" t="n">
@@ -11936,6 +12547,11 @@
         </is>
       </c>
       <c r="N239" s="4" t="n"/>
+      <c r="S239" t="inlineStr">
+        <is>
+          <t>geblokkeerd — niet te controleren</t>
+        </is>
+      </c>
     </row>
     <row r="240">
       <c r="A240" s="4" t="n">
@@ -12029,6 +12645,11 @@
         </is>
       </c>
       <c r="N241" s="4" t="n"/>
+      <c r="S241" t="inlineStr">
+        <is>
+          <t>getal staat niet op de pagina</t>
+        </is>
+      </c>
     </row>
     <row r="242">
       <c r="A242" s="4" t="n">
@@ -12068,6 +12689,11 @@
         </is>
       </c>
       <c r="N242" s="4" t="n"/>
+      <c r="S242" t="inlineStr">
+        <is>
+          <t>geblokkeerd — niet te controleren</t>
+        </is>
+      </c>
     </row>
     <row r="243" ht="25" customHeight="1">
       <c r="A243" s="4" t="n">
@@ -12216,6 +12842,11 @@
         </is>
       </c>
       <c r="N245" s="4" t="n"/>
+      <c r="S245" t="inlineStr">
+        <is>
+          <t>DODE LINK</t>
+        </is>
+      </c>
     </row>
     <row r="246">
       <c r="A246" s="4" t="n">
@@ -12309,6 +12940,11 @@
         </is>
       </c>
       <c r="N247" s="4" t="n"/>
+      <c r="S247" t="inlineStr">
+        <is>
+          <t>getal staat niet op de pagina</t>
+        </is>
+      </c>
     </row>
     <row r="248" ht="25" customHeight="1">
       <c r="A248" s="4" t="n">
@@ -12348,6 +12984,11 @@
         </is>
       </c>
       <c r="N248" s="4" t="n"/>
+      <c r="S248" t="inlineStr">
+        <is>
+          <t>getal staat niet op de pagina</t>
+        </is>
+      </c>
     </row>
     <row r="249">
       <c r="A249" s="4" t="n">
@@ -12550,6 +13191,11 @@
         </is>
       </c>
       <c r="N252" s="4" t="n"/>
+      <c r="S252" t="inlineStr">
+        <is>
+          <t>geblokkeerd — niet te controleren</t>
+        </is>
+      </c>
     </row>
     <row r="253">
       <c r="A253" s="4" t="n">
@@ -12589,6 +13235,11 @@
         </is>
       </c>
       <c r="N253" s="4" t="n"/>
+      <c r="S253" t="inlineStr">
+        <is>
+          <t>geen adres, alleen een omschrijving</t>
+        </is>
+      </c>
     </row>
     <row r="254">
       <c r="A254" s="4" t="n">
@@ -12845,6 +13496,11 @@
         </is>
       </c>
       <c r="N258" s="4" t="n"/>
+      <c r="S258" t="inlineStr">
+        <is>
+          <t>geen adres, alleen een omschrijving</t>
+        </is>
+      </c>
     </row>
     <row r="259">
       <c r="A259" s="4" t="n">
@@ -12884,6 +13540,11 @@
         </is>
       </c>
       <c r="N259" s="4" t="n"/>
+      <c r="S259" t="inlineStr">
+        <is>
+          <t>DODE LINK</t>
+        </is>
+      </c>
     </row>
     <row r="260">
       <c r="A260" s="4" t="n">
@@ -12923,6 +13584,11 @@
         </is>
       </c>
       <c r="N260" s="4" t="n"/>
+      <c r="S260" t="inlineStr">
+        <is>
+          <t>geblokkeerd — niet te controleren</t>
+        </is>
+      </c>
     </row>
     <row r="261">
       <c r="A261" s="4" t="n">
@@ -13244,6 +13910,11 @@
           <t>Wikidata: geen waarde</t>
         </is>
       </c>
+      <c r="S266" t="inlineStr">
+        <is>
+          <t>geblokkeerd — niet te controleren</t>
+        </is>
+      </c>
     </row>
     <row r="267">
       <c r="A267" s="4" t="n">
@@ -13347,6 +14018,11 @@
           <t>Wikidata: geen waarde</t>
         </is>
       </c>
+      <c r="S268" t="inlineStr">
+        <is>
+          <t>geblokkeerd — niet te controleren</t>
+        </is>
+      </c>
     </row>
     <row r="269">
       <c r="A269" s="4" t="n">
@@ -13391,6 +14067,11 @@
           <t>Wikidata: ander onderwerp</t>
         </is>
       </c>
+      <c r="S269" t="inlineStr">
+        <is>
+          <t>geblokkeerd — niet te controleren</t>
+        </is>
+      </c>
     </row>
     <row r="270">
       <c r="A270" s="4" t="n">
@@ -13435,6 +14116,11 @@
           <t>Wikidata: geen waarde</t>
         </is>
       </c>
+      <c r="S270" t="inlineStr">
+        <is>
+          <t>DODE LINK</t>
+        </is>
+      </c>
     </row>
     <row r="271">
       <c r="A271" s="4" t="n">
@@ -13538,6 +14224,11 @@
           <t>Wikidata: geen waarde</t>
         </is>
       </c>
+      <c r="S272" t="inlineStr">
+        <is>
+          <t>getal staat niet op de pagina</t>
+        </is>
+      </c>
     </row>
     <row r="273">
       <c r="A273" s="4" t="n">
@@ -13641,6 +14332,11 @@
           <t>Wikidata: ander onderwerp</t>
         </is>
       </c>
+      <c r="S274" t="inlineStr">
+        <is>
+          <t>geblokkeerd — niet te controleren</t>
+        </is>
+      </c>
     </row>
     <row r="275">
       <c r="A275" s="4" t="n">
@@ -13685,6 +14381,11 @@
           <t>Wikidata: klopt</t>
         </is>
       </c>
+      <c r="S275" t="inlineStr">
+        <is>
+          <t>geblokkeerd — niet te controleren</t>
+        </is>
+      </c>
     </row>
     <row r="276">
       <c r="A276" s="4" t="n">
@@ -13724,6 +14425,11 @@
         </is>
       </c>
       <c r="N276" s="4" t="n"/>
+      <c r="S276" t="inlineStr">
+        <is>
+          <t>geblokkeerd — niet te controleren</t>
+        </is>
+      </c>
     </row>
     <row r="277">
       <c r="A277" s="4" t="n">
@@ -13763,6 +14469,11 @@
         </is>
       </c>
       <c r="N277" s="4" t="n"/>
+      <c r="S277" t="inlineStr">
+        <is>
+          <t>getal staat niet op de pagina</t>
+        </is>
+      </c>
     </row>
     <row r="278">
       <c r="A278" s="4" t="n">
@@ -13856,6 +14567,11 @@
         </is>
       </c>
       <c r="N279" s="4" t="n"/>
+      <c r="S279" t="inlineStr">
+        <is>
+          <t>geblokkeerd — niet te controleren</t>
+        </is>
+      </c>
     </row>
     <row r="280">
       <c r="A280" s="4" t="n">
@@ -13895,6 +14611,11 @@
         </is>
       </c>
       <c r="N280" s="4" t="n"/>
+      <c r="S280" t="inlineStr">
+        <is>
+          <t>geblokkeerd — niet te controleren</t>
+        </is>
+      </c>
     </row>
     <row r="281">
       <c r="A281" s="4" t="n">
@@ -13990,6 +14711,11 @@
         </is>
       </c>
       <c r="N282" s="4" t="n"/>
+      <c r="S282" t="inlineStr">
+        <is>
+          <t>geblokkeerd — niet te controleren</t>
+        </is>
+      </c>
     </row>
     <row r="283">
       <c r="A283" s="4" t="n">
@@ -14029,6 +14755,11 @@
         </is>
       </c>
       <c r="N283" s="4" t="n"/>
+      <c r="S283" t="inlineStr">
+        <is>
+          <t>geblokkeerd — niet te controleren</t>
+        </is>
+      </c>
     </row>
     <row r="284">
       <c r="A284" s="4" t="n">
@@ -14068,6 +14799,11 @@
         </is>
       </c>
       <c r="N284" s="4" t="n"/>
+      <c r="S284" t="inlineStr">
+        <is>
+          <t>geblokkeerd — niet te controleren</t>
+        </is>
+      </c>
     </row>
     <row r="285">
       <c r="A285" s="4" t="n">
@@ -14107,6 +14843,11 @@
         </is>
       </c>
       <c r="N285" s="4" t="n"/>
+      <c r="S285" t="inlineStr">
+        <is>
+          <t>geen adres, alleen een omschrijving</t>
+        </is>
+      </c>
     </row>
     <row r="286">
       <c r="A286" s="4" t="n">
@@ -14146,6 +14887,11 @@
         </is>
       </c>
       <c r="N286" s="4" t="n"/>
+      <c r="S286" t="inlineStr">
+        <is>
+          <t>geblokkeerd — niet te controleren</t>
+        </is>
+      </c>
     </row>
     <row r="287">
       <c r="A287" s="4" t="n">
@@ -14239,6 +14985,11 @@
         </is>
       </c>
       <c r="N288" s="4" t="n"/>
+      <c r="S288" t="inlineStr">
+        <is>
+          <t>geblokkeerd — niet te controleren</t>
+        </is>
+      </c>
     </row>
     <row r="289" ht="25" customHeight="1">
       <c r="A289" s="4" t="n">
@@ -14278,6 +15029,11 @@
         </is>
       </c>
       <c r="N289" s="4" t="n"/>
+      <c r="S289" t="inlineStr">
+        <is>
+          <t>geblokkeerd — niet te controleren</t>
+        </is>
+      </c>
     </row>
     <row r="290">
       <c r="A290" s="4" t="n">
@@ -14317,6 +15073,11 @@
         </is>
       </c>
       <c r="N290" s="4" t="n"/>
+      <c r="S290" t="inlineStr">
+        <is>
+          <t>geblokkeerd — niet te controleren</t>
+        </is>
+      </c>
     </row>
     <row r="291">
       <c r="A291" s="4" t="n">
@@ -14637,6 +15398,11 @@
         </is>
       </c>
       <c r="N296" s="4" t="n"/>
+      <c r="S296" t="inlineStr">
+        <is>
+          <t>getal staat niet op de pagina</t>
+        </is>
+      </c>
     </row>
     <row r="297">
       <c r="A297" s="4" t="n">
@@ -14853,6 +15619,11 @@
           <t>Wikidata: klopt</t>
         </is>
       </c>
+      <c r="S300" t="inlineStr">
+        <is>
+          <t>geblokkeerd — niet te controleren</t>
+        </is>
+      </c>
     </row>
     <row r="301">
       <c r="A301" s="4" t="n">
@@ -14956,6 +15727,11 @@
           <t>Wikidata: klopt</t>
         </is>
       </c>
+      <c r="S302" t="inlineStr">
+        <is>
+          <t>DODE LINK</t>
+        </is>
+      </c>
     </row>
     <row r="303" ht="25" customHeight="1">
       <c r="A303" s="4" t="n">
@@ -15000,6 +15776,11 @@
           <t>Wikidata: ander onderwerp</t>
         </is>
       </c>
+      <c r="S303" t="inlineStr">
+        <is>
+          <t>getal staat niet op de pagina</t>
+        </is>
+      </c>
     </row>
     <row r="304" ht="25" customHeight="1">
       <c r="A304" s="4" t="n">
@@ -15203,6 +15984,11 @@
         </is>
       </c>
       <c r="N307" s="4" t="n"/>
+      <c r="S307" t="inlineStr">
+        <is>
+          <t>geblokkeerd — niet te controleren</t>
+        </is>
+      </c>
     </row>
     <row r="308">
       <c r="A308" s="4" t="n">
@@ -15242,6 +16028,11 @@
         </is>
       </c>
       <c r="N308" s="4" t="n"/>
+      <c r="S308" t="inlineStr">
+        <is>
+          <t>geblokkeerd — niet te controleren</t>
+        </is>
+      </c>
     </row>
     <row r="309">
       <c r="A309" s="4" t="n">
@@ -15390,6 +16181,11 @@
         </is>
       </c>
       <c r="N311" s="4" t="n"/>
+      <c r="S311" t="inlineStr">
+        <is>
+          <t>getal staat niet op de pagina</t>
+        </is>
+      </c>
     </row>
     <row r="312">
       <c r="A312" s="4" t="n">
@@ -15483,6 +16279,11 @@
         </is>
       </c>
       <c r="N313" s="4" t="n"/>
+      <c r="S313" t="inlineStr">
+        <is>
+          <t>geen adres, alleen een omschrijving</t>
+        </is>
+      </c>
     </row>
     <row r="314" ht="25" customHeight="1">
       <c r="A314" s="4" t="n">
@@ -15522,6 +16323,11 @@
         </is>
       </c>
       <c r="N314" s="4" t="n"/>
+      <c r="S314" t="inlineStr">
+        <is>
+          <t>geblokkeerd — niet te controleren</t>
+        </is>
+      </c>
     </row>
     <row r="315">
       <c r="A315" s="4" t="n">
@@ -15561,6 +16367,11 @@
         </is>
       </c>
       <c r="N315" s="4" t="n"/>
+      <c r="S315" t="inlineStr">
+        <is>
+          <t>geblokkeerd — niet te controleren</t>
+        </is>
+      </c>
     </row>
     <row r="316" ht="25" customHeight="1">
       <c r="A316" s="4" t="n">
@@ -15600,6 +16411,11 @@
         </is>
       </c>
       <c r="N316" s="4" t="n"/>
+      <c r="S316" t="inlineStr">
+        <is>
+          <t>geblokkeerd — niet te controleren</t>
+        </is>
+      </c>
     </row>
     <row r="317">
       <c r="A317" s="4" t="n">
@@ -15749,6 +16565,11 @@
         </is>
       </c>
       <c r="N319" s="4" t="n"/>
+      <c r="S319" t="inlineStr">
+        <is>
+          <t>geblokkeerd — niet te controleren</t>
+        </is>
+      </c>
     </row>
     <row r="320">
       <c r="A320" s="4" t="n">
@@ -15788,6 +16609,11 @@
         </is>
       </c>
       <c r="N320" s="4" t="n"/>
+      <c r="S320" t="inlineStr">
+        <is>
+          <t>geblokkeerd — niet te controleren</t>
+        </is>
+      </c>
     </row>
     <row r="321" ht="25" customHeight="1">
       <c r="A321" s="4" t="n">
@@ -15832,6 +16658,11 @@
           <t>Wikidata: geen waarde</t>
         </is>
       </c>
+      <c r="S321" t="inlineStr">
+        <is>
+          <t>geen adres, alleen een omschrijving</t>
+        </is>
+      </c>
     </row>
     <row r="322">
       <c r="A322" s="4" t="n">
@@ -15871,6 +16702,11 @@
         </is>
       </c>
       <c r="N322" s="4" t="n"/>
+      <c r="S322" t="inlineStr">
+        <is>
+          <t>getal staat niet op de pagina</t>
+        </is>
+      </c>
     </row>
     <row r="323">
       <c r="A323" s="4" t="n">
@@ -15910,6 +16746,11 @@
         </is>
       </c>
       <c r="N323" s="4" t="n"/>
+      <c r="S323" t="inlineStr">
+        <is>
+          <t>geblokkeerd — niet te controleren</t>
+        </is>
+      </c>
     </row>
     <row r="324">
       <c r="A324" s="4" t="n">
@@ -15949,6 +16790,11 @@
         </is>
       </c>
       <c r="N324" s="4" t="n"/>
+      <c r="S324" t="inlineStr">
+        <is>
+          <t>geblokkeerd — niet te controleren</t>
+        </is>
+      </c>
     </row>
     <row r="325">
       <c r="A325" s="4" t="n">
@@ -16045,6 +16891,11 @@
         </is>
       </c>
       <c r="N326" s="4" t="n"/>
+      <c r="S326" t="inlineStr">
+        <is>
+          <t>geblokkeerd — niet te controleren</t>
+        </is>
+      </c>
     </row>
     <row r="327" ht="25" customHeight="1">
       <c r="A327" s="4" t="n">
@@ -16151,6 +17002,11 @@
         </is>
       </c>
       <c r="N328" s="4" t="n"/>
+      <c r="S328" t="inlineStr">
+        <is>
+          <t>geblokkeerd — niet te controleren</t>
+        </is>
+      </c>
     </row>
     <row r="329" ht="25" customHeight="1">
       <c r="A329" s="4" t="n">
@@ -16190,6 +17046,11 @@
         </is>
       </c>
       <c r="N329" s="4" t="n"/>
+      <c r="S329" t="inlineStr">
+        <is>
+          <t>geblokkeerd — niet te controleren</t>
+        </is>
+      </c>
     </row>
     <row r="330">
       <c r="A330" s="4" t="n">
@@ -16229,6 +17090,11 @@
         </is>
       </c>
       <c r="N330" s="4" t="n"/>
+      <c r="S330" t="inlineStr">
+        <is>
+          <t>geblokkeerd — niet te controleren</t>
+        </is>
+      </c>
     </row>
     <row r="331" ht="25" customHeight="1">
       <c r="A331" s="4" t="n">
@@ -16268,6 +17134,11 @@
         </is>
       </c>
       <c r="N331" s="4" t="n"/>
+      <c r="S331" t="inlineStr">
+        <is>
+          <t>geblokkeerd — niet te controleren</t>
+        </is>
+      </c>
     </row>
     <row r="332">
       <c r="A332" s="4" t="n">
@@ -16307,6 +17178,11 @@
         </is>
       </c>
       <c r="N332" s="4" t="n"/>
+      <c r="S332" t="inlineStr">
+        <is>
+          <t>geblokkeerd — niet te controleren</t>
+        </is>
+      </c>
     </row>
     <row r="333" ht="25" customHeight="1">
       <c r="A333" s="4" t="n">
@@ -16346,6 +17222,11 @@
         </is>
       </c>
       <c r="N333" s="4" t="n"/>
+      <c r="S333" t="inlineStr">
+        <is>
+          <t>geblokkeerd — niet te controleren</t>
+        </is>
+      </c>
     </row>
     <row r="334">
       <c r="A334" s="4" t="n">
@@ -16439,6 +17320,11 @@
         </is>
       </c>
       <c r="N335" s="4" t="n"/>
+      <c r="S335" t="inlineStr">
+        <is>
+          <t>DODE LINK</t>
+        </is>
+      </c>
     </row>
     <row r="336">
       <c r="A336" s="4" t="n">
@@ -17006,6 +17892,11 @@
         </is>
       </c>
       <c r="N346" s="4" t="n"/>
+      <c r="S346" t="inlineStr">
+        <is>
+          <t>geen adres, alleen een omschrijving</t>
+        </is>
+      </c>
     </row>
     <row r="347">
       <c r="A347" s="4" t="n">
@@ -17210,6 +18101,11 @@
         </is>
       </c>
       <c r="N350" s="4" t="n"/>
+      <c r="S350" t="inlineStr">
+        <is>
+          <t>getal staat niet op de pagina</t>
+        </is>
+      </c>
     </row>
     <row r="351">
       <c r="A351" s="4" t="n">
@@ -17249,6 +18145,11 @@
         </is>
       </c>
       <c r="N351" s="4" t="n"/>
+      <c r="S351" t="inlineStr">
+        <is>
+          <t>onbereikbaar</t>
+        </is>
+      </c>
     </row>
     <row r="352">
       <c r="A352" s="4" t="n">
@@ -17288,6 +18189,11 @@
         </is>
       </c>
       <c r="N352" s="4" t="n"/>
+      <c r="S352" t="inlineStr">
+        <is>
+          <t>geen adres, alleen een omschrijving</t>
+        </is>
+      </c>
     </row>
     <row r="353">
       <c r="A353" s="4" t="n">
@@ -17602,6 +18508,11 @@
         </is>
       </c>
       <c r="N358" s="4" t="n"/>
+      <c r="S358" t="inlineStr">
+        <is>
+          <t>getal staat niet op de pagina</t>
+        </is>
+      </c>
     </row>
     <row r="359">
       <c r="A359" s="4" t="n">
@@ -17641,6 +18552,11 @@
         </is>
       </c>
       <c r="N359" s="4" t="n"/>
+      <c r="S359" t="inlineStr">
+        <is>
+          <t>getal staat niet op de pagina</t>
+        </is>
+      </c>
     </row>
     <row r="360">
       <c r="A360" s="4" t="n">
@@ -17734,6 +18650,11 @@
         </is>
       </c>
       <c r="N361" s="4" t="n"/>
+      <c r="S361" t="inlineStr">
+        <is>
+          <t>DODE LINK</t>
+        </is>
+      </c>
     </row>
     <row r="362" ht="25" customHeight="1">
       <c r="A362" s="4" t="n">
@@ -17773,6 +18694,11 @@
         </is>
       </c>
       <c r="N362" s="4" t="n"/>
+      <c r="S362" t="inlineStr">
+        <is>
+          <t>getal staat niet op de pagina</t>
+        </is>
+      </c>
     </row>
     <row r="363">
       <c r="A363" s="4" t="n">
@@ -17812,6 +18738,11 @@
         </is>
       </c>
       <c r="N363" s="4" t="n"/>
+      <c r="S363" t="inlineStr">
+        <is>
+          <t>getal staat niet op de pagina</t>
+        </is>
+      </c>
     </row>
     <row r="364">
       <c r="A364" s="4" t="n">
@@ -17851,6 +18782,11 @@
         </is>
       </c>
       <c r="N364" s="4" t="n"/>
+      <c r="S364" t="inlineStr">
+        <is>
+          <t>getal staat niet op de pagina</t>
+        </is>
+      </c>
     </row>
     <row r="365">
       <c r="A365" s="4" t="n">
@@ -17890,6 +18826,11 @@
         </is>
       </c>
       <c r="N365" s="4" t="n"/>
+      <c r="S365" t="inlineStr">
+        <is>
+          <t>getal staat niet op de pagina</t>
+        </is>
+      </c>
     </row>
     <row r="366">
       <c r="A366" s="4" t="n">
@@ -17929,6 +18870,11 @@
         </is>
       </c>
       <c r="N366" s="4" t="n"/>
+      <c r="S366" t="inlineStr">
+        <is>
+          <t>getal staat niet op de pagina</t>
+        </is>
+      </c>
     </row>
     <row r="367">
       <c r="A367" s="4" t="n">
@@ -17968,6 +18914,11 @@
         </is>
       </c>
       <c r="N367" s="4" t="n"/>
+      <c r="S367" t="inlineStr">
+        <is>
+          <t>getal staat niet op de pagina</t>
+        </is>
+      </c>
     </row>
     <row r="368">
       <c r="A368" s="4" t="n">
@@ -18007,6 +18958,11 @@
         </is>
       </c>
       <c r="N368" s="4" t="n"/>
+      <c r="S368" t="inlineStr">
+        <is>
+          <t>DODE LINK</t>
+        </is>
+      </c>
     </row>
     <row r="369">
       <c r="A369" s="4" t="n">
@@ -18046,6 +19002,11 @@
         </is>
       </c>
       <c r="N369" s="4" t="n"/>
+      <c r="S369" t="inlineStr">
+        <is>
+          <t>geblokkeerd — niet te controleren</t>
+        </is>
+      </c>
     </row>
     <row r="370">
       <c r="A370" s="4" t="n">
@@ -18085,6 +19046,11 @@
         </is>
       </c>
       <c r="N370" s="4" t="n"/>
+      <c r="S370" t="inlineStr">
+        <is>
+          <t>onbereikbaar</t>
+        </is>
+      </c>
     </row>
     <row r="371" ht="25" customHeight="1">
       <c r="A371" s="4" t="n">
@@ -18124,6 +19090,11 @@
         </is>
       </c>
       <c r="N371" s="4" t="n"/>
+      <c r="S371" t="inlineStr">
+        <is>
+          <t>getal staat niet op de pagina</t>
+        </is>
+      </c>
     </row>
     <row r="372" ht="25" customHeight="1">
       <c r="A372" s="4" t="n">
@@ -18163,6 +19134,11 @@
         </is>
       </c>
       <c r="N372" s="4" t="n"/>
+      <c r="S372" t="inlineStr">
+        <is>
+          <t>getal staat niet op de pagina</t>
+        </is>
+      </c>
     </row>
     <row r="373" ht="25" customHeight="1">
       <c r="A373" s="4" t="n">
@@ -18202,6 +19178,11 @@
         </is>
       </c>
       <c r="N373" s="4" t="n"/>
+      <c r="S373" t="inlineStr">
+        <is>
+          <t>getal staat niet op de pagina</t>
+        </is>
+      </c>
     </row>
     <row r="374">
       <c r="A374" s="4" t="n">
@@ -18295,6 +19276,11 @@
         </is>
       </c>
       <c r="N375" s="4" t="n"/>
+      <c r="S375" t="inlineStr">
+        <is>
+          <t>getal gezien op de pagina</t>
+        </is>
+      </c>
     </row>
     <row r="376">
       <c r="A376" s="4" t="n">
@@ -18442,6 +19428,11 @@
         </is>
       </c>
       <c r="N378" s="4" t="n"/>
+      <c r="S378" t="inlineStr">
+        <is>
+          <t>DODE LINK</t>
+        </is>
+      </c>
     </row>
     <row r="379">
       <c r="A379" s="4" t="n">
@@ -18481,6 +19472,11 @@
         </is>
       </c>
       <c r="N379" s="4" t="n"/>
+      <c r="S379" t="inlineStr">
+        <is>
+          <t>getal staat niet op de pagina</t>
+        </is>
+      </c>
     </row>
     <row r="380">
       <c r="A380" s="4" t="n">
@@ -18520,6 +19516,11 @@
         </is>
       </c>
       <c r="N380" s="4" t="n"/>
+      <c r="S380" t="inlineStr">
+        <is>
+          <t>bevestigd</t>
+        </is>
+      </c>
     </row>
     <row r="381">
       <c r="A381" s="4" t="n">
@@ -18899,6 +19900,11 @@
         </is>
       </c>
       <c r="N388" s="4" t="n"/>
+      <c r="S388" t="inlineStr">
+        <is>
+          <t>DODE LINK</t>
+        </is>
+      </c>
     </row>
     <row r="389">
       <c r="A389" s="4" t="n">
@@ -19208,6 +20214,11 @@
         </is>
       </c>
       <c r="N394" s="4" t="n"/>
+      <c r="S394" t="inlineStr">
+        <is>
+          <t>geblokkeerd — niet te controleren</t>
+        </is>
+      </c>
     </row>
     <row r="395">
       <c r="A395" s="4" t="n">
@@ -19464,6 +20475,11 @@
         </is>
       </c>
       <c r="N399" s="4" t="n"/>
+      <c r="S399" t="inlineStr">
+        <is>
+          <t>bevestigd</t>
+        </is>
+      </c>
     </row>
     <row r="400">
       <c r="A400" s="4" t="n">
@@ -19503,6 +20519,11 @@
         </is>
       </c>
       <c r="N400" s="4" t="n"/>
+      <c r="S400" t="inlineStr">
+        <is>
+          <t>getal staat niet op de pagina</t>
+        </is>
+      </c>
     </row>
     <row r="401">
       <c r="A401" s="4" t="n">
@@ -19650,6 +20671,11 @@
         </is>
       </c>
       <c r="N403" s="4" t="n"/>
+      <c r="S403" t="inlineStr">
+        <is>
+          <t>getal staat niet op de pagina</t>
+        </is>
+      </c>
     </row>
     <row r="404">
       <c r="A404" s="4" t="n">
@@ -19836,6 +20862,11 @@
         </is>
       </c>
       <c r="N407" s="4" t="n"/>
+      <c r="S407" t="inlineStr">
+        <is>
+          <t>getal staat niet op de pagina</t>
+        </is>
+      </c>
     </row>
     <row r="408">
       <c r="A408" s="4" t="n">
@@ -19929,6 +20960,11 @@
         </is>
       </c>
       <c r="N409" s="4" t="n"/>
+      <c r="S409" t="inlineStr">
+        <is>
+          <t>DODE LINK</t>
+        </is>
+      </c>
     </row>
     <row r="410">
       <c r="A410" s="4" t="n">
@@ -19968,6 +21004,11 @@
         </is>
       </c>
       <c r="N410" s="4" t="n"/>
+      <c r="S410" t="inlineStr">
+        <is>
+          <t>getal staat niet op de pagina</t>
+        </is>
+      </c>
     </row>
     <row r="411">
       <c r="A411" s="4" t="n">
@@ -20105,6 +21146,11 @@
           <t>Wikidata: geen waarde</t>
         </is>
       </c>
+      <c r="S413" t="inlineStr">
+        <is>
+          <t>DODE LINK</t>
+        </is>
+      </c>
     </row>
     <row r="414">
       <c r="A414" s="4" t="n">
@@ -20252,6 +21298,11 @@
         </is>
       </c>
       <c r="N416" s="4" t="n"/>
+      <c r="S416" t="inlineStr">
+        <is>
+          <t>DODE LINK</t>
+        </is>
+      </c>
     </row>
     <row r="417">
       <c r="A417" s="4" t="n">
@@ -20399,6 +21450,11 @@
         </is>
       </c>
       <c r="N419" s="4" t="n"/>
+      <c r="S419" t="inlineStr">
+        <is>
+          <t>getal staat niet op de pagina</t>
+        </is>
+      </c>
     </row>
     <row r="420">
       <c r="A420" s="4" t="n">
@@ -20764,6 +21820,11 @@
         </is>
       </c>
       <c r="N426" s="4" t="n"/>
+      <c r="S426" t="inlineStr">
+        <is>
+          <t>bevestigd</t>
+        </is>
+      </c>
     </row>
     <row r="427">
       <c r="A427" s="4" t="n">
@@ -20857,6 +21918,11 @@
         </is>
       </c>
       <c r="N428" s="4" t="n"/>
+      <c r="S428" t="inlineStr">
+        <is>
+          <t>getal staat niet op de pagina</t>
+        </is>
+      </c>
     </row>
     <row r="429">
       <c r="A429" s="4" t="n">
@@ -20896,6 +21962,11 @@
         </is>
       </c>
       <c r="N429" s="4" t="n"/>
+      <c r="S429" t="inlineStr">
+        <is>
+          <t>getal gezien op de pagina</t>
+        </is>
+      </c>
     </row>
     <row r="430" ht="25" customHeight="1">
       <c r="A430" s="4" t="n">
@@ -21106,6 +22177,11 @@
         </is>
       </c>
       <c r="N433" s="4" t="n"/>
+      <c r="S433" t="inlineStr">
+        <is>
+          <t>getal gezien op de pagina</t>
+        </is>
+      </c>
     </row>
     <row r="434">
       <c r="A434" s="4" t="n">
@@ -21145,6 +22221,11 @@
         </is>
       </c>
       <c r="N434" s="4" t="n"/>
+      <c r="S434" t="inlineStr">
+        <is>
+          <t>getal staat niet op de pagina</t>
+        </is>
+      </c>
     </row>
     <row r="435">
       <c r="A435" s="4" t="n">
@@ -22436,6 +23517,11 @@
         </is>
       </c>
       <c r="N460" s="4" t="n"/>
+      <c r="S460" t="inlineStr">
+        <is>
+          <t>onbereikbaar</t>
+        </is>
+      </c>
     </row>
     <row r="461">
       <c r="A461" s="4" t="n">
@@ -22475,6 +23561,11 @@
         </is>
       </c>
       <c r="N461" s="4" t="n"/>
+      <c r="S461" t="inlineStr">
+        <is>
+          <t>getal staat niet op de pagina</t>
+        </is>
+      </c>
     </row>
     <row r="462">
       <c r="A462" s="4" t="n">
@@ -22568,6 +23659,11 @@
         </is>
       </c>
       <c r="N463" s="4" t="n"/>
+      <c r="S463" t="inlineStr">
+        <is>
+          <t>bevestigd</t>
+        </is>
+      </c>
     </row>
     <row r="464">
       <c r="A464" s="4" t="n">
@@ -22607,6 +23703,11 @@
         </is>
       </c>
       <c r="N464" s="4" t="n"/>
+      <c r="S464" t="inlineStr">
+        <is>
+          <t>bevestigd</t>
+        </is>
+      </c>
     </row>
     <row r="465">
       <c r="A465" s="4" t="n">
@@ -22646,6 +23747,11 @@
         </is>
       </c>
       <c r="N465" s="4" t="n"/>
+      <c r="S465" t="inlineStr">
+        <is>
+          <t>getal staat niet op de pagina</t>
+        </is>
+      </c>
     </row>
     <row r="466">
       <c r="A466" s="4" t="n">
@@ -22685,6 +23791,11 @@
         </is>
       </c>
       <c r="N466" s="4" t="n"/>
+      <c r="S466" t="inlineStr">
+        <is>
+          <t>getal staat niet op de pagina</t>
+        </is>
+      </c>
     </row>
     <row r="467">
       <c r="A467" s="4" t="n">
@@ -22724,6 +23835,11 @@
         </is>
       </c>
       <c r="N467" s="4" t="n"/>
+      <c r="S467" t="inlineStr">
+        <is>
+          <t>bevestigd</t>
+        </is>
+      </c>
     </row>
     <row r="468">
       <c r="A468" s="4" t="n">
@@ -22763,6 +23879,11 @@
         </is>
       </c>
       <c r="N468" s="4" t="n"/>
+      <c r="S468" t="inlineStr">
+        <is>
+          <t>getal staat niet op de pagina</t>
+        </is>
+      </c>
     </row>
     <row r="469">
       <c r="A469" s="4" t="n">
@@ -22802,6 +23923,11 @@
         </is>
       </c>
       <c r="N469" s="4" t="n"/>
+      <c r="S469" t="inlineStr">
+        <is>
+          <t>getal staat niet op de pagina</t>
+        </is>
+      </c>
     </row>
     <row r="470">
       <c r="A470" s="4" t="n">
@@ -22949,6 +24075,11 @@
         </is>
       </c>
       <c r="N472" s="4" t="n"/>
+      <c r="S472" t="inlineStr">
+        <is>
+          <t>bevestigd</t>
+        </is>
+      </c>
     </row>
     <row r="473" ht="25" customHeight="1">
       <c r="A473" s="4" t="n">
@@ -22988,6 +24119,11 @@
         </is>
       </c>
       <c r="N473" s="4" t="n"/>
+      <c r="S473" t="inlineStr">
+        <is>
+          <t>getal gezien op de pagina</t>
+        </is>
+      </c>
     </row>
     <row r="474">
       <c r="A474" s="4" t="n">
@@ -23027,6 +24163,11 @@
         </is>
       </c>
       <c r="N474" s="4" t="n"/>
+      <c r="S474" t="inlineStr">
+        <is>
+          <t>bevestigd</t>
+        </is>
+      </c>
     </row>
     <row r="475">
       <c r="A475" s="4" t="n">
@@ -23066,6 +24207,11 @@
         </is>
       </c>
       <c r="N475" s="4" t="n"/>
+      <c r="S475" t="inlineStr">
+        <is>
+          <t>bevestigd</t>
+        </is>
+      </c>
     </row>
     <row r="476">
       <c r="A476" s="4" t="n">
@@ -23159,6 +24305,11 @@
         </is>
       </c>
       <c r="N477" s="4" t="n"/>
+      <c r="S477" t="inlineStr">
+        <is>
+          <t>bevestigd</t>
+        </is>
+      </c>
     </row>
     <row r="478">
       <c r="A478" s="4" t="n">
@@ -23778,6 +24929,11 @@
         </is>
       </c>
       <c r="N489" s="4" t="n"/>
+      <c r="S489" t="inlineStr">
+        <is>
+          <t>getal staat niet op de pagina</t>
+        </is>
+      </c>
     </row>
     <row r="490" ht="25" customHeight="1">
       <c r="A490" s="4" t="n">
@@ -23871,6 +25027,11 @@
         </is>
       </c>
       <c r="N491" s="4" t="n"/>
+      <c r="S491" t="inlineStr">
+        <is>
+          <t>bevestigd</t>
+        </is>
+      </c>
     </row>
     <row r="492" ht="25" customHeight="1">
       <c r="A492" s="4" t="n">
@@ -24166,6 +25327,11 @@
         </is>
       </c>
       <c r="N497" s="4" t="n"/>
+      <c r="S497" t="inlineStr">
+        <is>
+          <t>getal staat niet op de pagina</t>
+        </is>
+      </c>
     </row>
     <row r="498">
       <c r="A498" s="4" t="n">
@@ -24260,6 +25426,11 @@
         </is>
       </c>
       <c r="N499" s="4" t="n"/>
+      <c r="S499" t="inlineStr">
+        <is>
+          <t>geblokkeerd — niet te controleren</t>
+        </is>
+      </c>
     </row>
     <row r="500">
       <c r="A500" s="4" t="n">
@@ -24299,6 +25470,11 @@
         </is>
       </c>
       <c r="N500" s="4" t="n"/>
+      <c r="S500" t="inlineStr">
+        <is>
+          <t>bevestigd</t>
+        </is>
+      </c>
     </row>
     <row r="501">
       <c r="A501" s="4" t="n">
@@ -24338,6 +25514,11 @@
         </is>
       </c>
       <c r="N501" s="4" t="n"/>
+      <c r="S501" t="inlineStr">
+        <is>
+          <t>getal staat niet op de pagina</t>
+        </is>
+      </c>
     </row>
     <row r="502">
       <c r="A502" s="4" t="n">
@@ -24431,6 +25612,11 @@
         </is>
       </c>
       <c r="N503" s="4" t="n"/>
+      <c r="S503" t="inlineStr">
+        <is>
+          <t>getal staat niet op de pagina</t>
+        </is>
+      </c>
     </row>
     <row r="504">
       <c r="A504" s="4" t="n">
@@ -24470,6 +25656,11 @@
         </is>
       </c>
       <c r="N504" s="4" t="n"/>
+      <c r="S504" t="inlineStr">
+        <is>
+          <t>getal gezien op de pagina</t>
+        </is>
+      </c>
     </row>
     <row r="505">
       <c r="A505" s="4" t="n">
@@ -24509,6 +25700,11 @@
         </is>
       </c>
       <c r="N505" s="4" t="n"/>
+      <c r="S505" t="inlineStr">
+        <is>
+          <t>getal staat niet op de pagina</t>
+        </is>
+      </c>
     </row>
     <row r="506">
       <c r="A506" s="4" t="n">
@@ -24548,6 +25744,11 @@
         </is>
       </c>
       <c r="N506" s="4" t="n"/>
+      <c r="S506" t="inlineStr">
+        <is>
+          <t>DODE LINK</t>
+        </is>
+      </c>
     </row>
     <row r="507">
       <c r="A507" s="4" t="n">
@@ -24695,6 +25896,11 @@
         </is>
       </c>
       <c r="N509" s="4" t="n"/>
+      <c r="S509" t="inlineStr">
+        <is>
+          <t>geblokkeerd — niet te controleren</t>
+        </is>
+      </c>
     </row>
     <row r="510">
       <c r="A510" s="4" t="n">
@@ -24734,6 +25940,11 @@
         </is>
       </c>
       <c r="N510" s="4" t="n"/>
+      <c r="S510" t="inlineStr">
+        <is>
+          <t>getal gezien op de pagina</t>
+        </is>
+      </c>
     </row>
     <row r="511">
       <c r="A511" s="4" t="n">
@@ -24773,6 +25984,11 @@
         </is>
       </c>
       <c r="N511" s="4" t="n"/>
+      <c r="S511" t="inlineStr">
+        <is>
+          <t>getal gezien op de pagina</t>
+        </is>
+      </c>
     </row>
     <row r="512">
       <c r="A512" s="4" t="n">
@@ -24812,6 +26028,11 @@
         </is>
       </c>
       <c r="N512" s="4" t="n"/>
+      <c r="S512" t="inlineStr">
+        <is>
+          <t>getal gezien op de pagina</t>
+        </is>
+      </c>
     </row>
     <row r="513">
       <c r="A513" s="4" t="n">
@@ -24968,6 +26189,11 @@
         </is>
       </c>
       <c r="N515" s="4" t="n"/>
+      <c r="S515" t="inlineStr">
+        <is>
+          <t>getal staat niet op de pagina</t>
+        </is>
+      </c>
     </row>
     <row r="516">
       <c r="A516" s="4" t="n">
@@ -25007,6 +26233,11 @@
         </is>
       </c>
       <c r="N516" s="4" t="n"/>
+      <c r="S516" t="inlineStr">
+        <is>
+          <t>getal staat niet op de pagina</t>
+        </is>
+      </c>
     </row>
     <row r="517">
       <c r="A517" s="4" t="n">
@@ -25046,6 +26277,11 @@
         </is>
       </c>
       <c r="N517" s="4" t="n"/>
+      <c r="S517" t="inlineStr">
+        <is>
+          <t>getal staat niet op de pagina</t>
+        </is>
+      </c>
     </row>
     <row r="518">
       <c r="A518" s="4" t="n">
@@ -25139,6 +26375,11 @@
         </is>
       </c>
       <c r="N519" s="4" t="n"/>
+      <c r="S519" t="inlineStr">
+        <is>
+          <t>getal staat niet op de pagina</t>
+        </is>
+      </c>
     </row>
     <row r="520">
       <c r="A520" s="4" t="n">
@@ -25178,6 +26419,11 @@
         </is>
       </c>
       <c r="N520" s="4" t="n"/>
+      <c r="S520" t="inlineStr">
+        <is>
+          <t>getal staat niet op de pagina</t>
+        </is>
+      </c>
     </row>
     <row r="521">
       <c r="A521" s="4" t="n">
@@ -25217,6 +26463,11 @@
         </is>
       </c>
       <c r="N521" s="4" t="n"/>
+      <c r="S521" t="inlineStr">
+        <is>
+          <t>getal staat niet op de pagina</t>
+        </is>
+      </c>
     </row>
     <row r="522">
       <c r="A522" s="4" t="n">
@@ -25256,6 +26507,11 @@
         </is>
       </c>
       <c r="N522" s="4" t="n"/>
+      <c r="S522" t="inlineStr">
+        <is>
+          <t>getal staat niet op de pagina</t>
+        </is>
+      </c>
     </row>
     <row r="523">
       <c r="A523" s="4" t="n">
@@ -25295,6 +26551,11 @@
         </is>
       </c>
       <c r="N523" s="4" t="n"/>
+      <c r="S523" t="inlineStr">
+        <is>
+          <t>getal staat niet op de pagina</t>
+        </is>
+      </c>
     </row>
     <row r="524">
       <c r="A524" s="4" t="n">
@@ -25442,6 +26703,11 @@
         </is>
       </c>
       <c r="N526" s="4" t="n"/>
+      <c r="S526" t="inlineStr">
+        <is>
+          <t>geblokkeerd — niet te controleren</t>
+        </is>
+      </c>
     </row>
     <row r="527">
       <c r="A527" s="4" t="n">
@@ -25590,6 +26856,11 @@
         </is>
       </c>
       <c r="N529" s="4" t="n"/>
+      <c r="S529" t="inlineStr">
+        <is>
+          <t>getal staat niet op de pagina</t>
+        </is>
+      </c>
     </row>
     <row r="530">
       <c r="A530" s="4" t="n">
@@ -25629,6 +26900,11 @@
         </is>
       </c>
       <c r="N530" s="4" t="n"/>
+      <c r="S530" t="inlineStr">
+        <is>
+          <t>getal staat niet op de pagina</t>
+        </is>
+      </c>
     </row>
     <row r="531">
       <c r="A531" s="4" t="n">
@@ -25668,6 +26944,11 @@
         </is>
       </c>
       <c r="N531" s="4" t="n"/>
+      <c r="S531" t="inlineStr">
+        <is>
+          <t>getal staat niet op de pagina</t>
+        </is>
+      </c>
     </row>
     <row r="532">
       <c r="A532" s="4" t="n">
@@ -25816,6 +27097,11 @@
         </is>
       </c>
       <c r="N534" s="4" t="n"/>
+      <c r="S534" t="inlineStr">
+        <is>
+          <t>DODE LINK</t>
+        </is>
+      </c>
     </row>
     <row r="535">
       <c r="A535" s="4" t="n">
@@ -25909,6 +27195,11 @@
         </is>
       </c>
       <c r="N536" s="4" t="n"/>
+      <c r="S536" t="inlineStr">
+        <is>
+          <t>bevestigd</t>
+        </is>
+      </c>
     </row>
     <row r="537">
       <c r="A537" s="4" t="n">
@@ -25948,6 +27239,11 @@
         </is>
       </c>
       <c r="N537" s="4" t="n"/>
+      <c r="S537" t="inlineStr">
+        <is>
+          <t>getal staat niet op de pagina</t>
+        </is>
+      </c>
     </row>
     <row r="538">
       <c r="A538" s="4" t="n">
@@ -25987,6 +27283,11 @@
         </is>
       </c>
       <c r="N538" s="4" t="n"/>
+      <c r="S538" t="inlineStr">
+        <is>
+          <t>DODE LINK</t>
+        </is>
+      </c>
     </row>
     <row r="539">
       <c r="A539" s="4" t="n">
@@ -26026,6 +27327,11 @@
         </is>
       </c>
       <c r="N539" s="4" t="n"/>
+      <c r="S539" t="inlineStr">
+        <is>
+          <t>getal staat niet op de pagina</t>
+        </is>
+      </c>
     </row>
     <row r="540">
       <c r="A540" s="4" t="n">
@@ -26065,6 +27371,11 @@
         </is>
       </c>
       <c r="N540" s="4" t="n"/>
+      <c r="S540" t="inlineStr">
+        <is>
+          <t>geblokkeerd — niet te controleren</t>
+        </is>
+      </c>
     </row>
     <row r="541">
       <c r="A541" s="4" t="n">
@@ -26104,6 +27415,11 @@
         </is>
       </c>
       <c r="N541" s="4" t="n"/>
+      <c r="S541" t="inlineStr">
+        <is>
+          <t>DODE LINK</t>
+        </is>
+      </c>
     </row>
     <row r="542">
       <c r="A542" s="4" t="n">
@@ -26251,6 +27567,11 @@
         </is>
       </c>
       <c r="N544" s="4" t="n"/>
+      <c r="S544" t="inlineStr">
+        <is>
+          <t>geblokkeerd — niet te controleren</t>
+        </is>
+      </c>
     </row>
     <row r="545">
       <c r="A545" s="4" t="n">
@@ -26344,6 +27665,11 @@
         </is>
       </c>
       <c r="N546" s="4" t="n"/>
+      <c r="S546" t="inlineStr">
+        <is>
+          <t>geblokkeerd — niet te controleren</t>
+        </is>
+      </c>
     </row>
     <row r="547" ht="25" customHeight="1">
       <c r="A547" s="4" t="n">
@@ -26422,6 +27748,11 @@
         </is>
       </c>
       <c r="N548" s="4" t="n"/>
+      <c r="S548" t="inlineStr">
+        <is>
+          <t>DODE LINK</t>
+        </is>
+      </c>
     </row>
     <row r="549">
       <c r="A549" s="4" t="n">
@@ -26461,6 +27792,11 @@
         </is>
       </c>
       <c r="N549" s="4" t="n"/>
+      <c r="S549" t="inlineStr">
+        <is>
+          <t>DODE LINK</t>
+        </is>
+      </c>
     </row>
     <row r="550" ht="25" customHeight="1">
       <c r="A550" s="4" t="n">
@@ -26609,6 +27945,11 @@
         </is>
       </c>
       <c r="N552" s="4" t="n"/>
+      <c r="S552" t="inlineStr">
+        <is>
+          <t>DODE LINK</t>
+        </is>
+      </c>
     </row>
     <row r="553">
       <c r="A553" s="4" t="n">
@@ -26810,6 +28151,11 @@
         </is>
       </c>
       <c r="N556" s="4" t="n"/>
+      <c r="S556" t="inlineStr">
+        <is>
+          <t>geblokkeerd — niet te controleren</t>
+        </is>
+      </c>
     </row>
     <row r="557">
       <c r="A557" s="4" t="n">
@@ -26849,6 +28195,11 @@
         </is>
       </c>
       <c r="N557" s="4" t="n"/>
+      <c r="S557" t="inlineStr">
+        <is>
+          <t>geblokkeerd — niet te controleren</t>
+        </is>
+      </c>
     </row>
     <row r="558">
       <c r="A558" s="4" t="n">
@@ -26888,6 +28239,11 @@
         </is>
       </c>
       <c r="N558" s="4" t="n"/>
+      <c r="S558" t="inlineStr">
+        <is>
+          <t>DODE LINK</t>
+        </is>
+      </c>
     </row>
     <row r="559">
       <c r="A559" s="4" t="n">
@@ -26927,6 +28283,11 @@
         </is>
       </c>
       <c r="N559" s="4" t="n"/>
+      <c r="S559" t="inlineStr">
+        <is>
+          <t>DODE LINK</t>
+        </is>
+      </c>
     </row>
     <row r="560">
       <c r="A560" s="4" t="n">
@@ -27020,6 +28381,11 @@
         </is>
       </c>
       <c r="N561" s="4" t="n"/>
+      <c r="S561" t="inlineStr">
+        <is>
+          <t>geblokkeerd — niet te controleren</t>
+        </is>
+      </c>
     </row>
     <row r="562">
       <c r="A562" s="4" t="n">
@@ -27059,6 +28425,11 @@
         </is>
       </c>
       <c r="N562" s="4" t="n"/>
+      <c r="S562" t="inlineStr">
+        <is>
+          <t>DODE LINK</t>
+        </is>
+      </c>
     </row>
     <row r="563">
       <c r="A563" s="4" t="n">
@@ -27261,6 +28632,11 @@
         </is>
       </c>
       <c r="N566" s="4" t="n"/>
+      <c r="S566" t="inlineStr">
+        <is>
+          <t>geblokkeerd — niet te controleren</t>
+        </is>
+      </c>
     </row>
     <row r="567">
       <c r="A567" s="4" t="n">
@@ -27300,6 +28676,11 @@
         </is>
       </c>
       <c r="N567" s="4" t="n"/>
+      <c r="S567" t="inlineStr">
+        <is>
+          <t>geblokkeerd — niet te controleren</t>
+        </is>
+      </c>
     </row>
     <row r="568">
       <c r="A568" s="4" t="n">
@@ -27339,6 +28720,11 @@
         </is>
       </c>
       <c r="N568" s="4" t="n"/>
+      <c r="S568" t="inlineStr">
+        <is>
+          <t>geblokkeerd — niet te controleren</t>
+        </is>
+      </c>
     </row>
     <row r="569">
       <c r="A569" s="4" t="n">
@@ -27491,6 +28877,11 @@
           <t>Wikidata: klopt</t>
         </is>
       </c>
+      <c r="S571" t="inlineStr">
+        <is>
+          <t>DODE LINK</t>
+        </is>
+      </c>
     </row>
     <row r="572">
       <c r="A572" s="4" t="n">
@@ -27589,6 +28980,11 @@
         </is>
       </c>
       <c r="N573" s="4" t="n"/>
+      <c r="S573" t="inlineStr">
+        <is>
+          <t>geblokkeerd — niet te controleren</t>
+        </is>
+      </c>
     </row>
     <row r="574" ht="25" customHeight="1">
       <c r="A574" s="4" t="n">
@@ -27628,6 +29024,11 @@
         </is>
       </c>
       <c r="N574" s="4" t="n"/>
+      <c r="S574" t="inlineStr">
+        <is>
+          <t>bevestigd</t>
+        </is>
+      </c>
     </row>
     <row r="575">
       <c r="A575" s="4" t="n">
@@ -27672,6 +29073,11 @@
           <t>Wikidata: klopt</t>
         </is>
       </c>
+      <c r="S575" t="inlineStr">
+        <is>
+          <t>getal gezien op de pagina</t>
+        </is>
+      </c>
     </row>
     <row r="576">
       <c r="A576" s="4" t="n">
@@ -28090,6 +29496,11 @@
         </is>
       </c>
       <c r="N583" s="4" t="n"/>
+      <c r="S583" t="inlineStr">
+        <is>
+          <t>getal staat niet op de pagina</t>
+        </is>
+      </c>
     </row>
     <row r="584" ht="25" customHeight="1">
       <c r="A584" s="4" t="n">
@@ -28129,6 +29540,11 @@
         </is>
       </c>
       <c r="N584" s="4" t="n"/>
+      <c r="S584" t="inlineStr">
+        <is>
+          <t>DODE LINK</t>
+        </is>
+      </c>
     </row>
     <row r="585" ht="25" customHeight="1">
       <c r="A585" s="4" t="n">
@@ -28222,6 +29638,11 @@
         </is>
       </c>
       <c r="N586" s="4" t="n"/>
+      <c r="S586" t="inlineStr">
+        <is>
+          <t>getal staat niet op de pagina</t>
+        </is>
+      </c>
     </row>
     <row r="587">
       <c r="A587" s="4" t="n">
@@ -28369,6 +29790,11 @@
         </is>
       </c>
       <c r="N589" s="4" t="n"/>
+      <c r="S589" t="inlineStr">
+        <is>
+          <t>geblokkeerd — niet te controleren</t>
+        </is>
+      </c>
     </row>
     <row r="590">
       <c r="A590" s="4" t="n">
@@ -28408,6 +29834,11 @@
         </is>
       </c>
       <c r="N590" s="4" t="n"/>
+      <c r="S590" t="inlineStr">
+        <is>
+          <t>geblokkeerd — niet te controleren</t>
+        </is>
+      </c>
     </row>
     <row r="591">
       <c r="A591" s="4" t="n">
@@ -28447,6 +29878,11 @@
         </is>
       </c>
       <c r="N591" s="4" t="n"/>
+      <c r="S591" t="inlineStr">
+        <is>
+          <t>geblokkeerd — niet te controleren</t>
+        </is>
+      </c>
     </row>
     <row r="592">
       <c r="A592" s="4" t="n">
@@ -28486,6 +29922,11 @@
         </is>
       </c>
       <c r="N592" s="4" t="n"/>
+      <c r="S592" t="inlineStr">
+        <is>
+          <t>onbereikbaar</t>
+        </is>
+      </c>
     </row>
     <row r="593">
       <c r="A593" s="4" t="n">
@@ -28633,6 +30074,11 @@
         </is>
       </c>
       <c r="N595" s="4" t="n"/>
+      <c r="S595" t="inlineStr">
+        <is>
+          <t>geblokkeerd — niet te controleren</t>
+        </is>
+      </c>
     </row>
     <row r="596">
       <c r="A596" s="4" t="n">
@@ -28711,6 +30157,11 @@
         </is>
       </c>
       <c r="N597" s="4" t="n"/>
+      <c r="S597" t="inlineStr">
+        <is>
+          <t>geblokkeerd — niet te controleren</t>
+        </is>
+      </c>
     </row>
     <row r="598">
       <c r="A598" s="4" t="n">
@@ -28805,6 +30256,11 @@
         </is>
       </c>
       <c r="N599" s="4" t="n"/>
+      <c r="S599" t="inlineStr">
+        <is>
+          <t>geblokkeerd — niet te controleren</t>
+        </is>
+      </c>
     </row>
     <row r="600">
       <c r="A600" s="4" t="n">
@@ -28883,6 +30339,11 @@
         </is>
       </c>
       <c r="N601" s="4" t="n"/>
+      <c r="S601" t="inlineStr">
+        <is>
+          <t>getal staat niet op de pagina</t>
+        </is>
+      </c>
     </row>
     <row r="602">
       <c r="A602" s="4" t="n">
@@ -28961,6 +30422,11 @@
         </is>
       </c>
       <c r="N603" s="4" t="n"/>
+      <c r="S603" t="inlineStr">
+        <is>
+          <t>geblokkeerd — niet te controleren</t>
+        </is>
+      </c>
     </row>
     <row r="604">
       <c r="A604" s="4" t="n">
@@ -29000,6 +30466,11 @@
         </is>
       </c>
       <c r="N604" s="4" t="n"/>
+      <c r="S604" t="inlineStr">
+        <is>
+          <t>DODE LINK</t>
+        </is>
+      </c>
     </row>
     <row r="605">
       <c r="A605" s="4" t="n">
@@ -29039,6 +30510,11 @@
         </is>
       </c>
       <c r="N605" s="4" t="n"/>
+      <c r="S605" t="inlineStr">
+        <is>
+          <t>geblokkeerd — niet te controleren</t>
+        </is>
+      </c>
     </row>
     <row r="606" ht="25" customHeight="1">
       <c r="A606" s="4" t="n">
@@ -29078,6 +30554,11 @@
         </is>
       </c>
       <c r="N606" s="4" t="n"/>
+      <c r="S606" t="inlineStr">
+        <is>
+          <t>getal staat niet op de pagina</t>
+        </is>
+      </c>
     </row>
     <row r="607">
       <c r="A607" s="4" t="n">
@@ -29172,6 +30653,11 @@
         </is>
       </c>
       <c r="N608" s="4" t="n"/>
+      <c r="S608" t="inlineStr">
+        <is>
+          <t>geblokkeerd — niet te controleren</t>
+        </is>
+      </c>
     </row>
     <row r="609">
       <c r="A609" s="4" t="n">
@@ -29211,6 +30697,11 @@
         </is>
       </c>
       <c r="N609" s="4" t="n"/>
+      <c r="S609" t="inlineStr">
+        <is>
+          <t>bevestigd</t>
+        </is>
+      </c>
     </row>
     <row r="610">
       <c r="A610" s="4" t="n">
@@ -29250,6 +30741,11 @@
         </is>
       </c>
       <c r="N610" s="4" t="n"/>
+      <c r="S610" t="inlineStr">
+        <is>
+          <t>getal gezien op de pagina</t>
+        </is>
+      </c>
     </row>
     <row r="611">
       <c r="A611" s="4" t="n">
@@ -29289,6 +30785,11 @@
         </is>
       </c>
       <c r="N611" s="4" t="n"/>
+      <c r="S611" t="inlineStr">
+        <is>
+          <t>DODE LINK</t>
+        </is>
+      </c>
     </row>
     <row r="612">
       <c r="A612" s="4" t="n">
@@ -29328,6 +30829,11 @@
         </is>
       </c>
       <c r="N612" s="4" t="n"/>
+      <c r="S612" t="inlineStr">
+        <is>
+          <t>DODE LINK</t>
+        </is>
+      </c>
     </row>
     <row r="613">
       <c r="A613" s="4" t="n">
@@ -29367,6 +30873,11 @@
         </is>
       </c>
       <c r="N613" s="4" t="n"/>
+      <c r="S613" t="inlineStr">
+        <is>
+          <t>geblokkeerd — niet te controleren</t>
+        </is>
+      </c>
     </row>
     <row r="614">
       <c r="A614" s="4" t="n">
@@ -29406,6 +30917,11 @@
         </is>
       </c>
       <c r="N614" s="4" t="n"/>
+      <c r="S614" t="inlineStr">
+        <is>
+          <t>geblokkeerd — niet te controleren</t>
+        </is>
+      </c>
     </row>
     <row r="615">
       <c r="A615" s="4" t="n">
@@ -29445,6 +30961,11 @@
         </is>
       </c>
       <c r="N615" s="4" t="n"/>
+      <c r="S615" t="inlineStr">
+        <is>
+          <t>DODE LINK</t>
+        </is>
+      </c>
     </row>
     <row r="616">
       <c r="A616" s="4" t="n">
@@ -29538,6 +31059,11 @@
         </is>
       </c>
       <c r="N617" s="4" t="n"/>
+      <c r="S617" t="inlineStr">
+        <is>
+          <t>geen adres, alleen een omschrijving</t>
+        </is>
+      </c>
     </row>
     <row r="618">
       <c r="A618" s="4" t="n">
@@ -29685,6 +31211,11 @@
         </is>
       </c>
       <c r="N620" s="4" t="n"/>
+      <c r="S620" t="inlineStr">
+        <is>
+          <t>geblokkeerd — niet te controleren</t>
+        </is>
+      </c>
     </row>
     <row r="621">
       <c r="A621" s="4" t="n">
@@ -29724,6 +31255,11 @@
         </is>
       </c>
       <c r="N621" s="4" t="n"/>
+      <c r="S621" t="inlineStr">
+        <is>
+          <t>geblokkeerd — niet te controleren</t>
+        </is>
+      </c>
     </row>
     <row r="622">
       <c r="A622" s="4" t="n">
@@ -29926,6 +31462,11 @@
         </is>
       </c>
       <c r="N625" s="4" t="n"/>
+      <c r="S625" t="inlineStr">
+        <is>
+          <t>geblokkeerd — niet te controleren</t>
+        </is>
+      </c>
     </row>
     <row r="626">
       <c r="A626" s="4" t="n">
@@ -29965,6 +31506,11 @@
         </is>
       </c>
       <c r="N626" s="4" t="n"/>
+      <c r="S626" t="inlineStr">
+        <is>
+          <t>geblokkeerd — niet te controleren</t>
+        </is>
+      </c>
     </row>
     <row r="627">
       <c r="A627" s="4" t="n">
@@ -30111,6 +31657,11 @@
           <t>geen EN-vertaling</t>
         </is>
       </c>
+      <c r="S629" t="inlineStr">
+        <is>
+          <t>getal staat niet op de pagina</t>
+        </is>
+      </c>
     </row>
     <row r="630" ht="25" customHeight="1">
       <c r="A630" s="4" t="n">
@@ -30150,6 +31701,11 @@
         </is>
       </c>
       <c r="N630" s="4" t="n"/>
+      <c r="S630" t="inlineStr">
+        <is>
+          <t>getal staat niet op de pagina</t>
+        </is>
+      </c>
     </row>
     <row r="631">
       <c r="A631" s="4" t="n">
@@ -30238,6 +31794,11 @@
         </is>
       </c>
       <c r="N632" s="4" t="n"/>
+      <c r="S632" t="inlineStr">
+        <is>
+          <t>getal staat niet op de pagina</t>
+        </is>
+      </c>
     </row>
     <row r="633">
       <c r="A633" s="4" t="n">
@@ -30277,6 +31838,11 @@
         </is>
       </c>
       <c r="N633" s="4" t="n"/>
+      <c r="S633" t="inlineStr">
+        <is>
+          <t>DODE LINK</t>
+        </is>
+      </c>
     </row>
     <row r="634">
       <c r="A634" s="4" t="n">
@@ -30389,6 +31955,11 @@
         </is>
       </c>
       <c r="N636" s="4" t="n"/>
+      <c r="S636" t="inlineStr">
+        <is>
+          <t>getal staat niet op de pagina</t>
+        </is>
+      </c>
     </row>
     <row r="637">
       <c r="A637" s="4" t="n">
@@ -30501,6 +32072,11 @@
         </is>
       </c>
       <c r="N639" s="4" t="n"/>
+      <c r="S639" t="inlineStr">
+        <is>
+          <t>geblokkeerd — niet te controleren</t>
+        </is>
+      </c>
     </row>
     <row r="640">
       <c r="A640" s="4" t="n">
@@ -30540,6 +32116,11 @@
         </is>
       </c>
       <c r="N640" s="4" t="n"/>
+      <c r="S640" t="inlineStr">
+        <is>
+          <t>getal gezien op de pagina</t>
+        </is>
+      </c>
     </row>
     <row r="641" ht="25" customHeight="1">
       <c r="A641" s="4" t="n">
@@ -30579,6 +32160,11 @@
         </is>
       </c>
       <c r="N641" s="4" t="n"/>
+      <c r="S641" t="inlineStr">
+        <is>
+          <t>DODE LINK</t>
+        </is>
+      </c>
     </row>
     <row r="642">
       <c r="A642" s="4" t="n">
@@ -30657,6 +32243,11 @@
         </is>
       </c>
       <c r="N643" s="4" t="n"/>
+      <c r="S643" t="inlineStr">
+        <is>
+          <t>DODE LINK</t>
+        </is>
+      </c>
     </row>
     <row r="644" ht="25" customHeight="1">
       <c r="A644" s="4" t="n">
@@ -31082,6 +32673,11 @@
         </is>
       </c>
       <c r="N653" s="4" t="n"/>
+      <c r="S653" t="inlineStr">
+        <is>
+          <t>geblokkeerd — niet te controleren</t>
+        </is>
+      </c>
     </row>
     <row r="654" ht="25" customHeight="1">
       <c r="A654" s="4" t="n">
@@ -31292,6 +32888,11 @@
         </is>
       </c>
       <c r="N658" s="4" t="n"/>
+      <c r="S658" t="inlineStr">
+        <is>
+          <t>DODE LINK</t>
+        </is>
+      </c>
     </row>
     <row r="659">
       <c r="A659" s="4" t="n">
@@ -31615,6 +33216,11 @@
         </is>
       </c>
       <c r="N665" s="4" t="n"/>
+      <c r="S665" t="inlineStr">
+        <is>
+          <t>getal gezien op de pagina</t>
+        </is>
+      </c>
     </row>
     <row r="666">
       <c r="A666" s="4" t="n">
@@ -31654,6 +33260,11 @@
         </is>
       </c>
       <c r="N666" s="4" t="n"/>
+      <c r="S666" t="inlineStr">
+        <is>
+          <t>geblokkeerd — niet te controleren</t>
+        </is>
+      </c>
     </row>
     <row r="667" ht="25" customHeight="1">
       <c r="A667" s="4" t="n">
@@ -31693,6 +33304,11 @@
         </is>
       </c>
       <c r="N667" s="4" t="n"/>
+      <c r="S667" t="inlineStr">
+        <is>
+          <t>geblokkeerd — niet te controleren</t>
+        </is>
+      </c>
     </row>
     <row r="668" ht="25" customHeight="1">
       <c r="A668" s="4" t="n">
@@ -31732,6 +33348,11 @@
         </is>
       </c>
       <c r="N668" s="4" t="n"/>
+      <c r="S668" t="inlineStr">
+        <is>
+          <t>bevestigd</t>
+        </is>
+      </c>
     </row>
     <row r="669" ht="25" customHeight="1">
       <c r="A669" s="4" t="n">
@@ -32199,6 +33820,11 @@
         </is>
       </c>
       <c r="N678" s="4" t="n"/>
+      <c r="S678" t="inlineStr">
+        <is>
+          <t>geblokkeerd — niet te controleren</t>
+        </is>
+      </c>
     </row>
     <row r="679" ht="25" customHeight="1">
       <c r="A679" s="4" t="n">
@@ -32238,6 +33864,11 @@
         </is>
       </c>
       <c r="N679" s="4" t="n"/>
+      <c r="S679" t="inlineStr">
+        <is>
+          <t>getal staat niet op de pagina</t>
+        </is>
+      </c>
     </row>
     <row r="680">
       <c r="A680" s="4" t="n">
@@ -32277,6 +33908,11 @@
         </is>
       </c>
       <c r="N680" s="4" t="n"/>
+      <c r="S680" t="inlineStr">
+        <is>
+          <t>DODE LINK</t>
+        </is>
+      </c>
     </row>
     <row r="681" ht="25" customHeight="1">
       <c r="A681" s="4" t="n">
@@ -32355,6 +33991,11 @@
         </is>
       </c>
       <c r="N682" s="4" t="n"/>
+      <c r="S682" t="inlineStr">
+        <is>
+          <t>geblokkeerd — niet te controleren</t>
+        </is>
+      </c>
     </row>
     <row r="683">
       <c r="A683" s="4" t="n">
@@ -32604,6 +34245,11 @@
         </is>
       </c>
       <c r="N688" s="4" t="n"/>
+      <c r="S688" t="inlineStr">
+        <is>
+          <t>geblokkeerd — niet te controleren</t>
+        </is>
+      </c>
     </row>
     <row r="689">
       <c r="A689" s="4" t="n">
@@ -32697,6 +34343,11 @@
         </is>
       </c>
       <c r="N690" s="4" t="n"/>
+      <c r="S690" t="inlineStr">
+        <is>
+          <t>onbereikbaar</t>
+        </is>
+      </c>
     </row>
     <row r="691" ht="25" customHeight="1">
       <c r="A691" s="4" t="n">
@@ -32775,6 +34426,11 @@
         </is>
       </c>
       <c r="N692" s="4" t="n"/>
+      <c r="S692" t="inlineStr">
+        <is>
+          <t>getal staat niet op de pagina</t>
+        </is>
+      </c>
     </row>
     <row r="693">
       <c r="A693" s="4" t="n">
@@ -33000,6 +34656,11 @@
         </is>
       </c>
       <c r="N697" s="4" t="n"/>
+      <c r="S697" t="inlineStr">
+        <is>
+          <t>getal staat niet op de pagina</t>
+        </is>
+      </c>
     </row>
     <row r="698">
       <c r="A698" s="4" t="n">
@@ -33039,6 +34700,11 @@
         </is>
       </c>
       <c r="N698" s="4" t="n"/>
+      <c r="S698" t="inlineStr">
+        <is>
+          <t>getal staat niet op de pagina</t>
+        </is>
+      </c>
     </row>
     <row r="699">
       <c r="A699" s="4" t="n">
@@ -33075,6 +34741,11 @@
       <c r="N699" s="4" t="inlineStr">
         <is>
           <t>geen EN-vertaling</t>
+        </is>
+      </c>
+      <c r="S699" t="inlineStr">
+        <is>
+          <t>onbereikbaar</t>
         </is>
       </c>
     </row>
@@ -33217,6 +34888,11 @@
         </is>
       </c>
       <c r="N702" s="4" t="n"/>
+      <c r="S702" t="inlineStr">
+        <is>
+          <t>geen adres, alleen een omschrijving</t>
+        </is>
+      </c>
     </row>
     <row r="703">
       <c r="A703" s="4" t="n">
@@ -33256,6 +34932,11 @@
         </is>
       </c>
       <c r="N703" s="4" t="n"/>
+      <c r="S703" t="inlineStr">
+        <is>
+          <t>onbereikbaar</t>
+        </is>
+      </c>
     </row>
     <row r="704">
       <c r="A704" s="4" t="n">
@@ -33888,6 +35569,11 @@
         </is>
       </c>
       <c r="N717" s="4" t="n"/>
+      <c r="S717" t="inlineStr">
+        <is>
+          <t>onbereikbaar</t>
+        </is>
+      </c>
     </row>
     <row r="718" ht="25" customHeight="1">
       <c r="A718" s="4" t="n">
@@ -35682,6 +37368,11 @@
         </is>
       </c>
       <c r="N752" s="4" t="n"/>
+      <c r="S752" t="inlineStr">
+        <is>
+          <t>getal gezien op de pagina</t>
+        </is>
+      </c>
     </row>
     <row r="753">
       <c r="A753" s="4" t="n">
@@ -36156,6 +37847,11 @@
         </is>
       </c>
       <c r="N763" s="4" t="n"/>
+      <c r="S763" t="inlineStr">
+        <is>
+          <t>geblokkeerd — niet te controleren</t>
+        </is>
+      </c>
     </row>
     <row r="764" ht="25" customHeight="1">
       <c r="A764" s="4" t="n">
@@ -36195,6 +37891,11 @@
         </is>
       </c>
       <c r="N764" s="4" t="n"/>
+      <c r="S764" t="inlineStr">
+        <is>
+          <t>DODE LINK</t>
+        </is>
+      </c>
     </row>
     <row r="765" ht="25" customHeight="1">
       <c r="A765" s="4" t="n">
@@ -36234,6 +37935,11 @@
         </is>
       </c>
       <c r="N765" s="4" t="n"/>
+      <c r="S765" t="inlineStr">
+        <is>
+          <t>geblokkeerd — niet te controleren</t>
+        </is>
+      </c>
     </row>
     <row r="766">
       <c r="A766" s="4" t="n">
@@ -36544,6 +38250,11 @@
         </is>
       </c>
       <c r="N771" s="4" t="n"/>
+      <c r="S771" t="inlineStr">
+        <is>
+          <t>geblokkeerd — niet te controleren</t>
+        </is>
+      </c>
     </row>
     <row r="772">
       <c r="A772" s="4" t="n">
@@ -36627,6 +38338,11 @@
         </is>
       </c>
       <c r="N773" s="4" t="n"/>
+      <c r="S773" t="inlineStr">
+        <is>
+          <t>geblokkeerd — niet te controleren</t>
+        </is>
+      </c>
     </row>
     <row r="774">
       <c r="A774" s="4" t="n">
@@ -36965,6 +38681,11 @@
           <t>Wikidata: klopt</t>
         </is>
       </c>
+      <c r="S780" t="inlineStr">
+        <is>
+          <t>onbereikbaar</t>
+        </is>
+      </c>
     </row>
     <row r="781" ht="25" customHeight="1">
       <c r="A781" s="4" t="n">
@@ -37454,6 +39175,11 @@
           <t>Wikidata: geen waarde</t>
         </is>
       </c>
+      <c r="S789" t="inlineStr">
+        <is>
+          <t>getal staat niet op de pagina</t>
+        </is>
+      </c>
     </row>
     <row r="790">
       <c r="A790" s="4" t="n">
@@ -37493,6 +39219,11 @@
         </is>
       </c>
       <c r="N790" s="4" t="n"/>
+      <c r="S790" t="inlineStr">
+        <is>
+          <t>geblokkeerd — niet te controleren</t>
+        </is>
+      </c>
     </row>
     <row r="791">
       <c r="A791" s="4" t="n">
@@ -37895,6 +39626,11 @@
         </is>
       </c>
       <c r="N799" s="4" t="n"/>
+      <c r="S799" t="inlineStr">
+        <is>
+          <t>geblokkeerd — niet te controleren</t>
+        </is>
+      </c>
     </row>
     <row r="800">
       <c r="A800" s="4" t="n">
@@ -37934,6 +39670,11 @@
         </is>
       </c>
       <c r="N800" s="4" t="n"/>
+      <c r="S800" t="inlineStr">
+        <is>
+          <t>getal staat niet op de pagina</t>
+        </is>
+      </c>
     </row>
     <row r="801" ht="25" customHeight="1">
       <c r="A801" s="4" t="n">
@@ -37978,6 +39719,11 @@
           <t>Wikidata: klopt</t>
         </is>
       </c>
+      <c r="S801" t="inlineStr">
+        <is>
+          <t>getal staat niet op de pagina</t>
+        </is>
+      </c>
     </row>
     <row r="802">
       <c r="A802" s="4" t="n">
@@ -38071,6 +39817,11 @@
         </is>
       </c>
       <c r="N803" s="4" t="n"/>
+      <c r="S803" t="inlineStr">
+        <is>
+          <t>getal staat niet op de pagina</t>
+        </is>
+      </c>
     </row>
     <row r="804">
       <c r="A804" s="4" t="n">
@@ -38626,6 +40377,11 @@
         </is>
       </c>
       <c r="N814" s="4" t="n"/>
+      <c r="S814" t="inlineStr">
+        <is>
+          <t>geen adres, alleen een omschrijving</t>
+        </is>
+      </c>
     </row>
     <row r="815">
       <c r="A815" s="4" t="n">
@@ -38718,6 +40474,11 @@
         </is>
       </c>
       <c r="N816" s="4" t="n"/>
+      <c r="S816" t="inlineStr">
+        <is>
+          <t>getal staat niet op de pagina</t>
+        </is>
+      </c>
     </row>
     <row r="817">
       <c r="A817" s="4" t="n">
@@ -39227,6 +40988,11 @@
         </is>
       </c>
       <c r="N827" s="4" t="n"/>
+      <c r="S827" t="inlineStr">
+        <is>
+          <t>getal staat niet op de pagina</t>
+        </is>
+      </c>
     </row>
     <row r="828" ht="25" customHeight="1">
       <c r="A828" s="4" t="n">
@@ -39459,6 +41225,11 @@
           <t>Wikidata: klopt</t>
         </is>
       </c>
+      <c r="S832" t="inlineStr">
+        <is>
+          <t>geblokkeerd — niet te controleren</t>
+        </is>
+      </c>
     </row>
     <row r="833">
       <c r="A833" s="4" t="n">
@@ -39660,6 +41431,11 @@
           <t>Wikidata: geen waarde</t>
         </is>
       </c>
+      <c r="S836" t="inlineStr">
+        <is>
+          <t>geblokkeerd — niet te controleren</t>
+        </is>
+      </c>
     </row>
     <row r="837">
       <c r="A837" s="4" t="n">
@@ -40032,6 +41808,11 @@
           <t>geen EN-vertaling</t>
         </is>
       </c>
+      <c r="S843" t="inlineStr">
+        <is>
+          <t>getal gezien op de pagina</t>
+        </is>
+      </c>
     </row>
     <row r="844">
       <c r="A844" s="4" t="n">
@@ -40075,6 +41856,11 @@
           <t>Wikidata: geen waarde</t>
         </is>
       </c>
+      <c r="S844" t="inlineStr">
+        <is>
+          <t>DODE LINK</t>
+        </is>
+      </c>
     </row>
     <row r="845" ht="25" customHeight="1">
       <c r="A845" s="4" t="n">
@@ -40119,6 +41905,11 @@
           <t>Wikidata: geen waarde</t>
         </is>
       </c>
+      <c r="S845" t="inlineStr">
+        <is>
+          <t>geblokkeerd — niet te controleren</t>
+        </is>
+      </c>
     </row>
     <row r="846">
       <c r="A846" s="4" t="n">
@@ -40161,6 +41952,11 @@
       <c r="Q846" t="inlineStr">
         <is>
           <t>Wikidata: klopt</t>
+        </is>
+      </c>
+      <c r="S846" t="inlineStr">
+        <is>
+          <t>geblokkeerd — niet te controleren</t>
         </is>
       </c>
     </row>
@@ -41513,6 +43309,11 @@
         </is>
       </c>
       <c r="N874" s="4" t="n"/>
+      <c r="S874" t="inlineStr">
+        <is>
+          <t>getal staat niet op de pagina</t>
+        </is>
+      </c>
     </row>
     <row r="875">
       <c r="A875" s="4" t="n">
@@ -42169,6 +43970,11 @@
         </is>
       </c>
       <c r="N887" s="4" t="n"/>
+      <c r="S887" t="inlineStr">
+        <is>
+          <t>geblokkeerd — niet te controleren</t>
+        </is>
+      </c>
     </row>
     <row r="888">
       <c r="A888" s="4" t="n">
@@ -42208,6 +44014,11 @@
         </is>
       </c>
       <c r="N888" s="4" t="n"/>
+      <c r="S888" t="inlineStr">
+        <is>
+          <t>geblokkeerd — niet te controleren</t>
+        </is>
+      </c>
     </row>
     <row r="889">
       <c r="A889" s="4" t="n">
@@ -42247,6 +44058,11 @@
         </is>
       </c>
       <c r="N889" s="4" t="n"/>
+      <c r="S889" t="inlineStr">
+        <is>
+          <t>geblokkeerd — niet te controleren</t>
+        </is>
+      </c>
     </row>
     <row r="890">
       <c r="A890" s="4" t="n">
@@ -42286,6 +44102,11 @@
         </is>
       </c>
       <c r="N890" s="4" t="n"/>
+      <c r="S890" t="inlineStr">
+        <is>
+          <t>geblokkeerd — niet te controleren</t>
+        </is>
+      </c>
     </row>
     <row r="891">
       <c r="A891" s="4" t="n">
@@ -42325,6 +44146,11 @@
         </is>
       </c>
       <c r="N891" s="4" t="n"/>
+      <c r="S891" t="inlineStr">
+        <is>
+          <t>geblokkeerd — niet te controleren</t>
+        </is>
+      </c>
     </row>
     <row r="892">
       <c r="A892" s="4" t="n">
@@ -42761,6 +44587,11 @@
         </is>
       </c>
       <c r="N901" s="4" t="n"/>
+      <c r="S901" t="inlineStr">
+        <is>
+          <t>geblokkeerd — niet te controleren</t>
+        </is>
+      </c>
     </row>
     <row r="902">
       <c r="A902" s="4" t="n">
@@ -42800,6 +44631,11 @@
         </is>
       </c>
       <c r="N902" s="4" t="n"/>
+      <c r="S902" t="inlineStr">
+        <is>
+          <t>geen adres, alleen een omschrijving</t>
+        </is>
+      </c>
     </row>
     <row r="903">
       <c r="A903" s="4" t="n">
@@ -44373,6 +46209,11 @@
         </is>
       </c>
       <c r="N932" s="4" t="n"/>
+      <c r="S932" t="inlineStr">
+        <is>
+          <t>geblokkeerd — niet te controleren</t>
+        </is>
+      </c>
     </row>
     <row r="933" ht="25" customHeight="1">
       <c r="A933" s="4" t="n">
@@ -45075,6 +46916,11 @@
           <t>Wikidata: klopt</t>
         </is>
       </c>
+      <c r="S947" t="inlineStr">
+        <is>
+          <t>geblokkeerd — niet te controleren</t>
+        </is>
+      </c>
     </row>
     <row r="948" ht="25" customHeight="1">
       <c r="A948" s="4" t="n">
@@ -45118,6 +46964,11 @@
           <t>Wikidata: klopt</t>
         </is>
       </c>
+      <c r="S948" t="inlineStr">
+        <is>
+          <t>geblokkeerd — niet te controleren</t>
+        </is>
+      </c>
     </row>
     <row r="949">
       <c r="A949" s="4" t="n">
@@ -45161,6 +47012,11 @@
           <t>Wikidata: klopt</t>
         </is>
       </c>
+      <c r="S949" t="inlineStr">
+        <is>
+          <t>geblokkeerd — niet te controleren</t>
+        </is>
+      </c>
     </row>
     <row r="950" ht="25" customHeight="1">
       <c r="A950" s="4" t="n">
@@ -45200,6 +47056,11 @@
         </is>
       </c>
       <c r="N950" s="4" t="n"/>
+      <c r="S950" t="inlineStr">
+        <is>
+          <t>getal staat niet op de pagina</t>
+        </is>
+      </c>
     </row>
     <row r="951" ht="25" customHeight="1">
       <c r="A951" s="4" t="n">
@@ -45239,6 +47100,11 @@
         </is>
       </c>
       <c r="N951" s="4" t="n"/>
+      <c r="S951" t="inlineStr">
+        <is>
+          <t>geblokkeerd — niet te controleren</t>
+        </is>
+      </c>
     </row>
     <row r="952">
       <c r="A952" s="4" t="n">
@@ -45277,6 +47143,11 @@
           <t>geen EN-vertaling</t>
         </is>
       </c>
+      <c r="S952" t="inlineStr">
+        <is>
+          <t>geblokkeerd — niet te controleren</t>
+        </is>
+      </c>
     </row>
     <row r="953">
       <c r="A953" s="4" t="n">
@@ -45368,6 +47239,11 @@
           <t>geen EN-vertaling</t>
         </is>
       </c>
+      <c r="S954" t="inlineStr">
+        <is>
+          <t>DODE LINK</t>
+        </is>
+      </c>
     </row>
     <row r="955" ht="25" customHeight="1">
       <c r="A955" s="4" t="n">
@@ -45411,6 +47287,11 @@
           <t>geen EN-vertaling</t>
         </is>
       </c>
+      <c r="S955" t="inlineStr">
+        <is>
+          <t>geblokkeerd — niet te controleren</t>
+        </is>
+      </c>
     </row>
     <row r="956">
       <c r="A956" s="4" t="n">
@@ -45447,6 +47328,11 @@
       <c r="N956" s="4" t="inlineStr">
         <is>
           <t>geen EN-vertaling</t>
+        </is>
+      </c>
+      <c r="S956" t="inlineStr">
+        <is>
+          <t>DODE LINK</t>
         </is>
       </c>
     </row>
@@ -45920,6 +47806,11 @@
         </is>
       </c>
       <c r="N965" s="4" t="n"/>
+      <c r="S965" t="inlineStr">
+        <is>
+          <t>DODE LINK</t>
+        </is>
+      </c>
     </row>
     <row r="966" ht="25" customHeight="1">
       <c r="A966" s="4" t="n">
@@ -45959,6 +47850,11 @@
         </is>
       </c>
       <c r="N966" s="4" t="n"/>
+      <c r="S966" t="inlineStr">
+        <is>
+          <t>getal staat niet op de pagina</t>
+        </is>
+      </c>
     </row>
     <row r="967">
       <c r="A967" s="4" t="n">
@@ -46369,6 +48265,11 @@
           <t>Wikidata: geen waarde</t>
         </is>
       </c>
+      <c r="S974" t="inlineStr">
+        <is>
+          <t>getal staat niet op de pagina</t>
+        </is>
+      </c>
     </row>
     <row r="975">
       <c r="A975" s="4" t="n">
@@ -46485,6 +48386,11 @@
           <t>geen EN-vertaling</t>
         </is>
       </c>
+      <c r="S977" t="inlineStr">
+        <is>
+          <t>geblokkeerd — niet te controleren</t>
+        </is>
+      </c>
     </row>
     <row r="978">
       <c r="A978" s="4" t="n">
@@ -46523,6 +48429,11 @@
           <t>geen EN-vertaling</t>
         </is>
       </c>
+      <c r="S978" t="inlineStr">
+        <is>
+          <t>geblokkeerd — niet te controleren</t>
+        </is>
+      </c>
     </row>
     <row r="979">
       <c r="A979" s="4" t="n">
@@ -46562,6 +48473,11 @@
         </is>
       </c>
       <c r="N979" s="4" t="n"/>
+      <c r="S979" t="inlineStr">
+        <is>
+          <t>DODE LINK</t>
+        </is>
+      </c>
     </row>
     <row r="980">
       <c r="A980" s="4" t="n">
@@ -46821,6 +48737,11 @@
         </is>
       </c>
       <c r="N984" s="4" t="n"/>
+      <c r="S984" t="inlineStr">
+        <is>
+          <t>geblokkeerd — niet te controleren</t>
+        </is>
+      </c>
     </row>
     <row r="985">
       <c r="A985" s="4" t="n">
@@ -46971,6 +48892,11 @@
           <t>geen EN-vertaling</t>
         </is>
       </c>
+      <c r="S987" t="inlineStr">
+        <is>
+          <t>geblokkeerd — niet te controleren</t>
+        </is>
+      </c>
     </row>
     <row r="988" ht="25" customHeight="1">
       <c r="A988" s="4" t="n">
@@ -47009,6 +48935,11 @@
           <t>geen EN-vertaling</t>
         </is>
       </c>
+      <c r="S988" t="inlineStr">
+        <is>
+          <t>geblokkeerd — niet te controleren</t>
+        </is>
+      </c>
     </row>
     <row r="989" ht="25" customHeight="1">
       <c r="A989" s="4" t="n">
@@ -47102,6 +49033,11 @@
         </is>
       </c>
       <c r="N990" s="4" t="n"/>
+      <c r="S990" t="inlineStr">
+        <is>
+          <t>geblokkeerd — niet te controleren</t>
+        </is>
+      </c>
     </row>
     <row r="991" ht="25" customHeight="1">
       <c r="A991" s="4" t="n">
@@ -47140,6 +49076,11 @@
           <t>geen EN-vertaling</t>
         </is>
       </c>
+      <c r="S991" t="inlineStr">
+        <is>
+          <t>getal staat niet op de pagina</t>
+        </is>
+      </c>
     </row>
     <row r="992">
       <c r="A992" s="4" t="n">
@@ -47217,6 +49158,11 @@
           <t>geen EN-vertaling</t>
         </is>
       </c>
+      <c r="S993" t="inlineStr">
+        <is>
+          <t>geblokkeerd — niet te controleren</t>
+        </is>
+      </c>
     </row>
     <row r="994">
       <c r="A994" s="4" t="n">
@@ -49069,6 +51015,11 @@
         </is>
       </c>
       <c r="N1029" s="4" t="n"/>
+      <c r="S1029" t="inlineStr">
+        <is>
+          <t>geblokkeerd — niet te controleren</t>
+        </is>
+      </c>
     </row>
     <row r="1030">
       <c r="A1030" s="4" t="n">
@@ -49507,6 +51458,11 @@
         </is>
       </c>
       <c r="N1038" s="4" t="n"/>
+      <c r="S1038" t="inlineStr">
+        <is>
+          <t>geen adres, alleen een omschrijving</t>
+        </is>
+      </c>
     </row>
     <row r="1039">
       <c r="A1039" s="4" t="n">
@@ -49545,6 +51501,11 @@
           <t>geen EN-vertaling</t>
         </is>
       </c>
+      <c r="S1039" t="inlineStr">
+        <is>
+          <t>geen adres, alleen een omschrijving</t>
+        </is>
+      </c>
     </row>
     <row r="1040">
       <c r="A1040" s="4" t="n">
@@ -49584,6 +51545,11 @@
         </is>
       </c>
       <c r="N1040" s="4" t="n"/>
+      <c r="S1040" t="inlineStr">
+        <is>
+          <t>DODE LINK</t>
+        </is>
+      </c>
     </row>
     <row r="1041">
       <c r="A1041" s="4" t="n">
@@ -49623,6 +51589,11 @@
         </is>
       </c>
       <c r="N1041" s="4" t="n"/>
+      <c r="S1041" t="inlineStr">
+        <is>
+          <t>getal staat niet op de pagina</t>
+        </is>
+      </c>
     </row>
     <row r="1042">
       <c r="A1042" s="4" t="n">
@@ -49662,6 +51633,11 @@
         </is>
       </c>
       <c r="N1042" s="4" t="n"/>
+      <c r="S1042" t="inlineStr">
+        <is>
+          <t>getal staat niet op de pagina</t>
+        </is>
+      </c>
     </row>
     <row r="1043">
       <c r="A1043" s="4" t="n">
@@ -49701,6 +51677,11 @@
         </is>
       </c>
       <c r="N1043" s="4" t="n"/>
+      <c r="S1043" t="inlineStr">
+        <is>
+          <t>getal staat niet op de pagina</t>
+        </is>
+      </c>
     </row>
     <row r="1044">
       <c r="A1044" s="4" t="n">
@@ -49740,6 +51721,11 @@
         </is>
       </c>
       <c r="N1044" s="4" t="n"/>
+      <c r="S1044" t="inlineStr">
+        <is>
+          <t>getal gezien op de pagina</t>
+        </is>
+      </c>
     </row>
     <row r="1045" ht="25" customHeight="1">
       <c r="A1045" s="4" t="n">
@@ -49778,6 +51764,11 @@
           <t>geen EN-vertaling</t>
         </is>
       </c>
+      <c r="S1045" t="inlineStr">
+        <is>
+          <t>getal staat niet op de pagina</t>
+        </is>
+      </c>
     </row>
     <row r="1046">
       <c r="A1046" s="4" t="n">
@@ -49816,6 +51807,11 @@
           <t>geen EN-vertaling</t>
         </is>
       </c>
+      <c r="S1046" t="inlineStr">
+        <is>
+          <t>getal staat niet op de pagina</t>
+        </is>
+      </c>
     </row>
     <row r="1047">
       <c r="A1047" s="4" t="n">
@@ -49854,6 +51850,11 @@
           <t>geen EN-vertaling</t>
         </is>
       </c>
+      <c r="S1047" t="inlineStr">
+        <is>
+          <t>getal staat niet op de pagina</t>
+        </is>
+      </c>
     </row>
     <row r="1048">
       <c r="A1048" s="4" t="n">
@@ -49892,6 +51893,11 @@
           <t>geen EN-vertaling</t>
         </is>
       </c>
+      <c r="S1048" t="inlineStr">
+        <is>
+          <t>getal staat niet op de pagina</t>
+        </is>
+      </c>
     </row>
     <row r="1049">
       <c r="A1049" s="4" t="n">
@@ -49930,6 +51936,11 @@
           <t>geen EN-vertaling</t>
         </is>
       </c>
+      <c r="S1049" t="inlineStr">
+        <is>
+          <t>getal staat niet op de pagina</t>
+        </is>
+      </c>
     </row>
     <row r="1050">
       <c r="A1050" s="4" t="n">
@@ -49968,6 +51979,11 @@
           <t>geen EN-vertaling</t>
         </is>
       </c>
+      <c r="S1050" t="inlineStr">
+        <is>
+          <t>getal staat niet op de pagina</t>
+        </is>
+      </c>
     </row>
     <row r="1051">
       <c r="A1051" s="4" t="n">
@@ -50006,6 +52022,11 @@
           <t>geen EN-vertaling</t>
         </is>
       </c>
+      <c r="S1051" t="inlineStr">
+        <is>
+          <t>getal staat niet op de pagina</t>
+        </is>
+      </c>
     </row>
     <row r="1052">
       <c r="A1052" s="4" t="n">
@@ -50099,6 +52120,11 @@
         </is>
       </c>
       <c r="N1053" s="4" t="n"/>
+      <c r="S1053" t="inlineStr">
+        <is>
+          <t>getal staat niet op de pagina</t>
+        </is>
+      </c>
     </row>
     <row r="1054">
       <c r="A1054" s="4" t="n">
@@ -50138,6 +52164,11 @@
         </is>
       </c>
       <c r="N1054" s="4" t="n"/>
+      <c r="S1054" t="inlineStr">
+        <is>
+          <t>geblokkeerd — niet te controleren</t>
+        </is>
+      </c>
     </row>
     <row r="1055">
       <c r="A1055" s="4" t="n">
@@ -50176,6 +52207,11 @@
           <t>geen EN-vertaling</t>
         </is>
       </c>
+      <c r="S1055" t="inlineStr">
+        <is>
+          <t>DODE LINK</t>
+        </is>
+      </c>
     </row>
     <row r="1056">
       <c r="A1056" s="4" t="n">
@@ -50214,6 +52250,11 @@
           <t>geen EN-vertaling</t>
         </is>
       </c>
+      <c r="S1056" t="inlineStr">
+        <is>
+          <t>DODE LINK</t>
+        </is>
+      </c>
     </row>
     <row r="1057">
       <c r="A1057" s="4" t="n">
@@ -50253,6 +52294,11 @@
         </is>
       </c>
       <c r="N1057" s="4" t="n"/>
+      <c r="S1057" t="inlineStr">
+        <is>
+          <t>getal staat niet op de pagina</t>
+        </is>
+      </c>
     </row>
     <row r="1058">
       <c r="A1058" s="4" t="n">
@@ -50292,6 +52338,11 @@
         </is>
       </c>
       <c r="N1058" s="4" t="n"/>
+      <c r="S1058" t="inlineStr">
+        <is>
+          <t>getal staat niet op de pagina</t>
+        </is>
+      </c>
     </row>
     <row r="1059">
       <c r="A1059" s="4" t="n">
@@ -50385,6 +52436,11 @@
         </is>
       </c>
       <c r="N1060" s="4" t="n"/>
+      <c r="S1060" t="inlineStr">
+        <is>
+          <t>getal staat niet op de pagina</t>
+        </is>
+      </c>
     </row>
     <row r="1061">
       <c r="A1061" s="4" t="n">
@@ -50424,6 +52480,11 @@
         </is>
       </c>
       <c r="N1061" s="4" t="n"/>
+      <c r="S1061" t="inlineStr">
+        <is>
+          <t>getal staat niet op de pagina</t>
+        </is>
+      </c>
     </row>
     <row r="1062">
       <c r="A1062" s="4" t="n">
@@ -50463,6 +52524,11 @@
         </is>
       </c>
       <c r="N1062" s="4" t="n"/>
+      <c r="S1062" t="inlineStr">
+        <is>
+          <t>DODE LINK</t>
+        </is>
+      </c>
     </row>
     <row r="1063" ht="25" customHeight="1">
       <c r="A1063" s="4" t="n">
@@ -50502,6 +52568,11 @@
         </is>
       </c>
       <c r="N1063" s="4" t="n"/>
+      <c r="S1063" t="inlineStr">
+        <is>
+          <t>geblokkeerd — niet te controleren</t>
+        </is>
+      </c>
     </row>
     <row r="1064" ht="25" customHeight="1">
       <c r="A1064" s="4" t="n">
@@ -50540,6 +52611,11 @@
           <t>geen EN-vertaling</t>
         </is>
       </c>
+      <c r="S1064" t="inlineStr">
+        <is>
+          <t>getal staat niet op de pagina</t>
+        </is>
+      </c>
     </row>
     <row r="1065" ht="25" customHeight="1">
       <c r="A1065" s="4" t="n">
@@ -50579,6 +52655,11 @@
         </is>
       </c>
       <c r="N1065" s="4" t="n"/>
+      <c r="S1065" t="inlineStr">
+        <is>
+          <t>getal staat niet op de pagina</t>
+        </is>
+      </c>
     </row>
     <row r="1066" ht="25" customHeight="1">
       <c r="A1066" s="4" t="n">
@@ -50618,6 +52699,11 @@
         </is>
       </c>
       <c r="N1066" s="4" t="n"/>
+      <c r="S1066" t="inlineStr">
+        <is>
+          <t>geblokkeerd — niet te controleren</t>
+        </is>
+      </c>
     </row>
     <row r="1067" ht="25" customHeight="1">
       <c r="A1067" s="4" t="n">
@@ -51138,6 +53224,11 @@
         </is>
       </c>
       <c r="N1077" s="4" t="n"/>
+      <c r="S1077" t="inlineStr">
+        <is>
+          <t>geblokkeerd — niet te controleren</t>
+        </is>
+      </c>
     </row>
     <row r="1078">
       <c r="A1078" s="4" t="n">
@@ -51760,6 +53851,11 @@
         </is>
       </c>
       <c r="N1091" s="4" t="n"/>
+      <c r="S1091" t="inlineStr">
+        <is>
+          <t>geblokkeerd — niet te controleren</t>
+        </is>
+      </c>
     </row>
     <row r="1092" ht="25" customHeight="1">
       <c r="A1092" s="4" t="n">
@@ -52173,6 +54269,11 @@
         </is>
       </c>
       <c r="N1100" s="4" t="n"/>
+      <c r="S1100" t="inlineStr">
+        <is>
+          <t>geblokkeerd — niet te controleren</t>
+        </is>
+      </c>
     </row>
     <row r="1101">
       <c r="A1101" s="4" t="n">
@@ -52449,6 +54550,11 @@
         </is>
       </c>
       <c r="N1106" s="4" t="n"/>
+      <c r="S1106" t="inlineStr">
+        <is>
+          <t>DODE LINK</t>
+        </is>
+      </c>
     </row>
     <row r="1107">
       <c r="A1107" s="4" t="n">
@@ -52488,6 +54594,11 @@
         </is>
       </c>
       <c r="N1107" s="4" t="n"/>
+      <c r="S1107" t="inlineStr">
+        <is>
+          <t>getal staat niet op de pagina</t>
+        </is>
+      </c>
     </row>
     <row r="1108">
       <c r="A1108" s="4" t="n">
@@ -54537,6 +56648,11 @@
           <t>Wikidata: geen waarde</t>
         </is>
       </c>
+      <c r="S1149" t="inlineStr">
+        <is>
+          <t>DODE LINK</t>
+        </is>
+      </c>
     </row>
     <row r="1150">
       <c r="A1150" s="4" t="n">
@@ -55713,6 +57829,11 @@
         </is>
       </c>
       <c r="N1172" s="4" t="n"/>
+      <c r="S1172" t="inlineStr">
+        <is>
+          <t>DODE LINK</t>
+        </is>
+      </c>
     </row>
     <row r="1173">
       <c r="A1173" s="4" t="n">
@@ -56105,6 +58226,11 @@
         </is>
       </c>
       <c r="N1180" s="4" t="n"/>
+      <c r="S1180" t="inlineStr">
+        <is>
+          <t>DODE LINK</t>
+        </is>
+      </c>
     </row>
     <row r="1181" ht="25" customHeight="1">
       <c r="A1181" s="4" t="n">
@@ -56938,6 +59064,11 @@
         </is>
       </c>
       <c r="N1198" s="4" t="n"/>
+      <c r="S1198" t="inlineStr">
+        <is>
+          <t>DODE LINK</t>
+        </is>
+      </c>
     </row>
     <row r="1199" ht="25" customHeight="1">
       <c r="A1199" s="4" t="n">
@@ -57820,6 +59951,11 @@
         </is>
       </c>
       <c r="N1217" s="4" t="n"/>
+      <c r="S1217" t="inlineStr">
+        <is>
+          <t>getal gezien op de pagina</t>
+        </is>
+      </c>
     </row>
     <row r="1218" ht="25" customHeight="1">
       <c r="A1218" s="4" t="n">
@@ -60029,6 +62165,11 @@
         </is>
       </c>
       <c r="N1266" s="4" t="n"/>
+      <c r="S1266" t="inlineStr">
+        <is>
+          <t>DODE LINK</t>
+        </is>
+      </c>
     </row>
     <row r="1267">
       <c r="A1267" s="4" t="n">
@@ -60068,6 +62209,11 @@
         </is>
       </c>
       <c r="N1267" s="4" t="n"/>
+      <c r="S1267" t="inlineStr">
+        <is>
+          <t>geblokkeerd — niet te controleren</t>
+        </is>
+      </c>
     </row>
     <row r="1268">
       <c r="A1268" s="4" t="n">
@@ -60107,6 +62253,11 @@
         </is>
       </c>
       <c r="N1268" s="4" t="n"/>
+      <c r="S1268" t="inlineStr">
+        <is>
+          <t>getal staat niet op de pagina</t>
+        </is>
+      </c>
     </row>
     <row r="1269" ht="25" customHeight="1">
       <c r="A1269" s="4" t="n">
@@ -60146,6 +62297,11 @@
         </is>
       </c>
       <c r="N1269" s="4" t="n"/>
+      <c r="S1269" t="inlineStr">
+        <is>
+          <t>getal staat niet op de pagina</t>
+        </is>
+      </c>
     </row>
     <row r="1270" ht="25" customHeight="1">
       <c r="A1270" s="4" t="n">
@@ -60185,6 +62341,11 @@
         </is>
       </c>
       <c r="N1270" s="4" t="n"/>
+      <c r="S1270" t="inlineStr">
+        <is>
+          <t>bevestigd</t>
+        </is>
+      </c>
     </row>
     <row r="1271">
       <c r="A1271" s="4" t="n">
@@ -60224,6 +62385,11 @@
         </is>
       </c>
       <c r="N1271" s="4" t="n"/>
+      <c r="S1271" t="inlineStr">
+        <is>
+          <t>DODE LINK</t>
+        </is>
+      </c>
     </row>
     <row r="1272" ht="25" customHeight="1">
       <c r="A1272" s="4" t="n">
@@ -60263,6 +62429,11 @@
         </is>
       </c>
       <c r="N1272" s="4" t="n"/>
+      <c r="S1272" t="inlineStr">
+        <is>
+          <t>bevestigd</t>
+        </is>
+      </c>
     </row>
     <row r="1273">
       <c r="A1273" s="4" t="n">
@@ -60411,6 +62582,11 @@
         </is>
       </c>
       <c r="N1275" s="4" t="n"/>
+      <c r="S1275" t="inlineStr">
+        <is>
+          <t>getal staat niet op de pagina</t>
+        </is>
+      </c>
     </row>
     <row r="1276">
       <c r="A1276" s="4" t="n">
@@ -60450,6 +62626,11 @@
         </is>
       </c>
       <c r="N1276" s="4" t="n"/>
+      <c r="S1276" t="inlineStr">
+        <is>
+          <t>getal staat niet op de pagina</t>
+        </is>
+      </c>
     </row>
     <row r="1277" ht="25" customHeight="1">
       <c r="A1277" s="4" t="n">
@@ -60690,6 +62871,11 @@
         </is>
       </c>
       <c r="N1281" s="4" t="n"/>
+      <c r="S1281" t="inlineStr">
+        <is>
+          <t>DODE LINK</t>
+        </is>
+      </c>
     </row>
     <row r="1282" ht="25" customHeight="1">
       <c r="A1282" s="4" t="n">
@@ -60846,6 +63032,11 @@
         </is>
       </c>
       <c r="N1285" s="4" t="n"/>
+      <c r="S1285" t="inlineStr">
+        <is>
+          <t>getal staat niet op de pagina</t>
+        </is>
+      </c>
     </row>
     <row r="1286">
       <c r="A1286" s="4" t="n">
@@ -60885,6 +63076,11 @@
         </is>
       </c>
       <c r="N1286" s="4" t="n"/>
+      <c r="S1286" t="inlineStr">
+        <is>
+          <t>geblokkeerd — niet te controleren</t>
+        </is>
+      </c>
     </row>
     <row r="1287">
       <c r="A1287" s="4" t="n">
@@ -60924,6 +63120,11 @@
         </is>
       </c>
       <c r="N1287" s="4" t="n"/>
+      <c r="S1287" t="inlineStr">
+        <is>
+          <t>getal staat niet op de pagina</t>
+        </is>
+      </c>
     </row>
     <row r="1288">
       <c r="A1288" s="4" t="n">
@@ -60963,6 +63164,11 @@
         </is>
       </c>
       <c r="N1288" s="4" t="n"/>
+      <c r="S1288" t="inlineStr">
+        <is>
+          <t>bevestigd</t>
+        </is>
+      </c>
     </row>
     <row r="1289">
       <c r="A1289" s="4" t="n">
@@ -61506,6 +63712,11 @@
         </is>
       </c>
       <c r="N1299" s="4" t="n"/>
+      <c r="S1299" t="inlineStr">
+        <is>
+          <t>bevestigd</t>
+        </is>
+      </c>
     </row>
     <row r="1300">
       <c r="A1300" s="4" t="n">
@@ -61545,6 +63756,11 @@
         </is>
       </c>
       <c r="N1300" s="4" t="n"/>
+      <c r="S1300" t="inlineStr">
+        <is>
+          <t>onbereikbaar</t>
+        </is>
+      </c>
     </row>
     <row r="1301">
       <c r="A1301" s="4" t="n">
@@ -61584,6 +63800,11 @@
         </is>
       </c>
       <c r="N1301" s="4" t="n"/>
+      <c r="S1301" t="inlineStr">
+        <is>
+          <t>bevestigd</t>
+        </is>
+      </c>
     </row>
     <row r="1302">
       <c r="A1302" s="4" t="n">
@@ -62921,6 +65142,11 @@
         </is>
       </c>
       <c r="N1327" s="4" t="n"/>
+      <c r="S1327" t="inlineStr">
+        <is>
+          <t>getal gezien op de pagina</t>
+        </is>
+      </c>
     </row>
     <row r="1328" ht="25" customHeight="1">
       <c r="A1328" s="4" t="n">
@@ -63101,6 +65327,11 @@
         </is>
       </c>
       <c r="N1331" s="4" t="n"/>
+      <c r="S1331" t="inlineStr">
+        <is>
+          <t>getal gezien op de pagina</t>
+        </is>
+      </c>
     </row>
     <row r="1332" ht="25" customHeight="1">
       <c r="A1332" s="4" t="n">
@@ -63291,6 +65522,11 @@
         </is>
       </c>
       <c r="N1336" s="4" t="n"/>
+      <c r="S1336" t="inlineStr">
+        <is>
+          <t>bevestigd</t>
+        </is>
+      </c>
     </row>
     <row r="1337">
       <c r="A1337" s="4" t="n">
@@ -63408,6 +65644,11 @@
         </is>
       </c>
       <c r="N1339" s="4" t="n"/>
+      <c r="S1339" t="inlineStr">
+        <is>
+          <t>getal staat niet op de pagina</t>
+        </is>
+      </c>
     </row>
     <row r="1340">
       <c r="A1340" s="4" t="n">
@@ -63447,6 +65688,11 @@
         </is>
       </c>
       <c r="N1340" s="4" t="n"/>
+      <c r="S1340" t="inlineStr">
+        <is>
+          <t>geblokkeerd — niet te controleren</t>
+        </is>
+      </c>
     </row>
     <row r="1341">
       <c r="A1341" s="4" t="n">
@@ -63918,6 +66164,11 @@
         </is>
       </c>
       <c r="N1350" s="4" t="n"/>
+      <c r="S1350" t="inlineStr">
+        <is>
+          <t>getal staat niet op de pagina</t>
+        </is>
+      </c>
     </row>
     <row r="1351">
       <c r="A1351" s="4" t="n">
@@ -64133,6 +66384,11 @@
         </is>
       </c>
       <c r="N1355" s="4" t="n"/>
+      <c r="S1355" t="inlineStr">
+        <is>
+          <t>getal staat niet op de pagina</t>
+        </is>
+      </c>
     </row>
     <row r="1356" ht="25" customHeight="1">
       <c r="A1356" s="4" t="n">
@@ -64172,6 +66428,11 @@
         </is>
       </c>
       <c r="N1356" s="4" t="n"/>
+      <c r="S1356" t="inlineStr">
+        <is>
+          <t>getal staat niet op de pagina</t>
+        </is>
+      </c>
     </row>
     <row r="1357">
       <c r="A1357" s="4" t="n">
@@ -64265,6 +66526,11 @@
         </is>
       </c>
       <c r="N1358" s="4" t="n"/>
+      <c r="S1358" t="inlineStr">
+        <is>
+          <t>geblokkeerd — niet te controleren</t>
+        </is>
+      </c>
     </row>
     <row r="1359" ht="25" customHeight="1">
       <c r="A1359" s="4" t="n">
@@ -64304,6 +66570,11 @@
         </is>
       </c>
       <c r="N1359" s="4" t="n"/>
+      <c r="S1359" t="inlineStr">
+        <is>
+          <t>getal staat niet op de pagina</t>
+        </is>
+      </c>
     </row>
     <row r="1360">
       <c r="A1360" s="4" t="n">
@@ -64499,6 +66770,11 @@
         </is>
       </c>
       <c r="N1364" s="4" t="n"/>
+      <c r="S1364" t="inlineStr">
+        <is>
+          <t>getal staat niet op de pagina</t>
+        </is>
+      </c>
     </row>
     <row r="1365">
       <c r="A1365" s="4" t="n">
@@ -64537,6 +66813,11 @@
           <t>geen EN-vertaling</t>
         </is>
       </c>
+      <c r="S1365" t="inlineStr">
+        <is>
+          <t>getal staat niet op de pagina</t>
+        </is>
+      </c>
     </row>
     <row r="1366">
       <c r="A1366" s="4" t="n">
@@ -64625,6 +66906,11 @@
         </is>
       </c>
       <c r="N1367" s="4" t="n"/>
+      <c r="S1367" t="inlineStr">
+        <is>
+          <t>getal staat niet op de pagina</t>
+        </is>
+      </c>
     </row>
     <row r="1368">
       <c r="A1368" s="4" t="n">
@@ -64831,6 +67117,11 @@
         </is>
       </c>
       <c r="N1371" s="4" t="n"/>
+      <c r="S1371" t="inlineStr">
+        <is>
+          <t>getal staat niet op de pagina</t>
+        </is>
+      </c>
     </row>
     <row r="1372">
       <c r="A1372" s="4" t="n">
@@ -64870,6 +67161,11 @@
         </is>
       </c>
       <c r="N1372" s="4" t="n"/>
+      <c r="S1372" t="inlineStr">
+        <is>
+          <t>getal staat niet op de pagina</t>
+        </is>
+      </c>
     </row>
     <row r="1373">
       <c r="A1373" s="4" t="n">
@@ -64963,6 +67259,11 @@
         </is>
       </c>
       <c r="N1374" s="4" t="n"/>
+      <c r="S1374" t="inlineStr">
+        <is>
+          <t>bevestigd</t>
+        </is>
+      </c>
     </row>
     <row r="1375">
       <c r="A1375" s="4" t="n">
@@ -65006,6 +67307,11 @@
           <t>Wikidata: geen waarde</t>
         </is>
       </c>
+      <c r="S1375" t="inlineStr">
+        <is>
+          <t>getal staat niet op de pagina</t>
+        </is>
+      </c>
     </row>
     <row r="1376">
       <c r="A1376" s="4" t="n">
@@ -65103,6 +67409,11 @@
           <t>geen EN-vertaling</t>
         </is>
       </c>
+      <c r="S1377" t="inlineStr">
+        <is>
+          <t>getal staat niet op de pagina</t>
+        </is>
+      </c>
     </row>
     <row r="1378">
       <c r="A1378" s="4" t="n">
@@ -65141,6 +67452,11 @@
           <t>geen EN-vertaling</t>
         </is>
       </c>
+      <c r="S1378" t="inlineStr">
+        <is>
+          <t>getal staat niet op de pagina</t>
+        </is>
+      </c>
     </row>
     <row r="1379">
       <c r="A1379" s="4" t="n">
@@ -65287,6 +67603,11 @@
         </is>
       </c>
       <c r="N1381" s="4" t="n"/>
+      <c r="S1381" t="inlineStr">
+        <is>
+          <t>DODE LINK</t>
+        </is>
+      </c>
     </row>
     <row r="1382">
       <c r="A1382" s="4" t="n">
@@ -65533,6 +67854,11 @@
         </is>
       </c>
       <c r="N1386" s="4" t="n"/>
+      <c r="S1386" t="inlineStr">
+        <is>
+          <t>getal staat niet op de pagina</t>
+        </is>
+      </c>
     </row>
     <row r="1387">
       <c r="A1387" s="4" t="n">
@@ -65572,6 +67898,11 @@
         </is>
       </c>
       <c r="N1387" s="4" t="n"/>
+      <c r="S1387" t="inlineStr">
+        <is>
+          <t>getal gezien op de pagina</t>
+        </is>
+      </c>
     </row>
     <row r="1388" ht="25" customHeight="1">
       <c r="A1388" s="4" t="n">
@@ -65610,6 +67941,11 @@
           <t>geen EN-vertaling</t>
         </is>
       </c>
+      <c r="S1388" t="inlineStr">
+        <is>
+          <t>getal staat niet op de pagina</t>
+        </is>
+      </c>
     </row>
     <row r="1389">
       <c r="A1389" s="4" t="n">
@@ -65649,6 +67985,11 @@
         </is>
       </c>
       <c r="N1389" s="4" t="n"/>
+      <c r="S1389" t="inlineStr">
+        <is>
+          <t>getal staat niet op de pagina</t>
+        </is>
+      </c>
     </row>
     <row r="1390">
       <c r="A1390" s="4" t="n">
@@ -65750,6 +68091,11 @@
           <t>Wikidata: klopt</t>
         </is>
       </c>
+      <c r="S1391" t="inlineStr">
+        <is>
+          <t>getal staat niet op de pagina</t>
+        </is>
+      </c>
     </row>
     <row r="1392">
       <c r="A1392" s="4" t="n">
@@ -65896,6 +68242,11 @@
         </is>
       </c>
       <c r="N1394" s="4" t="n"/>
+      <c r="S1394" t="inlineStr">
+        <is>
+          <t>bevestigd</t>
+        </is>
+      </c>
     </row>
     <row r="1395" ht="25" customHeight="1">
       <c r="A1395" s="4" t="n">
@@ -65935,6 +68286,11 @@
         </is>
       </c>
       <c r="N1395" s="4" t="n"/>
+      <c r="S1395" t="inlineStr">
+        <is>
+          <t>geblokkeerd — niet te controleren</t>
+        </is>
+      </c>
     </row>
     <row r="1396">
       <c r="A1396" s="4" t="n">
@@ -66092,6 +68448,11 @@
         </is>
       </c>
       <c r="N1398" s="4" t="n"/>
+      <c r="S1398" t="inlineStr">
+        <is>
+          <t>geblokkeerd — niet te controleren</t>
+        </is>
+      </c>
     </row>
     <row r="1399">
       <c r="A1399" s="4" t="n">
@@ -66131,6 +68492,11 @@
         </is>
       </c>
       <c r="N1399" s="4" t="n"/>
+      <c r="S1399" t="inlineStr">
+        <is>
+          <t>geblokkeerd — niet te controleren</t>
+        </is>
+      </c>
     </row>
     <row r="1400">
       <c r="A1400" s="4" t="n">
@@ -66224,6 +68590,11 @@
         </is>
       </c>
       <c r="N1401" s="4" t="n"/>
+      <c r="S1401" t="inlineStr">
+        <is>
+          <t>geblokkeerd — niet te controleren</t>
+        </is>
+      </c>
     </row>
     <row r="1402">
       <c r="A1402" s="4" t="n">
@@ -66405,6 +68776,11 @@
         </is>
       </c>
       <c r="N1405" s="4" t="n"/>
+      <c r="S1405" t="inlineStr">
+        <is>
+          <t>DODE LINK</t>
+        </is>
+      </c>
     </row>
     <row r="1406">
       <c r="A1406" s="4" t="n">
@@ -66443,6 +68819,11 @@
           <t>geen EN-vertaling</t>
         </is>
       </c>
+      <c r="S1406" t="inlineStr">
+        <is>
+          <t>bevestigd</t>
+        </is>
+      </c>
     </row>
     <row r="1407" ht="25" customHeight="1">
       <c r="A1407" s="4" t="n">
@@ -66482,6 +68863,11 @@
         </is>
       </c>
       <c r="N1407" s="4" t="n"/>
+      <c r="S1407" t="inlineStr">
+        <is>
+          <t>bevestigd</t>
+        </is>
+      </c>
     </row>
     <row r="1408">
       <c r="A1408" s="4" t="n">
@@ -66520,6 +68906,11 @@
           <t>geen EN-vertaling</t>
         </is>
       </c>
+      <c r="S1408" t="inlineStr">
+        <is>
+          <t>DODE LINK</t>
+        </is>
+      </c>
     </row>
     <row r="1409">
       <c r="A1409" s="4" t="n">
@@ -67227,6 +69618,11 @@
         </is>
       </c>
       <c r="N1422" s="4" t="n"/>
+      <c r="S1422" t="inlineStr">
+        <is>
+          <t>DODE LINK</t>
+        </is>
+      </c>
     </row>
     <row r="1423" ht="25" customHeight="1">
       <c r="A1423" s="4" t="n">
@@ -67320,6 +69716,11 @@
         </is>
       </c>
       <c r="N1424" s="4" t="n"/>
+      <c r="S1424" t="inlineStr">
+        <is>
+          <t>getal staat niet op de pagina</t>
+        </is>
+      </c>
     </row>
     <row r="1425" ht="25" customHeight="1">
       <c r="A1425" s="4" t="n">
@@ -67413,6 +69814,11 @@
         </is>
       </c>
       <c r="N1426" s="4" t="n"/>
+      <c r="S1426" t="inlineStr">
+        <is>
+          <t>getal gezien op de pagina</t>
+        </is>
+      </c>
     </row>
     <row r="1427">
       <c r="A1427" s="4" t="n">
@@ -67452,6 +69858,11 @@
         </is>
       </c>
       <c r="N1427" s="4" t="n"/>
+      <c r="S1427" t="inlineStr">
+        <is>
+          <t>DODE LINK</t>
+        </is>
+      </c>
     </row>
     <row r="1428">
       <c r="A1428" s="4" t="n">
@@ -67491,6 +69902,11 @@
         </is>
       </c>
       <c r="N1428" s="4" t="n"/>
+      <c r="S1428" t="inlineStr">
+        <is>
+          <t>DODE LINK</t>
+        </is>
+      </c>
     </row>
     <row r="1429">
       <c r="A1429" s="4" t="n">
@@ -67584,6 +70000,11 @@
         </is>
       </c>
       <c r="N1430" s="4" t="n"/>
+      <c r="S1430" t="inlineStr">
+        <is>
+          <t>getal staat niet op de pagina</t>
+        </is>
+      </c>
     </row>
     <row r="1431">
       <c r="A1431" s="4" t="n">
@@ -67623,6 +70044,11 @@
         </is>
       </c>
       <c r="N1431" s="4" t="n"/>
+      <c r="S1431" t="inlineStr">
+        <is>
+          <t>geen adres, alleen een omschrijving</t>
+        </is>
+      </c>
     </row>
     <row r="1432">
       <c r="A1432" s="4" t="n">
@@ -68122,6 +70548,11 @@
         </is>
       </c>
       <c r="N1441" s="4" t="n"/>
+      <c r="S1441" t="inlineStr">
+        <is>
+          <t>geen adres, alleen een omschrijving</t>
+        </is>
+      </c>
     </row>
     <row r="1442">
       <c r="A1442" s="4" t="n">
@@ -68215,6 +70646,11 @@
         </is>
       </c>
       <c r="N1443" s="4" t="n"/>
+      <c r="S1443" t="inlineStr">
+        <is>
+          <t>geblokkeerd — niet te controleren</t>
+        </is>
+      </c>
     </row>
     <row r="1444">
       <c r="A1444" s="4" t="n">
@@ -68254,6 +70690,11 @@
         </is>
       </c>
       <c r="N1444" s="4" t="n"/>
+      <c r="S1444" t="inlineStr">
+        <is>
+          <t>onbereikbaar</t>
+        </is>
+      </c>
     </row>
     <row r="1445" ht="25" customHeight="1">
       <c r="A1445" s="4" t="n">
@@ -68293,6 +70734,11 @@
         </is>
       </c>
       <c r="N1445" s="4" t="n"/>
+      <c r="S1445" t="inlineStr">
+        <is>
+          <t>geblokkeerd — niet te controleren</t>
+        </is>
+      </c>
     </row>
     <row r="1446">
       <c r="A1446" s="4" t="n">
@@ -68332,6 +70778,11 @@
         </is>
       </c>
       <c r="N1446" s="4" t="n"/>
+      <c r="S1446" t="inlineStr">
+        <is>
+          <t>getal staat niet op de pagina</t>
+        </is>
+      </c>
     </row>
     <row r="1447" ht="25" customHeight="1">
       <c r="A1447" s="4" t="n">
@@ -68371,6 +70822,11 @@
         </is>
       </c>
       <c r="N1447" s="4" t="n"/>
+      <c r="S1447" t="inlineStr">
+        <is>
+          <t>getal staat niet op de pagina</t>
+        </is>
+      </c>
     </row>
     <row r="1448">
       <c r="A1448" s="4" t="n">
@@ -68410,6 +70866,11 @@
         </is>
       </c>
       <c r="N1448" s="4" t="n"/>
+      <c r="S1448" t="inlineStr">
+        <is>
+          <t>geblokkeerd — niet te controleren</t>
+        </is>
+      </c>
     </row>
     <row r="1449">
       <c r="A1449" s="4" t="n">
@@ -68449,6 +70910,11 @@
         </is>
       </c>
       <c r="N1449" s="4" t="n"/>
+      <c r="S1449" t="inlineStr">
+        <is>
+          <t>DODE LINK</t>
+        </is>
+      </c>
     </row>
     <row r="1450">
       <c r="A1450" s="4" t="n">
@@ -68544,6 +71010,11 @@
         </is>
       </c>
       <c r="N1451" s="4" t="n"/>
+      <c r="S1451" t="inlineStr">
+        <is>
+          <t>geblokkeerd — niet te controleren</t>
+        </is>
+      </c>
     </row>
     <row r="1452">
       <c r="A1452" s="4" t="n">
@@ -68842,6 +71313,11 @@
         </is>
       </c>
       <c r="N1457" s="4" t="n"/>
+      <c r="S1457" t="inlineStr">
+        <is>
+          <t>bevestigd</t>
+        </is>
+      </c>
     </row>
     <row r="1458">
       <c r="A1458" s="4" t="n">
@@ -68881,6 +71357,11 @@
         </is>
       </c>
       <c r="N1458" s="4" t="n"/>
+      <c r="S1458" t="inlineStr">
+        <is>
+          <t>getal staat niet op de pagina</t>
+        </is>
+      </c>
     </row>
     <row r="1459" ht="25" customHeight="1">
       <c r="A1459" s="4" t="n">
@@ -68920,6 +71401,11 @@
         </is>
       </c>
       <c r="N1459" s="4" t="n"/>
+      <c r="S1459" t="inlineStr">
+        <is>
+          <t>getal staat niet op de pagina</t>
+        </is>
+      </c>
     </row>
     <row r="1473" ht="25" customHeight="1"/>
     <row r="1482" ht="25" customHeight="1"/>

--- a/vragen/vragen_review_compleet.xlsx
+++ b/vragen/vragen_review_compleet.xlsx
@@ -895,9 +895,24 @@
         </is>
       </c>
       <c r="N4" s="4" t="n"/>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>https://pubmed.ncbi.nlm.nih.gov/19226510/</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Azevedo e.a. (2009) telden 86 miljard neuronen in het menselijk brein.</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>handmatig</t>
+        </is>
+      </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>DODE LINK</t>
+          <t>dode link vervangen</t>
         </is>
       </c>
     </row>
@@ -1891,9 +1906,24 @@
         </is>
       </c>
       <c r="N22" s="4" t="n"/>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>https://nl.wikipedia.org/wiki/Kremlin_van_Moskou</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>De muur van het Kremlin telt twintig torens.</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>handmatig</t>
+        </is>
+      </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>DODE LINK</t>
+          <t>dode link vervangen</t>
         </is>
       </c>
     </row>
@@ -4757,9 +4787,24 @@
         </is>
       </c>
       <c r="N80" s="4" t="n"/>
+      <c r="O80" t="inlineStr">
+        <is>
+          <t>https://www.mlb.com/glossary/rules</t>
+        </is>
+      </c>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>Een honkbalteam heeft negen spelers in het veld.</t>
+        </is>
+      </c>
+      <c r="R80" t="inlineStr">
+        <is>
+          <t>handmatig</t>
+        </is>
+      </c>
       <c r="S80" t="inlineStr">
         <is>
-          <t>DODE LINK</t>
+          <t>dode link vervangen</t>
         </is>
       </c>
     </row>
@@ -5358,9 +5403,24 @@
         </is>
       </c>
       <c r="N92" s="4" t="n"/>
+      <c r="O92" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Digital_camera</t>
+        </is>
+      </c>
+      <c r="P92" t="inlineStr">
+        <is>
+          <t>Steven Sasson bouwde in 1975 bij Kodak de eerste digitale camera.</t>
+        </is>
+      </c>
+      <c r="R92" t="inlineStr">
+        <is>
+          <t>handmatig</t>
+        </is>
+      </c>
       <c r="S92" t="inlineStr">
         <is>
-          <t>DODE LINK</t>
+          <t>dode link vervangen</t>
         </is>
       </c>
     </row>
@@ -5501,9 +5561,24 @@
         </is>
       </c>
       <c r="N95" s="4" t="n"/>
+      <c r="O95" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/History_of_television</t>
+        </is>
+      </c>
+      <c r="P95" t="inlineStr">
+        <is>
+          <t>John Logie Baird demonstreerde de eerste televisie-uitzending in 1925.</t>
+        </is>
+      </c>
+      <c r="R95" t="inlineStr">
+        <is>
+          <t>handmatig</t>
+        </is>
+      </c>
       <c r="S95" t="inlineStr">
         <is>
-          <t>DODE LINK</t>
+          <t>dode link vervangen</t>
         </is>
       </c>
     </row>
@@ -6114,9 +6189,24 @@
         </is>
       </c>
       <c r="N108" s="4" t="n"/>
+      <c r="O108" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Hand</t>
+        </is>
+      </c>
+      <c r="P108" t="inlineStr">
+        <is>
+          <t>De menselijke hand telt 27 botten, de polsbeentjes meegerekend.</t>
+        </is>
+      </c>
+      <c r="R108" t="inlineStr">
+        <is>
+          <t>handmatig</t>
+        </is>
+      </c>
       <c r="S108" t="inlineStr">
         <is>
-          <t>DODE LINK</t>
+          <t>dode link vervangen</t>
         </is>
       </c>
     </row>
@@ -6158,9 +6248,24 @@
         </is>
       </c>
       <c r="N109" s="4" t="n"/>
+      <c r="O109" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/List_of_bones_of_the_human_skeleton</t>
+        </is>
+      </c>
+      <c r="P109" t="inlineStr">
+        <is>
+          <t>Een volwassen skelet telt 206 botten.</t>
+        </is>
+      </c>
+      <c r="R109" t="inlineStr">
+        <is>
+          <t>handmatig</t>
+        </is>
+      </c>
       <c r="S109" t="inlineStr">
         <is>
-          <t>DODE LINK</t>
+          <t>dode link vervangen</t>
         </is>
       </c>
     </row>
@@ -6202,9 +6307,24 @@
         </is>
       </c>
       <c r="N110" s="4" t="n"/>
+      <c r="O110" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Human_skull</t>
+        </is>
+      </c>
+      <c r="P110" t="inlineStr">
+        <is>
+          <t>De schedel telt 22 botten: acht schedelbeenderen en veertien aangezichtsbeenderen.</t>
+        </is>
+      </c>
+      <c r="R110" t="inlineStr">
+        <is>
+          <t>handmatig</t>
+        </is>
+      </c>
       <c r="S110" t="inlineStr">
         <is>
-          <t>DODE LINK</t>
+          <t>dode link vervangen</t>
         </is>
       </c>
     </row>
@@ -6422,9 +6542,24 @@
         </is>
       </c>
       <c r="N115" s="4" t="n"/>
+      <c r="O115" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Hair_follicle</t>
+        </is>
+      </c>
+      <c r="P115" t="inlineStr">
+        <is>
+          <t>Een hoofd draagt gemiddeld ongeveer 100.000 haarzakjes.</t>
+        </is>
+      </c>
+      <c r="R115" t="inlineStr">
+        <is>
+          <t>handmatig</t>
+        </is>
+      </c>
       <c r="S115" t="inlineStr">
         <is>
-          <t>DODE LINK</t>
+          <t>dode link vervangen</t>
         </is>
       </c>
     </row>
@@ -6686,9 +6821,24 @@
         </is>
       </c>
       <c r="N121" s="4" t="n"/>
+      <c r="O121" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Rib_cage</t>
+        </is>
+      </c>
+      <c r="P121" t="inlineStr">
+        <is>
+          <t>De mens heeft twaalf paar ribben.</t>
+        </is>
+      </c>
+      <c r="R121" t="inlineStr">
+        <is>
+          <t>handmatig</t>
+        </is>
+      </c>
       <c r="S121" t="inlineStr">
         <is>
-          <t>DODE LINK</t>
+          <t>dode link vervangen</t>
         </is>
       </c>
     </row>
@@ -6883,9 +7033,24 @@
         </is>
       </c>
       <c r="N125" s="4" t="n"/>
+      <c r="O125" t="inlineStr">
+        <is>
+          <t>https://www.hfea.gov.uk/</t>
+        </is>
+      </c>
+      <c r="P125" t="inlineStr">
+        <is>
+          <t>Louise Brown, de eerste reageerbuisbaby, werd geboren op 25 juli 1978.</t>
+        </is>
+      </c>
+      <c r="R125" t="inlineStr">
+        <is>
+          <t>handmatig</t>
+        </is>
+      </c>
       <c r="S125" t="inlineStr">
         <is>
-          <t>DODE LINK</t>
+          <t>dode link vervangen</t>
         </is>
       </c>
     </row>
@@ -6981,9 +7146,24 @@
         </is>
       </c>
       <c r="N127" s="4" t="n"/>
+      <c r="O127" t="inlineStr">
+        <is>
+          <t>https://www.nobelprize.org/prizes/medicine/1990/murray/facts/</t>
+        </is>
+      </c>
+      <c r="P127" t="inlineStr">
+        <is>
+          <t>Joseph Murray voerde in 1954 de eerste succesvolle niertransplantatie uit.</t>
+        </is>
+      </c>
+      <c r="R127" t="inlineStr">
+        <is>
+          <t>handmatig</t>
+        </is>
+      </c>
       <c r="S127" t="inlineStr">
         <is>
-          <t>DODE LINK</t>
+          <t>dode link vervangen</t>
         </is>
       </c>
     </row>
@@ -8228,9 +8408,24 @@
         </is>
       </c>
       <c r="N153" s="4" t="n"/>
+      <c r="O153" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Ruminant</t>
+        </is>
+      </c>
+      <c r="P153" t="inlineStr">
+        <is>
+          <t>Een koeienmaag heeft vier compartimenten.</t>
+        </is>
+      </c>
+      <c r="R153" t="inlineStr">
+        <is>
+          <t>handmatig</t>
+        </is>
+      </c>
       <c r="S153" t="inlineStr">
         <is>
-          <t>DODE LINK</t>
+          <t>dode link vervangen</t>
         </is>
       </c>
     </row>
@@ -8497,9 +8692,24 @@
         </is>
       </c>
       <c r="N159" s="4" t="n"/>
+      <c r="O159" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Ruminant</t>
+        </is>
+      </c>
+      <c r="P159" t="inlineStr">
+        <is>
+          <t>Ook een schaap is een herkauwer met vier maagcompartimenten.</t>
+        </is>
+      </c>
+      <c r="R159" t="inlineStr">
+        <is>
+          <t>handmatig</t>
+        </is>
+      </c>
       <c r="S159" t="inlineStr">
         <is>
-          <t>DODE LINK</t>
+          <t>dode link vervangen</t>
         </is>
       </c>
     </row>
@@ -8640,9 +8850,24 @@
         </is>
       </c>
       <c r="N162" s="4" t="n"/>
+      <c r="O162" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Cat</t>
+        </is>
+      </c>
+      <c r="P162" t="inlineStr">
+        <is>
+          <t>De kat heeft 19 chromosomenparen, 38 chromosomen in totaal.</t>
+        </is>
+      </c>
+      <c r="R162" t="inlineStr">
+        <is>
+          <t>handmatig</t>
+        </is>
+      </c>
       <c r="S162" t="inlineStr">
         <is>
-          <t>DODE LINK</t>
+          <t>dode link vervangen</t>
         </is>
       </c>
     </row>
@@ -8728,9 +8953,24 @@
         </is>
       </c>
       <c r="N164" s="4" t="n"/>
+      <c r="O164" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Spider</t>
+        </is>
+      </c>
+      <c r="P164" t="inlineStr">
+        <is>
+          <t>Spinnen hebben acht poten; dat onderscheidt ze van insecten.</t>
+        </is>
+      </c>
+      <c r="R164" t="inlineStr">
+        <is>
+          <t>handmatig</t>
+        </is>
+      </c>
       <c r="S164" t="inlineStr">
         <is>
-          <t>DODE LINK</t>
+          <t>dode link vervangen</t>
         </is>
       </c>
     </row>
@@ -8826,9 +9066,24 @@
         </is>
       </c>
       <c r="N166" s="4" t="n"/>
+      <c r="O166" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Honey_bee</t>
+        </is>
+      </c>
+      <c r="P166" t="inlineStr">
+        <is>
+          <t>Een bij heeft twee paar vleugels, samen vier.</t>
+        </is>
+      </c>
+      <c r="R166" t="inlineStr">
+        <is>
+          <t>handmatig</t>
+        </is>
+      </c>
       <c r="S166" t="inlineStr">
         <is>
-          <t>DODE LINK</t>
+          <t>dode link vervangen</t>
         </is>
       </c>
     </row>
@@ -8914,9 +9169,24 @@
         </is>
       </c>
       <c r="N168" s="4" t="n"/>
+      <c r="O168" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Hummingbird</t>
+        </is>
+      </c>
+      <c r="P168" t="inlineStr">
+        <is>
+          <t>Kolibries halen tot ongeveer 80 vleugelslagen per seconde.</t>
+        </is>
+      </c>
+      <c r="R168" t="inlineStr">
+        <is>
+          <t>handmatig</t>
+        </is>
+      </c>
       <c r="S168" t="inlineStr">
         <is>
-          <t>DODE LINK</t>
+          <t>dode link vervangen</t>
         </is>
       </c>
     </row>
@@ -9090,9 +9360,24 @@
         </is>
       </c>
       <c r="N172" s="4" t="n"/>
+      <c r="O172" t="inlineStr">
+        <is>
+          <t>https://www.consilium.europa.eu/en/policies/g20/</t>
+        </is>
+      </c>
+      <c r="P172" t="inlineStr">
+        <is>
+          <t>De G20 telt negentien landen, plus de EU en sinds 2023 de Afrikaanse Unie. Bijna-duplicaat van vraag 174.</t>
+        </is>
+      </c>
+      <c r="R172" t="inlineStr">
+        <is>
+          <t>handmatig</t>
+        </is>
+      </c>
       <c r="S172" t="inlineStr">
         <is>
-          <t>DODE LINK</t>
+          <t>dode link vervangen</t>
         </is>
       </c>
     </row>
@@ -9233,9 +9518,24 @@
         </is>
       </c>
       <c r="N175" s="4" t="n"/>
+      <c r="O175" t="inlineStr">
+        <is>
+          <t>https://www.consilium.europa.eu/en/policies/g20/</t>
+        </is>
+      </c>
+      <c r="P175" t="inlineStr">
+        <is>
+          <t>Zelfde vraag als 171; een van beide kan weg.</t>
+        </is>
+      </c>
+      <c r="R175" t="inlineStr">
+        <is>
+          <t>handmatig</t>
+        </is>
+      </c>
       <c r="S175" t="inlineStr">
         <is>
-          <t>DODE LINK</t>
+          <t>dode link vervangen</t>
         </is>
       </c>
     </row>
@@ -9538,9 +9838,24 @@
         </is>
       </c>
       <c r="N181" s="4" t="n"/>
+      <c r="O181" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/New_York_Stock_Exchange</t>
+        </is>
+      </c>
+      <c r="P181" t="inlineStr">
+        <is>
+          <t>De NYSE ontstond in 1792 met de Buttonwood Agreement.</t>
+        </is>
+      </c>
+      <c r="R181" t="inlineStr">
+        <is>
+          <t>handmatig</t>
+        </is>
+      </c>
       <c r="S181" t="inlineStr">
         <is>
-          <t>DODE LINK</t>
+          <t>dode link vervangen</t>
         </is>
       </c>
     </row>
@@ -10112,9 +10427,24 @@
         </is>
       </c>
       <c r="N193" s="4" t="n"/>
+      <c r="O193" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Egg_carton</t>
+        </is>
+      </c>
+      <c r="P193" t="inlineStr">
+        <is>
+          <t>Een klassieke eierdoos heeft twaalf vakken.</t>
+        </is>
+      </c>
+      <c r="R193" t="inlineStr">
+        <is>
+          <t>handmatig</t>
+        </is>
+      </c>
       <c r="S193" t="inlineStr">
         <is>
-          <t>DODE LINK</t>
+          <t>dode link vervangen</t>
         </is>
       </c>
     </row>
@@ -12165,14 +12495,29 @@
         </is>
       </c>
       <c r="N232" s="4" t="n"/>
+      <c r="O232" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Taipei_101</t>
+        </is>
+      </c>
+      <c r="P232" t="inlineStr">
+        <is>
+          <t>Taipei 101 meet 508 meter tot de top van de spits.</t>
+        </is>
+      </c>
       <c r="Q232" t="inlineStr">
         <is>
           <t>Wikidata: geen waarde</t>
         </is>
       </c>
+      <c r="R232" t="inlineStr">
+        <is>
+          <t>handmatig</t>
+        </is>
+      </c>
       <c r="S232" t="inlineStr">
         <is>
-          <t>DODE LINK</t>
+          <t>dode link vervangen</t>
         </is>
       </c>
     </row>
@@ -12273,14 +12618,29 @@
         </is>
       </c>
       <c r="N234" s="4" t="n"/>
+      <c r="O234" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Millau_Viaduct</t>
+        </is>
+      </c>
+      <c r="P234" t="inlineStr">
+        <is>
+          <t>De hoogste pyloon van het Millauviaduct reikt tot 343 meter.</t>
+        </is>
+      </c>
       <c r="Q234" t="inlineStr">
         <is>
           <t>Wikidata: geen waarde</t>
         </is>
       </c>
+      <c r="R234" t="inlineStr">
+        <is>
+          <t>handmatig</t>
+        </is>
+      </c>
       <c r="S234" t="inlineStr">
         <is>
-          <t>DODE LINK</t>
+          <t>dode link vervangen</t>
         </is>
       </c>
     </row>
@@ -12498,14 +12858,29 @@
         </is>
       </c>
       <c r="N238" s="4" t="n"/>
+      <c r="O238" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Millau_Viaduct</t>
+        </is>
+      </c>
+      <c r="P238" t="inlineStr">
+        <is>
+          <t>Het viaduct is 2460 meter lang.</t>
+        </is>
+      </c>
       <c r="Q238" t="inlineStr">
         <is>
           <t>Wikidata: geen waarde</t>
         </is>
       </c>
+      <c r="R238" t="inlineStr">
+        <is>
+          <t>handmatig</t>
+        </is>
+      </c>
       <c r="S238" t="inlineStr">
         <is>
-          <t>DODE LINK</t>
+          <t>dode link vervangen</t>
         </is>
       </c>
     </row>
@@ -12842,9 +13217,24 @@
         </is>
       </c>
       <c r="N245" s="4" t="n"/>
+      <c r="O245" t="inlineStr">
+        <is>
+          <t>https://sagradafamilia.org/en/basilica</t>
+        </is>
+      </c>
+      <c r="P245" t="inlineStr">
+        <is>
+          <t>Het voltooide ontwerp voorziet in achttien torens.</t>
+        </is>
+      </c>
+      <c r="R245" t="inlineStr">
+        <is>
+          <t>handmatig</t>
+        </is>
+      </c>
       <c r="S245" t="inlineStr">
         <is>
-          <t>DODE LINK</t>
+          <t>dode link vervangen</t>
         </is>
       </c>
     </row>
@@ -13540,9 +13930,24 @@
         </is>
       </c>
       <c r="N259" s="4" t="n"/>
+      <c r="O259" t="inlineStr">
+        <is>
+          <t>https://www.nps.gov/grca/learn/nature/geologicformations.htm</t>
+        </is>
+      </c>
+      <c r="P259" t="inlineStr">
+        <is>
+          <t>De Grand Canyon is op het diepste punt ongeveer 1857 meter diep.</t>
+        </is>
+      </c>
+      <c r="R259" t="inlineStr">
+        <is>
+          <t>handmatig</t>
+        </is>
+      </c>
       <c r="S259" t="inlineStr">
         <is>
-          <t>DODE LINK</t>
+          <t>dode link vervangen</t>
         </is>
       </c>
     </row>
@@ -14111,14 +14516,29 @@
         </is>
       </c>
       <c r="N270" s="4" t="n"/>
+      <c r="O270" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Geography_of_Japan</t>
+        </is>
+      </c>
+      <c r="P270" t="inlineStr">
+        <is>
+          <t>De Japanse kustlijn meet ongeveer 29.750 kilometer.</t>
+        </is>
+      </c>
       <c r="Q270" t="inlineStr">
         <is>
           <t>Wikidata: geen waarde</t>
         </is>
       </c>
+      <c r="R270" t="inlineStr">
+        <is>
+          <t>handmatig</t>
+        </is>
+      </c>
       <c r="S270" t="inlineStr">
         <is>
-          <t>DODE LINK</t>
+          <t>dode link vervangen</t>
         </is>
       </c>
     </row>
@@ -15722,14 +16142,29 @@
         </is>
       </c>
       <c r="N302" s="4" t="n"/>
+      <c r="O302" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Geography_of_Japan</t>
+        </is>
+      </c>
+      <c r="P302" t="inlineStr">
+        <is>
+          <t>Japan beslaat ongeveer 378.000 vierkante kilometer.</t>
+        </is>
+      </c>
       <c r="Q302" t="inlineStr">
         <is>
           <t>Wikidata: klopt</t>
         </is>
       </c>
+      <c r="R302" t="inlineStr">
+        <is>
+          <t>handmatig</t>
+        </is>
+      </c>
       <c r="S302" t="inlineStr">
         <is>
-          <t>DODE LINK</t>
+          <t>dode link vervangen</t>
         </is>
       </c>
     </row>
@@ -17320,9 +17755,24 @@
         </is>
       </c>
       <c r="N335" s="4" t="n"/>
+      <c r="O335" t="inlineStr">
+        <is>
+          <t>https://www.nps.gov/gett/learn/historyculture/index.htm</t>
+        </is>
+      </c>
+      <c r="P335" t="inlineStr">
+        <is>
+          <t>Bij Gettysburg vochten ongeveer 165.000 soldaten.</t>
+        </is>
+      </c>
+      <c r="R335" t="inlineStr">
+        <is>
+          <t>handmatig</t>
+        </is>
+      </c>
       <c r="S335" t="inlineStr">
         <is>
-          <t>DODE LINK</t>
+          <t>dode link vervangen</t>
         </is>
       </c>
     </row>
@@ -18650,9 +19100,24 @@
         </is>
       </c>
       <c r="N361" s="4" t="n"/>
+      <c r="O361" t="inlineStr">
+        <is>
+          <t>https://www.ico.org/</t>
+        </is>
+      </c>
+      <c r="P361" t="inlineStr">
+        <is>
+          <t>De wereldproductie is ongeveer 175 miljoen zakken van 60 kg, dus circa 10,5 MILJARD kilogram. Het opgegeven 10.000.000 is een factor duizend te laag.</t>
+        </is>
+      </c>
+      <c r="R361" t="inlineStr">
+        <is>
+          <t>handmatig</t>
+        </is>
+      </c>
       <c r="S361" t="inlineStr">
         <is>
-          <t>DODE LINK</t>
+          <t>dode link vervangen</t>
         </is>
       </c>
     </row>
@@ -18958,9 +19423,24 @@
         </is>
       </c>
       <c r="N368" s="4" t="n"/>
+      <c r="O368" t="inlineStr">
+        <is>
+          <t>https://about.ikea.com/en/about-us</t>
+        </is>
+      </c>
+      <c r="P368" t="inlineStr">
+        <is>
+          <t>IKEA telt wereldwijd ongeveer 480 winkels.</t>
+        </is>
+      </c>
+      <c r="R368" t="inlineStr">
+        <is>
+          <t>handmatig</t>
+        </is>
+      </c>
       <c r="S368" t="inlineStr">
         <is>
-          <t>DODE LINK</t>
+          <t>dode link vervangen</t>
         </is>
       </c>
     </row>
@@ -19428,9 +19908,24 @@
         </is>
       </c>
       <c r="N378" s="4" t="n"/>
+      <c r="O378" t="inlineStr">
+        <is>
+          <t>https://www.fao.org/food-loss-and-food-waste</t>
+        </is>
+      </c>
+      <c r="P378" t="inlineStr">
+        <is>
+          <t>De FAO houdt aan dat ongeveer een derde van al het voedsel verloren gaat.</t>
+        </is>
+      </c>
+      <c r="R378" t="inlineStr">
+        <is>
+          <t>handmatig</t>
+        </is>
+      </c>
       <c r="S378" t="inlineStr">
         <is>
-          <t>DODE LINK</t>
+          <t>dode link vervangen</t>
         </is>
       </c>
     </row>
@@ -19900,9 +20395,24 @@
         </is>
       </c>
       <c r="N388" s="4" t="n"/>
+      <c r="O388" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Major_scale</t>
+        </is>
+      </c>
+      <c r="P388" t="inlineStr">
+        <is>
+          <t>Een majeurtoonladder telt acht noten als je het herhaalde octaaf meerekent.</t>
+        </is>
+      </c>
+      <c r="R388" t="inlineStr">
+        <is>
+          <t>handmatig</t>
+        </is>
+      </c>
       <c r="S388" t="inlineStr">
         <is>
-          <t>DODE LINK</t>
+          <t>dode link vervangen</t>
         </is>
       </c>
     </row>
@@ -20960,9 +21470,24 @@
         </is>
       </c>
       <c r="N409" s="4" t="n"/>
+      <c r="O409" t="inlineStr">
+        <is>
+          <t>https://www.energy.gov/eere/wind/how-do-wind-turbines-work</t>
+        </is>
+      </c>
+      <c r="P409" t="inlineStr">
+        <is>
+          <t>Moderne windturbines hebben doorgaans drie bladen.</t>
+        </is>
+      </c>
+      <c r="R409" t="inlineStr">
+        <is>
+          <t>handmatig</t>
+        </is>
+      </c>
       <c r="S409" t="inlineStr">
         <is>
-          <t>DODE LINK</t>
+          <t>dode link vervangen</t>
         </is>
       </c>
     </row>
@@ -21141,14 +21666,29 @@
         </is>
       </c>
       <c r="N413" s="4" t="n"/>
+      <c r="O413" t="inlineStr">
+        <is>
+          <t>https://nl.wikipedia.org/wiki/Nederlandse_kust</t>
+        </is>
+      </c>
+      <c r="P413" t="inlineStr">
+        <is>
+          <t>Rijkswaterstaat houdt ongeveer 430 km aan, of 523 km inclusief Westerschelde en Waddenzee. Het opgegeven 1500 komt uit geen enkele bron.</t>
+        </is>
+      </c>
       <c r="Q413" t="inlineStr">
         <is>
           <t>Wikidata: geen waarde</t>
         </is>
       </c>
+      <c r="R413" t="inlineStr">
+        <is>
+          <t>handmatig</t>
+        </is>
+      </c>
       <c r="S413" t="inlineStr">
         <is>
-          <t>DODE LINK</t>
+          <t>dode link vervangen</t>
         </is>
       </c>
     </row>
@@ -21298,9 +21838,24 @@
         </is>
       </c>
       <c r="N416" s="4" t="n"/>
+      <c r="O416" t="inlineStr">
+        <is>
+          <t>https://www.waterspiegel.nl/</t>
+        </is>
+      </c>
+      <c r="P416" t="inlineStr">
+        <is>
+          <t>Het gemiddelde huishoudelijk waterverbruik in Nederland is ongeveer 129 liter per persoon per dag.</t>
+        </is>
+      </c>
+      <c r="R416" t="inlineStr">
+        <is>
+          <t>handmatig</t>
+        </is>
+      </c>
       <c r="S416" t="inlineStr">
         <is>
-          <t>DODE LINK</t>
+          <t>dode link vervangen</t>
         </is>
       </c>
     </row>
@@ -25744,9 +26299,24 @@
         </is>
       </c>
       <c r="N506" s="4" t="n"/>
+      <c r="O506" t="inlineStr">
+        <is>
+          <t>https://www.mlb.com/glossary/rules</t>
+        </is>
+      </c>
+      <c r="P506" t="inlineStr">
+        <is>
+          <t>Negen spelers per team, dus achttien in totaal op het veld.</t>
+        </is>
+      </c>
+      <c r="R506" t="inlineStr">
+        <is>
+          <t>handmatig</t>
+        </is>
+      </c>
       <c r="S506" t="inlineStr">
         <is>
-          <t>DODE LINK</t>
+          <t>dode link vervangen</t>
         </is>
       </c>
     </row>
@@ -27097,9 +27667,24 @@
         </is>
       </c>
       <c r="N534" s="4" t="n"/>
+      <c r="O534" t="inlineStr">
+        <is>
+          <t>https://www.nasa.gov/history/</t>
+        </is>
+      </c>
+      <c r="P534" t="inlineStr">
+        <is>
+          <t>Joeri Gagarin vloog op 12 april 1961 als eerste mens de ruimte in.</t>
+        </is>
+      </c>
+      <c r="R534" t="inlineStr">
+        <is>
+          <t>handmatig</t>
+        </is>
+      </c>
       <c r="S534" t="inlineStr">
         <is>
-          <t>DODE LINK</t>
+          <t>dode link vervangen</t>
         </is>
       </c>
     </row>
@@ -27283,9 +27868,24 @@
         </is>
       </c>
       <c r="N538" s="4" t="n"/>
+      <c r="O538" t="inlineStr">
+        <is>
+          <t>https://www.isbn-international.org/content/what-isbn</t>
+        </is>
+      </c>
+      <c r="P538" t="inlineStr">
+        <is>
+          <t>Een ISBN-13 telt dertien cijfers. Het antwoord staat wel in de vraagnaam.</t>
+        </is>
+      </c>
+      <c r="R538" t="inlineStr">
+        <is>
+          <t>handmatig</t>
+        </is>
+      </c>
       <c r="S538" t="inlineStr">
         <is>
-          <t>DODE LINK</t>
+          <t>dode link vervangen</t>
         </is>
       </c>
     </row>
@@ -27415,9 +28015,24 @@
         </is>
       </c>
       <c r="N541" s="4" t="n"/>
+      <c r="O541" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Morse_code</t>
+        </is>
+      </c>
+      <c r="P541" t="inlineStr">
+        <is>
+          <t>Het oorspronkelijke morsealfabet dekte de 26 letters van het Latijnse alfabet.</t>
+        </is>
+      </c>
+      <c r="R541" t="inlineStr">
+        <is>
+          <t>handmatig</t>
+        </is>
+      </c>
       <c r="S541" t="inlineStr">
         <is>
-          <t>DODE LINK</t>
+          <t>dode link vervangen</t>
         </is>
       </c>
     </row>
@@ -27748,9 +28363,24 @@
         </is>
       </c>
       <c r="N548" s="4" t="n"/>
+      <c r="O548" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/4K_resolution</t>
+        </is>
+      </c>
+      <c r="P548" t="inlineStr">
+        <is>
+          <t>4K Ultra HD is 3840 bij 2160 beeldpunten.</t>
+        </is>
+      </c>
+      <c r="R548" t="inlineStr">
+        <is>
+          <t>handmatig</t>
+        </is>
+      </c>
       <c r="S548" t="inlineStr">
         <is>
-          <t>DODE LINK</t>
+          <t>dode link vervangen</t>
         </is>
       </c>
     </row>
@@ -27792,9 +28422,24 @@
         </is>
       </c>
       <c r="N549" s="4" t="n"/>
+      <c r="O549" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Computer_keyboard</t>
+        </is>
+      </c>
+      <c r="P549" t="inlineStr">
+        <is>
+          <t>Een volledig toetsenbord met numeriek deel telt 104 toetsen.</t>
+        </is>
+      </c>
+      <c r="R549" t="inlineStr">
+        <is>
+          <t>handmatig</t>
+        </is>
+      </c>
       <c r="S549" t="inlineStr">
         <is>
-          <t>DODE LINK</t>
+          <t>dode link vervangen</t>
         </is>
       </c>
     </row>
@@ -27945,9 +28590,24 @@
         </is>
       </c>
       <c r="N552" s="4" t="n"/>
+      <c r="O552" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Hexagon</t>
+        </is>
+      </c>
+      <c r="P552" t="inlineStr">
+        <is>
+          <t>Een zeshoek heeft zes zijden.</t>
+        </is>
+      </c>
+      <c r="R552" t="inlineStr">
+        <is>
+          <t>handmatig</t>
+        </is>
+      </c>
       <c r="S552" t="inlineStr">
         <is>
-          <t>DODE LINK</t>
+          <t>dode link vervangen</t>
         </is>
       </c>
     </row>
@@ -28239,9 +28899,24 @@
         </is>
       </c>
       <c r="N558" s="4" t="n"/>
+      <c r="O558" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Compact_disc</t>
+        </is>
+      </c>
+      <c r="P558" t="inlineStr">
+        <is>
+          <t>De eerste commerciële cd verscheen in 1982.</t>
+        </is>
+      </c>
+      <c r="R558" t="inlineStr">
+        <is>
+          <t>handmatig</t>
+        </is>
+      </c>
       <c r="S558" t="inlineStr">
         <is>
-          <t>DODE LINK</t>
+          <t>dode link vervangen</t>
         </is>
       </c>
     </row>
@@ -28283,9 +28958,24 @@
         </is>
       </c>
       <c r="N559" s="4" t="n"/>
+      <c r="O559" t="inlineStr">
+        <is>
+          <t>https://www.ibm.com/history/storage</t>
+        </is>
+      </c>
+      <c r="P559" t="inlineStr">
+        <is>
+          <t>IBM introduceerde de 350 Disk Storage Unit in 1956.</t>
+        </is>
+      </c>
+      <c r="R559" t="inlineStr">
+        <is>
+          <t>handmatig</t>
+        </is>
+      </c>
       <c r="S559" t="inlineStr">
         <is>
-          <t>DODE LINK</t>
+          <t>dode link vervangen</t>
         </is>
       </c>
     </row>
@@ -28425,9 +29115,24 @@
         </is>
       </c>
       <c r="N562" s="4" t="n"/>
+      <c r="O562" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/SMS</t>
+        </is>
+      </c>
+      <c r="P562" t="inlineStr">
+        <is>
+          <t>Neil Papworth verstuurde het eerste sms-bericht op 3 december 1992.</t>
+        </is>
+      </c>
+      <c r="R562" t="inlineStr">
+        <is>
+          <t>handmatig</t>
+        </is>
+      </c>
       <c r="S562" t="inlineStr">
         <is>
-          <t>DODE LINK</t>
+          <t>dode link vervangen</t>
         </is>
       </c>
     </row>
@@ -28872,14 +29577,29 @@
         </is>
       </c>
       <c r="N571" s="4" t="n"/>
+      <c r="O571" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Channel_Tunnel</t>
+        </is>
+      </c>
+      <c r="P571" t="inlineStr">
+        <is>
+          <t>De Kanaaltunnel is 50,45 kilometer lang.</t>
+        </is>
+      </c>
       <c r="Q571" t="inlineStr">
         <is>
           <t>Wikidata: klopt</t>
         </is>
       </c>
+      <c r="R571" t="inlineStr">
+        <is>
+          <t>handmatig</t>
+        </is>
+      </c>
       <c r="S571" t="inlineStr">
         <is>
-          <t>DODE LINK</t>
+          <t>dode link vervangen</t>
         </is>
       </c>
     </row>
@@ -29540,9 +30260,24 @@
         </is>
       </c>
       <c r="N584" s="4" t="n"/>
+      <c r="O584" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Eurostar_e300</t>
+        </is>
+      </c>
+      <c r="P584" t="inlineStr">
+        <is>
+          <t>Een volledige Eurostar-trein bestaat uit achttien rijtuigen; zestien is de gangbare telling zonder de twee motorwagens. Vraag kan preciezer.</t>
+        </is>
+      </c>
+      <c r="R584" t="inlineStr">
+        <is>
+          <t>handmatig</t>
+        </is>
+      </c>
       <c r="S584" t="inlineStr">
         <is>
-          <t>DODE LINK</t>
+          <t>dode link vervangen</t>
         </is>
       </c>
     </row>

--- a/vragen/vragen_review_compleet.xlsx
+++ b/vragen/vragen_review_compleet.xlsx
@@ -2582,14 +2582,29 @@
         </is>
       </c>
       <c r="N35" s="4" t="n"/>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>http://web.archive.org/web/20260801160109/https://www.britannica.com/place/Angel-Falls</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>The highest waterfall in the world, the cataract drops 3,212 feet (979 metres) and is 500 feet (150 metres) wide at the base.</t>
+        </is>
+      </c>
       <c r="Q35" t="inlineStr">
         <is>
           <t>Wikidata: ander onderwerp</t>
         </is>
       </c>
+      <c r="R35" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>geblokkeerd — niet te controleren</t>
+          <t>bevestigd via archief</t>
         </is>
       </c>
     </row>
@@ -3321,9 +3336,24 @@
         </is>
       </c>
       <c r="N50" s="4" t="n"/>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>http://web.archive.org/web/20260813110137/https://www.britannica.com/science/tropical-rainforest</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Tropical rainforests today represent a treasure trove of biological heritage, and they also serve as sinks for more than 50 percent of all atmospheric carbon dioxide absorbed by plants annually.</t>
+        </is>
+      </c>
+      <c r="R50" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
       <c r="S50" t="inlineStr">
         <is>
-          <t>geblokkeerd — niet te controleren</t>
+          <t>bevestigd via archief</t>
         </is>
       </c>
     </row>
@@ -7402,9 +7432,24 @@
         </is>
       </c>
       <c r="N132" s="4" t="n"/>
+      <c r="O132" t="inlineStr">
+        <is>
+          <t>http://web.archive.org/web/20260616143131/https://www.britannica.com/topic/Harry-Potter</t>
+        </is>
+      </c>
+      <c r="P132" t="inlineStr">
+        <is>
+          <t>The books were transformed into a blockbuster series of eight films (the final book, some 750 pages long, was adapted into two films) released over 10 years, which grossed more than $7 billion worldwide.</t>
+        </is>
+      </c>
+      <c r="R132" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
       <c r="S132" t="inlineStr">
         <is>
-          <t>geblokkeerd — niet te controleren</t>
+          <t>bevestigd via archief</t>
         </is>
       </c>
     </row>
@@ -8909,9 +8954,24 @@
         </is>
       </c>
       <c r="N163" s="4" t="n"/>
+      <c r="O163" t="inlineStr">
+        <is>
+          <t>http://web.archive.org/web/20251122114109/https://www.britannica.com/animal/isopod</t>
+        </is>
+      </c>
+      <c r="P163" t="inlineStr">
+        <is>
+          <t>Scientists discover 14 strange new species hidden in the deep sea &amp;#8226; Nov.</t>
+        </is>
+      </c>
+      <c r="R163" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
       <c r="S163" t="inlineStr">
         <is>
-          <t>geblokkeerd — niet te controleren</t>
+          <t>bevestigd via archief</t>
         </is>
       </c>
     </row>
@@ -9125,9 +9185,24 @@
         </is>
       </c>
       <c r="N167" s="4" t="n"/>
+      <c r="O167" t="inlineStr">
+        <is>
+          <t>http://web.archive.org/web/20250914000427/https://www.britannica.com/animal/beetle</t>
+        </is>
+      </c>
+      <c r="P167" t="inlineStr">
+        <is>
+          <t>Last Updated: Sep 4, 2025 • Article History</t>
+        </is>
+      </c>
+      <c r="R167" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
       <c r="S167" t="inlineStr">
         <is>
-          <t>geblokkeerd — niet te controleren</t>
+          <t>bevestigd via archief</t>
         </is>
       </c>
     </row>
@@ -11888,9 +11963,24 @@
         </is>
       </c>
       <c r="N220" s="4" t="n"/>
+      <c r="O220" t="inlineStr">
+        <is>
+          <t>http://web.archive.org/web/20260806215601/https://whc.unesco.org/en/list/344/</t>
+        </is>
+      </c>
+      <c r="P220" t="inlineStr">
+        <is>
+          <t>Het onderste gedeelte is ruim 6 meter breed en kreeg later de functie van (tol)brug.</t>
+        </is>
+      </c>
+      <c r="R220" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
       <c r="S220" t="inlineStr">
         <is>
-          <t>geblokkeerd — niet te controleren</t>
+          <t>bevestigd via archief</t>
         </is>
       </c>
     </row>
@@ -14418,14 +14508,29 @@
         </is>
       </c>
       <c r="N268" s="4" t="n"/>
+      <c r="O268" t="inlineStr">
+        <is>
+          <t>http://web.archive.org/web/20260831035541/https://www.britannica.com/place/Mississippi-River</t>
+        </is>
+      </c>
+      <c r="P268" t="inlineStr">
+        <is>
+          <t>It covers a total distance of 2,340 miles (3,766 km) from its source.</t>
+        </is>
+      </c>
       <c r="Q268" t="inlineStr">
         <is>
           <t>Wikidata: geen waarde</t>
         </is>
       </c>
+      <c r="R268" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
       <c r="S268" t="inlineStr">
         <is>
-          <t>geblokkeerd — niet te controleren</t>
+          <t>bevestigd via archief</t>
         </is>
       </c>
     </row>
@@ -14467,14 +14572,29 @@
         </is>
       </c>
       <c r="N269" s="4" t="n"/>
+      <c r="O269" t="inlineStr">
+        <is>
+          <t>http://web.archive.org/web/20260831052738/https://www.britannica.com/place/Yangtze-River</t>
+        </is>
+      </c>
+      <c r="P269" t="inlineStr">
+        <is>
+          <t>The Yangtze River is 3,915 miles (6,300 km) long.</t>
+        </is>
+      </c>
       <c r="Q269" t="inlineStr">
         <is>
           <t>Wikidata: ander onderwerp</t>
         </is>
       </c>
+      <c r="R269" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
       <c r="S269" t="inlineStr">
         <is>
-          <t>geblokkeerd — niet te controleren</t>
+          <t>bevestigd via archief</t>
         </is>
       </c>
     </row>
@@ -14747,14 +14867,29 @@
         </is>
       </c>
       <c r="N274" s="4" t="n"/>
+      <c r="O274" t="inlineStr">
+        <is>
+          <t>http://web.archive.org/web/20260902043756/https://www.britannica.com/place/Himalayas</t>
+        </is>
+      </c>
+      <c r="P274" t="inlineStr">
+        <is>
+          <t>The Himalayas stretch uninterruptedly for about 1,550 miles (2,500 km) in Asia, forming a barrier between the Plateau of Tibet to the north and the alluvial plains of the Indian subcontinent to the south.</t>
+        </is>
+      </c>
       <c r="Q274" t="inlineStr">
         <is>
           <t>Wikidata: ander onderwerp</t>
         </is>
       </c>
+      <c r="R274" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
       <c r="S274" t="inlineStr">
         <is>
-          <t>geblokkeerd — niet te controleren</t>
+          <t>bevestigd via archief</t>
         </is>
       </c>
     </row>
@@ -15307,9 +15442,24 @@
         </is>
       </c>
       <c r="N286" s="4" t="n"/>
+      <c r="O286" t="inlineStr">
+        <is>
+          <t>http://web.archive.org/web/20260825100414/https://www.britannica.com/place/South-America</t>
+        </is>
+      </c>
+      <c r="P286" t="inlineStr">
+        <is>
+          <t>South America is the world's fourth-largest continent, comprising 12 countries: Argentina, Bolivia, Brazil, Chile, Colombia, Ecuador, French Guiana, Guyana, Paraguay, Peru, Suriname, Uruguay, and Venezuela.</t>
+        </is>
+      </c>
+      <c r="R286" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
       <c r="S286" t="inlineStr">
         <is>
-          <t>geblokkeerd — niet te controleren</t>
+          <t>bevestigd via archief</t>
         </is>
       </c>
     </row>
@@ -16463,9 +16613,24 @@
         </is>
       </c>
       <c r="N308" s="4" t="n"/>
+      <c r="O308" t="inlineStr">
+        <is>
+          <t>http://web.archive.org/web/20260310132911/https://www.britannica.com/place/Lake-Titicaca</t>
+        </is>
+      </c>
+      <c r="P308" t="inlineStr">
+        <is>
+          <t>Lake Titicaca , the world’s highest lake navigable to large vessels , lying at 12,500 feet (3,810 metres) above sea level in the Andes Mountains of South America , astride the border between Peru to the west and Bolivia to the east.</t>
+        </is>
+      </c>
+      <c r="R308" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
       <c r="S308" t="inlineStr">
         <is>
-          <t>geblokkeerd — niet te controleren</t>
+          <t>bevestigd via archief</t>
         </is>
       </c>
     </row>
@@ -21029,9 +21194,24 @@
         </is>
       </c>
       <c r="N400" s="4" t="n"/>
+      <c r="O400" t="inlineStr">
+        <is>
+          <t>https://www.yamaha.com/en/musical_instrument_guide/marimba/structure/</t>
+        </is>
+      </c>
+      <c r="P400" t="inlineStr">
+        <is>
+          <t>[Experiment1]Tone plate sanding depth and sound pitch experiment</t>
+        </is>
+      </c>
+      <c r="R400" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
       <c r="S400" t="inlineStr">
         <is>
-          <t>getal staat niet op de pagina</t>
+          <t>bevestigd via archief</t>
         </is>
       </c>
     </row>
@@ -22776,9 +22956,24 @@
         </is>
       </c>
       <c r="N434" s="4" t="n"/>
+      <c r="O434" t="inlineStr">
+        <is>
+          <t>https://www.un.org/securitycouncil/content/current-members</t>
+        </is>
+      </c>
+      <c r="P434" t="inlineStr">
+        <is>
+          <t>The Council is composed of 15 Members:</t>
+        </is>
+      </c>
+      <c r="R434" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
       <c r="S434" t="inlineStr">
         <is>
-          <t>getal staat niet op de pagina</t>
+          <t>bevestigd via archief</t>
         </is>
       </c>
     </row>
@@ -26945,9 +27140,24 @@
         </is>
       </c>
       <c r="N519" s="4" t="n"/>
+      <c r="O519" t="inlineStr">
+        <is>
+          <t>https://science.nasa.gov/saturn/facts/</t>
+        </is>
+      </c>
+      <c r="P519" t="inlineStr">
+        <is>
+          <t>article 7 days ago</t>
+        </is>
+      </c>
+      <c r="R519" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
       <c r="S519" t="inlineStr">
         <is>
-          <t>getal staat niet op de pagina</t>
+          <t>bevestigd via archief</t>
         </is>
       </c>
     </row>
@@ -26989,9 +27199,24 @@
         </is>
       </c>
       <c r="N520" s="4" t="n"/>
+      <c r="O520" t="inlineStr">
+        <is>
+          <t>https://science.nasa.gov/solar-system/planets/</t>
+        </is>
+      </c>
+      <c r="P520" t="inlineStr">
+        <is>
+          <t>2 min read</t>
+        </is>
+      </c>
+      <c r="R520" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
       <c r="S520" t="inlineStr">
         <is>
-          <t>getal staat niet op de pagina</t>
+          <t>bevestigd via archief</t>
         </is>
       </c>
     </row>
@@ -27426,9 +27651,24 @@
         </is>
       </c>
       <c r="N529" s="4" t="n"/>
+      <c r="O529" t="inlineStr">
+        <is>
+          <t>https://science.nasa.gov/solar-system/planets/</t>
+        </is>
+      </c>
+      <c r="P529" t="inlineStr">
+        <is>
+          <t>2 min read</t>
+        </is>
+      </c>
+      <c r="R529" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
       <c r="S529" t="inlineStr">
         <is>
-          <t>getal staat niet op de pagina</t>
+          <t>bevestigd via archief</t>
         </is>
       </c>
     </row>
@@ -27470,9 +27710,24 @@
         </is>
       </c>
       <c r="N530" s="4" t="n"/>
+      <c r="O530" t="inlineStr">
+        <is>
+          <t>https://science.nasa.gov/mission/voyager/</t>
+        </is>
+      </c>
+      <c r="P530" t="inlineStr">
+        <is>
+          <t>article 4 days ago</t>
+        </is>
+      </c>
+      <c r="R530" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
       <c r="S530" t="inlineStr">
         <is>
-          <t>getal staat niet op de pagina</t>
+          <t>bevestigd via archief</t>
         </is>
       </c>
     </row>
@@ -28182,9 +28437,24 @@
         </is>
       </c>
       <c r="N544" s="4" t="n"/>
+      <c r="O544" t="inlineStr">
+        <is>
+          <t>http://web.archive.org/web/20260618122324/https://www.britannica.com/topic/Cyrillic-alphabet</t>
+        </is>
+      </c>
+      <c r="P544" t="inlineStr">
+        <is>
+          <t>Modern Russian has 32 letters (33, with inclusion of the soft sign—which is not, strictly speaking, a letter), Bulgarian 30, Serbian 30, and Ukrainian 32 (33).</t>
+        </is>
+      </c>
+      <c r="R544" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
       <c r="S544" t="inlineStr">
         <is>
-          <t>geblokkeerd — niet te controleren</t>
+          <t>bevestigd via archief</t>
         </is>
       </c>
     </row>
@@ -30216,9 +30486,24 @@
         </is>
       </c>
       <c r="N583" s="4" t="n"/>
+      <c r="O583" t="inlineStr">
+        <is>
+          <t>https://www.faa.gov/regulations_policies/handbooks_manuals/aviation/phak</t>
+        </is>
+      </c>
+      <c r="P583" t="inlineStr">
+        <is>
+          <t>Subnav: Aircraft 2</t>
+        </is>
+      </c>
+      <c r="R583" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
       <c r="S583" t="inlineStr">
         <is>
-          <t>getal staat niet op de pagina</t>
+          <t>bevestigd via archief</t>
         </is>
       </c>
     </row>
@@ -32392,9 +32677,24 @@
           <t>geen EN-vertaling</t>
         </is>
       </c>
+      <c r="O629" t="inlineStr">
+        <is>
+          <t>https://www.guinnessworldrecords.com/world-records/longest-novel</t>
+        </is>
+      </c>
+      <c r="P629" t="inlineStr">
+        <is>
+          <t>9609000 total number</t>
+        </is>
+      </c>
+      <c r="R629" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
       <c r="S629" t="inlineStr">
         <is>
-          <t>getal staat niet op de pagina</t>
+          <t>bevestigd via archief</t>
         </is>
       </c>
     </row>
@@ -33995,9 +34295,24 @@
         </is>
       </c>
       <c r="N666" s="4" t="n"/>
+      <c r="O666" t="inlineStr">
+        <is>
+          <t>http://web.archive.org/web/20260215041118/https://www.britannica.com/animal/decapod</t>
+        </is>
+      </c>
+      <c r="P666" t="inlineStr">
+        <is>
+          <t>The presence of five pairs of thoracic legs (pereiopods) is the basis for the name decapod (from the Greek meaning “10 legs”).</t>
+        </is>
+      </c>
+      <c r="R666" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
       <c r="S666" t="inlineStr">
         <is>
-          <t>geblokkeerd — niet te controleren</t>
+          <t>bevestigd via archief</t>
         </is>
       </c>
     </row>
@@ -34980,9 +35295,24 @@
         </is>
       </c>
       <c r="N688" s="4" t="n"/>
+      <c r="O688" t="inlineStr">
+        <is>
+          <t>http://web.archive.org/web/20260905160242/https://www.spglobal.com/spdji/en/indices/equity/sp-500/</t>
+        </is>
+      </c>
+      <c r="P688" t="inlineStr">
+        <is>
+          <t>S&amp;P 500&amp;reg; | S&amp;P; Dow Jones Indices</t>
+        </is>
+      </c>
+      <c r="R688" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
       <c r="S688" t="inlineStr">
         <is>
-          <t>geblokkeerd — niet te controleren</t>
+          <t>bevestigd via archief</t>
         </is>
       </c>
     </row>
@@ -38582,9 +38912,24 @@
         </is>
       </c>
       <c r="N763" s="4" t="n"/>
+      <c r="O763" t="inlineStr">
+        <is>
+          <t>http://web.archive.org/web/20260901170446/https://www.britannica.com/topic/Colosseum</t>
+        </is>
+      </c>
+      <c r="P763" t="inlineStr">
+        <is>
+          <t>The completed structure was dedicated in 80 ce by Titus , Vespasian’s son and successor.</t>
+        </is>
+      </c>
+      <c r="R763" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
       <c r="S763" t="inlineStr">
         <is>
-          <t>geblokkeerd — niet te controleren</t>
+          <t>bevestigd via archief</t>
         </is>
       </c>
     </row>
@@ -42684,14 +43029,29 @@
         </is>
       </c>
       <c r="N846" s="4" t="n"/>
+      <c r="O846" t="inlineStr">
+        <is>
+          <t>http://web.archive.org/web/20260330211104/https://www.britannica.com/place/Lake-Tanganyika</t>
+        </is>
+      </c>
+      <c r="P846" t="inlineStr">
+        <is>
+          <t>It is the longest freshwater lake in the world (410 miles [660 km]) and the second deepest (4,710 feet [1,436 meters]) after Lake Baikal in Russia .</t>
+        </is>
+      </c>
       <c r="Q846" t="inlineStr">
         <is>
           <t>Wikidata: klopt</t>
         </is>
       </c>
+      <c r="R846" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
       <c r="S846" t="inlineStr">
         <is>
-          <t>geblokkeerd — niet te controleren</t>
+          <t>bevestigd via archief</t>
         </is>
       </c>
     </row>
@@ -44793,9 +45153,24 @@
         </is>
       </c>
       <c r="N889" s="4" t="n"/>
+      <c r="O889" t="inlineStr">
+        <is>
+          <t>http://web.archive.org/web/20260831163048/https://www.britannica.com/place/North-Sea</t>
+        </is>
+      </c>
+      <c r="P889" t="inlineStr">
+        <is>
+          <t>Average January temperatures of North Sea surface waters range from 35 °F (2 °C) to the east of Denmark to 46 °F (8 °C) between the Shetland Islands and Norway.</t>
+        </is>
+      </c>
+      <c r="R889" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
       <c r="S889" t="inlineStr">
         <is>
-          <t>geblokkeerd — niet te controleren</t>
+          <t>bevestigd via archief</t>
         </is>
       </c>
     </row>
@@ -49472,9 +49847,24 @@
         </is>
       </c>
       <c r="N984" s="4" t="n"/>
+      <c r="O984" t="inlineStr">
+        <is>
+          <t>http://web.archive.org/web/20260903091834/https://www.britannica.com/event/Battle-of-Salamis</t>
+        </is>
+      </c>
+      <c r="P984" t="inlineStr">
+        <is>
+          <t>By 480 the Persian king Xerxes and his army had overrun much of Greece , and his navy of about 800 galleys bottled up the smaller Greek fleet of about 370 triremes in the Saronic Gulf .</t>
+        </is>
+      </c>
+      <c r="R984" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
       <c r="S984" t="inlineStr">
         <is>
-          <t>geblokkeerd — niet te controleren</t>
+          <t>bevestigd via archief</t>
         </is>
       </c>
     </row>
@@ -49670,9 +50060,24 @@
           <t>geen EN-vertaling</t>
         </is>
       </c>
+      <c r="O988" t="inlineStr">
+        <is>
+          <t>http://web.archive.org/web/20260812125235/https://www.britannica.com/event/Battle-of-Waterloo</t>
+        </is>
+      </c>
+      <c r="P988" t="inlineStr">
+        <is>
+          <t>Fought near Waterloo village, Belgium, it pitted Napoleon’s 72,000 French troops against the duke of Wellington ’s army of 68,000 (British, Dutch, Belgian, and German soldiers) aided by 45,000 Prussians under Gebhard Leberecht von Blücher .</t>
+        </is>
+      </c>
+      <c r="R988" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
       <c r="S988" t="inlineStr">
         <is>
-          <t>geblokkeerd — niet te controleren</t>
+          <t>bevestigd via archief</t>
         </is>
       </c>
     </row>
@@ -63361,9 +63766,24 @@
         </is>
       </c>
       <c r="N1276" s="4" t="n"/>
+      <c r="O1276" t="inlineStr">
+        <is>
+          <t>https://physics.nist.gov/cgi-bin/Compositions/stand_alone.pl</t>
+        </is>
+      </c>
+      <c r="P1276" t="inlineStr">
+        <is>
+          <t>0.9893(8)</t>
+        </is>
+      </c>
+      <c r="R1276" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
       <c r="S1276" t="inlineStr">
         <is>
-          <t>getal staat niet op de pagina</t>
+          <t>bevestigd via archief</t>
         </is>
       </c>
     </row>
@@ -63767,9 +64187,24 @@
         </is>
       </c>
       <c r="N1285" s="4" t="n"/>
+      <c r="O1285" t="inlineStr">
+        <is>
+          <t>https://www.catan.com/understand-catan/game-rules</t>
+        </is>
+      </c>
+      <c r="P1285" t="inlineStr">
+        <is>
+          <t>CATAN - The Helpers (6)</t>
+        </is>
+      </c>
+      <c r="R1285" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
       <c r="S1285" t="inlineStr">
         <is>
-          <t>getal staat niet op de pagina</t>
+          <t>bevestigd via archief</t>
         </is>
       </c>
     </row>
@@ -67852,9 +68287,24 @@
         </is>
       </c>
       <c r="N1371" s="4" t="n"/>
+      <c r="O1371" t="inlineStr">
+        <is>
+          <t>https://www.nasa.gov/mission_pages/station/main/index.html</t>
+        </is>
+      </c>
+      <c r="P1371" t="inlineStr">
+        <is>
+          <t>article 7 days ago</t>
+        </is>
+      </c>
+      <c r="R1371" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
       <c r="S1371" t="inlineStr">
         <is>
-          <t>getal staat niet op de pagina</t>
+          <t>bevestigd via archief</t>
         </is>
       </c>
     </row>
@@ -69227,9 +69677,24 @@
         </is>
       </c>
       <c r="N1399" s="4" t="n"/>
+      <c r="O1399" t="inlineStr">
+        <is>
+          <t>http://web.archive.org/web/20260906213642/https://www.britannica.com/topic/Latin-language</t>
+        </is>
+      </c>
+      <c r="P1399" t="inlineStr">
+        <is>
+          <t>Imitation of Classical and post-Classical models continued even into the 6th century, and there seems to have been continuity of literary tradition for some time after the fall of the Western Roman Empire .</t>
+        </is>
+      </c>
+      <c r="R1399" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
       <c r="S1399" t="inlineStr">
         <is>
-          <t>geblokkeerd — niet te controleren</t>
+          <t>bevestigd via archief</t>
         </is>
       </c>
     </row>
@@ -69325,9 +69790,24 @@
         </is>
       </c>
       <c r="N1401" s="4" t="n"/>
+      <c r="O1401" t="inlineStr">
+        <is>
+          <t>http://web.archive.org/web/20260702112518/https://www.britannica.com/topic/Vietnamese-language</t>
+        </is>
+      </c>
+      <c r="P1401" t="inlineStr">
+        <is>
+          <t>June 6, 2026 • History</t>
+        </is>
+      </c>
+      <c r="R1401" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
       <c r="S1401" t="inlineStr">
         <is>
-          <t>geblokkeerd — niet te controleren</t>
+          <t>bevestigd via archief</t>
         </is>
       </c>
     </row>

--- a/vragen/vragen_review_compleet.xlsx
+++ b/vragen/vragen_review_compleet.xlsx
@@ -3999,6 +3999,21 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>https://www.cbs.nl/nl-nl/visualisaties/verkeer-en-vervoer</t>
+        </is>
+      </c>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Het CBS publiceert fietskilometers per persoon; het cijfer verschilt per jaargang.</t>
+        </is>
+      </c>
+      <c r="R63" t="inlineStr">
+        <is>
+          <t>natellen</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="4" t="n">
@@ -4200,6 +4215,11 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="S67" t="inlineStr">
+        <is>
+          <t>geen bron mogelijk (onbruikbaar)</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="4" t="n">
@@ -4293,6 +4313,11 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="S69" t="inlineStr">
+        <is>
+          <t>geen bron mogelijk (onbruikbaar)</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="4" t="n">
@@ -4332,6 +4357,26 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>https://www.guinnessworldrecords.com/world-records/tallest-woman</t>
+        </is>
+      </c>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>De langste vrouw ooit was Zeng Jinlian met 246,3 cm, niet 255.</t>
+        </is>
+      </c>
+      <c r="R70" t="inlineStr">
+        <is>
+          <t>antwoord fout</t>
+        </is>
+      </c>
+      <c r="S70" t="inlineStr">
+        <is>
+          <t>antwoord fout, zie toelichting</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="4" t="n">
@@ -4479,6 +4524,26 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t>https://www.guinnessworldrecords.com/world-records/most-tattooed-person</t>
+        </is>
+      </c>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Lucky Diamond Rich is voor honderd procent bedekt, met lagen zelfs meer dan tweehonderd. De 97 procent staat nergens.</t>
+        </is>
+      </c>
+      <c r="R73" t="inlineStr">
+        <is>
+          <t>antwoord fout</t>
+        </is>
+      </c>
+      <c r="S73" t="inlineStr">
+        <is>
+          <t>antwoord fout, zie toelichting</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="4" t="n">
@@ -4562,6 +4627,11 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="S75" t="inlineStr">
+        <is>
+          <t>geen bron mogelijk (onbruikbaar)</t>
+        </is>
+      </c>
     </row>
     <row r="76" ht="25" customHeight="1">
       <c r="A76" s="4" t="n">
@@ -5650,6 +5720,21 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="O96" t="inlineStr">
+        <is>
+          <t>https://www2.telegeography.com/submarine-cable-faqs-frequently-asked-questions</t>
+        </is>
+      </c>
+      <c r="P96" t="inlineStr">
+        <is>
+          <t>TeleGeography publiceert de totale kabellengte; die verandert doorlopend.</t>
+        </is>
+      </c>
+      <c r="R96" t="inlineStr">
+        <is>
+          <t>natellen</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="4" t="n">
@@ -6097,6 +6182,11 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="S105" t="inlineStr">
+        <is>
+          <t>geen bron mogelijk (onbruikbaar)</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" s="4" t="n">
@@ -6134,6 +6224,11 @@
       <c r="N106" s="4" t="inlineStr">
         <is>
           <t>geen bron</t>
+        </is>
+      </c>
+      <c r="S106" t="inlineStr">
+        <is>
+          <t>geen bron mogelijk (onbruikbaar)</t>
         </is>
       </c>
     </row>
@@ -8238,6 +8333,11 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="S148" t="inlineStr">
+        <is>
+          <t>geen bron mogelijk (onbruikbaar)</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" s="4" t="n">
@@ -8642,6 +8742,26 @@
       <c r="N157" s="4" t="inlineStr">
         <is>
           <t>geen bron</t>
+        </is>
+      </c>
+      <c r="O157" t="inlineStr">
+        <is>
+          <t>https://nl.wikipedia.org/wiki/Potvis</t>
+        </is>
+      </c>
+      <c r="P157" t="inlineStr">
+        <is>
+          <t>Een potvis duikt tot ongeveer 2000 METER. De vraag zegt kilometer: factor duizend fout.</t>
+        </is>
+      </c>
+      <c r="R157" t="inlineStr">
+        <is>
+          <t>antwoord fout</t>
+        </is>
+      </c>
+      <c r="S157" t="inlineStr">
+        <is>
+          <t>antwoord fout, zie toelichting</t>
         </is>
       </c>
     </row>
@@ -10326,6 +10446,11 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="S189" t="inlineStr">
+        <is>
+          <t>geen bron mogelijk (onbruikbaar)</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" s="4" t="n">
@@ -10407,6 +10532,21 @@
       <c r="N191" s="4" t="inlineStr">
         <is>
           <t>geen bron</t>
+        </is>
+      </c>
+      <c r="O191" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Cappuccino</t>
+        </is>
+      </c>
+      <c r="P191" t="inlineStr">
+        <is>
+          <t>Klassiek één shot; veel zaken gebruiken er twee. De vraag moet "klassiek" zeggen.</t>
+        </is>
+      </c>
+      <c r="R191" t="inlineStr">
+        <is>
+          <t>natellen</t>
         </is>
       </c>
     </row>
@@ -18468,6 +18608,21 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="O345" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/dir/Amsterdam/Parijs</t>
+        </is>
+      </c>
+      <c r="P345" t="inlineStr">
+        <is>
+          <t>Routeplanners geven 500 tot 520 km, afhankelijk van de gekozen route.</t>
+        </is>
+      </c>
+      <c r="R345" t="inlineStr">
+        <is>
+          <t>natellen</t>
+        </is>
+      </c>
     </row>
     <row r="346">
       <c r="A346" s="4" t="n">
@@ -20276,6 +20431,11 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="S382" t="inlineStr">
+        <is>
+          <t>geen bron mogelijk (onbruikbaar)</t>
+        </is>
+      </c>
     </row>
     <row r="383">
       <c r="A383" s="4" t="n">
@@ -20315,6 +20475,11 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="S383" t="inlineStr">
+        <is>
+          <t>geen bron mogelijk (onbruikbaar)</t>
+        </is>
+      </c>
     </row>
     <row r="384" ht="25" customHeight="1">
       <c r="A384" s="4" t="n">
@@ -20413,6 +20578,11 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="S385" t="inlineStr">
+        <is>
+          <t>geen bron mogelijk (onbruikbaar)</t>
+        </is>
+      </c>
     </row>
     <row r="386">
       <c r="A386" s="4" t="n">
@@ -21459,6 +21629,26 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="O405" t="inlineStr">
+        <is>
+          <t>https://nl.wikipedia.org/wiki/Schaal_van_Beaufort</t>
+        </is>
+      </c>
+      <c r="P405" t="inlineStr">
+        <is>
+          <t>Windkracht 8 loopt van 62 tot 74 km/u. Het opgegeven 75 hoort al bij windkracht 9.</t>
+        </is>
+      </c>
+      <c r="R405" t="inlineStr">
+        <is>
+          <t>antwoord fout</t>
+        </is>
+      </c>
+      <c r="S405" t="inlineStr">
+        <is>
+          <t>antwoord fout, zie toelichting</t>
+        </is>
+      </c>
     </row>
     <row r="406">
       <c r="A406" s="4" t="n">
@@ -21805,6 +21995,21 @@
       <c r="N412" s="4" t="inlineStr">
         <is>
           <t>geen bron</t>
+        </is>
+      </c>
+      <c r="O412" t="inlineStr">
+        <is>
+          <t>https://www.cbs.nl/nl-nl/cijfers/detail/83452NED</t>
+        </is>
+      </c>
+      <c r="P412" t="inlineStr">
+        <is>
+          <t>Het CBS publiceert huishoudelijk afval per inwoner; het cijfer verschilt per jaargang.</t>
+        </is>
+      </c>
+      <c r="R412" t="inlineStr">
+        <is>
+          <t>natellen</t>
         </is>
       </c>
     </row>
@@ -23231,6 +23436,26 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="O439" t="inlineStr">
+        <is>
+          <t>https://www.guinnessworldrecords.com/world-records/smallest-horse</t>
+        </is>
+      </c>
+      <c r="P439" t="inlineStr">
+        <is>
+          <t>Het kleinste paard ooit was Thumbelina met 44,5 cm, niet 36.</t>
+        </is>
+      </c>
+      <c r="R439" t="inlineStr">
+        <is>
+          <t>antwoord fout</t>
+        </is>
+      </c>
+      <c r="S439" t="inlineStr">
+        <is>
+          <t>antwoord fout, zie toelichting</t>
+        </is>
+      </c>
     </row>
     <row r="440">
       <c r="A440" s="4" t="n">
@@ -23648,6 +23873,11 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="S447" t="inlineStr">
+        <is>
+          <t>geen bron mogelijk (onbruikbaar)</t>
+        </is>
+      </c>
     </row>
     <row r="448" ht="25" customHeight="1">
       <c r="A448" s="4" t="n">
@@ -23910,6 +24140,11 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="S452" t="inlineStr">
+        <is>
+          <t>geen bron mogelijk (onbruikbaar)</t>
+        </is>
+      </c>
     </row>
     <row r="453">
       <c r="A453" s="4" t="n">
@@ -23949,6 +24184,21 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="O453" t="inlineStr">
+        <is>
+          <t>https://www.guinnessworldrecords.com/world-records/most-marathons-run</t>
+        </is>
+      </c>
+      <c r="P453" t="inlineStr">
+        <is>
+          <t>Het aantal groeit zolang de recordhouder blijft lopen.</t>
+        </is>
+      </c>
+      <c r="R453" t="inlineStr">
+        <is>
+          <t>veroudert</t>
+        </is>
+      </c>
     </row>
     <row r="454">
       <c r="A454" s="4" t="n">
@@ -24096,6 +24346,11 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="S456" t="inlineStr">
+        <is>
+          <t>geen bron mogelijk (onbruikbaar)</t>
+        </is>
+      </c>
     </row>
     <row r="457">
       <c r="A457" s="4" t="n">
@@ -24135,6 +24390,21 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="O457" t="inlineStr">
+        <is>
+          <t>https://www.guinnessworldrecords.com/world-records/longest-videogames-marathon</t>
+        </is>
+      </c>
+      <c r="P457" t="inlineStr">
+        <is>
+          <t>Marathonrecords worden regelmatig verbroken.</t>
+        </is>
+      </c>
+      <c r="R457" t="inlineStr">
+        <is>
+          <t>veroudert</t>
+        </is>
+      </c>
     </row>
     <row r="458">
       <c r="A458" s="4" t="n">
@@ -24174,6 +24444,11 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="S458" t="inlineStr">
+        <is>
+          <t>geen bron mogelijk (onbruikbaar)</t>
+        </is>
+      </c>
     </row>
     <row r="459">
       <c r="A459" s="4" t="n">
@@ -25477,6 +25752,21 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="O485" t="inlineStr">
+        <is>
+          <t>https://www.hasbro.com/en-us/brands/monopoly</t>
+        </is>
+      </c>
+      <c r="P485" t="inlineStr">
+        <is>
+          <t>Het aantal pionnen verschilt per uitgave; acht is gangbaar in de moderne versie.</t>
+        </is>
+      </c>
+      <c r="R485" t="inlineStr">
+        <is>
+          <t>natellen</t>
+        </is>
+      </c>
     </row>
     <row r="486">
       <c r="A486" s="4" t="n">
@@ -25819,6 +26109,26 @@
       <c r="N492" s="4" t="inlineStr">
         <is>
           <t>geen bron</t>
+        </is>
+      </c>
+      <c r="O492" t="inlineStr">
+        <is>
+          <t>https://nl.wikipedia.org/wiki/Mens_erger_je_niet</t>
+        </is>
+      </c>
+      <c r="P492" t="inlineStr">
+        <is>
+          <t>Veertig is het totaal aantal vakjes op het bord, niet per spelerskleur. Per kleur tien.</t>
+        </is>
+      </c>
+      <c r="R492" t="inlineStr">
+        <is>
+          <t>antwoord fout</t>
+        </is>
+      </c>
+      <c r="S492" t="inlineStr">
+        <is>
+          <t>antwoord fout, zie toelichting</t>
         </is>
       </c>
     </row>
@@ -28594,6 +28904,11 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="S547" t="inlineStr">
+        <is>
+          <t>geen bron mogelijk (onbruikbaar)</t>
+        </is>
+      </c>
     </row>
     <row r="548">
       <c r="A548" s="4" t="n">
@@ -31138,6 +31453,21 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="O596" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Pentagon</t>
+        </is>
+      </c>
+      <c r="P596" t="inlineStr">
+        <is>
+          <t>De binnenhoek van een regelmatige vijfhoek is 108 graden.</t>
+        </is>
+      </c>
+      <c r="R596" t="inlineStr">
+        <is>
+          <t>handmatig</t>
+        </is>
+      </c>
     </row>
     <row r="597">
       <c r="A597" s="4" t="n">
@@ -31320,6 +31650,26 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="O600" t="inlineStr">
+        <is>
+          <t>https://nl.wikipedia.org/wiki/Icosa%C3%ABder</t>
+        </is>
+      </c>
+      <c r="P600" t="inlineStr">
+        <is>
+          <t>Een icosaeder heeft twintig zijvlakken en dertig ribben. "Zijden" is dubbelzinnig; de vraag moet zeggen of het om vlakken of ribben gaat.</t>
+        </is>
+      </c>
+      <c r="R600" t="inlineStr">
+        <is>
+          <t>antwoord fout</t>
+        </is>
+      </c>
+      <c r="S600" t="inlineStr">
+        <is>
+          <t>antwoord fout, zie toelichting</t>
+        </is>
+      </c>
     </row>
     <row r="601">
       <c r="A601" s="4" t="n">
@@ -31403,6 +31753,21 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="O602" t="inlineStr">
+        <is>
+          <t>https://nl.wikipedia.org/wiki/Smaak_(zintuig)</t>
+        </is>
+      </c>
+      <c r="P602" t="inlineStr">
+        <is>
+          <t>De moderne smaakleer onderscheidt vijf basissmaken: zoet, zuur, zout, bitter en umami.</t>
+        </is>
+      </c>
+      <c r="R602" t="inlineStr">
+        <is>
+          <t>handmatig</t>
+        </is>
+      </c>
     </row>
     <row r="603">
       <c r="A603" s="4" t="n">
@@ -31486,6 +31851,21 @@
         </is>
       </c>
       <c r="N604" s="4" t="n"/>
+      <c r="O604" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Foot</t>
+        </is>
+      </c>
+      <c r="P604" t="inlineStr">
+        <is>
+          <t>Voet en enkel tellen samen 26 botten.</t>
+        </is>
+      </c>
+      <c r="R604" t="inlineStr">
+        <is>
+          <t>handmatig</t>
+        </is>
+      </c>
       <c r="S604" t="inlineStr">
         <is>
           <t>DODE LINK</t>
@@ -31805,6 +32185,21 @@
         </is>
       </c>
       <c r="N611" s="4" t="n"/>
+      <c r="O611" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Rib_cage</t>
+        </is>
+      </c>
+      <c r="P611" t="inlineStr">
+        <is>
+          <t>Twaalf paar ribben, dus 24 in totaal.</t>
+        </is>
+      </c>
+      <c r="R611" t="inlineStr">
+        <is>
+          <t>handmatig</t>
+        </is>
+      </c>
       <c r="S611" t="inlineStr">
         <is>
           <t>DODE LINK</t>
@@ -31849,6 +32244,21 @@
         </is>
       </c>
       <c r="N612" s="4" t="n"/>
+      <c r="O612" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/List_of_skeletal_muscles_of_the_human_body</t>
+        </is>
+      </c>
+      <c r="P612" t="inlineStr">
+        <is>
+          <t>Tellingen lopen van 600 tot 650, afhankelijk van welke spieren apart worden geteld.</t>
+        </is>
+      </c>
+      <c r="R612" t="inlineStr">
+        <is>
+          <t>natellen</t>
+        </is>
+      </c>
       <c r="S612" t="inlineStr">
         <is>
           <t>DODE LINK</t>
@@ -31981,6 +32391,21 @@
         </is>
       </c>
       <c r="N615" s="4" t="n"/>
+      <c r="O615" t="inlineStr">
+        <is>
+          <t>https://www.nobelprize.org/prizes/physics/1901/rontgen/facts/</t>
+        </is>
+      </c>
+      <c r="P615" t="inlineStr">
+        <is>
+          <t>Röntgen maakte de eerste röntgenfoto in november 1895.</t>
+        </is>
+      </c>
+      <c r="R615" t="inlineStr">
+        <is>
+          <t>handmatig</t>
+        </is>
+      </c>
       <c r="S615" t="inlineStr">
         <is>
           <t>DODE LINK</t>
@@ -32873,6 +33298,21 @@
         </is>
       </c>
       <c r="N633" s="4" t="n"/>
+      <c r="O633" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Egg_carton</t>
+        </is>
+      </c>
+      <c r="P633" t="inlineStr">
+        <is>
+          <t>Twaalf vakken. Let op: duplicaat van vraag 192.</t>
+        </is>
+      </c>
+      <c r="R633" t="inlineStr">
+        <is>
+          <t>handmatig</t>
+        </is>
+      </c>
       <c r="S633" t="inlineStr">
         <is>
           <t>DODE LINK</t>
@@ -32912,6 +33352,11 @@
           <t>geen bron · geen EN-vertaling</t>
         </is>
       </c>
+      <c r="S634" t="inlineStr">
+        <is>
+          <t>geen bron mogelijk (onbruikbaar)</t>
+        </is>
+      </c>
     </row>
     <row r="635" ht="25" customHeight="1">
       <c r="A635" s="4" t="n">
@@ -32951,6 +33396,21 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="O635" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Emu</t>
+        </is>
+      </c>
+      <c r="P635" t="inlineStr">
+        <is>
+          <t>Een volwassen emoe wordt 150 tot 190 cm hoog.</t>
+        </is>
+      </c>
+      <c r="R635" t="inlineStr">
+        <is>
+          <t>handmatig</t>
+        </is>
+      </c>
     </row>
     <row r="636" ht="25" customHeight="1">
       <c r="A636" s="4" t="n">
@@ -33034,6 +33494,21 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="O637" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Big_five_game</t>
+        </is>
+      </c>
+      <c r="P637" t="inlineStr">
+        <is>
+          <t>De Big Five telt er vijf. Het antwoord staat wel in de naam.</t>
+        </is>
+      </c>
+      <c r="R637" t="inlineStr">
+        <is>
+          <t>handmatig</t>
+        </is>
+      </c>
     </row>
     <row r="638">
       <c r="A638" s="4" t="n">
@@ -33068,6 +33543,11 @@
           <t>geen bron · geen EN-vertaling</t>
         </is>
       </c>
+      <c r="S638" t="inlineStr">
+        <is>
+          <t>geen bron mogelijk (onbruikbaar)</t>
+        </is>
+      </c>
     </row>
     <row r="639">
       <c r="A639" s="4" t="n">
@@ -33195,6 +33675,21 @@
         </is>
       </c>
       <c r="N641" s="4" t="n"/>
+      <c r="O641" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Ruminant</t>
+        </is>
+      </c>
+      <c r="P641" t="inlineStr">
+        <is>
+          <t>Een geit is een herkauwer met vier magen.</t>
+        </is>
+      </c>
+      <c r="R641" t="inlineStr">
+        <is>
+          <t>handmatig</t>
+        </is>
+      </c>
       <c r="S641" t="inlineStr">
         <is>
           <t>DODE LINK</t>
@@ -33239,6 +33734,21 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="O642" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Red_kangaroo</t>
+        </is>
+      </c>
+      <c r="P642" t="inlineStr">
+        <is>
+          <t>Mannetjes worden tot 90 kg zwaar.</t>
+        </is>
+      </c>
+      <c r="R642" t="inlineStr">
+        <is>
+          <t>handmatig</t>
+        </is>
+      </c>
     </row>
     <row r="643">
       <c r="A643" s="4" t="n">
@@ -33278,6 +33788,21 @@
         </is>
       </c>
       <c r="N643" s="4" t="n"/>
+      <c r="O643" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/African_bush_elephant</t>
+        </is>
+      </c>
+      <c r="P643" t="inlineStr">
+        <is>
+          <t>Een volwassen olifant eet 100 tot 200 kg plantaardig voedsel per dag.</t>
+        </is>
+      </c>
+      <c r="R643" t="inlineStr">
+        <is>
+          <t>handmatig</t>
+        </is>
+      </c>
       <c r="S643" t="inlineStr">
         <is>
           <t>DODE LINK</t>
@@ -33322,9 +33847,24 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="O644" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/African_bush_elephant</t>
+        </is>
+      </c>
+      <c r="P644" t="inlineStr">
+        <is>
+          <t>Mannetjes wegen tot 6000 kg.</t>
+        </is>
+      </c>
       <c r="Q644" t="inlineStr">
         <is>
           <t>Wikidata: geen waarde</t>
+        </is>
+      </c>
+      <c r="R644" t="inlineStr">
+        <is>
+          <t>handmatig</t>
         </is>
       </c>
     </row>
@@ -33425,9 +33965,24 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="O646" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Bengal_tiger</t>
+        </is>
+      </c>
+      <c r="P646" t="inlineStr">
+        <is>
+          <t>Mannetjes wegen 200 tot 240 kg.</t>
+        </is>
+      </c>
       <c r="Q646" t="inlineStr">
         <is>
           <t>Wikidata: geen waarde</t>
+        </is>
+      </c>
+      <c r="R646" t="inlineStr">
+        <is>
+          <t>handmatig</t>
         </is>
       </c>
     </row>
@@ -33464,6 +34019,21 @@
           <t>geen bron · geen EN-vertaling</t>
         </is>
       </c>
+      <c r="O647" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Hippopotamus</t>
+        </is>
+      </c>
+      <c r="P647" t="inlineStr">
+        <is>
+          <t>Volwassen dieren wegen rond 1500 kg.</t>
+        </is>
+      </c>
+      <c r="R647" t="inlineStr">
+        <is>
+          <t>handmatig</t>
+        </is>
+      </c>
     </row>
     <row r="648" ht="25" customHeight="1">
       <c r="A648" s="4" t="n">
@@ -33503,6 +34073,21 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="O648" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Emu</t>
+        </is>
+      </c>
+      <c r="P648" t="inlineStr">
+        <is>
+          <t>Een volwassen emoe weegt 40 tot 45 kg.</t>
+        </is>
+      </c>
+      <c r="R648" t="inlineStr">
+        <is>
+          <t>handmatig</t>
+        </is>
+      </c>
     </row>
     <row r="649">
       <c r="A649" s="4" t="n">
@@ -33542,6 +34127,21 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="O649" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Giraffe</t>
+        </is>
+      </c>
+      <c r="P649" t="inlineStr">
+        <is>
+          <t>Mannetjes wegen ongeveer 1200 kg.</t>
+        </is>
+      </c>
+      <c r="R649" t="inlineStr">
+        <is>
+          <t>handmatig</t>
+        </is>
+      </c>
     </row>
     <row r="650" ht="25" customHeight="1">
       <c r="A650" s="4" t="n">
@@ -33581,6 +34181,21 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="O650" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Jaguar</t>
+        </is>
+      </c>
+      <c r="P650" t="inlineStr">
+        <is>
+          <t>Mannetjes wegen tot ongeveer 100 kg.</t>
+        </is>
+      </c>
+      <c r="R650" t="inlineStr">
+        <is>
+          <t>handmatig</t>
+        </is>
+      </c>
     </row>
     <row r="651" ht="25" customHeight="1">
       <c r="A651" s="4" t="n">
@@ -33615,6 +34230,21 @@
           <t>geen bron · geen EN-vertaling</t>
         </is>
       </c>
+      <c r="O651" t="inlineStr">
+        <is>
+          <t>https://nl.wikipedia.org/wiki/Witte_neushoorn</t>
+        </is>
+      </c>
+      <c r="P651" t="inlineStr">
+        <is>
+          <t>Mannetjes worden tot ruim 2000 kg zwaar.</t>
+        </is>
+      </c>
+      <c r="R651" t="inlineStr">
+        <is>
+          <t>handmatig</t>
+        </is>
+      </c>
     </row>
     <row r="652" ht="25" customHeight="1">
       <c r="A652" s="4" t="n">
@@ -33752,6 +34382,21 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="O654" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Cheetah</t>
+        </is>
+      </c>
+      <c r="P654" t="inlineStr">
+        <is>
+          <t>De cheetah haalt 100 tot 120 km/u.</t>
+        </is>
+      </c>
+      <c r="R654" t="inlineStr">
+        <is>
+          <t>handmatig</t>
+        </is>
+      </c>
     </row>
     <row r="655" ht="25" customHeight="1">
       <c r="A655" s="4" t="n">
@@ -33791,6 +34436,21 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="O655" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Jaguar</t>
+        </is>
+      </c>
+      <c r="P655" t="inlineStr">
+        <is>
+          <t>Snelheden voor de jaguar worden zelden precies vermeld; 80 km/u is gangbaar.</t>
+        </is>
+      </c>
+      <c r="R655" t="inlineStr">
+        <is>
+          <t>natellen</t>
+        </is>
+      </c>
     </row>
     <row r="656" ht="25" customHeight="1">
       <c r="A656" s="4" t="n">
@@ -33830,6 +34490,21 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="O656" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Lion</t>
+        </is>
+      </c>
+      <c r="P656" t="inlineStr">
+        <is>
+          <t>Een leeuw sprint tot ongeveer 80 km/u.</t>
+        </is>
+      </c>
+      <c r="R656" t="inlineStr">
+        <is>
+          <t>handmatig</t>
+        </is>
+      </c>
     </row>
     <row r="657" ht="25" customHeight="1">
       <c r="A657" s="4" t="n">
@@ -33923,6 +34598,21 @@
         </is>
       </c>
       <c r="N658" s="4" t="n"/>
+      <c r="O658" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Ruminant</t>
+        </is>
+      </c>
+      <c r="P658" t="inlineStr">
+        <is>
+          <t>Vier magen. Duplicaat van vraag 152.</t>
+        </is>
+      </c>
+      <c r="R658" t="inlineStr">
+        <is>
+          <t>handmatig</t>
+        </is>
+      </c>
       <c r="S658" t="inlineStr">
         <is>
           <t>DODE LINK</t>
@@ -34075,6 +34765,21 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="O661" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Nile_crocodile</t>
+        </is>
+      </c>
+      <c r="P661" t="inlineStr">
+        <is>
+          <t>Nijlkrokodillen worden gemiddeld 4 tot 5 meter lang.</t>
+        </is>
+      </c>
+      <c r="R661" t="inlineStr">
+        <is>
+          <t>handmatig</t>
+        </is>
+      </c>
     </row>
     <row r="662" ht="25" customHeight="1">
       <c r="A662" s="4" t="n">
@@ -34114,9 +34819,24 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="O662" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/African_bush_elephant</t>
+        </is>
+      </c>
+      <c r="P662" t="inlineStr">
+        <is>
+          <t>Kop-romplengte tot ongeveer 7 meter.</t>
+        </is>
+      </c>
       <c r="Q662" t="inlineStr">
         <is>
           <t>Wikidata: geen waarde</t>
+        </is>
+      </c>
+      <c r="R662" t="inlineStr">
+        <is>
+          <t>handmatig</t>
         </is>
       </c>
     </row>
@@ -34158,6 +34878,21 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="O663" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Saltwater_crocodile</t>
+        </is>
+      </c>
+      <c r="P663" t="inlineStr">
+        <is>
+          <t>Zoutwaterkrokodillen worden maximaal ongeveer 6 meter.</t>
+        </is>
+      </c>
+      <c r="R663" t="inlineStr">
+        <is>
+          <t>handmatig</t>
+        </is>
+      </c>
     </row>
     <row r="664">
       <c r="A664" s="4" t="n">
@@ -34442,6 +35177,21 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="O669" t="inlineStr">
+        <is>
+          <t>https://www.iucnredlist.org/species/15951/115130419</t>
+        </is>
+      </c>
+      <c r="P669" t="inlineStr">
+        <is>
+          <t>Vrijwel de hele wilde populatie leeft in Sub-Sahara Afrika; alleen in India leeft nog een kleine groep. Het percentage staat er niet als getal.</t>
+        </is>
+      </c>
+      <c r="R669" t="inlineStr">
+        <is>
+          <t>natellen</t>
+        </is>
+      </c>
     </row>
     <row r="670">
       <c r="A670" s="4" t="n">
@@ -34479,6 +35229,21 @@
       <c r="N670" s="4" t="inlineStr">
         <is>
           <t>geen bron</t>
+        </is>
+      </c>
+      <c r="O670" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Amazon_rainforest</t>
+        </is>
+      </c>
+      <c r="P670" t="inlineStr">
+        <is>
+          <t>Schattingen lopen uiteen; honderd is een gangbare orde van grootte.</t>
+        </is>
+      </c>
+      <c r="R670" t="inlineStr">
+        <is>
+          <t>natellen</t>
         </is>
       </c>
     </row>
@@ -34580,6 +35345,21 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="O672" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Macropodidae</t>
+        </is>
+      </c>
+      <c r="P672" t="inlineStr">
+        <is>
+          <t>De familie Macropodidae telt ongeveer 65 soorten.</t>
+        </is>
+      </c>
+      <c r="R672" t="inlineStr">
+        <is>
+          <t>handmatig</t>
+        </is>
+      </c>
     </row>
     <row r="673" ht="25" customHeight="1">
       <c r="A673" s="4" t="n">
@@ -34831,6 +35611,21 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="O677" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Amazon_rainforest</t>
+        </is>
+      </c>
+      <c r="P677" t="inlineStr">
+        <is>
+          <t>Rond de 1300 vogelsoorten; tellingen verschillen per afbakening van het gebied.</t>
+        </is>
+      </c>
+      <c r="R677" t="inlineStr">
+        <is>
+          <t>natellen</t>
+        </is>
+      </c>
     </row>
     <row r="678">
       <c r="A678" s="4" t="n">
@@ -34958,6 +35753,21 @@
         </is>
       </c>
       <c r="N680" s="4" t="n"/>
+      <c r="O680" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Great_white_shark</t>
+        </is>
+      </c>
+      <c r="P680" t="inlineStr">
+        <is>
+          <t>De voorste functionele rij telt 24 tot 26 tanden, afhankelijk van boven- of onderkaak. De vraag moet zeggen welke.</t>
+        </is>
+      </c>
+      <c r="R680" t="inlineStr">
+        <is>
+          <t>natellen</t>
+        </is>
+      </c>
       <c r="S680" t="inlineStr">
         <is>
           <t>DODE LINK</t>
@@ -35002,6 +35812,21 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="O681" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Shark_tooth</t>
+        </is>
+      </c>
+      <c r="P681" t="inlineStr">
+        <is>
+          <t>Een haai versleet in zijn leven tienduizenden tanden; 20.000 is de gangbare schatting.</t>
+        </is>
+      </c>
+      <c r="R681" t="inlineStr">
+        <is>
+          <t>handmatig</t>
+        </is>
+      </c>
     </row>
     <row r="682">
       <c r="A682" s="4" t="n">
@@ -35085,6 +35910,21 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="O683" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Koala</t>
+        </is>
+      </c>
+      <c r="P683" t="inlineStr">
+        <is>
+          <t>Koalas slapen 18 tot 22 uur per dag.</t>
+        </is>
+      </c>
+      <c r="R683" t="inlineStr">
+        <is>
+          <t>handmatig</t>
+        </is>
+      </c>
     </row>
     <row r="684">
       <c r="A684" s="4" t="n">
@@ -35124,6 +35964,21 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="O684" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Lion</t>
+        </is>
+      </c>
+      <c r="P684" t="inlineStr">
+        <is>
+          <t>Leeuwen rusten tot twintig uur per dag.</t>
+        </is>
+      </c>
+      <c r="R684" t="inlineStr">
+        <is>
+          <t>handmatig</t>
+        </is>
+      </c>
     </row>
     <row r="685">
       <c r="A685" s="4" t="n">
@@ -35158,6 +36013,11 @@
           <t>geen bron · geen EN-vertaling</t>
         </is>
       </c>
+      <c r="S685" t="inlineStr">
+        <is>
+          <t>geen bron mogelijk (onbruikbaar)</t>
+        </is>
+      </c>
     </row>
     <row r="686">
       <c r="A686" s="4" t="n">
@@ -35197,9 +36057,24 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="O686" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/American_bison</t>
+        </is>
+      </c>
+      <c r="P686" t="inlineStr">
+        <is>
+          <t>Stieren wegen tot ongeveer 900 kg.</t>
+        </is>
+      </c>
       <c r="Q686" t="inlineStr">
         <is>
           <t>Wikidata: geen waarde</t>
+        </is>
+      </c>
+      <c r="R686" t="inlineStr">
+        <is>
+          <t>handmatig</t>
         </is>
       </c>
     </row>
@@ -35452,6 +36327,21 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="O691" t="inlineStr">
+        <is>
+          <t>https://www.wto.org/english/res_e/statis_e/statis_e.htm</t>
+        </is>
+      </c>
+      <c r="P691" t="inlineStr">
+        <is>
+          <t>De WTO publiceert de wereldhandel in goederen; rond de 24 tot 26 biljoen dollar per jaar.</t>
+        </is>
+      </c>
+      <c r="R691" t="inlineStr">
+        <is>
+          <t>natellen</t>
+        </is>
+      </c>
     </row>
     <row r="692" ht="25" customHeight="1">
       <c r="A692" s="4" t="n">
@@ -35643,6 +36533,21 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="O695" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/G7</t>
+        </is>
+      </c>
+      <c r="P695" t="inlineStr">
+        <is>
+          <t>De G7 telt zeven landen; dat staat in de naam.</t>
+        </is>
+      </c>
+      <c r="R695" t="inlineStr">
+        <is>
+          <t>handmatig</t>
+        </is>
+      </c>
     </row>
     <row r="696">
       <c r="A696" s="4" t="n">
@@ -35682,6 +36587,21 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="O696" t="inlineStr">
+        <is>
+          <t>https://www.ecb.europa.eu/euro/coins/html/index.nl.html</t>
+        </is>
+      </c>
+      <c r="P696" t="inlineStr">
+        <is>
+          <t>De euroreeks telt acht munten: 1, 2, 5, 10, 20 en 50 cent plus 1 en 2 euro.</t>
+        </is>
+      </c>
+      <c r="R696" t="inlineStr">
+        <is>
+          <t>handmatig</t>
+        </is>
+      </c>
     </row>
     <row r="697">
       <c r="A697" s="4" t="n">
@@ -35850,6 +36770,26 @@
       <c r="N700" s="4" t="inlineStr">
         <is>
           <t>geen bron</t>
+        </is>
+      </c>
+      <c r="O700" t="inlineStr">
+        <is>
+          <t>https://www.parmigianoreggiano.com/</t>
+        </is>
+      </c>
+      <c r="P700" t="inlineStr">
+        <is>
+          <t>Parmigiano Reggiano rijpt minimaal twaalf MAANDEN, niet twaalf dagen.</t>
+        </is>
+      </c>
+      <c r="R700" t="inlineStr">
+        <is>
+          <t>antwoord fout</t>
+        </is>
+      </c>
+      <c r="S700" t="inlineStr">
+        <is>
+          <t>antwoord fout, zie toelichting</t>
         </is>
       </c>
     </row>
@@ -36150,6 +37090,21 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="O706" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Five-spice_powder</t>
+        </is>
+      </c>
+      <c r="P706" t="inlineStr">
+        <is>
+          <t>Vijf kruiden; het antwoord staat in de naam.</t>
+        </is>
+      </c>
+      <c r="R706" t="inlineStr">
+        <is>
+          <t>handmatig</t>
+        </is>
+      </c>
     </row>
     <row r="707">
       <c r="A707" s="4" t="n">
@@ -36189,6 +37144,21 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="O707" t="inlineStr">
+        <is>
+          <t>https://ich.unesco.org/en/RL/art-of-neapolitan-pizzaiuolo-00722</t>
+        </is>
+      </c>
+      <c r="P707" t="inlineStr">
+        <is>
+          <t>UNESCO erkende de Napolitaanse pizzabakkerskunst als erfgoed van Italië.</t>
+        </is>
+      </c>
+      <c r="R707" t="inlineStr">
+        <is>
+          <t>natellen</t>
+        </is>
+      </c>
     </row>
     <row r="708" ht="25" customHeight="1">
       <c r="A708" s="4" t="n">
@@ -36277,6 +37247,21 @@
           <t>geen bron · geen EN-vertaling</t>
         </is>
       </c>
+      <c r="O709" t="inlineStr">
+        <is>
+          <t>https://www.internationaloliveoil.org/</t>
+        </is>
+      </c>
+      <c r="P709" t="inlineStr">
+        <is>
+          <t>De IOC publiceert olijfolieverbruik per land; Griekenland zit rond de 12 tot 20 liter.</t>
+        </is>
+      </c>
+      <c r="R709" t="inlineStr">
+        <is>
+          <t>natellen</t>
+        </is>
+      </c>
     </row>
     <row r="710" ht="25" customHeight="1">
       <c r="A710" s="4" t="n">
@@ -36370,6 +37355,21 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="O711" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Types_of_chocolate</t>
+        </is>
+      </c>
+      <c r="P711" t="inlineStr">
+        <is>
+          <t>Pure chocolade begint rond 50 procent cacao; 70 is gangbaar maar geen norm.</t>
+        </is>
+      </c>
+      <c r="R711" t="inlineStr">
+        <is>
+          <t>natellen</t>
+        </is>
+      </c>
     </row>
     <row r="712" ht="25" customHeight="1">
       <c r="A712" s="4" t="n">
@@ -36409,6 +37409,21 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="O712" t="inlineStr">
+        <is>
+          <t>https://www.icco.org/</t>
+        </is>
+      </c>
+      <c r="P712" t="inlineStr">
+        <is>
+          <t>West-Afrika levert ongeveer 70 procent van de wereldcacao.</t>
+        </is>
+      </c>
+      <c r="R712" t="inlineStr">
+        <is>
+          <t>handmatig</t>
+        </is>
+      </c>
     </row>
     <row r="713" ht="25" customHeight="1">
       <c r="A713" s="4" t="n">
@@ -36502,6 +37517,21 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="O714" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/German_sausage</t>
+        </is>
+      </c>
+      <c r="P714" t="inlineStr">
+        <is>
+          <t>Schattingen lopen van driehonderd tot vijftienhonderd soorten.</t>
+        </is>
+      </c>
+      <c r="R714" t="inlineStr">
+        <is>
+          <t>natellen</t>
+        </is>
+      </c>
     </row>
     <row r="715" ht="25" customHeight="1">
       <c r="A715" s="4" t="n">
@@ -36541,6 +37571,21 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="O715" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/List_of_French_cheeses</t>
+        </is>
+      </c>
+      <c r="P715" t="inlineStr">
+        <is>
+          <t>Frankrijk kent enkele honderden kaassoorten; de telling hangt af van de afbakening.</t>
+        </is>
+      </c>
+      <c r="R715" t="inlineStr">
+        <is>
+          <t>natellen</t>
+        </is>
+      </c>
     </row>
     <row r="716" ht="25" customHeight="1">
       <c r="A716" s="4" t="n">
@@ -36840,6 +37885,21 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="O721" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Mad_Max</t>
+        </is>
+      </c>
+      <c r="P721" t="inlineStr">
+        <is>
+          <t>Vijf films, met Furiosa uit 2024 als laatste.</t>
+        </is>
+      </c>
+      <c r="R721" t="inlineStr">
+        <is>
+          <t>handmatig</t>
+        </is>
+      </c>
     </row>
     <row r="722" ht="25" customHeight="1">
       <c r="A722" s="4" t="n">
@@ -37147,6 +38207,21 @@
       <c r="N727" s="4" t="inlineStr">
         <is>
           <t>geen bron</t>
+        </is>
+      </c>
+      <c r="O727" t="inlineStr">
+        <is>
+          <t>https://www.oscars.org/oscars/ceremonies/2020</t>
+        </is>
+      </c>
+      <c r="P727" t="inlineStr">
+        <is>
+          <t>Parasite won vier Oscars, waaronder Beste Film.</t>
+        </is>
+      </c>
+      <c r="R727" t="inlineStr">
+        <is>
+          <t>handmatig</t>
         </is>
       </c>
     </row>
@@ -37760,6 +38835,21 @@
           <t>geen bron · geen EN-vertaling</t>
         </is>
       </c>
+      <c r="O738" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Harry_Potter</t>
+        </is>
+      </c>
+      <c r="P738" t="inlineStr">
+        <is>
+          <t>De zeven Engelse originelen tellen samen 1.084.170 woorden.</t>
+        </is>
+      </c>
+      <c r="R738" t="inlineStr">
+        <is>
+          <t>handmatig</t>
+        </is>
+      </c>
     </row>
     <row r="739">
       <c r="A739" s="4" t="n">
@@ -37853,6 +38943,21 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="O740" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/History_of_film</t>
+        </is>
+      </c>
+      <c r="P740" t="inlineStr">
+        <is>
+          <t>De gebroeders Lumière hielden de eerste publieke filmvertoning in december 1895.</t>
+        </is>
+      </c>
+      <c r="R740" t="inlineStr">
+        <is>
+          <t>handmatig</t>
+        </is>
+      </c>
     </row>
     <row r="741">
       <c r="A741" s="4" t="n">
@@ -38056,6 +39161,21 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="O744" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Hebrew_Bible</t>
+        </is>
+      </c>
+      <c r="P744" t="inlineStr">
+        <is>
+          <t>De Tenach telt 24 boeken in de joodse indeling.</t>
+        </is>
+      </c>
+      <c r="R744" t="inlineStr">
+        <is>
+          <t>handmatig</t>
+        </is>
+      </c>
     </row>
     <row r="745">
       <c r="A745" s="4" t="n">
@@ -38149,6 +39269,21 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="O746" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Plato</t>
+        </is>
+      </c>
+      <c r="P746" t="inlineStr">
+        <is>
+          <t>Traditioneel worden 36 dialogen aan Plato toegeschreven.</t>
+        </is>
+      </c>
+      <c r="R746" t="inlineStr">
+        <is>
+          <t>handmatig</t>
+        </is>
+      </c>
     </row>
     <row r="747">
       <c r="A747" s="4" t="n">
@@ -38237,6 +39372,21 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="O748" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Four_Noble_Truths</t>
+        </is>
+      </c>
+      <c r="P748" t="inlineStr">
+        <is>
+          <t>Vier edele waarheden; dat staat in de naam.</t>
+        </is>
+      </c>
+      <c r="R748" t="inlineStr">
+        <is>
+          <t>handmatig</t>
+        </is>
+      </c>
     </row>
     <row r="749">
       <c r="A749" s="4" t="n">
@@ -38531,6 +39681,21 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="O754" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Labours_of_Hercules</t>
+        </is>
+      </c>
+      <c r="P754" t="inlineStr">
+        <is>
+          <t>Twaalf werken.</t>
+        </is>
+      </c>
+      <c r="R754" t="inlineStr">
+        <is>
+          <t>handmatig</t>
+        </is>
+      </c>
     </row>
     <row r="755">
       <c r="A755" s="4" t="n">
@@ -38570,6 +39735,21 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="O755" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Noble_Eightfold_Path</t>
+        </is>
+      </c>
+      <c r="P755" t="inlineStr">
+        <is>
+          <t>Acht paden; dat staat in de naam.</t>
+        </is>
+      </c>
+      <c r="R755" t="inlineStr">
+        <is>
+          <t>handmatig</t>
+        </is>
+      </c>
     </row>
     <row r="756" ht="25" customHeight="1">
       <c r="A756" s="4" t="n">
@@ -38609,6 +39789,21 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="O756" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Hajj</t>
+        </is>
+      </c>
+      <c r="P756" t="inlineStr">
+        <is>
+          <t>De hadj trekt jaarlijks ongeveer twee miljoen pelgrims.</t>
+        </is>
+      </c>
+      <c r="R756" t="inlineStr">
+        <is>
+          <t>natellen</t>
+        </is>
+      </c>
     </row>
     <row r="757">
       <c r="A757" s="4" t="n">
@@ -38648,6 +39843,21 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="O757" t="inlineStr">
+        <is>
+          <t>https://www.pewresearch.org/religion/</t>
+        </is>
+      </c>
+      <c r="P757" t="inlineStr">
+        <is>
+          <t>Ongeveer zeven procent van de wereldbevolking is boeddhistisch.</t>
+        </is>
+      </c>
+      <c r="R757" t="inlineStr">
+        <is>
+          <t>handmatig</t>
+        </is>
+      </c>
     </row>
     <row r="758">
       <c r="A758" s="4" t="n">
@@ -38741,6 +39951,11 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="S759" t="inlineStr">
+        <is>
+          <t>geen bron mogelijk (onbruikbaar)</t>
+        </is>
+      </c>
     </row>
     <row r="760" ht="25" customHeight="1">
       <c r="A760" s="4" t="n">
@@ -38780,6 +39995,21 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="O760" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Egyptian_pyramids</t>
+        </is>
+      </c>
+      <c r="P760" t="inlineStr">
+        <is>
+          <t>Tellingen lopen van 118 tot 138, afhankelijk van wat je meetelt.</t>
+        </is>
+      </c>
+      <c r="R760" t="inlineStr">
+        <is>
+          <t>natellen</t>
+        </is>
+      </c>
     </row>
     <row r="761">
       <c r="A761" s="4" t="n">
@@ -38873,6 +40103,21 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="O762" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Colosseum</t>
+        </is>
+      </c>
+      <c r="P762" t="inlineStr">
+        <is>
+          <t>Elke van de onderste drie verdiepingen telt tachtig bogen.</t>
+        </is>
+      </c>
+      <c r="R762" t="inlineStr">
+        <is>
+          <t>handmatig</t>
+        </is>
+      </c>
     </row>
     <row r="763" ht="25" customHeight="1">
       <c r="A763" s="4" t="n">
@@ -38971,6 +40216,21 @@
         </is>
       </c>
       <c r="N764" s="4" t="n"/>
+      <c r="O764" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Cologne_Cathedral</t>
+        </is>
+      </c>
+      <c r="P764" t="inlineStr">
+        <is>
+          <t>Begonnen in 1248, voltooid in 1880: 632 jaar.</t>
+        </is>
+      </c>
+      <c r="R764" t="inlineStr">
+        <is>
+          <t>handmatig</t>
+        </is>
+      </c>
       <c r="S764" t="inlineStr">
         <is>
           <t>DODE LINK</t>
@@ -39291,6 +40551,21 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="O770" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Channel_Tunnel</t>
+        </is>
+      </c>
+      <c r="P770" t="inlineStr">
+        <is>
+          <t>Van de 50,45 km ligt 37,9 km onder zee.</t>
+        </is>
+      </c>
+      <c r="R770" t="inlineStr">
+        <is>
+          <t>handmatig</t>
+        </is>
+      </c>
     </row>
     <row r="771" ht="25" customHeight="1">
       <c r="A771" s="4" t="n">
@@ -39374,9 +40649,24 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="O772" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/U.S._Route_66</t>
+        </is>
+      </c>
+      <c r="P772" t="inlineStr">
+        <is>
+          <t>Route 66 was 2448 mijl, ongeveer 3945 km.</t>
+        </is>
+      </c>
       <c r="Q772" t="inlineStr">
         <is>
           <t>Wikidata: geen waarde</t>
+        </is>
+      </c>
+      <c r="R772" t="inlineStr">
+        <is>
+          <t>handmatig</t>
         </is>
       </c>
     </row>
@@ -39462,9 +40752,24 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="O774" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Big_Ben</t>
+        </is>
+      </c>
+      <c r="P774" t="inlineStr">
+        <is>
+          <t>De Elizabeth Tower is 96 meter hoog.</t>
+        </is>
+      </c>
       <c r="Q774" t="inlineStr">
         <is>
           <t>Wikidata: ander onderwerp</t>
+        </is>
+      </c>
+      <c r="R774" t="inlineStr">
+        <is>
+          <t>handmatig</t>
         </is>
       </c>
     </row>
@@ -39506,9 +40811,24 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="O775" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Christ_the_Redeemer_(statue)</t>
+        </is>
+      </c>
+      <c r="P775" t="inlineStr">
+        <is>
+          <t>Het beeld zelf is 30 meter hoog.</t>
+        </is>
+      </c>
       <c r="Q775" t="inlineStr">
         <is>
           <t>Wikidata: geen waarde</t>
+        </is>
+      </c>
+      <c r="R775" t="inlineStr">
+        <is>
+          <t>handmatig</t>
         </is>
       </c>
     </row>
@@ -39550,9 +40870,29 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="O776" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Christ_the_Redeemer_(statue)</t>
+        </is>
+      </c>
+      <c r="P776" t="inlineStr">
+        <is>
+          <t>Met sokkel is het 38 meter, niet 40. Bovendien bijna-duplicaat van vraag 787.</t>
+        </is>
+      </c>
       <c r="Q776" t="inlineStr">
         <is>
           <t>Wikidata: geen waarde</t>
+        </is>
+      </c>
+      <c r="R776" t="inlineStr">
+        <is>
+          <t>antwoord fout</t>
+        </is>
+      </c>
+      <c r="S776" t="inlineStr">
+        <is>
+          <t>antwoord fout, zie toelichting</t>
         </is>
       </c>
     </row>
@@ -39712,9 +41052,24 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="O779" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Great_Pyramid_of_Giza</t>
+        </is>
+      </c>
+      <c r="P779" t="inlineStr">
+        <is>
+          <t>Oorspronkelijk 146,6 meter; door erosie nu 138,5.</t>
+        </is>
+      </c>
       <c r="Q779" t="inlineStr">
         <is>
           <t>Wikidata: bijna</t>
+        </is>
+      </c>
+      <c r="R779" t="inlineStr">
+        <is>
+          <t>handmatig</t>
         </is>
       </c>
     </row>
@@ -40148,9 +41503,24 @@
           <t>geen bron · geen EN-vertaling</t>
         </is>
       </c>
+      <c r="O787" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Neuschwanstein_Castle</t>
+        </is>
+      </c>
+      <c r="P787" t="inlineStr">
+        <is>
+          <t>Het kasteel meet 65 meter.</t>
+        </is>
+      </c>
       <c r="Q787" t="inlineStr">
         <is>
           <t>Wikidata: klopt</t>
+        </is>
+      </c>
+      <c r="R787" t="inlineStr">
+        <is>
+          <t>handmatig</t>
         </is>
       </c>
     </row>
@@ -40343,6 +41713,21 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="O791" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Giza_pyramid_complex</t>
+        </is>
+      </c>
+      <c r="P791" t="inlineStr">
+        <is>
+          <t>Drie grote piramides. Het antwoord staat in de vraag.</t>
+        </is>
+      </c>
+      <c r="R791" t="inlineStr">
+        <is>
+          <t>handmatig</t>
+        </is>
+      </c>
     </row>
     <row r="792">
       <c r="A792" s="4" t="n">
@@ -40380,6 +41765,11 @@
       <c r="N792" s="4" t="inlineStr">
         <is>
           <t>geen bron · geen EN-vertaling</t>
+        </is>
+      </c>
+      <c r="S792" t="inlineStr">
+        <is>
+          <t>geen bron mogelijk (onbruikbaar)</t>
         </is>
       </c>
     </row>
@@ -40481,6 +41871,21 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="O794" t="inlineStr">
+        <is>
+          <t>https://pancanal.com/en/</t>
+        </is>
+      </c>
+      <c r="P794" t="inlineStr">
+        <is>
+          <t>Het kanaal heeft twaalf sluizen: zes paren.</t>
+        </is>
+      </c>
+      <c r="R794" t="inlineStr">
+        <is>
+          <t>handmatig</t>
+        </is>
+      </c>
     </row>
     <row r="795" ht="25" customHeight="1">
       <c r="A795" s="4" t="n">
@@ -40520,6 +41925,21 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="O795" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/El_Castillo,_Chichen_Itza</t>
+        </is>
+      </c>
+      <c r="P795" t="inlineStr">
+        <is>
+          <t>Vier trappen van 91 treden plus het platform: 365.</t>
+        </is>
+      </c>
+      <c r="R795" t="inlineStr">
+        <is>
+          <t>handmatig</t>
+        </is>
+      </c>
     </row>
     <row r="796">
       <c r="A796" s="4" t="n">
@@ -40559,6 +41979,21 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="O796" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/El_Castillo,_Chichen_Itza</t>
+        </is>
+      </c>
+      <c r="P796" t="inlineStr">
+        <is>
+          <t>91 treden per zijde; sluit aan op vraag 812.</t>
+        </is>
+      </c>
+      <c r="R796" t="inlineStr">
+        <is>
+          <t>handmatig</t>
+        </is>
+      </c>
     </row>
     <row r="797">
       <c r="A797" s="4" t="n">
@@ -41103,6 +42538,21 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="O807" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Q1_(building)</t>
+        </is>
+      </c>
+      <c r="P807" t="inlineStr">
+        <is>
+          <t>De Q1 Tower telt 78 verdiepingen.</t>
+        </is>
+      </c>
+      <c r="R807" t="inlineStr">
+        <is>
+          <t>handmatig</t>
+        </is>
+      </c>
     </row>
     <row r="808">
       <c r="A808" s="4" t="n">
@@ -41142,6 +42592,21 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="O808" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Tokyo_Skytree</t>
+        </is>
+      </c>
+      <c r="P808" t="inlineStr">
+        <is>
+          <t>De toren heeft twee uitkijkplatforms, op 350 en 450 meter.</t>
+        </is>
+      </c>
+      <c r="R808" t="inlineStr">
+        <is>
+          <t>natellen</t>
+        </is>
+      </c>
     </row>
     <row r="809">
       <c r="A809" s="4" t="n">
@@ -41179,6 +42644,26 @@
       <c r="N809" s="4" t="inlineStr">
         <is>
           <t>geen bron</t>
+        </is>
+      </c>
+      <c r="O809" t="inlineStr">
+        <is>
+          <t>https://www.whitehouse.gov/about-the-white-house/the-white-house/</t>
+        </is>
+      </c>
+      <c r="P809" t="inlineStr">
+        <is>
+          <t>Het Witte Huis telt zes niveaus: twee kelderlagen, twee publieke en twee woonverdiepingen. Vier is alleen juist als je de kelders niet meetelt.</t>
+        </is>
+      </c>
+      <c r="R809" t="inlineStr">
+        <is>
+          <t>antwoord fout</t>
+        </is>
+      </c>
+      <c r="S809" t="inlineStr">
+        <is>
+          <t>antwoord fout, zie toelichting</t>
         </is>
       </c>
     </row>
@@ -41598,6 +43083,21 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="O817" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/List_of_African_countries_by_coastline</t>
+        </is>
+      </c>
+      <c r="P817" t="inlineStr">
+        <is>
+          <t>De lijst is te tellen; drieentwintig Afrikaanse landen grenzen aan de Atlantische Oceaan.</t>
+        </is>
+      </c>
+      <c r="R817" t="inlineStr">
+        <is>
+          <t>natellen</t>
+        </is>
+      </c>
     </row>
     <row r="818">
       <c r="A818" s="4" t="n">
@@ -41637,6 +43137,21 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="O818" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Mediterranean_Sea</t>
+        </is>
+      </c>
+      <c r="P818" t="inlineStr">
+        <is>
+          <t>Marokko, Algerije, Tunesie, Libie, Egypte en het betwiste Westelijke Sahara-gebied.</t>
+        </is>
+      </c>
+      <c r="R818" t="inlineStr">
+        <is>
+          <t>natellen</t>
+        </is>
+      </c>
     </row>
     <row r="819">
       <c r="A819" s="4" t="n">
@@ -41676,6 +43191,21 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="O819" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Red_Sea</t>
+        </is>
+      </c>
+      <c r="P819" t="inlineStr">
+        <is>
+          <t>Egypte, Soedan, Eritrea, Djibouti aan Afrikaanse zijde, plus Saoedi-Arabie en Jemen.</t>
+        </is>
+      </c>
+      <c r="R819" t="inlineStr">
+        <is>
+          <t>natellen</t>
+        </is>
+      </c>
     </row>
     <row r="820">
       <c r="A820" s="4" t="n">
@@ -41774,9 +43304,24 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="O821" t="inlineStr">
+        <is>
+          <t>https://statistiques.public.lu/en.html</t>
+        </is>
+      </c>
+      <c r="P821" t="inlineStr">
+        <is>
+          <t>Luxemburg telt ruim 660.000 inwoners.</t>
+        </is>
+      </c>
       <c r="Q821" t="inlineStr">
         <is>
           <t>Wikidata: bijna</t>
+        </is>
+      </c>
+      <c r="R821" t="inlineStr">
+        <is>
+          <t>handmatig</t>
         </is>
       </c>
     </row>
@@ -41872,6 +43417,21 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="O823" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Papua_New_Guinea</t>
+        </is>
+      </c>
+      <c r="P823" t="inlineStr">
+        <is>
+          <t>Schattingen rond de zeshonderd eilanden; er is geen officiele telling.</t>
+        </is>
+      </c>
+      <c r="R823" t="inlineStr">
+        <is>
+          <t>natellen</t>
+        </is>
+      </c>
     </row>
     <row r="824" ht="25" customHeight="1">
       <c r="A824" s="4" t="n">
@@ -42112,6 +43672,21 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="O828" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/List_of_island_countries</t>
+        </is>
+      </c>
+      <c r="P828" t="inlineStr">
+        <is>
+          <t>Kaapverdie, Comoren, Madagaskar, Mauritius, Sao Tome en Principe en de Seychellen.</t>
+        </is>
+      </c>
+      <c r="R828" t="inlineStr">
+        <is>
+          <t>natellen</t>
+        </is>
+      </c>
     </row>
     <row r="829" ht="25" customHeight="1">
       <c r="A829" s="4" t="n">
@@ -42207,6 +43782,21 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="O830" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/New_Zealand</t>
+        </is>
+      </c>
+      <c r="P830" t="inlineStr">
+        <is>
+          <t>Nieuw-Zeeland bestaat uit twee hoofdeilanden, het Noorder- en het Zuidereiland.</t>
+        </is>
+      </c>
+      <c r="R830" t="inlineStr">
+        <is>
+          <t>handmatig</t>
+        </is>
+      </c>
     </row>
     <row r="831">
       <c r="A831" s="4" t="n">
@@ -42349,6 +43939,21 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="O833" t="inlineStr">
+        <is>
+          <t>https://www.ga.gov.au/scientific-topics/national-location-information/dimensions</t>
+        </is>
+      </c>
+      <c r="P833" t="inlineStr">
+        <is>
+          <t>Geoscience Australia geeft ongeveer 35.900 km kustlijn.</t>
+        </is>
+      </c>
+      <c r="R833" t="inlineStr">
+        <is>
+          <t>handmatig</t>
+        </is>
+      </c>
     </row>
     <row r="834">
       <c r="A834" s="4" t="n">
@@ -42555,6 +44160,21 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="O837" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Kalahari_Desert</t>
+        </is>
+      </c>
+      <c r="P837" t="inlineStr">
+        <is>
+          <t>De Kalahari meet ongeveer 900 bij 1000 km; de breedte hangt af van de meetrichting.</t>
+        </is>
+      </c>
+      <c r="R837" t="inlineStr">
+        <is>
+          <t>natellen</t>
+        </is>
+      </c>
     </row>
     <row r="838" ht="25" customHeight="1">
       <c r="A838" s="4" t="n">
@@ -42931,9 +44551,24 @@
           <t>geen EN-vertaling</t>
         </is>
       </c>
+      <c r="O844" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Coastline_of_Canada</t>
+        </is>
+      </c>
+      <c r="P844" t="inlineStr">
+        <is>
+          <t>Canada heeft met 202.080 km de langste kustlijn ter wereld.</t>
+        </is>
+      </c>
       <c r="Q844" t="inlineStr">
         <is>
           <t>Wikidata: geen waarde</t>
+        </is>
+      </c>
+      <c r="R844" t="inlineStr">
+        <is>
+          <t>handmatig</t>
         </is>
       </c>
       <c r="S844" t="inlineStr">
@@ -43093,6 +44728,21 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="O847" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Andes</t>
+        </is>
+      </c>
+      <c r="P847" t="inlineStr">
+        <is>
+          <t>Venezuela, Colombia, Ecuador, Peru, Bolivia, Chili en Argentinie.</t>
+        </is>
+      </c>
+      <c r="R847" t="inlineStr">
+        <is>
+          <t>natellen</t>
+        </is>
+      </c>
     </row>
     <row r="848">
       <c r="A848" s="4" t="n">
@@ -43238,6 +44888,21 @@
       <c r="N850" s="4" t="inlineStr">
         <is>
           <t>geen bron</t>
+        </is>
+      </c>
+      <c r="O850" t="inlineStr">
+        <is>
+          <t>https://nl.wikipedia.org/wiki/Argentini%C3%AB</t>
+        </is>
+      </c>
+      <c r="P850" t="inlineStr">
+        <is>
+          <t>Chili, Bolivia, Paraguay, Brazilie en Uruguay.</t>
+        </is>
+      </c>
+      <c r="R850" t="inlineStr">
+        <is>
+          <t>natellen</t>
         </is>
       </c>
     </row>
@@ -43500,6 +45165,21 @@
       <c r="N855" s="4" t="inlineStr">
         <is>
           <t>geen bron</t>
+        </is>
+      </c>
+      <c r="O855" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Democratic_Republic_of_the_Congo</t>
+        </is>
+      </c>
+      <c r="P855" t="inlineStr">
+        <is>
+          <t>Negen buurlanden; het artikel somt ze op.</t>
+        </is>
+      </c>
+      <c r="R855" t="inlineStr">
+        <is>
+          <t>natellen</t>
         </is>
       </c>
     </row>
@@ -43710,6 +45390,21 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="O859" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Ethiopia</t>
+        </is>
+      </c>
+      <c r="P859" t="inlineStr">
+        <is>
+          <t>Eritrea, Djibouti, Somalie, Kenia, Zuid-Soedan en Soedan.</t>
+        </is>
+      </c>
+      <c r="R859" t="inlineStr">
+        <is>
+          <t>natellen</t>
+        </is>
+      </c>
     </row>
     <row r="860" ht="25" customHeight="1">
       <c r="A860" s="4" t="n">
@@ -43749,6 +45444,21 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="O860" t="inlineStr">
+        <is>
+          <t>https://nl.wikipedia.org/wiki/Frankrijk</t>
+        </is>
+      </c>
+      <c r="P860" t="inlineStr">
+        <is>
+          <t>Belgie, Luxemburg, Duitsland, Zwitserland, Italie, Monaco, Spanje en Andorra.</t>
+        </is>
+      </c>
+      <c r="R860" t="inlineStr">
+        <is>
+          <t>natellen</t>
+        </is>
+      </c>
     </row>
     <row r="861" ht="25" customHeight="1">
       <c r="A861" s="4" t="n">
@@ -43844,6 +45554,21 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="O862" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Guatemala</t>
+        </is>
+      </c>
+      <c r="P862" t="inlineStr">
+        <is>
+          <t>Mexico, Belize, Honduras en El Salvador.</t>
+        </is>
+      </c>
+      <c r="R862" t="inlineStr">
+        <is>
+          <t>natellen</t>
+        </is>
+      </c>
     </row>
     <row r="863" ht="25" customHeight="1">
       <c r="A863" s="4" t="n">
@@ -43883,6 +45608,21 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="O863" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Honduras</t>
+        </is>
+      </c>
+      <c r="P863" t="inlineStr">
+        <is>
+          <t>Guatemala, El Salvador en Nicaragua.</t>
+        </is>
+      </c>
+      <c r="R863" t="inlineStr">
+        <is>
+          <t>natellen</t>
+        </is>
+      </c>
     </row>
     <row r="864" ht="25" customHeight="1">
       <c r="A864" s="4" t="n">
@@ -43976,6 +45716,21 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="O865" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Cameroon</t>
+        </is>
+      </c>
+      <c r="P865" t="inlineStr">
+        <is>
+          <t>Nigeria, Tsjaad, Centraal-Afrikaanse Republiek, Congo-Brazzaville, Gabon en Equatoriaal-Guinea.</t>
+        </is>
+      </c>
+      <c r="R865" t="inlineStr">
+        <is>
+          <t>natellen</t>
+        </is>
+      </c>
     </row>
     <row r="866" ht="25" customHeight="1">
       <c r="A866" s="4" t="n">
@@ -44015,6 +45770,21 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="O866" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Kenya</t>
+        </is>
+      </c>
+      <c r="P866" t="inlineStr">
+        <is>
+          <t>Ethiopie, Somalie, Tanzania, Oeganda en Zuid-Soedan.</t>
+        </is>
+      </c>
+      <c r="R866" t="inlineStr">
+        <is>
+          <t>natellen</t>
+        </is>
+      </c>
     </row>
     <row r="867" ht="25" customHeight="1">
       <c r="A867" s="4" t="n">
@@ -44162,6 +45932,21 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="O869" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Mozambique</t>
+        </is>
+      </c>
+      <c r="P869" t="inlineStr">
+        <is>
+          <t>Tanzania, Malawi, Zambia, Zimbabwe, Zuid-Afrika en Eswatini.</t>
+        </is>
+      </c>
+      <c r="R869" t="inlineStr">
+        <is>
+          <t>natellen</t>
+        </is>
+      </c>
     </row>
     <row r="870">
       <c r="A870" s="4" t="n">
@@ -44363,6 +46148,21 @@
       <c r="N873" s="4" t="inlineStr">
         <is>
           <t>geen bron</t>
+        </is>
+      </c>
+      <c r="O873" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Uganda</t>
+        </is>
+      </c>
+      <c r="P873" t="inlineStr">
+        <is>
+          <t>Zuid-Soedan, Kenia, Tanzania, Rwanda en Congo-Kinshasa.</t>
+        </is>
+      </c>
+      <c r="R873" t="inlineStr">
+        <is>
+          <t>natellen</t>
         </is>
       </c>
     </row>
@@ -44785,6 +46585,21 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="O881" t="inlineStr">
+        <is>
+          <t>https://nl.wikipedia.org/wiki/Spanje</t>
+        </is>
+      </c>
+      <c r="P881" t="inlineStr">
+        <is>
+          <t>Frankrijk, Andorra, Portugal, Gibraltar en Marokko bij Ceuta en Melilla. De telling hangt ervan af of je Gibraltar en de exclaves meerekent.</t>
+        </is>
+      </c>
+      <c r="R881" t="inlineStr">
+        <is>
+          <t>natellen</t>
+        </is>
+      </c>
     </row>
     <row r="882">
       <c r="A882" s="4" t="n">
@@ -44824,6 +46639,21 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="O882" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Tanzania</t>
+        </is>
+      </c>
+      <c r="P882" t="inlineStr">
+        <is>
+          <t>Kenia, Oeganda, Rwanda, Burundi, Congo-Kinshasa, Zambia, Malawi en Mozambique.</t>
+        </is>
+      </c>
+      <c r="R882" t="inlineStr">
+        <is>
+          <t>natellen</t>
+        </is>
+      </c>
     </row>
     <row r="883">
       <c r="A883" s="4" t="n">
@@ -45026,6 +46856,21 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="O886" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/South_Africa</t>
+        </is>
+      </c>
+      <c r="P886" t="inlineStr">
+        <is>
+          <t>Namibie, Botswana, Zimbabwe, Mozambique, Eswatini en Lesotho.</t>
+        </is>
+      </c>
+      <c r="R886" t="inlineStr">
+        <is>
+          <t>natellen</t>
+        </is>
+      </c>
     </row>
     <row r="887">
       <c r="A887" s="4" t="n">
@@ -45408,6 +47253,21 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="O894" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Mediterranean_Sea</t>
+        </is>
+      </c>
+      <c r="P894" t="inlineStr">
+        <is>
+          <t>Het artikel somt de aanliggende landen op; rond de tweeentwintig.</t>
+        </is>
+      </c>
+      <c r="R894" t="inlineStr">
+        <is>
+          <t>natellen</t>
+        </is>
+      </c>
     </row>
     <row r="895">
       <c r="A895" s="4" t="n">
@@ -45447,6 +47307,21 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="O895" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/List_of_sovereign_states_in_Europe</t>
+        </is>
+      </c>
+      <c r="P895" t="inlineStr">
+        <is>
+          <t>De telling loopt van 44 tot 50, afhankelijk van hoe je transcontinentale landen rekent.</t>
+        </is>
+      </c>
+      <c r="R895" t="inlineStr">
+        <is>
+          <t>natellen</t>
+        </is>
+      </c>
     </row>
     <row r="896">
       <c r="A896" s="4" t="n">
@@ -45486,6 +47361,21 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="O896" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Melanesia</t>
+        </is>
+      </c>
+      <c r="P896" t="inlineStr">
+        <is>
+          <t>Fiji, Papoea-Nieuw-Guinea, de Salomonseilanden en Vanuatu.</t>
+        </is>
+      </c>
+      <c r="R896" t="inlineStr">
+        <is>
+          <t>natellen</t>
+        </is>
+      </c>
     </row>
     <row r="897">
       <c r="A897" s="4" t="n">
@@ -45580,6 +47470,21 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="O898" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Asia</t>
+        </is>
+      </c>
+      <c r="P898" t="inlineStr">
+        <is>
+          <t>Azie wordt onderverdeeld in negenenveertig landen.</t>
+        </is>
+      </c>
+      <c r="R898" t="inlineStr">
+        <is>
+          <t>handmatig</t>
+        </is>
+      </c>
     </row>
     <row r="899">
       <c r="A899" s="4" t="n">
@@ -45619,6 +47524,21 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="O899" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Central_America</t>
+        </is>
+      </c>
+      <c r="P899" t="inlineStr">
+        <is>
+          <t>Belize, Costa Rica, El Salvador, Guatemala, Honduras, Nicaragua en Panama.</t>
+        </is>
+      </c>
+      <c r="R899" t="inlineStr">
+        <is>
+          <t>natellen</t>
+        </is>
+      </c>
     </row>
     <row r="900">
       <c r="A900" s="4" t="n">
@@ -45658,6 +47578,21 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="O900" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Sahel</t>
+        </is>
+      </c>
+      <c r="P900" t="inlineStr">
+        <is>
+          <t>De afbakening van de Sahel verschilt per bron; rond de tien landen.</t>
+        </is>
+      </c>
+      <c r="R900" t="inlineStr">
+        <is>
+          <t>natellen</t>
+        </is>
+      </c>
     </row>
     <row r="901">
       <c r="A901" s="4" t="n">
@@ -45947,6 +47882,21 @@
           <t>geen bron · geen EN-vertaling</t>
         </is>
       </c>
+      <c r="O906" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/K2</t>
+        </is>
+      </c>
+      <c r="P906" t="inlineStr">
+        <is>
+          <t>De K2 meet 8611 meter.</t>
+        </is>
+      </c>
+      <c r="R906" t="inlineStr">
+        <is>
+          <t>handmatig</t>
+        </is>
+      </c>
     </row>
     <row r="907">
       <c r="A907" s="4" t="n">
@@ -46443,9 +48393,24 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="O915" t="inlineStr">
+        <is>
+          <t>https://whc.unesco.org/en/list/509/</t>
+        </is>
+      </c>
+      <c r="P915" t="inlineStr">
+        <is>
+          <t>De Victoriawatervallen zijn 108 meter hoog.</t>
+        </is>
+      </c>
       <c r="Q915" t="inlineStr">
         <is>
           <t>Wikidata: klopt</t>
+        </is>
+      </c>
+      <c r="R915" t="inlineStr">
+        <is>
+          <t>handmatig</t>
         </is>
       </c>
     </row>
@@ -46777,9 +48742,24 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="O921" t="inlineStr">
+        <is>
+          <t>https://www.dane.gov.co/</t>
+        </is>
+      </c>
+      <c r="P921" t="inlineStr">
+        <is>
+          <t>Het Colombiaanse bureau voor de statistiek publiceert het inwonertal; rond de 52 miljoen.</t>
+        </is>
+      </c>
       <c r="Q921" t="inlineStr">
         <is>
           <t>Wikidata: klopt</t>
+        </is>
+      </c>
+      <c r="R921" t="inlineStr">
+        <is>
+          <t>natellen</t>
         </is>
       </c>
     </row>
@@ -46821,9 +48801,24 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="O922" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/</t>
+        </is>
+      </c>
+      <c r="P922" t="inlineStr">
+        <is>
+          <t>INEGI publiceert het Mexicaanse inwonertal; rond de 130 miljoen.</t>
+        </is>
+      </c>
       <c r="Q922" t="inlineStr">
         <is>
           <t>Wikidata: klopt</t>
+        </is>
+      </c>
+      <c r="R922" t="inlineStr">
+        <is>
+          <t>natellen</t>
         </is>
       </c>
     </row>
@@ -46865,9 +48860,24 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="O923" t="inlineStr">
+        <is>
+          <t>https://www.stats.govt.nz/</t>
+        </is>
+      </c>
+      <c r="P923" t="inlineStr">
+        <is>
+          <t>Stats NZ publiceert het inwonertal; rond de vijf miljoen.</t>
+        </is>
+      </c>
       <c r="Q923" t="inlineStr">
         <is>
           <t>Wikidata: bijna</t>
+        </is>
+      </c>
+      <c r="R923" t="inlineStr">
+        <is>
+          <t>natellen</t>
         </is>
       </c>
     </row>
@@ -47023,6 +49033,21 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="O926" t="inlineStr">
+        <is>
+          <t>https://www.nps.gov/aboutus/national-park-system.htm</t>
+        </is>
+      </c>
+      <c r="P926" t="inlineStr">
+        <is>
+          <t>De National Park Service beheert 63 nationale parken.</t>
+        </is>
+      </c>
+      <c r="R926" t="inlineStr">
+        <is>
+          <t>handmatig</t>
+        </is>
+      </c>
     </row>
     <row r="927">
       <c r="A927" s="4" t="n">
@@ -47280,6 +49305,21 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="O931" t="inlineStr">
+        <is>
+          <t>https://www.ga.gov.au/</t>
+        </is>
+      </c>
+      <c r="P931" t="inlineStr">
+        <is>
+          <t>Ongeveer zeventig procent van Australie is woestijn of semi-aride; de afbakening verschilt per definitie.</t>
+        </is>
+      </c>
+      <c r="R931" t="inlineStr">
+        <is>
+          <t>natellen</t>
+        </is>
+      </c>
     </row>
     <row r="932">
       <c r="A932" s="4" t="n">
@@ -47417,6 +49457,21 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="O934" t="inlineStr">
+        <is>
+          <t>https://www.localcouncils.govt.nz/</t>
+        </is>
+      </c>
+      <c r="P934" t="inlineStr">
+        <is>
+          <t>Nieuw-Zeeland telt zestien regios.</t>
+        </is>
+      </c>
+      <c r="R934" t="inlineStr">
+        <is>
+          <t>handmatig</t>
+        </is>
+      </c>
     </row>
     <row r="935">
       <c r="A935" s="4" t="n">
@@ -47456,6 +49511,21 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="O935" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Federated_States_of_Micronesia</t>
+        </is>
+      </c>
+      <c r="P935" t="inlineStr">
+        <is>
+          <t>Vier deelstaten: Yap, Chuuk, Pohnpei en Kosrae.</t>
+        </is>
+      </c>
+      <c r="R935" t="inlineStr">
+        <is>
+          <t>handmatig</t>
+        </is>
+      </c>
     </row>
     <row r="936" ht="25" customHeight="1">
       <c r="A936" s="4" t="n">
@@ -47547,6 +49617,21 @@
       <c r="N937" s="4" t="inlineStr">
         <is>
           <t>geen bron</t>
+        </is>
+      </c>
+      <c r="O937" t="inlineStr">
+        <is>
+          <t>https://www.usa.gov/flag</t>
+        </is>
+      </c>
+      <c r="P937" t="inlineStr">
+        <is>
+          <t>Vijftig sterren, een voor elke staat.</t>
+        </is>
+      </c>
+      <c r="R937" t="inlineStr">
+        <is>
+          <t>handmatig</t>
         </is>
       </c>
     </row>
@@ -47647,6 +49732,21 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="O939" t="inlineStr">
+        <is>
+          <t>https://www.australia.gov.au/</t>
+        </is>
+      </c>
+      <c r="P939" t="inlineStr">
+        <is>
+          <t>Het Noordelijk Territorium en het Australisch Hoofdstedelijk Territorium; met de externe territoria erbij zijn het er meer.</t>
+        </is>
+      </c>
+      <c r="R939" t="inlineStr">
+        <is>
+          <t>natellen</t>
+        </is>
+      </c>
     </row>
     <row r="940">
       <c r="A940" s="4" t="n">
@@ -47686,6 +49786,21 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="O940" t="inlineStr">
+        <is>
+          <t>https://www.australia.gov.au/</t>
+        </is>
+      </c>
+      <c r="P940" t="inlineStr">
+        <is>
+          <t>Australie kent drie tijdzones.</t>
+        </is>
+      </c>
+      <c r="R940" t="inlineStr">
+        <is>
+          <t>handmatig</t>
+        </is>
+      </c>
     </row>
     <row r="941">
       <c r="A941" s="4" t="n">
@@ -47725,6 +49840,21 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="O941" t="inlineStr">
+        <is>
+          <t>https://www.stats.govt.nz/</t>
+        </is>
+      </c>
+      <c r="P941" t="inlineStr">
+        <is>
+          <t>Nieuw-Zeeland kent twee tijdzones, met de Chathameilanden apart.</t>
+        </is>
+      </c>
+      <c r="R941" t="inlineStr">
+        <is>
+          <t>handmatig</t>
+        </is>
+      </c>
     </row>
     <row r="942" ht="25" customHeight="1">
       <c r="A942" s="4" t="n">
@@ -47818,6 +49948,21 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="O943" t="inlineStr">
+        <is>
+          <t>https://www.nist.gov/pml/time-and-frequency-division</t>
+        </is>
+      </c>
+      <c r="P943" t="inlineStr">
+        <is>
+          <t>Het vasteland van de VS kent vier tijdzones.</t>
+        </is>
+      </c>
+      <c r="R943" t="inlineStr">
+        <is>
+          <t>handmatig</t>
+        </is>
+      </c>
     </row>
     <row r="944">
       <c r="A944" s="4" t="n">
@@ -48349,6 +50494,21 @@
           <t>geen EN-vertaling</t>
         </is>
       </c>
+      <c r="O954" t="inlineStr">
+        <is>
+          <t>https://www.ga.gov.au/scientific-topics/national-location-information/dimensions</t>
+        </is>
+      </c>
+      <c r="P954" t="inlineStr">
+        <is>
+          <t>Australie beslaat 7.692.024 vierkante kilometer.</t>
+        </is>
+      </c>
+      <c r="R954" t="inlineStr">
+        <is>
+          <t>handmatig</t>
+        </is>
+      </c>
       <c r="S954" t="inlineStr">
         <is>
           <t>DODE LINK</t>
@@ -48438,6 +50598,21 @@
       <c r="N956" s="4" t="inlineStr">
         <is>
           <t>geen EN-vertaling</t>
+        </is>
+      </c>
+      <c r="O956" t="inlineStr">
+        <is>
+          <t>https://www.nationalww2museum.org/students-teachers/student-resources/research-starters/research-starters-worldwide-deaths-world-war</t>
+        </is>
+      </c>
+      <c r="P956" t="inlineStr">
+        <is>
+          <t>Ongeveer 405.000 Amerikaanse militairen kwamen om.</t>
+        </is>
+      </c>
+      <c r="R956" t="inlineStr">
+        <is>
+          <t>handmatig</t>
         </is>
       </c>
       <c r="S956" t="inlineStr">
@@ -48916,6 +51091,21 @@
         </is>
       </c>
       <c r="N965" s="4" t="n"/>
+      <c r="O965" t="inlineStr">
+        <is>
+          <t>https://www.nps.gov/civilwar/facts.htm</t>
+        </is>
+      </c>
+      <c r="P965" t="inlineStr">
+        <is>
+          <t>De Amerikaanse Burgeroorlog duurde van 1861 tot 1865.</t>
+        </is>
+      </c>
+      <c r="R965" t="inlineStr">
+        <is>
+          <t>handmatig</t>
+        </is>
+      </c>
       <c r="S965" t="inlineStr">
         <is>
           <t>DODE LINK</t>
@@ -49004,6 +51194,21 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="O967" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Nigerian_Civil_War</t>
+        </is>
+      </c>
+      <c r="P967" t="inlineStr">
+        <is>
+          <t>De Biafra-oorlog duurde van 1967 tot 1970.</t>
+        </is>
+      </c>
+      <c r="R967" t="inlineStr">
+        <is>
+          <t>handmatig</t>
+        </is>
+      </c>
     </row>
     <row r="968">
       <c r="A968" s="4" t="n">
@@ -49419,6 +51624,21 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="O975" t="inlineStr">
+        <is>
+          <t>https://european-union.europa.eu/principles-countries-history/history-eu_nl</t>
+        </is>
+      </c>
+      <c r="P975" t="inlineStr">
+        <is>
+          <t>Zes landen ondertekenden het Verdrag van Rome: Belgie, Duitsland, Frankrijk, Italie, Luxemburg en Nederland.</t>
+        </is>
+      </c>
+      <c r="R975" t="inlineStr">
+        <is>
+          <t>handmatig</t>
+        </is>
+      </c>
     </row>
     <row r="976" ht="25" customHeight="1">
       <c r="A976" s="4" t="n">
@@ -49458,6 +51678,21 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="O976" t="inlineStr">
+        <is>
+          <t>https://www.nato.int/cps/en/natohq/topics_52044.htm</t>
+        </is>
+      </c>
+      <c r="P976" t="inlineStr">
+        <is>
+          <t>De NAVO begon in 1949 met twaalf leden.</t>
+        </is>
+      </c>
+      <c r="R976" t="inlineStr">
+        <is>
+          <t>handmatig</t>
+        </is>
+      </c>
     </row>
     <row r="977" ht="25" customHeight="1">
       <c r="A977" s="4" t="n">
@@ -49583,6 +51818,21 @@
         </is>
       </c>
       <c r="N979" s="4" t="n"/>
+      <c r="O979" t="inlineStr">
+        <is>
+          <t>https://www.nationalww2museum.org/students-teachers/student-resources/research-starters/research-starters-us-military-numbers</t>
+        </is>
+      </c>
+      <c r="P979" t="inlineStr">
+        <is>
+          <t>Ruim zestien miljoen Amerikanen dienden in de Tweede Wereldoorlog.</t>
+        </is>
+      </c>
+      <c r="R979" t="inlineStr">
+        <is>
+          <t>handmatig</t>
+        </is>
+      </c>
       <c r="S979" t="inlineStr">
         <is>
           <t>DODE LINK</t>
@@ -50260,6 +52510,21 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="O992" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Ream_(unit)</t>
+        </is>
+      </c>
+      <c r="P992" t="inlineStr">
+        <is>
+          <t>Een riem printpapier telt 500 vel.</t>
+        </is>
+      </c>
+      <c r="R992" t="inlineStr">
+        <is>
+          <t>handmatig</t>
+        </is>
+      </c>
     </row>
     <row r="993">
       <c r="A993" s="4" t="n">
@@ -52116,6 +54381,21 @@
           <t>geen bron · geen EN-vertaling</t>
         </is>
       </c>
+      <c r="O1028" t="inlineStr">
+        <is>
+          <t>https://presse.louvre.fr/</t>
+        </is>
+      </c>
+      <c r="P1028" t="inlineStr">
+        <is>
+          <t>Het Louvre ontving in 2023 ongeveer 8,9 miljoen bezoekers.</t>
+        </is>
+      </c>
+      <c r="R1028" t="inlineStr">
+        <is>
+          <t>handmatig</t>
+        </is>
+      </c>
     </row>
     <row r="1029">
       <c r="A1029" s="4" t="n">
@@ -52199,9 +54479,24 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="O1030" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Moai</t>
+        </is>
+      </c>
+      <c r="P1030" t="inlineStr">
+        <is>
+          <t>Moai lopen sterk uiteen in gewicht; 12,5 ton is een gangbaar gemiddelde voor de grotere.</t>
+        </is>
+      </c>
       <c r="Q1030" t="inlineStr">
         <is>
           <t>Wikidata: geen waarde</t>
+        </is>
+      </c>
+      <c r="R1030" t="inlineStr">
+        <is>
+          <t>natellen</t>
         </is>
       </c>
     </row>
@@ -52305,6 +54600,21 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="O1032" t="inlineStr">
+        <is>
+          <t>https://whc.unesco.org/en/statesparties/cn</t>
+        </is>
+      </c>
+      <c r="P1032" t="inlineStr">
+        <is>
+          <t>UNESCO houdt het aantal per land bij. Het cijfer groeit jaarlijks, dus zonder peiljaar veroudert dit antwoord.</t>
+        </is>
+      </c>
+      <c r="R1032" t="inlineStr">
+        <is>
+          <t>natellen</t>
+        </is>
+      </c>
     </row>
     <row r="1033">
       <c r="A1033" s="4" t="n">
@@ -52344,6 +54654,21 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="O1033" t="inlineStr">
+        <is>
+          <t>https://whc.unesco.org/en/statesparties/de</t>
+        </is>
+      </c>
+      <c r="P1033" t="inlineStr">
+        <is>
+          <t>Zelfde lijst voor Duitsland; ook dit cijfer groeit.</t>
+        </is>
+      </c>
+      <c r="R1033" t="inlineStr">
+        <is>
+          <t>natellen</t>
+        </is>
+      </c>
     </row>
     <row r="1034" ht="25" customHeight="1">
       <c r="A1034" s="4" t="n">
@@ -52435,6 +54760,21 @@
       <c r="N1035" s="4" t="inlineStr">
         <is>
           <t>geen bron</t>
+        </is>
+      </c>
+      <c r="O1035" t="inlineStr">
+        <is>
+          <t>https://closertovaneyck.kikirpa.be/</t>
+        </is>
+      </c>
+      <c r="P1035" t="inlineStr">
+        <is>
+          <t>Het Lam Gods telt twaalf panelen.</t>
+        </is>
+      </c>
+      <c r="R1035" t="inlineStr">
+        <is>
+          <t>handmatig</t>
         </is>
       </c>
     </row>
@@ -52685,6 +55025,21 @@
         </is>
       </c>
       <c r="N1040" s="4" t="n"/>
+      <c r="O1040" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Beehive</t>
+        </is>
+      </c>
+      <c r="P1040" t="inlineStr">
+        <is>
+          <t>Een sterk volk telt in de zomer 50.000 tot 60.000 bijen.</t>
+        </is>
+      </c>
+      <c r="R1040" t="inlineStr">
+        <is>
+          <t>handmatig</t>
+        </is>
+      </c>
       <c r="S1040" t="inlineStr">
         <is>
           <t>DODE LINK</t>
@@ -53347,6 +55702,21 @@
           <t>geen EN-vertaling</t>
         </is>
       </c>
+      <c r="O1055" t="inlineStr">
+        <is>
+          <t>https://www.aldi.nl/</t>
+        </is>
+      </c>
+      <c r="P1055" t="inlineStr">
+        <is>
+          <t>Aldi zit rond de 12.000 winkels wereldwijd; het aantal groeit.</t>
+        </is>
+      </c>
+      <c r="R1055" t="inlineStr">
+        <is>
+          <t>natellen</t>
+        </is>
+      </c>
       <c r="S1055" t="inlineStr">
         <is>
           <t>DODE LINK</t>
@@ -53390,9 +55760,24 @@
           <t>geen EN-vertaling</t>
         </is>
       </c>
+      <c r="O1056" t="inlineStr">
+        <is>
+          <t>https://www.lidl.nl/</t>
+        </is>
+      </c>
+      <c r="P1056" t="inlineStr">
+        <is>
+          <t>Lidl passeerde 13.000 filialen. Het opgegeven 12.500 is te laag, en identiek aan dat van Aldi in vraag 1088 — twee verschillende ketens met precies hetzelfde getal.</t>
+        </is>
+      </c>
+      <c r="R1056" t="inlineStr">
+        <is>
+          <t>antwoord fout</t>
+        </is>
+      </c>
       <c r="S1056" t="inlineStr">
         <is>
-          <t>DODE LINK</t>
+          <t>antwoord fout, zie toelichting</t>
         </is>
       </c>
     </row>
@@ -53664,6 +56049,21 @@
         </is>
       </c>
       <c r="N1062" s="4" t="n"/>
+      <c r="O1062" t="inlineStr">
+        <is>
+          <t>https://www.ramsar.org/</t>
+        </is>
+      </c>
+      <c r="P1062" t="inlineStr">
+        <is>
+          <t>Ramsar houdt aan dat sinds 1700 ongeveer 85 procent van de wetlands is verdwenen.</t>
+        </is>
+      </c>
+      <c r="R1062" t="inlineStr">
+        <is>
+          <t>handmatig</t>
+        </is>
+      </c>
       <c r="S1062" t="inlineStr">
         <is>
           <t>DODE LINK</t>
@@ -53937,6 +56337,21 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="O1068" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Dress_shirt</t>
+        </is>
+      </c>
+      <c r="P1068" t="inlineStr">
+        <is>
+          <t>Overhemden hebben doorgaans zes tot acht knopen aan de voorkant.</t>
+        </is>
+      </c>
+      <c r="R1068" t="inlineStr">
+        <is>
+          <t>natellen</t>
+        </is>
+      </c>
     </row>
     <row r="1069" ht="25" customHeight="1">
       <c r="A1069" s="4" t="n">
@@ -54084,6 +56499,21 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="O1071" t="inlineStr">
+        <is>
+          <t>https://www.grammy.com/artists/acdc/2277</t>
+        </is>
+      </c>
+      <c r="P1071" t="inlineStr">
+        <is>
+          <t>AC/DC won een Grammy in 2010 voor War Machine.</t>
+        </is>
+      </c>
+      <c r="R1071" t="inlineStr">
+        <is>
+          <t>handmatig</t>
+        </is>
+      </c>
     </row>
     <row r="1072">
       <c r="A1072" s="4" t="n">
@@ -54177,6 +56607,21 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="O1073" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/AC/DC_discography</t>
+        </is>
+      </c>
+      <c r="P1073" t="inlineStr">
+        <is>
+          <t>AC/DC bracht zeventien studioalbums uit.</t>
+        </is>
+      </c>
+      <c r="R1073" t="inlineStr">
+        <is>
+          <t>handmatig</t>
+        </is>
+      </c>
     </row>
     <row r="1074">
       <c r="A1074" s="4" t="n">
@@ -54271,6 +56716,21 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="O1075" t="inlineStr">
+        <is>
+          <t>https://ich.unesco.org/en/RL/rumba-in-cuba-01185</t>
+        </is>
+      </c>
+      <c r="P1075" t="inlineStr">
+        <is>
+          <t>De Cubaanse rumba kent drie hoofdstijlen: yambu, guaguanco en columbia.</t>
+        </is>
+      </c>
+      <c r="R1075" t="inlineStr">
+        <is>
+          <t>handmatig</t>
+        </is>
+      </c>
     </row>
     <row r="1076">
       <c r="A1076" s="4" t="n">
@@ -54406,6 +56866,21 @@
       <c r="N1078" s="4" t="inlineStr">
         <is>
           <t>geen bron</t>
+        </is>
+      </c>
+      <c r="O1078" t="inlineStr">
+        <is>
+          <t>https://ich.unesco.org/en/RL/mariachi-string-music-song-and-trumpet-01061</t>
+        </is>
+      </c>
+      <c r="P1078" t="inlineStr">
+        <is>
+          <t>Een mariachiband telt doorgaans acht tot twaalf muzikanten.</t>
+        </is>
+      </c>
+      <c r="R1078" t="inlineStr">
+        <is>
+          <t>natellen</t>
         </is>
       </c>
     </row>
@@ -54620,6 +57095,11 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="S1082" t="inlineStr">
+        <is>
+          <t>geen bron mogelijk (onbruikbaar)</t>
+        </is>
+      </c>
     </row>
     <row r="1083">
       <c r="A1083" s="4" t="n">
@@ -54659,6 +57139,21 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="O1083" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Krar</t>
+        </is>
+      </c>
+      <c r="P1083" t="inlineStr">
+        <is>
+          <t>De krar heeft vijf of zes snaren.</t>
+        </is>
+      </c>
+      <c r="R1083" t="inlineStr">
+        <is>
+          <t>handmatig</t>
+        </is>
+      </c>
     </row>
     <row r="1084">
       <c r="A1084" s="4" t="n">
@@ -54698,6 +57193,21 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="O1084" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Sitar</t>
+        </is>
+      </c>
+      <c r="P1084" t="inlineStr">
+        <is>
+          <t>Een sitar heeft achttien tot eenentwintig snaren, afhankelijk van het model.</t>
+        </is>
+      </c>
+      <c r="R1084" t="inlineStr">
+        <is>
+          <t>natellen</t>
+        </is>
+      </c>
     </row>
     <row r="1085">
       <c r="A1085" s="4" t="n">
@@ -54737,6 +57247,11 @@
           <t>geen bron · geen EN-vertaling</t>
         </is>
       </c>
+      <c r="S1085" t="inlineStr">
+        <is>
+          <t>geen bron mogelijk (onbruikbaar)</t>
+        </is>
+      </c>
     </row>
     <row r="1086">
       <c r="A1086" s="4" t="n">
@@ -54776,6 +57291,21 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="O1086" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Kora_(instrument)</t>
+        </is>
+      </c>
+      <c r="P1086" t="inlineStr">
+        <is>
+          <t>De kora heeft traditioneel eenentwintig snaren.</t>
+        </is>
+      </c>
+      <c r="R1086" t="inlineStr">
+        <is>
+          <t>handmatig</t>
+        </is>
+      </c>
     </row>
     <row r="1087">
       <c r="A1087" s="4" t="n">
@@ -54869,6 +57399,21 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="O1088" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Tiple_(Colombian)</t>
+        </is>
+      </c>
+      <c r="P1088" t="inlineStr">
+        <is>
+          <t>De Colombiaanse tiple heeft twaalf snaren, in vier koren van drie.</t>
+        </is>
+      </c>
+      <c r="R1088" t="inlineStr">
+        <is>
+          <t>handmatig</t>
+        </is>
+      </c>
     </row>
     <row r="1089">
       <c r="A1089" s="4" t="n">
@@ -54913,6 +57458,11 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="S1089" t="inlineStr">
+        <is>
+          <t>geen bron mogelijk (onbruikbaar)</t>
+        </is>
+      </c>
     </row>
     <row r="1090">
       <c r="A1090" s="4" t="n">
@@ -54952,6 +57502,21 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="O1090" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Koto_(instrument)</t>
+        </is>
+      </c>
+      <c r="P1090" t="inlineStr">
+        <is>
+          <t>De koto heeft dertien snaren.</t>
+        </is>
+      </c>
+      <c r="R1090" t="inlineStr">
+        <is>
+          <t>handmatig</t>
+        </is>
+      </c>
     </row>
     <row r="1091" ht="25" customHeight="1">
       <c r="A1091" s="4" t="n">
@@ -55084,6 +57649,21 @@
           <t>geen bron · geen EN-vertaling</t>
         </is>
       </c>
+      <c r="O1093" t="inlineStr">
+        <is>
+          <t>https://newsroom.spotify.com/</t>
+        </is>
+      </c>
+      <c r="P1093" t="inlineStr">
+        <is>
+          <t>Streamingaantallen groeien doorlopend; zonder peildatum verloopt dit antwoord.</t>
+        </is>
+      </c>
+      <c r="R1093" t="inlineStr">
+        <is>
+          <t>natellen</t>
+        </is>
+      </c>
     </row>
     <row r="1094" ht="25" customHeight="1">
       <c r="A1094" s="4" t="n">
@@ -55123,6 +57703,21 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="O1094" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Kylie_Minogue_discography</t>
+        </is>
+      </c>
+      <c r="P1094" t="inlineStr">
+        <is>
+          <t>Zestien studioalbums; de discografie groeit nog.</t>
+        </is>
+      </c>
+      <c r="R1094" t="inlineStr">
+        <is>
+          <t>natellen</t>
+        </is>
+      </c>
     </row>
     <row r="1095" ht="25" customHeight="1">
       <c r="A1095" s="4" t="n">
@@ -55214,6 +57809,21 @@
       <c r="N1096" s="4" t="inlineStr">
         <is>
           <t>geen bron</t>
+        </is>
+      </c>
+      <c r="O1096" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/The_Beatles_discography</t>
+        </is>
+      </c>
+      <c r="P1096" t="inlineStr">
+        <is>
+          <t>In het Verenigd Koninkrijk verschenen twaalf studioalbums.</t>
+        </is>
+      </c>
+      <c r="R1096" t="inlineStr">
+        <is>
+          <t>handmatig</t>
         </is>
       </c>
     </row>
@@ -55370,6 +57980,21 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="O1099" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov/niosh/noise/about/noise.html</t>
+        </is>
+      </c>
+      <c r="P1099" t="inlineStr">
+        <is>
+          <t>Een normaal gesprek zit rond de zestig decibel.</t>
+        </is>
+      </c>
+      <c r="R1099" t="inlineStr">
+        <is>
+          <t>handmatig</t>
+        </is>
+      </c>
     </row>
     <row r="1100">
       <c r="A1100" s="4" t="n">
@@ -55554,6 +58179,21 @@
       <c r="N1103" s="4" t="inlineStr">
         <is>
           <t>geen bron · geen EN-vertaling</t>
+        </is>
+      </c>
+      <c r="O1103" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Challenger_Deep</t>
+        </is>
+      </c>
+      <c r="P1103" t="inlineStr">
+        <is>
+          <t>De Challengerdiepte meet ongeveer 10.935 meter.</t>
+        </is>
+      </c>
+      <c r="R1103" t="inlineStr">
+        <is>
+          <t>handmatig</t>
         </is>
       </c>
     </row>
@@ -55651,6 +58291,21 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="O1105" t="inlineStr">
+        <is>
+          <t>https://nl.wikipedia.org/wiki/Schaal_van_Beaufort</t>
+        </is>
+      </c>
+      <c r="P1105" t="inlineStr">
+        <is>
+          <t>Windkracht 5 loopt van 8,0 tot 10,7 meter per seconde.</t>
+        </is>
+      </c>
+      <c r="R1105" t="inlineStr">
+        <is>
+          <t>handmatig</t>
+        </is>
+      </c>
     </row>
     <row r="1106" ht="25" customHeight="1">
       <c r="A1106" s="4" t="n">
@@ -55690,6 +58345,21 @@
         </is>
       </c>
       <c r="N1106" s="4" t="n"/>
+      <c r="O1106" t="inlineStr">
+        <is>
+          <t>https://nl.wikipedia.org/wiki/Geluidssnelheid</t>
+        </is>
+      </c>
+      <c r="P1106" t="inlineStr">
+        <is>
+          <t>Bij 20 graden is de geluidssnelheid 343 m/s, oftewel 1235 km/u.</t>
+        </is>
+      </c>
+      <c r="R1106" t="inlineStr">
+        <is>
+          <t>handmatig</t>
+        </is>
+      </c>
       <c r="S1106" t="inlineStr">
         <is>
           <t>DODE LINK</t>
@@ -55845,6 +58515,21 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="O1109" t="inlineStr">
+        <is>
+          <t>https://www.hollandsewaterlinies.nl/</t>
+        </is>
+      </c>
+      <c r="P1109" t="inlineStr">
+        <is>
+          <t>De Oude Hollandse Waterlinie, de Nieuwe Hollandse Waterlinie en de Stelling van Amsterdam worden verschillend geteld.</t>
+        </is>
+      </c>
+      <c r="R1109" t="inlineStr">
+        <is>
+          <t>natellen</t>
+        </is>
+      </c>
     </row>
     <row r="1110" ht="25" customHeight="1">
       <c r="A1110" s="4" t="n">
@@ -55943,6 +58628,11 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="S1111" t="inlineStr">
+        <is>
+          <t>geen bron mogelijk (onbruikbaar)</t>
+        </is>
+      </c>
     </row>
     <row r="1112">
       <c r="A1112" s="4" t="n">
@@ -55982,6 +58672,21 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="O1112" t="inlineStr">
+        <is>
+          <t>https://www.nobelprize.org/prizes/lists/all-nobel-prizes/</t>
+        </is>
+      </c>
+      <c r="P1112" t="inlineStr">
+        <is>
+          <t>De Nobelstichting publiceert alle laureaten; de Nederlandse zijn eruit te tellen.</t>
+        </is>
+      </c>
+      <c r="R1112" t="inlineStr">
+        <is>
+          <t>natellen</t>
+        </is>
+      </c>
     </row>
     <row r="1113" ht="25" customHeight="1">
       <c r="A1113" s="4" t="n">
@@ -56021,6 +58726,21 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="O1113" t="inlineStr">
+        <is>
+          <t>https://www.esa.int/</t>
+        </is>
+      </c>
+      <c r="P1113" t="inlineStr">
+        <is>
+          <t>Wubbo Ockels, Andre Kuipers en Lodewijk van den Berg vlogen de ruimte in.</t>
+        </is>
+      </c>
+      <c r="R1113" t="inlineStr">
+        <is>
+          <t>natellen</t>
+        </is>
+      </c>
     </row>
     <row r="1114">
       <c r="A1114" s="4" t="n">
@@ -56340,6 +59060,21 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="O1119" t="inlineStr">
+        <is>
+          <t>https://ivdnt.org/woordenboeken/woordenboek-der-nederlandsche-taal/</t>
+        </is>
+      </c>
+      <c r="P1119" t="inlineStr">
+        <is>
+          <t>Het WNT telt tienduizenden kolommen; het aantal bladzijden hangt af van de editie.</t>
+        </is>
+      </c>
+      <c r="R1119" t="inlineStr">
+        <is>
+          <t>natellen</t>
+        </is>
+      </c>
     </row>
     <row r="1120">
       <c r="A1120" s="4" t="n">
@@ -56379,6 +59114,11 @@
           <t>geen bron · geen EN-vertaling</t>
         </is>
       </c>
+      <c r="S1120" t="inlineStr">
+        <is>
+          <t>geen bron mogelijk (onbruikbaar)</t>
+        </is>
+      </c>
     </row>
     <row r="1121" ht="25" customHeight="1">
       <c r="A1121" s="4" t="n">
@@ -56423,6 +59163,11 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="S1121" t="inlineStr">
+        <is>
+          <t>geen bron mogelijk (onbruikbaar)</t>
+        </is>
+      </c>
     </row>
     <row r="1122">
       <c r="A1122" s="4" t="n">
@@ -56465,6 +59210,11 @@
       <c r="N1122" s="4" t="inlineStr">
         <is>
           <t>geen bron</t>
+        </is>
+      </c>
+      <c r="S1122" t="inlineStr">
+        <is>
+          <t>geen bron mogelijk (onbruikbaar)</t>
         </is>
       </c>
     </row>
@@ -56626,9 +59376,24 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="O1125" t="inlineStr">
+        <is>
+          <t>https://www.cbs.nl/nl-nl/cijfers/detail/70072ned</t>
+        </is>
+      </c>
+      <c r="P1125" t="inlineStr">
+        <is>
+          <t>Het CBS publiceert inwonertallen per gemeente.</t>
+        </is>
+      </c>
       <c r="Q1125" t="inlineStr">
         <is>
           <t>Wikidata: klopt</t>
+        </is>
+      </c>
+      <c r="R1125" t="inlineStr">
+        <is>
+          <t>natellen</t>
         </is>
       </c>
     </row>
@@ -56840,6 +59605,21 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="O1129" t="inlineStr">
+        <is>
+          <t>https://www.knmi.nl/nederland-nu/klimatologie</t>
+        </is>
+      </c>
+      <c r="P1129" t="inlineStr">
+        <is>
+          <t>Het KNMI publiceert maandgemiddelden; de zomer zit rond de 17 a 18 graden.</t>
+        </is>
+      </c>
+      <c r="R1129" t="inlineStr">
+        <is>
+          <t>natellen</t>
+        </is>
+      </c>
     </row>
     <row r="1130" ht="25" customHeight="1">
       <c r="A1130" s="4" t="n">
@@ -56879,6 +59659,11 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="S1130" t="inlineStr">
+        <is>
+          <t>geen bron mogelijk (onbruikbaar)</t>
+        </is>
+      </c>
     </row>
     <row r="1131">
       <c r="A1131" s="4" t="n">
@@ -56913,6 +59698,11 @@
           <t>geen bron · geen EN-vertaling</t>
         </is>
       </c>
+      <c r="S1131" t="inlineStr">
+        <is>
+          <t>geen bron mogelijk (onbruikbaar)</t>
+        </is>
+      </c>
     </row>
     <row r="1132">
       <c r="A1132" s="4" t="n">
@@ -56952,6 +59742,11 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="S1132" t="inlineStr">
+        <is>
+          <t>geen bron mogelijk (onbruikbaar)</t>
+        </is>
+      </c>
     </row>
     <row r="1133">
       <c r="A1133" s="4" t="n">
@@ -56986,9 +59781,24 @@
           <t>geen bron · geen EN-vertaling</t>
         </is>
       </c>
+      <c r="O1133" t="inlineStr">
+        <is>
+          <t>https://www.cbs.nl/nl-nl/cijfers/detail/70072ned</t>
+        </is>
+      </c>
+      <c r="P1133" t="inlineStr">
+        <is>
+          <t>Zelfde CBS-tabel; Amsterdam zit rond de 930.000 inwoners.</t>
+        </is>
+      </c>
       <c r="Q1133" t="inlineStr">
         <is>
           <t>Wikidata: klopt</t>
+        </is>
+      </c>
+      <c r="R1133" t="inlineStr">
+        <is>
+          <t>natellen</t>
         </is>
       </c>
     </row>
@@ -57107,6 +59917,11 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="S1135" t="inlineStr">
+        <is>
+          <t>geen bron mogelijk (onbruikbaar)</t>
+        </is>
+      </c>
     </row>
     <row r="1136">
       <c r="A1136" s="4" t="n">
@@ -57205,6 +60020,11 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="S1137" t="inlineStr">
+        <is>
+          <t>geen bron mogelijk (onbruikbaar)</t>
+        </is>
+      </c>
     </row>
     <row r="1138" ht="25" customHeight="1">
       <c r="A1138" s="4" t="n">
@@ -57293,6 +60113,21 @@
           <t>geen bron · geen EN-vertaling</t>
         </is>
       </c>
+      <c r="O1139" t="inlineStr">
+        <is>
+          <t>https://www.fifa.com/tournaments/mens/worldcup</t>
+        </is>
+      </c>
+      <c r="P1139" t="inlineStr">
+        <is>
+          <t>Nederland won het WK nooit. Het antwoord nul maakt wel elke deelsom stuk.</t>
+        </is>
+      </c>
+      <c r="R1139" t="inlineStr">
+        <is>
+          <t>natellen</t>
+        </is>
+      </c>
     </row>
     <row r="1140">
       <c r="A1140" s="4" t="n">
@@ -57330,6 +60165,21 @@
       <c r="N1140" s="4" t="inlineStr">
         <is>
           <t>geen bron</t>
+        </is>
+      </c>
+      <c r="O1140" t="inlineStr">
+        <is>
+          <t>https://www.fietsersbond.nl/</t>
+        </is>
+      </c>
+      <c r="P1140" t="inlineStr">
+        <is>
+          <t>Nederland telt ongeveer 35.000 km fietspad.</t>
+        </is>
+      </c>
+      <c r="R1140" t="inlineStr">
+        <is>
+          <t>natellen</t>
         </is>
       </c>
     </row>
@@ -57558,6 +60408,21 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="O1144" t="inlineStr">
+        <is>
+          <t>https://www.rijkswaterstaat.nl/water/vaarwegenoverzicht/maas</t>
+        </is>
+      </c>
+      <c r="P1144" t="inlineStr">
+        <is>
+          <t>Van de ruim 900 km Maas ligt ongeveer 250 km in Nederland.</t>
+        </is>
+      </c>
+      <c r="R1144" t="inlineStr">
+        <is>
+          <t>natellen</t>
+        </is>
+      </c>
     </row>
     <row r="1145">
       <c r="A1145" s="4" t="n">
@@ -57597,9 +60462,24 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="O1145" t="inlineStr">
+        <is>
+          <t>https://www.ret.nl/</t>
+        </is>
+      </c>
+      <c r="P1145" t="inlineStr">
+        <is>
+          <t>Het Rotterdamse metronet meet ongeveer 78 km.</t>
+        </is>
+      </c>
       <c r="Q1145" t="inlineStr">
         <is>
           <t>Wikidata: geen waarde</t>
+        </is>
+      </c>
+      <c r="R1145" t="inlineStr">
+        <is>
+          <t>handmatig</t>
         </is>
       </c>
     </row>
@@ -57641,9 +60521,24 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="O1146" t="inlineStr">
+        <is>
+          <t>https://www.gvb.nl/noordzuidlijn</t>
+        </is>
+      </c>
+      <c r="P1146" t="inlineStr">
+        <is>
+          <t>De Noord-Zuidlijn is ongeveer negen kilometer lang.</t>
+        </is>
+      </c>
       <c r="Q1146" t="inlineStr">
         <is>
           <t>Wikidata: geen waarde</t>
+        </is>
+      </c>
+      <c r="R1146" t="inlineStr">
+        <is>
+          <t>handmatig</t>
         </is>
       </c>
     </row>
@@ -57680,9 +60575,29 @@
           <t>geen bron · geen EN-vertaling</t>
         </is>
       </c>
+      <c r="O1147" t="inlineStr">
+        <is>
+          <t>https://nl.wikipedia.org/wiki/Van_Brienenoordbrug</t>
+        </is>
+      </c>
+      <c r="P1147" t="inlineStr">
+        <is>
+          <t>De vraag vraagt kilometers maar het antwoord 300 staat in meters.</t>
+        </is>
+      </c>
       <c r="Q1147" t="inlineStr">
         <is>
           <t>Wikidata: WIJKT AF</t>
+        </is>
+      </c>
+      <c r="R1147" t="inlineStr">
+        <is>
+          <t>antwoord fout</t>
+        </is>
+      </c>
+      <c r="S1147" t="inlineStr">
+        <is>
+          <t>antwoord fout, zie toelichting</t>
         </is>
       </c>
     </row>
@@ -57783,9 +60698,24 @@
         </is>
       </c>
       <c r="N1149" s="4" t="n"/>
+      <c r="O1149" t="inlineStr">
+        <is>
+          <t>https://www.waddenzee.nl/</t>
+        </is>
+      </c>
+      <c r="P1149" t="inlineStr">
+        <is>
+          <t>De kustlengte van de Waddeneilanden hangt af van de meetmethode.</t>
+        </is>
+      </c>
       <c r="Q1149" t="inlineStr">
         <is>
           <t>Wikidata: geen waarde</t>
+        </is>
+      </c>
+      <c r="R1149" t="inlineStr">
+        <is>
+          <t>natellen</t>
         </is>
       </c>
       <c r="S1149" t="inlineStr">
@@ -57832,6 +60762,21 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="O1150" t="inlineStr">
+        <is>
+          <t>https://www.koninklijkhuis.nl/</t>
+        </is>
+      </c>
+      <c r="P1150" t="inlineStr">
+        <is>
+          <t>Willem-Alexander heeft drie dochters.</t>
+        </is>
+      </c>
+      <c r="R1150" t="inlineStr">
+        <is>
+          <t>handmatig</t>
+        </is>
+      </c>
     </row>
     <row r="1151">
       <c r="A1151" s="4" t="n">
@@ -57984,9 +60929,24 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="O1153" t="inlineStr">
+        <is>
+          <t>https://www.provincie-utrecht.nl/</t>
+        </is>
+      </c>
+      <c r="P1153" t="inlineStr">
+        <is>
+          <t>De provincie Utrecht beslaat ongeveer 1449 vierkante kilometer.</t>
+        </is>
+      </c>
       <c r="Q1153" t="inlineStr">
         <is>
           <t>Wikidata: WIJKT AF</t>
+        </is>
+      </c>
+      <c r="R1153" t="inlineStr">
+        <is>
+          <t>handmatig</t>
         </is>
       </c>
     </row>
@@ -58033,6 +60993,11 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="S1154" t="inlineStr">
+        <is>
+          <t>geen bron mogelijk (onbruikbaar)</t>
+        </is>
+      </c>
     </row>
     <row r="1155" ht="25" customHeight="1">
       <c r="A1155" s="4" t="n">
@@ -58300,6 +61265,11 @@
           <t>geen bron · geen EN-vertaling</t>
         </is>
       </c>
+      <c r="S1159" t="inlineStr">
+        <is>
+          <t>geen bron mogelijk (onbruikbaar)</t>
+        </is>
+      </c>
     </row>
     <row r="1160" ht="25" customHeight="1">
       <c r="A1160" s="4" t="n">
@@ -58550,6 +61520,21 @@
           <t>geen bron · geen EN-vertaling</t>
         </is>
       </c>
+      <c r="O1164" t="inlineStr">
+        <is>
+          <t>https://www.cbs.nl/nl-nl/cijfers/detail/7425</t>
+        </is>
+      </c>
+      <c r="P1164" t="inlineStr">
+        <is>
+          <t>Het CBS publiceert melkconsumptie per hoofd; het cijfer verschilt per jaargang.</t>
+        </is>
+      </c>
+      <c r="R1164" t="inlineStr">
+        <is>
+          <t>natellen</t>
+        </is>
+      </c>
     </row>
     <row r="1165">
       <c r="A1165" s="4" t="n">
@@ -58587,6 +61572,21 @@
       <c r="N1165" s="4" t="inlineStr">
         <is>
           <t>geen bron</t>
+        </is>
+      </c>
+      <c r="O1165" t="inlineStr">
+        <is>
+          <t>https://www.cbs.nl/nl-nl/cijfers/detail/7425</t>
+        </is>
+      </c>
+      <c r="P1165" t="inlineStr">
+        <is>
+          <t>Het CBS publiceert de melkproductie per koe; rond de 9000 liter per jaar.</t>
+        </is>
+      </c>
+      <c r="R1165" t="inlineStr">
+        <is>
+          <t>natellen</t>
         </is>
       </c>
     </row>
@@ -58925,9 +61925,24 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="O1171" t="inlineStr">
+        <is>
+          <t>https://www.hollandamerica.com/</t>
+        </is>
+      </c>
+      <c r="P1171" t="inlineStr">
+        <is>
+          <t>Het ms Rotterdam meet ongeveer 300 meter.</t>
+        </is>
+      </c>
       <c r="Q1171" t="inlineStr">
         <is>
           <t>Wikidata: geen waarde</t>
+        </is>
+      </c>
+      <c r="R1171" t="inlineStr">
+        <is>
+          <t>handmatig</t>
         </is>
       </c>
     </row>
@@ -58969,6 +61984,21 @@
         </is>
       </c>
       <c r="N1172" s="4" t="n"/>
+      <c r="O1172" t="inlineStr">
+        <is>
+          <t>https://nl.wikipedia.org/wiki/Zuidplaspolder</t>
+        </is>
+      </c>
+      <c r="P1172" t="inlineStr">
+        <is>
+          <t>Het diepste punt ligt bij Nieuwerkerk aan den IJssel, 6,76 meter onder NAP.</t>
+        </is>
+      </c>
+      <c r="R1172" t="inlineStr">
+        <is>
+          <t>handmatig</t>
+        </is>
+      </c>
       <c r="S1172" t="inlineStr">
         <is>
           <t>DODE LINK</t>
@@ -59011,6 +62041,21 @@
       <c r="N1173" s="4" t="inlineStr">
         <is>
           <t>geen bron</t>
+        </is>
+      </c>
+      <c r="O1173" t="inlineStr">
+        <is>
+          <t>https://www.rijksoverheid.nl/onderwerpen/defensie</t>
+        </is>
+      </c>
+      <c r="P1173" t="inlineStr">
+        <is>
+          <t>Het defensiebudget verschilt per begrotingsjaar.</t>
+        </is>
+      </c>
+      <c r="R1173" t="inlineStr">
+        <is>
+          <t>natellen</t>
         </is>
       </c>
     </row>
@@ -59217,6 +62262,21 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="O1177" t="inlineStr">
+        <is>
+          <t>https://www.dezaanseschans.nl/</t>
+        </is>
+      </c>
+      <c r="P1177" t="inlineStr">
+        <is>
+          <t>Op de Zaanse Schans staan acht molens.</t>
+        </is>
+      </c>
+      <c r="R1177" t="inlineStr">
+        <is>
+          <t>handmatig</t>
+        </is>
+      </c>
     </row>
     <row r="1178" ht="25" customHeight="1">
       <c r="A1178" s="4" t="n">
@@ -59366,6 +62426,21 @@
         </is>
       </c>
       <c r="N1180" s="4" t="n"/>
+      <c r="O1180" t="inlineStr">
+        <is>
+          <t>https://www.rijkswaterstaat.nl/</t>
+        </is>
+      </c>
+      <c r="P1180" t="inlineStr">
+        <is>
+          <t>Ongeveer een kwart van Nederland ligt onder zeeniveau; de telling hangt af van de gekozen referentiehoogte.</t>
+        </is>
+      </c>
+      <c r="R1180" t="inlineStr">
+        <is>
+          <t>natellen</t>
+        </is>
+      </c>
       <c r="S1180" t="inlineStr">
         <is>
           <t>DODE LINK</t>
@@ -59410,6 +62485,21 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="O1181" t="inlineStr">
+        <is>
+          <t>https://www.cbs.nl/nl-nl/cijfers/detail/82900NED</t>
+        </is>
+      </c>
+      <c r="P1181" t="inlineStr">
+        <is>
+          <t>Het CBS publiceert de woningvoorraad naar type; het percentage moet je zelf afleiden.</t>
+        </is>
+      </c>
+      <c r="R1181" t="inlineStr">
+        <is>
+          <t>natellen</t>
+        </is>
+      </c>
     </row>
     <row r="1182">
       <c r="A1182" s="4" t="n">
@@ -59449,6 +62539,21 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="O1182" t="inlineStr">
+        <is>
+          <t>https://www.cbs.nl/nl-nl/visualisaties/verkeer-en-vervoer</t>
+        </is>
+      </c>
+      <c r="P1182" t="inlineStr">
+        <is>
+          <t>Het CBS publiceert fietsgebruik; het percentage hangt af van de vraagstelling.</t>
+        </is>
+      </c>
+      <c r="R1182" t="inlineStr">
+        <is>
+          <t>natellen</t>
+        </is>
+      </c>
     </row>
     <row r="1183" ht="25" customHeight="1">
       <c r="A1183" s="4" t="n">
@@ -59488,6 +62593,21 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="O1183" t="inlineStr">
+        <is>
+          <t>https://www.dnb.nl/betalen/</t>
+        </is>
+      </c>
+      <c r="P1183" t="inlineStr">
+        <is>
+          <t>DNB publiceert het aandeel pin- en contactloze betalingen; rond de 80 procent.</t>
+        </is>
+      </c>
+      <c r="R1183" t="inlineStr">
+        <is>
+          <t>natellen</t>
+        </is>
+      </c>
     </row>
     <row r="1184">
       <c r="A1184" s="4" t="n">
@@ -59527,6 +62647,21 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="O1184" t="inlineStr">
+        <is>
+          <t>https://www.cbs.nl/nl-nl/cijfers/detail/70072ned</t>
+        </is>
+      </c>
+      <c r="P1184" t="inlineStr">
+        <is>
+          <t>Het aandeel Randstadbewoners is uit de CBS-cijfers af te leiden.</t>
+        </is>
+      </c>
+      <c r="R1184" t="inlineStr">
+        <is>
+          <t>natellen</t>
+        </is>
+      </c>
     </row>
     <row r="1185">
       <c r="A1185" s="4" t="n">
@@ -59674,6 +62809,21 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="O1187" t="inlineStr">
+        <is>
+          <t>https://www.knkv.nl/</t>
+        </is>
+      </c>
+      <c r="P1187" t="inlineStr">
+        <is>
+          <t>Een korfbalteam telt acht spelers op het veld.</t>
+        </is>
+      </c>
+      <c r="R1187" t="inlineStr">
+        <is>
+          <t>handmatig</t>
+        </is>
+      </c>
     </row>
     <row r="1188" ht="25" customHeight="1">
       <c r="A1188" s="4" t="n">
@@ -59772,6 +62922,21 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="O1189" t="inlineStr">
+        <is>
+          <t>https://www.rijksoverheid.nl/onderwerpen/grondwet-en-statuut/vlag</t>
+        </is>
+      </c>
+      <c r="P1189" t="inlineStr">
+        <is>
+          <t>De Nederlandse vlag heeft drie horizontale banen.</t>
+        </is>
+      </c>
+      <c r="R1189" t="inlineStr">
+        <is>
+          <t>handmatig</t>
+        </is>
+      </c>
     </row>
     <row r="1190">
       <c r="A1190" s="4" t="n">
@@ -59811,6 +62976,21 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="O1190" t="inlineStr">
+        <is>
+          <t>https://www.rijksmuseum.nl/nl/zoeken</t>
+        </is>
+      </c>
+      <c r="P1190" t="inlineStr">
+        <is>
+          <t>De collectiedatabase is te doorzoeken; het aantal wisselt met de catalogisering.</t>
+        </is>
+      </c>
+      <c r="R1190" t="inlineStr">
+        <is>
+          <t>natellen</t>
+        </is>
+      </c>
     </row>
     <row r="1191" ht="25" customHeight="1">
       <c r="A1191" s="4" t="n">
@@ -60072,6 +63252,21 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="O1195" t="inlineStr">
+        <is>
+          <t>https://www.vlinderstichting.nl/vlinders/</t>
+        </is>
+      </c>
+      <c r="P1195" t="inlineStr">
+        <is>
+          <t>De Vlinderstichting houdt de Nederlandse dagvlindersoorten bij; rond de 53 soorten.</t>
+        </is>
+      </c>
+      <c r="R1195" t="inlineStr">
+        <is>
+          <t>natellen</t>
+        </is>
+      </c>
     </row>
     <row r="1196">
       <c r="A1196" s="4" t="n">
@@ -60111,6 +63306,21 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="O1196" t="inlineStr">
+        <is>
+          <t>https://www.eredivisie.nl/</t>
+        </is>
+      </c>
+      <c r="P1196" t="inlineStr">
+        <is>
+          <t>De Johan Cruijff Arena en De Kuip zitten boven de 50.000; capaciteiten veranderen bij verbouwingen.</t>
+        </is>
+      </c>
+      <c r="R1196" t="inlineStr">
+        <is>
+          <t>natellen</t>
+        </is>
+      </c>
     </row>
     <row r="1197">
       <c r="A1197" s="4" t="n">
@@ -60204,6 +63414,21 @@
         </is>
       </c>
       <c r="N1198" s="4" t="n"/>
+      <c r="O1198" t="inlineStr">
+        <is>
+          <t>https://www.rijksmuseum.nl/nl/over-ons/gebouw</t>
+        </is>
+      </c>
+      <c r="P1198" t="inlineStr">
+        <is>
+          <t>Het aantal zuilen aan de voorgevel is nergens als getal vastgelegd; zelf tellen op een foto.</t>
+        </is>
+      </c>
+      <c r="R1198" t="inlineStr">
+        <is>
+          <t>natellen</t>
+        </is>
+      </c>
       <c r="S1198" t="inlineStr">
         <is>
           <t>DODE LINK</t>
@@ -60307,9 +63532,24 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="O1200" t="inlineStr">
+        <is>
+          <t>https://censusindia.gov.in/</t>
+        </is>
+      </c>
+      <c r="P1200" t="inlineStr">
+        <is>
+          <t>Het Indiase inwonertal ligt rond de 1,44 miljard en groeit.</t>
+        </is>
+      </c>
       <c r="Q1200" t="inlineStr">
         <is>
           <t>Wikidata: bijna</t>
+        </is>
+      </c>
+      <c r="R1200" t="inlineStr">
+        <is>
+          <t>natellen</t>
         </is>
       </c>
     </row>
@@ -60351,6 +63591,21 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="O1201" t="inlineStr">
+        <is>
+          <t>https://www.un.org/en/about-us/universal-declaration-of-human-rights</t>
+        </is>
+      </c>
+      <c r="P1201" t="inlineStr">
+        <is>
+          <t>De Universele Verklaring telt dertig artikelen.</t>
+        </is>
+      </c>
+      <c r="R1201" t="inlineStr">
+        <is>
+          <t>handmatig</t>
+        </is>
+      </c>
     </row>
     <row r="1202" ht="25" customHeight="1">
       <c r="A1202" s="4" t="n">
@@ -60556,6 +63811,21 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="O1205" t="inlineStr">
+        <is>
+          <t>https://www.archives.gov/electoral-college/allocation</t>
+        </is>
+      </c>
+      <c r="P1205" t="inlineStr">
+        <is>
+          <t>Californie heeft 54 kiesmannen.</t>
+        </is>
+      </c>
+      <c r="R1205" t="inlineStr">
+        <is>
+          <t>handmatig</t>
+        </is>
+      </c>
     </row>
     <row r="1206">
       <c r="A1206" s="4" t="n">
@@ -60649,6 +63919,21 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="O1207" t="inlineStr">
+        <is>
+          <t>https://www.archives.gov/electoral-college/about</t>
+        </is>
+      </c>
+      <c r="P1207" t="inlineStr">
+        <is>
+          <t>Van de 538 kiesmannen zijn er 270 nodig voor een meerderheid.</t>
+        </is>
+      </c>
+      <c r="R1207" t="inlineStr">
+        <is>
+          <t>handmatig</t>
+        </is>
+      </c>
     </row>
     <row r="1208">
       <c r="A1208" s="4" t="n">
@@ -60693,6 +63978,11 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="S1208" t="inlineStr">
+        <is>
+          <t>geen bron mogelijk (onbruikbaar)</t>
+        </is>
+      </c>
     </row>
     <row r="1209">
       <c r="A1209" s="4" t="n">
@@ -60732,6 +64022,21 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="O1209" t="inlineStr">
+        <is>
+          <t>https://www.aph.gov.au/</t>
+        </is>
+      </c>
+      <c r="P1209" t="inlineStr">
+        <is>
+          <t>Een termijn duurt maximaal drie jaar.</t>
+        </is>
+      </c>
+      <c r="R1209" t="inlineStr">
+        <is>
+          <t>handmatig</t>
+        </is>
+      </c>
     </row>
     <row r="1210">
       <c r="A1210" s="4" t="n">
@@ -60771,6 +64076,21 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="O1210" t="inlineStr">
+        <is>
+          <t>https://www.parliament.nz/</t>
+        </is>
+      </c>
+      <c r="P1210" t="inlineStr">
+        <is>
+          <t>Een parlementstermijn duurt drie jaar.</t>
+        </is>
+      </c>
+      <c r="R1210" t="inlineStr">
+        <is>
+          <t>handmatig</t>
+        </is>
+      </c>
     </row>
     <row r="1211" ht="25" customHeight="1">
       <c r="A1211" s="4" t="n">
@@ -60810,6 +64130,21 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="O1211" t="inlineStr">
+        <is>
+          <t>https://www.senate.gov/</t>
+        </is>
+      </c>
+      <c r="P1211" t="inlineStr">
+        <is>
+          <t>Een senaatstermijn duurt zes jaar.</t>
+        </is>
+      </c>
+      <c r="R1211" t="inlineStr">
+        <is>
+          <t>handmatig</t>
+        </is>
+      </c>
     </row>
     <row r="1212">
       <c r="A1212" s="4" t="n">
@@ -60959,6 +64294,21 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="O1214" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Central_African_CFA_franc</t>
+        </is>
+      </c>
+      <c r="P1214" t="inlineStr">
+        <is>
+          <t>Zes landen gebruiken de Centraal-Afrikaanse CFA-frank.</t>
+        </is>
+      </c>
+      <c r="R1214" t="inlineStr">
+        <is>
+          <t>handmatig</t>
+        </is>
+      </c>
     </row>
     <row r="1215" ht="25" customHeight="1">
       <c r="A1215" s="4" t="n">
@@ -60998,6 +64348,21 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="O1215" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/West_African_CFA_franc</t>
+        </is>
+      </c>
+      <c r="P1215" t="inlineStr">
+        <is>
+          <t>Acht landen gebruiken de West-Afrikaanse CFA-frank.</t>
+        </is>
+      </c>
+      <c r="R1215" t="inlineStr">
+        <is>
+          <t>handmatig</t>
+        </is>
+      </c>
     </row>
     <row r="1216" ht="25" customHeight="1">
       <c r="A1216" s="4" t="n">
@@ -61135,6 +64500,21 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="O1218" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Oceania</t>
+        </is>
+      </c>
+      <c r="P1218" t="inlineStr">
+        <is>
+          <t>Veertien onafhankelijke landen; de telling hangt af van welke gebieden je meerekent.</t>
+        </is>
+      </c>
+      <c r="R1218" t="inlineStr">
+        <is>
+          <t>natellen</t>
+        </is>
+      </c>
     </row>
     <row r="1219">
       <c r="A1219" s="4" t="n">
@@ -61174,6 +64554,21 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="O1219" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Community_of_Latin_American_and_Caribbean_States</t>
+        </is>
+      </c>
+      <c r="P1219" t="inlineStr">
+        <is>
+          <t>De CELAC telt 33 lidstaten.</t>
+        </is>
+      </c>
+      <c r="R1219" t="inlineStr">
+        <is>
+          <t>handmatig</t>
+        </is>
+      </c>
     </row>
     <row r="1220" ht="25" customHeight="1">
       <c r="A1220" s="4" t="n">
@@ -61375,6 +64770,21 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="O1223" t="inlineStr">
+        <is>
+          <t>https://asean.org/member-states/</t>
+        </is>
+      </c>
+      <c r="P1223" t="inlineStr">
+        <is>
+          <t>De ASEAN telt tien leden.</t>
+        </is>
+      </c>
+      <c r="R1223" t="inlineStr">
+        <is>
+          <t>handmatig</t>
+        </is>
+      </c>
     </row>
     <row r="1224" ht="25" customHeight="1">
       <c r="A1224" s="4" t="n">
@@ -61578,6 +64988,21 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="O1227" t="inlineStr">
+        <is>
+          <t>https://www.saarc-sec.org/</t>
+        </is>
+      </c>
+      <c r="P1227" t="inlineStr">
+        <is>
+          <t>De SAARC telt acht leden.</t>
+        </is>
+      </c>
+      <c r="R1227" t="inlineStr">
+        <is>
+          <t>handmatig</t>
+        </is>
+      </c>
     </row>
     <row r="1228">
       <c r="A1228" s="4" t="n">
@@ -61878,6 +65303,21 @@
           <t>geen bron · geen EN-vertaling</t>
         </is>
       </c>
+      <c r="O1233" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Provinces_of_Argentina</t>
+        </is>
+      </c>
+      <c r="P1233" t="inlineStr">
+        <is>
+          <t>Argentinie telt 23 provincies plus de autonome stad Buenos Aires.</t>
+        </is>
+      </c>
+      <c r="R1233" t="inlineStr">
+        <is>
+          <t>handmatig</t>
+        </is>
+      </c>
     </row>
     <row r="1234" ht="25" customHeight="1">
       <c r="A1234" s="4" t="n">
@@ -62085,6 +65525,11 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="S1237" t="inlineStr">
+        <is>
+          <t>geen bron mogelijk (onbruikbaar)</t>
+        </is>
+      </c>
     </row>
     <row r="1238" ht="25" customHeight="1">
       <c r="A1238" s="4" t="n">
@@ -62179,6 +65624,21 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="O1239" t="inlineStr">
+        <is>
+          <t>https://www.australia.gov.au/</t>
+        </is>
+      </c>
+      <c r="P1239" t="inlineStr">
+        <is>
+          <t>Zes staten en twee territoria.</t>
+        </is>
+      </c>
+      <c r="R1239" t="inlineStr">
+        <is>
+          <t>handmatig</t>
+        </is>
+      </c>
     </row>
     <row r="1240" ht="25" customHeight="1">
       <c r="A1240" s="4" t="n">
@@ -62382,6 +65842,21 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="O1243" t="inlineStr">
+        <is>
+          <t>https://www.parliament.nz/</t>
+        </is>
+      </c>
+      <c r="P1243" t="inlineStr">
+        <is>
+          <t>Het aantal zetels schommelt rond de 120.</t>
+        </is>
+      </c>
+      <c r="R1243" t="inlineStr">
+        <is>
+          <t>natellen</t>
+        </is>
+      </c>
     </row>
     <row r="1244">
       <c r="A1244" s="4" t="n">
@@ -62421,6 +65896,21 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="O1244" t="inlineStr">
+        <is>
+          <t>https://www.aph.gov.au/</t>
+        </is>
+      </c>
+      <c r="P1244" t="inlineStr">
+        <is>
+          <t>Het Huis van Afgevaardigden telt 151 zetels.</t>
+        </is>
+      </c>
+      <c r="R1244" t="inlineStr">
+        <is>
+          <t>handmatig</t>
+        </is>
+      </c>
     </row>
     <row r="1245" ht="25" customHeight="1">
       <c r="A1245" s="4" t="n">
@@ -62564,6 +66054,21 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="O1247" t="inlineStr">
+        <is>
+          <t>https://www.guinnessworldrecords.com/world-records/highest-dive</t>
+        </is>
+      </c>
+      <c r="P1247" t="inlineStr">
+        <is>
+          <t>Klifduikrecords worden met enige regelmaat verbroken.</t>
+        </is>
+      </c>
+      <c r="R1247" t="inlineStr">
+        <is>
+          <t>veroudert</t>
+        </is>
+      </c>
     </row>
     <row r="1248">
       <c r="A1248" s="4" t="n">
@@ -62603,6 +66108,21 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="O1248" t="inlineStr">
+        <is>
+          <t>https://www.guinnessworldrecords.com/world-records/tallest-humanoid-robot</t>
+        </is>
+      </c>
+      <c r="P1248" t="inlineStr">
+        <is>
+          <t>Guinness voert een categorie voor de hoogste humanoide robot.</t>
+        </is>
+      </c>
+      <c r="R1248" t="inlineStr">
+        <is>
+          <t>natellen</t>
+        </is>
+      </c>
     </row>
     <row r="1249">
       <c r="A1249" s="4" t="n">
@@ -62642,6 +66162,21 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="O1249" t="inlineStr">
+        <is>
+          <t>https://www.guinnessworldrecords.com/world-records/longest-beard</t>
+        </is>
+      </c>
+      <c r="P1249" t="inlineStr">
+        <is>
+          <t>De langste baard ooit mat 5,33 meter (Hans Langseth).</t>
+        </is>
+      </c>
+      <c r="R1249" t="inlineStr">
+        <is>
+          <t>handmatig</t>
+        </is>
+      </c>
     </row>
     <row r="1250">
       <c r="A1250" s="4" t="n">
@@ -62681,6 +66216,21 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="O1250" t="inlineStr">
+        <is>
+          <t>https://www.guinnessworldrecords.com/world-records/tallest-man-ever</t>
+        </is>
+      </c>
+      <c r="P1250" t="inlineStr">
+        <is>
+          <t>Robert Wadlow mat 272 cm.</t>
+        </is>
+      </c>
+      <c r="R1250" t="inlineStr">
+        <is>
+          <t>handmatig</t>
+        </is>
+      </c>
     </row>
     <row r="1251">
       <c r="A1251" s="4" t="n">
@@ -62774,6 +66324,21 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="O1252" t="inlineStr">
+        <is>
+          <t>https://www.guinnessworldrecords.com/world-records/longest-cake</t>
+        </is>
+      </c>
+      <c r="P1252" t="inlineStr">
+        <is>
+          <t>Guinness voert een categorie voor de langste taart.</t>
+        </is>
+      </c>
+      <c r="R1252" t="inlineStr">
+        <is>
+          <t>natellen</t>
+        </is>
+      </c>
     </row>
     <row r="1253">
       <c r="A1253" s="4" t="n">
@@ -62813,6 +66378,21 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="O1253" t="inlineStr">
+        <is>
+          <t>https://www.guinnessworldrecords.com/world-records/longest-train</t>
+        </is>
+      </c>
+      <c r="P1253" t="inlineStr">
+        <is>
+          <t>De langste trein ooit mat ruim zeven kilometer (BHP, Australie, 2001).</t>
+        </is>
+      </c>
+      <c r="R1253" t="inlineStr">
+        <is>
+          <t>handmatig</t>
+        </is>
+      </c>
     </row>
     <row r="1254">
       <c r="A1254" s="4" t="n">
@@ -62847,6 +66427,21 @@
           <t>geen bron · geen EN-vertaling</t>
         </is>
       </c>
+      <c r="O1254" t="inlineStr">
+        <is>
+          <t>https://www.guinnessworldrecords.com/world-records/longest-wedding-dress-train</t>
+        </is>
+      </c>
+      <c r="P1254" t="inlineStr">
+        <is>
+          <t>De langste trouwjurksleep mat 8095 meter.</t>
+        </is>
+      </c>
+      <c r="R1254" t="inlineStr">
+        <is>
+          <t>handmatig</t>
+        </is>
+      </c>
     </row>
     <row r="1255">
       <c r="A1255" s="4" t="n">
@@ -62886,6 +66481,21 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="O1255" t="inlineStr">
+        <is>
+          <t>https://www.guinnessworldrecords.com/world-records/longest-hair</t>
+        </is>
+      </c>
+      <c r="P1255" t="inlineStr">
+        <is>
+          <t>Het langste haar ooit mat ruim vijf meter (Xie Qiuping).</t>
+        </is>
+      </c>
+      <c r="R1255" t="inlineStr">
+        <is>
+          <t>handmatig</t>
+        </is>
+      </c>
     </row>
     <row r="1256">
       <c r="A1256" s="4" t="n">
@@ -62925,6 +66535,21 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="O1256" t="inlineStr">
+        <is>
+          <t>https://www.guinnessworldrecords.com/world-records/oldest-cat-ever</t>
+        </is>
+      </c>
+      <c r="P1256" t="inlineStr">
+        <is>
+          <t>Creme Puff werd 38 jaar.</t>
+        </is>
+      </c>
+      <c r="R1256" t="inlineStr">
+        <is>
+          <t>handmatig</t>
+        </is>
+      </c>
     </row>
     <row r="1257">
       <c r="A1257" s="4" t="n">
@@ -62959,6 +66584,21 @@
           <t>geen bron · geen EN-vertaling</t>
         </is>
       </c>
+      <c r="O1257" t="inlineStr">
+        <is>
+          <t>https://www.guinnessworldrecords.com/world-records/largest-chocolate-bar</t>
+        </is>
+      </c>
+      <c r="P1257" t="inlineStr">
+        <is>
+          <t>De grootste chocoladereep woog 5792,5 kg; het opgegeven getal hoort mogelijk bij een andere categorie. Nakijken.</t>
+        </is>
+      </c>
+      <c r="R1257" t="inlineStr">
+        <is>
+          <t>handmatig</t>
+        </is>
+      </c>
     </row>
     <row r="1258">
       <c r="A1258" s="4" t="n">
@@ -62998,6 +66638,21 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="O1258" t="inlineStr">
+        <is>
+          <t>https://www.guinnessworldrecords.com/world-records/largest-serving-of-chips</t>
+        </is>
+      </c>
+      <c r="P1258" t="inlineStr">
+        <is>
+          <t>Guinness voert een categorie voor de grootste portie friet.</t>
+        </is>
+      </c>
+      <c r="R1258" t="inlineStr">
+        <is>
+          <t>natellen</t>
+        </is>
+      </c>
     </row>
     <row r="1259" ht="25" customHeight="1">
       <c r="A1259" s="4" t="n">
@@ -63037,6 +66692,21 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="O1259" t="inlineStr">
+        <is>
+          <t>https://www.guinnessworldrecords.com/world-records/heaviest-turtle</t>
+        </is>
+      </c>
+      <c r="P1259" t="inlineStr">
+        <is>
+          <t>De zwaarste schildpad woog 916 kg.</t>
+        </is>
+      </c>
+      <c r="R1259" t="inlineStr">
+        <is>
+          <t>handmatig</t>
+        </is>
+      </c>
     </row>
     <row r="1260" ht="25" customHeight="1">
       <c r="A1260" s="4" t="n">
@@ -63071,6 +66741,21 @@
           <t>geen bron · geen EN-vertaling</t>
         </is>
       </c>
+      <c r="O1260" t="inlineStr">
+        <is>
+          <t>https://www.guinnessworldrecords.com/world-records/largest-lego-brick-sculpture</t>
+        </is>
+      </c>
+      <c r="P1260" t="inlineStr">
+        <is>
+          <t>Guinness voert meerdere LEGO-categorieen; welke bedoeld is, moet de vraag zeggen.</t>
+        </is>
+      </c>
+      <c r="R1260" t="inlineStr">
+        <is>
+          <t>natellen</t>
+        </is>
+      </c>
     </row>
     <row r="1261">
       <c r="A1261" s="4" t="n">
@@ -63110,6 +66795,21 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="O1261" t="inlineStr">
+        <is>
+          <t>https://www.guinnessworldrecords.com/</t>
+        </is>
+      </c>
+      <c r="P1261" t="inlineStr">
+        <is>
+          <t>Deelnemersrecords worden vaak verbroken.</t>
+        </is>
+      </c>
+      <c r="R1261" t="inlineStr">
+        <is>
+          <t>veroudert</t>
+        </is>
+      </c>
     </row>
     <row r="1262">
       <c r="A1262" s="4" t="n">
@@ -63149,6 +66849,21 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="O1262" t="inlineStr">
+        <is>
+          <t>https://www.guinnessworldrecords.com/world-records/largest-serving-of-soup</t>
+        </is>
+      </c>
+      <c r="P1262" t="inlineStr">
+        <is>
+          <t>Guinness voert een categorie voor de grootste portie soep.</t>
+        </is>
+      </c>
+      <c r="R1262" t="inlineStr">
+        <is>
+          <t>natellen</t>
+        </is>
+      </c>
     </row>
     <row r="1263" ht="25" customHeight="1">
       <c r="A1263" s="4" t="n">
@@ -63188,6 +66903,21 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="O1263" t="inlineStr">
+        <is>
+          <t>https://www.guinnessworldrecords.com/world-records/largest-water-balloon-fight</t>
+        </is>
+      </c>
+      <c r="P1263" t="inlineStr">
+        <is>
+          <t>Het grootste waterballonnengevecht telde 8957 deelnemers.</t>
+        </is>
+      </c>
+      <c r="R1263" t="inlineStr">
+        <is>
+          <t>handmatig</t>
+        </is>
+      </c>
     </row>
     <row r="1264">
       <c r="A1264" s="4" t="n">
@@ -63227,6 +66957,21 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="O1264" t="inlineStr">
+        <is>
+          <t>https://www.guinnessworldrecords.com/world-records/most-push-ups-in-24-hours</t>
+        </is>
+      </c>
+      <c r="P1264" t="inlineStr">
+        <is>
+          <t>Push-uprecords worden regelmatig verbroken.</t>
+        </is>
+      </c>
+      <c r="R1264" t="inlineStr">
+        <is>
+          <t>veroudert</t>
+        </is>
+      </c>
     </row>
     <row r="1265">
       <c r="A1265" s="4" t="n">
@@ -63266,6 +67011,21 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="O1265" t="inlineStr">
+        <is>
+          <t>https://www.guinnessworldrecords.com/world-records/longest-passenger-train</t>
+        </is>
+      </c>
+      <c r="P1265" t="inlineStr">
+        <is>
+          <t>De langste passagierstrein telde honderd rijtuigen (Zwitserland, 2022).</t>
+        </is>
+      </c>
+      <c r="R1265" t="inlineStr">
+        <is>
+          <t>handmatig</t>
+        </is>
+      </c>
     </row>
     <row r="1266" ht="25" customHeight="1">
       <c r="A1266" s="4" t="n">
@@ -63305,6 +67065,21 @@
         </is>
       </c>
       <c r="N1266" s="4" t="n"/>
+      <c r="O1266" t="inlineStr">
+        <is>
+          <t>https://stories.hilton.com/</t>
+        </is>
+      </c>
+      <c r="P1266" t="inlineStr">
+        <is>
+          <t>Hilton publiceert het aantal hotels in zijn persmap; rond de 7500 en groeiend.</t>
+        </is>
+      </c>
+      <c r="R1266" t="inlineStr">
+        <is>
+          <t>natellen</t>
+        </is>
+      </c>
       <c r="S1266" t="inlineStr">
         <is>
           <t>DODE LINK</t>
@@ -63525,6 +67300,21 @@
         </is>
       </c>
       <c r="N1271" s="4" t="n"/>
+      <c r="O1271" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Electron_shell</t>
+        </is>
+      </c>
+      <c r="P1271" t="inlineStr">
+        <is>
+          <t>De derde schil bevat maximaal achttien elektronen.</t>
+        </is>
+      </c>
+      <c r="R1271" t="inlineStr">
+        <is>
+          <t>handmatig</t>
+        </is>
+      </c>
       <c r="S1271" t="inlineStr">
         <is>
           <t>DODE LINK</t>
@@ -63987,6 +67777,21 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="O1280" t="inlineStr">
+        <is>
+          <t>https://www.lego.com/en-us/service/help-topics/article/how-lego-bricks-are-made</t>
+        </is>
+      </c>
+      <c r="P1280" t="inlineStr">
+        <is>
+          <t>Een 2x4-steen heeft acht studs.</t>
+        </is>
+      </c>
+      <c r="R1280" t="inlineStr">
+        <is>
+          <t>handmatig</t>
+        </is>
+      </c>
     </row>
     <row r="1281">
       <c r="A1281" s="4" t="n">
@@ -64026,6 +67831,21 @@
         </is>
       </c>
       <c r="N1281" s="4" t="n"/>
+      <c r="O1281" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Rubik%27s_Cube</t>
+        </is>
+      </c>
+      <c r="P1281" t="inlineStr">
+        <is>
+          <t>Zes vlakken van negen vierkantjes: 54.</t>
+        </is>
+      </c>
+      <c r="R1281" t="inlineStr">
+        <is>
+          <t>handmatig</t>
+        </is>
+      </c>
       <c r="S1281" t="inlineStr">
         <is>
           <t>DODE LINK</t>
@@ -64070,6 +67890,21 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="O1282" t="inlineStr">
+        <is>
+          <t>https://www.catan.com/</t>
+        </is>
+      </c>
+      <c r="P1282" t="inlineStr">
+        <is>
+          <t>Het basisspel bevat 95 grondstoffenkaarten.</t>
+        </is>
+      </c>
+      <c r="R1282" t="inlineStr">
+        <is>
+          <t>handmatig</t>
+        </is>
+      </c>
     </row>
     <row r="1283">
       <c r="A1283" s="4" t="n">
@@ -64109,6 +67944,21 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="O1283" t="inlineStr">
+        <is>
+          <t>https://www.hasbro.com/en-us/brands/monopoly</t>
+        </is>
+      </c>
+      <c r="P1283" t="inlineStr">
+        <is>
+          <t>28 eigendomskaarten, 16 kanskaarten en 16 algemeenfondskaarten.</t>
+        </is>
+      </c>
+      <c r="R1283" t="inlineStr">
+        <is>
+          <t>natellen</t>
+        </is>
+      </c>
     </row>
     <row r="1284">
       <c r="A1284" s="4" t="n">
@@ -64148,6 +67998,21 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="O1284" t="inlineStr">
+        <is>
+          <t>https://www.unorules.com/</t>
+        </is>
+      </c>
+      <c r="P1284" t="inlineStr">
+        <is>
+          <t>Elke speler krijgt zeven kaarten.</t>
+        </is>
+      </c>
+      <c r="R1284" t="inlineStr">
+        <is>
+          <t>handmatig</t>
+        </is>
+      </c>
     </row>
     <row r="1285">
       <c r="A1285" s="4" t="n">
@@ -64378,6 +68243,21 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="O1289" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/International_draughts</t>
+        </is>
+      </c>
+      <c r="P1289" t="inlineStr">
+        <is>
+          <t>Een internationaal dambord heeft honderd velden.</t>
+        </is>
+      </c>
+      <c r="R1289" t="inlineStr">
+        <is>
+          <t>handmatig</t>
+        </is>
+      </c>
     </row>
     <row r="1290">
       <c r="A1290" s="4" t="n">
@@ -64415,6 +68295,21 @@
       <c r="N1290" s="4" t="inlineStr">
         <is>
           <t>geen bron</t>
+        </is>
+      </c>
+      <c r="O1290" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Draughts</t>
+        </is>
+      </c>
+      <c r="P1290" t="inlineStr">
+        <is>
+          <t>Het Engelse dambord telt 64 velden; het internationale honderd. De vraag moet zeggen welke variant, want vraag 1339 geeft het andere antwoord.</t>
+        </is>
+      </c>
+      <c r="R1290" t="inlineStr">
+        <is>
+          <t>natellen</t>
         </is>
       </c>
     </row>
@@ -64786,6 +68681,21 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="O1297" t="inlineStr">
+        <is>
+          <t>https://www.wimbledon.com/en_GB/atoz/scoring.html</t>
+        </is>
+      </c>
+      <c r="P1297" t="inlineStr">
+        <is>
+          <t>Een set gaat naar zes games met twee verschil; bij 6-6 volgt een tiebreak.</t>
+        </is>
+      </c>
+      <c r="R1297" t="inlineStr">
+        <is>
+          <t>natellen</t>
+        </is>
+      </c>
     </row>
     <row r="1298">
       <c r="A1298" s="4" t="n">
@@ -65068,6 +68978,21 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="O1303" t="inlineStr">
+        <is>
+          <t>https://www.fifa.com/tournaments/mens/worldcup</t>
+        </is>
+      </c>
+      <c r="P1303" t="inlineStr">
+        <is>
+          <t>Het WK voetbal wordt elke vier jaar gehouden.</t>
+        </is>
+      </c>
+      <c r="R1303" t="inlineStr">
+        <is>
+          <t>handmatig</t>
+        </is>
+      </c>
     </row>
     <row r="1304">
       <c r="A1304" s="4" t="n">
@@ -65107,6 +69032,21 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="O1304" t="inlineStr">
+        <is>
+          <t>https://olympics.com/ioc</t>
+        </is>
+      </c>
+      <c r="P1304" t="inlineStr">
+        <is>
+          <t>De zomerspelen worden elke vier jaar gehouden.</t>
+        </is>
+      </c>
+      <c r="R1304" t="inlineStr">
+        <is>
+          <t>handmatig</t>
+        </is>
+      </c>
     </row>
     <row r="1305">
       <c r="A1305" s="4" t="n">
@@ -65146,6 +69086,21 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="O1305" t="inlineStr">
+        <is>
+          <t>https://olympics.com/ioc</t>
+        </is>
+      </c>
+      <c r="P1305" t="inlineStr">
+        <is>
+          <t>Melbourne 1956, Sydney 2000 en Brisbane 2032.</t>
+        </is>
+      </c>
+      <c r="R1305" t="inlineStr">
+        <is>
+          <t>handmatig</t>
+        </is>
+      </c>
     </row>
     <row r="1306">
       <c r="A1306" s="4" t="n">
@@ -66165,6 +70120,11 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="S1324" t="inlineStr">
+        <is>
+          <t>geen bron mogelijk (onbruikbaar)</t>
+        </is>
+      </c>
     </row>
     <row r="1325" ht="25" customHeight="1">
       <c r="A1325" s="4" t="n">
@@ -66351,6 +70311,21 @@
           <t>geen bron · geen EN-vertaling</t>
         </is>
       </c>
+      <c r="O1328" t="inlineStr">
+        <is>
+          <t>https://worldathletics.org/</t>
+        </is>
+      </c>
+      <c r="P1328" t="inlineStr">
+        <is>
+          <t>De klassieke sprintafstand is honderd meter.</t>
+        </is>
+      </c>
+      <c r="R1328" t="inlineStr">
+        <is>
+          <t>handmatig</t>
+        </is>
+      </c>
     </row>
     <row r="1329">
       <c r="A1329" s="4" t="n">
@@ -66536,6 +70511,21 @@
           <t>geen bron · geen EN-vertaling</t>
         </is>
       </c>
+      <c r="O1332" t="inlineStr">
+        <is>
+          <t>https://www.isu.org/</t>
+        </is>
+      </c>
+      <c r="P1332" t="inlineStr">
+        <is>
+          <t>De kortste schaatsafstand is 500 meter.</t>
+        </is>
+      </c>
+      <c r="R1332" t="inlineStr">
+        <is>
+          <t>handmatig</t>
+        </is>
+      </c>
     </row>
     <row r="1333">
       <c r="A1333" s="4" t="n">
@@ -66575,6 +70565,21 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="O1333" t="inlineStr">
+        <is>
+          <t>https://official.nba.com/rulebook/</t>
+        </is>
+      </c>
+      <c r="P1333" t="inlineStr">
+        <is>
+          <t>Vier kwarten van twaalf minuten: 48. Let op: duplicaat van vraag 1388.</t>
+        </is>
+      </c>
+      <c r="R1333" t="inlineStr">
+        <is>
+          <t>handmatig</t>
+        </is>
+      </c>
     </row>
     <row r="1334" ht="25" customHeight="1">
       <c r="A1334" s="4" t="n">
@@ -66614,6 +70619,21 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="O1334" t="inlineStr">
+        <is>
+          <t>https://www.iihf.com/en/statichub/6141/rules</t>
+        </is>
+      </c>
+      <c r="P1334" t="inlineStr">
+        <is>
+          <t>Drie periodes van twintig minuten.</t>
+        </is>
+      </c>
+      <c r="R1334" t="inlineStr">
+        <is>
+          <t>handmatig</t>
+        </is>
+      </c>
     </row>
     <row r="1335">
       <c r="A1335" s="4" t="n">
@@ -66653,6 +70673,21 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="O1335" t="inlineStr">
+        <is>
+          <t>https://www.world.rugby/organisation/governance/laws</t>
+        </is>
+      </c>
+      <c r="P1335" t="inlineStr">
+        <is>
+          <t>Twee helften van veertig minuten.</t>
+        </is>
+      </c>
+      <c r="R1335" t="inlineStr">
+        <is>
+          <t>handmatig</t>
+        </is>
+      </c>
     </row>
     <row r="1336">
       <c r="A1336" s="4" t="n">
@@ -66736,6 +70771,21 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="O1337" t="inlineStr">
+        <is>
+          <t>https://official.nba.com/rulebook/</t>
+        </is>
+      </c>
+      <c r="P1337" t="inlineStr">
+        <is>
+          <t>Zelfde vraag als 1384; een van beide kan weg.</t>
+        </is>
+      </c>
+      <c r="R1337" t="inlineStr">
+        <is>
+          <t>handmatig</t>
+        </is>
+      </c>
     </row>
     <row r="1338">
       <c r="A1338" s="4" t="n">
@@ -66775,6 +70825,21 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="O1338" t="inlineStr">
+        <is>
+          <t>https://operations.nfl.com/the-rules/</t>
+        </is>
+      </c>
+      <c r="P1338" t="inlineStr">
+        <is>
+          <t>Vier kwarten van vijftien minuten.</t>
+        </is>
+      </c>
+      <c r="R1338" t="inlineStr">
+        <is>
+          <t>handmatig</t>
+        </is>
+      </c>
     </row>
     <row r="1339">
       <c r="A1339" s="4" t="n">
@@ -66902,6 +70967,21 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="O1341" t="inlineStr">
+        <is>
+          <t>https://www.pdc.tv/</t>
+        </is>
+      </c>
+      <c r="P1341" t="inlineStr">
+        <is>
+          <t>Drie pijlen per beurt.</t>
+        </is>
+      </c>
+      <c r="R1341" t="inlineStr">
+        <is>
+          <t>handmatig</t>
+        </is>
+      </c>
     </row>
     <row r="1342">
       <c r="A1342" s="4" t="n">
@@ -66941,6 +71021,21 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="O1342" t="inlineStr">
+        <is>
+          <t>https://iwf.sport/</t>
+        </is>
+      </c>
+      <c r="P1342" t="inlineStr">
+        <is>
+          <t>Drie pogingen per onderdeel.</t>
+        </is>
+      </c>
+      <c r="R1342" t="inlineStr">
+        <is>
+          <t>handmatig</t>
+        </is>
+      </c>
     </row>
     <row r="1343">
       <c r="A1343" s="4" t="n">
@@ -66980,6 +71075,11 @@
           <t>geen bron · geen EN-vertaling</t>
         </is>
       </c>
+      <c r="S1343" t="inlineStr">
+        <is>
+          <t>geen bron mogelijk (onbruikbaar)</t>
+        </is>
+      </c>
     </row>
     <row r="1344">
       <c r="A1344" s="4" t="n">
@@ -67017,6 +71117,21 @@
       <c r="N1344" s="4" t="inlineStr">
         <is>
           <t>geen bron</t>
+        </is>
+      </c>
+      <c r="O1344" t="inlineStr">
+        <is>
+          <t>https://www.pdc.tv/</t>
+        </is>
+      </c>
+      <c r="P1344" t="inlineStr">
+        <is>
+          <t>Drie keer triple twintig: 180.</t>
+        </is>
+      </c>
+      <c r="R1344" t="inlineStr">
+        <is>
+          <t>handmatig</t>
         </is>
       </c>
     </row>
@@ -67376,6 +71491,21 @@
       <c r="N1351" s="4" t="inlineStr">
         <is>
           <t>geen bron</t>
+        </is>
+      </c>
+      <c r="O1351" t="inlineStr">
+        <is>
+          <t>https://official.nba.com/rulebook/</t>
+        </is>
+      </c>
+      <c r="P1351" t="inlineStr">
+        <is>
+          <t>Vijf spelers per ploeg.</t>
+        </is>
+      </c>
+      <c r="R1351" t="inlineStr">
+        <is>
+          <t>handmatig</t>
         </is>
       </c>
     </row>
@@ -67476,6 +71606,21 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="O1353" t="inlineStr">
+        <is>
+          <t>https://www.fih.ch/rules/</t>
+        </is>
+      </c>
+      <c r="P1353" t="inlineStr">
+        <is>
+          <t>Elf spelers per ploeg, keeper meegerekend.</t>
+        </is>
+      </c>
+      <c r="R1353" t="inlineStr">
+        <is>
+          <t>handmatig</t>
+        </is>
+      </c>
     </row>
     <row r="1354">
       <c r="A1354" s="4" t="n">
@@ -67515,6 +71660,21 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="O1354" t="inlineStr">
+        <is>
+          <t>https://www.world.rugby/organisation/governance/laws</t>
+        </is>
+      </c>
+      <c r="P1354" t="inlineStr">
+        <is>
+          <t>Vijftien spelers per ploeg bij rugby union.</t>
+        </is>
+      </c>
+      <c r="R1354" t="inlineStr">
+        <is>
+          <t>handmatig</t>
+        </is>
+      </c>
     </row>
     <row r="1355">
       <c r="A1355" s="4" t="n">
@@ -67784,6 +71944,21 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="O1360" t="inlineStr">
+        <is>
+          <t>https://www.rugby-league.com/</t>
+        </is>
+      </c>
+      <c r="P1360" t="inlineStr">
+        <is>
+          <t>Dertien spelers per ploeg bij rugby league.</t>
+        </is>
+      </c>
+      <c r="R1360" t="inlineStr">
+        <is>
+          <t>handmatig</t>
+        </is>
+      </c>
     </row>
     <row r="1361" ht="25" customHeight="1">
       <c r="A1361" s="4" t="n">
@@ -67823,6 +71998,21 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="O1361" t="inlineStr">
+        <is>
+          <t>https://www.fivb.com/</t>
+        </is>
+      </c>
+      <c r="P1361" t="inlineStr">
+        <is>
+          <t>Zes spelers per ploeg op het veld.</t>
+        </is>
+      </c>
+      <c r="R1361" t="inlineStr">
+        <is>
+          <t>handmatig</t>
+        </is>
+      </c>
     </row>
     <row r="1362">
       <c r="A1362" s="4" t="n">
@@ -67862,6 +72052,21 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="O1362" t="inlineStr">
+        <is>
+          <t>https://www.nba.com/teams</t>
+        </is>
+      </c>
+      <c r="P1362" t="inlineStr">
+        <is>
+          <t>De NBA telt dertig teams.</t>
+        </is>
+      </c>
+      <c r="R1362" t="inlineStr">
+        <is>
+          <t>handmatig</t>
+        </is>
+      </c>
     </row>
     <row r="1363">
       <c r="A1363" s="4" t="n">
@@ -67901,6 +72106,21 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="O1363" t="inlineStr">
+        <is>
+          <t>https://www.nfl.com/teams/</t>
+        </is>
+      </c>
+      <c r="P1363" t="inlineStr">
+        <is>
+          <t>De NFL telt tweeendertig teams.</t>
+        </is>
+      </c>
+      <c r="R1363" t="inlineStr">
+        <is>
+          <t>handmatig</t>
+        </is>
+      </c>
     </row>
     <row r="1364" ht="25" customHeight="1">
       <c r="A1364" s="4" t="n">
@@ -68788,6 +73008,21 @@
         </is>
       </c>
       <c r="N1381" s="4" t="n"/>
+      <c r="O1381" t="inlineStr">
+        <is>
+          <t>https://science.nasa.gov/universe/galaxies/milky-way/</t>
+        </is>
+      </c>
+      <c r="P1381" t="inlineStr">
+        <is>
+          <t>Schattingen lopen van honderd tot vierhonderd miljard sterren.</t>
+        </is>
+      </c>
+      <c r="R1381" t="inlineStr">
+        <is>
+          <t>natellen</t>
+        </is>
+      </c>
       <c r="S1381" t="inlineStr">
         <is>
           <t>DODE LINK</t>
@@ -68939,6 +73174,21 @@
       <c r="N1384" s="4" t="inlineStr">
         <is>
           <t>geen bron</t>
+        </is>
+      </c>
+      <c r="O1384" t="inlineStr">
+        <is>
+          <t>https://www.isro.gov.in/</t>
+        </is>
+      </c>
+      <c r="P1384" t="inlineStr">
+        <is>
+          <t>ISRO lanceerde in februari 2017 104 satellieten met een enkele PSLV.</t>
+        </is>
+      </c>
+      <c r="R1384" t="inlineStr">
+        <is>
+          <t>handmatig</t>
         </is>
       </c>
     </row>
@@ -69903,6 +74153,21 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="O1403" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Frame_rate</t>
+        </is>
+      </c>
+      <c r="P1403" t="inlineStr">
+        <is>
+          <t>De bioscoopstandaard is 24 beelden per seconde.</t>
+        </is>
+      </c>
+      <c r="R1403" t="inlineStr">
+        <is>
+          <t>handmatig</t>
+        </is>
+      </c>
     </row>
     <row r="1404">
       <c r="A1404" s="4" t="n">
@@ -69991,6 +74256,21 @@
         </is>
       </c>
       <c r="N1405" s="4" t="n"/>
+      <c r="O1405" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Subpixel_rendering</t>
+        </is>
+      </c>
+      <c r="P1405" t="inlineStr">
+        <is>
+          <t>Rood, groen en blauw: drie subpixels.</t>
+        </is>
+      </c>
+      <c r="R1405" t="inlineStr">
+        <is>
+          <t>handmatig</t>
+        </is>
+      </c>
       <c r="S1405" t="inlineStr">
         <is>
           <t>DODE LINK</t>
@@ -70121,6 +74401,21 @@
           <t>geen EN-vertaling</t>
         </is>
       </c>
+      <c r="O1408" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/4K_resolution</t>
+        </is>
+      </c>
+      <c r="P1408" t="inlineStr">
+        <is>
+          <t>3840 bij 2160 is 8.294.400 beeldpunten.</t>
+        </is>
+      </c>
+      <c r="R1408" t="inlineStr">
+        <is>
+          <t>handmatig</t>
+        </is>
+      </c>
       <c r="S1408" t="inlineStr">
         <is>
           <t>DODE LINK</t>
@@ -70794,6 +75089,11 @@
           <t>geen bron · geen EN-vertaling</t>
         </is>
       </c>
+      <c r="S1421" t="inlineStr">
+        <is>
+          <t>geen bron mogelijk (onbruikbaar)</t>
+        </is>
+      </c>
     </row>
     <row r="1422">
       <c r="A1422" s="4" t="n">
@@ -70833,6 +75133,21 @@
         </is>
       </c>
       <c r="N1422" s="4" t="n"/>
+      <c r="O1422" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Motorola_DynaTAC</t>
+        </is>
+      </c>
+      <c r="P1422" t="inlineStr">
+        <is>
+          <t>De DynaTAC 8000X kwam in 1983 op de markt.</t>
+        </is>
+      </c>
+      <c r="R1422" t="inlineStr">
+        <is>
+          <t>handmatig</t>
+        </is>
+      </c>
       <c r="S1422" t="inlineStr">
         <is>
           <t>DODE LINK</t>
@@ -71073,6 +75388,21 @@
         </is>
       </c>
       <c r="N1427" s="4" t="n"/>
+      <c r="O1427" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Osborne_1</t>
+        </is>
+      </c>
+      <c r="P1427" t="inlineStr">
+        <is>
+          <t>De Osborne 1 verscheen in 1981.</t>
+        </is>
+      </c>
+      <c r="R1427" t="inlineStr">
+        <is>
+          <t>handmatig</t>
+        </is>
+      </c>
       <c r="S1427" t="inlineStr">
         <is>
           <t>DODE LINK</t>
@@ -71117,6 +75447,21 @@
         </is>
       </c>
       <c r="N1428" s="4" t="n"/>
+      <c r="O1428" t="inlineStr">
+        <is>
+          <t>https://info.cern.ch/</t>
+        </is>
+      </c>
+      <c r="P1428" t="inlineStr">
+        <is>
+          <t>De eerste website ging in 1991 online.</t>
+        </is>
+      </c>
+      <c r="R1428" t="inlineStr">
+        <is>
+          <t>handmatig</t>
+        </is>
+      </c>
       <c r="S1428" t="inlineStr">
         <is>
           <t>DODE LINK</t>
@@ -71465,6 +75810,21 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="O1435" t="inlineStr">
+        <is>
+          <t>https://www.atl.com/</t>
+        </is>
+      </c>
+      <c r="P1435" t="inlineStr">
+        <is>
+          <t>Atlanta Airport heeft zeven concourses.</t>
+        </is>
+      </c>
+      <c r="R1435" t="inlineStr">
+        <is>
+          <t>handmatig</t>
+        </is>
+      </c>
     </row>
     <row r="1436">
       <c r="A1436" s="4" t="n">
@@ -71562,6 +75922,21 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="O1437" t="inlineStr">
+        <is>
+          <t>https://www.oica.net/production-statistics/</t>
+        </is>
+      </c>
+      <c r="P1437" t="inlineStr">
+        <is>
+          <t>OICA publiceert de wereldproductie; rond de 85 miljoen personenautos per jaar.</t>
+        </is>
+      </c>
+      <c r="R1437" t="inlineStr">
+        <is>
+          <t>natellen</t>
+        </is>
+      </c>
     </row>
     <row r="1438">
       <c r="A1438" s="4" t="n">
@@ -72125,6 +76500,21 @@
         </is>
       </c>
       <c r="N1449" s="4" t="n"/>
+      <c r="O1449" t="inlineStr">
+        <is>
+          <t>https://airandspace.si.edu/collection-objects/1903-wright-flyer</t>
+        </is>
+      </c>
+      <c r="P1449" t="inlineStr">
+        <is>
+          <t>De Wright Flyer vloog op 17 december 1903.</t>
+        </is>
+      </c>
+      <c r="R1449" t="inlineStr">
+        <is>
+          <t>handmatig</t>
+        </is>
+      </c>
       <c r="S1449" t="inlineStr">
         <is>
           <t>DODE LINK</t>
@@ -72433,6 +76823,21 @@
       <c r="N1455" s="4" t="inlineStr">
         <is>
           <t>geen bron</t>
+        </is>
+      </c>
+      <c r="O1455" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Hexagon</t>
+        </is>
+      </c>
+      <c r="P1455" t="inlineStr">
+        <is>
+          <t>De binnenhoek van een regelmatige zeshoek is 120 graden.</t>
+        </is>
+      </c>
+      <c r="R1455" t="inlineStr">
+        <is>
+          <t>handmatig</t>
         </is>
       </c>
     </row>

--- a/vragen/vragen_review_compleet.xlsx
+++ b/vragen/vragen_review_compleet.xlsx
@@ -959,6 +959,21 @@
         </is>
       </c>
       <c r="N5" s="4" t="n"/>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>https://www.who.int/news-room/spotlight/history-of-vaccination/history-of-smallpox-vaccination</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Bestaande bron opgehaald; het antwoord staat op de pagina.</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
       <c r="S5" t="inlineStr">
         <is>
           <t>getal gezien op de pagina</t>
@@ -1125,6 +1140,21 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/King_penguin</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Bestaande bron opgehaald; het antwoord staat op de pagina.</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
       <c r="S8" t="inlineStr">
         <is>
           <t>getal gezien op de pagina</t>
@@ -1227,6 +1257,21 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>https://www.ifaw.org/international/journal/fastest-whales-dolphins-ocean</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Bestaande bron opgehaald; het antwoord staat op de pagina.</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
       <c r="S10" t="inlineStr">
         <is>
           <t>getal gezien op de pagina</t>
@@ -1281,6 +1326,21 @@
         </is>
       </c>
       <c r="N11" s="4" t="n"/>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Crab</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Bestaande bron opgehaald; het antwoord staat op de pagina.</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
       <c r="S11" t="inlineStr">
         <is>
           <t>bevestigd</t>
@@ -1388,6 +1448,21 @@
           <t>geen bron</t>
         </is>
       </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>https://www.coca-cola.com/ng/en/about-us/faq/how-much-sugar-is-in-cocacola-original-taste</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Bestaande bron opgehaald; het antwoord staat op de pagina.</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
       <c r="S13" t="inlineStr">
         <is>
           <t>getal gezien op de pagina</t>
@@ -2063,6 +2138,21 @@
         </is>
       </c>
       <c r="N25" s="4" t="n"/>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>https://www.esbnyc.com/about/facts-figures</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Bestaande bron opgehaald; het antwoord staat op de pagina.</t>
+        </is>
+      </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
       <c r="S25" t="inlineStr">
         <is>
           <t>getal gezien op de pagina</t>
@@ -2789,6 +2879,21 @@
         </is>
       </c>
       <c r="N39" s="4" t="n"/>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>https://plimoth.org/learn/just-kids/homework-help/mayflower</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Bestaande bron opgehaald; het antwoord staat op de pagina.</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
       <c r="S39" t="inlineStr">
         <is>
           <t>getal gezien op de pagina</t>
@@ -4583,6 +4688,21 @@
         </is>
       </c>
       <c r="N74" s="4" t="n"/>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>https://www.rsc.org/periodic-table/element/79/gold</t>
+        </is>
+      </c>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>Bestaande bron opgehaald; het antwoord staat op de pagina.</t>
+        </is>
+      </c>
+      <c r="R74" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
       <c r="S74" t="inlineStr">
         <is>
           <t>bevestigd</t>
@@ -6270,6 +6390,21 @@
         </is>
       </c>
       <c r="N107" s="4" t="n"/>
+      <c r="O107" t="inlineStr">
+        <is>
+          <t>https://www.nhs.uk/conditions/blood-groups/</t>
+        </is>
+      </c>
+      <c r="P107" t="inlineStr">
+        <is>
+          <t>Bestaande bron opgehaald; het antwoord staat op de pagina.</t>
+        </is>
+      </c>
+      <c r="R107" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
       <c r="S107" t="inlineStr">
         <is>
           <t>bevestigd</t>
@@ -6814,6 +6949,21 @@
         </is>
       </c>
       <c r="N118" s="4" t="n"/>
+      <c r="O118" t="inlineStr">
+        <is>
+          <t>https://www.mouthhealthy.org/all-topics-a-z/eruption-charts</t>
+        </is>
+      </c>
+      <c r="P118" t="inlineStr">
+        <is>
+          <t>Bestaande bron opgehaald; het antwoord staat op de pagina.</t>
+        </is>
+      </c>
+      <c r="R118" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
       <c r="S118" t="inlineStr">
         <is>
           <t>bevestigd</t>
@@ -7005,6 +7155,21 @@
         </is>
       </c>
       <c r="N122" s="4" t="n"/>
+      <c r="O122" t="inlineStr">
+        <is>
+          <t>https://www.nidcd.nih.gov/health/taste-disorders</t>
+        </is>
+      </c>
+      <c r="P122" t="inlineStr">
+        <is>
+          <t>Bestaande bron opgehaald; het antwoord staat op de pagina.</t>
+        </is>
+      </c>
+      <c r="R122" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
       <c r="S122" t="inlineStr">
         <is>
           <t>bevestigd</t>
@@ -7330,6 +7495,21 @@
         </is>
       </c>
       <c r="N128" s="4" t="n"/>
+      <c r="O128" t="inlineStr">
+        <is>
+          <t>https://www.genome.gov/human-genome-project/Completion-FAQ</t>
+        </is>
+      </c>
+      <c r="P128" t="inlineStr">
+        <is>
+          <t>Bestaande bron opgehaald; het antwoord staat op de pagina.</t>
+        </is>
+      </c>
+      <c r="R128" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
       <c r="S128" t="inlineStr">
         <is>
           <t>getal gezien op de pagina</t>
@@ -8421,6 +8601,21 @@
         </is>
       </c>
       <c r="N150" s="4" t="n"/>
+      <c r="O150" t="inlineStr">
+        <is>
+          <t>https://animals.sandiegozoo.org/animals/camel</t>
+        </is>
+      </c>
+      <c r="P150" t="inlineStr">
+        <is>
+          <t>Bestaande bron opgehaald; het antwoord staat op de pagina.</t>
+        </is>
+      </c>
+      <c r="R150" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
       <c r="S150" t="inlineStr">
         <is>
           <t>bevestigd</t>
@@ -8465,6 +8660,21 @@
         </is>
       </c>
       <c r="N151" s="4" t="n"/>
+      <c r="O151" t="inlineStr">
+        <is>
+          <t>https://animals.sandiegozoo.org/animals/camel</t>
+        </is>
+      </c>
+      <c r="P151" t="inlineStr">
+        <is>
+          <t>Bestaande bron opgehaald; het antwoord staat op de pagina.</t>
+        </is>
+      </c>
+      <c r="R151" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
       <c r="S151" t="inlineStr">
         <is>
           <t>bevestigd</t>
@@ -9614,6 +9824,21 @@
         </is>
       </c>
       <c r="N173" s="4" t="n"/>
+      <c r="O173" t="inlineStr">
+        <is>
+          <t>https://www.bceao.int/en/content/west-african-cfa-franc</t>
+        </is>
+      </c>
+      <c r="P173" t="inlineStr">
+        <is>
+          <t>Bestaande bron opgehaald; het antwoord staat op de pagina.</t>
+        </is>
+      </c>
+      <c r="R173" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
       <c r="S173" t="inlineStr">
         <is>
           <t>getal gezien op de pagina</t>
@@ -9826,6 +10051,21 @@
         </is>
       </c>
       <c r="N177" s="4" t="n"/>
+      <c r="O177" t="inlineStr">
+        <is>
+          <t>https://www.g7italy.it/en/about-g7/</t>
+        </is>
+      </c>
+      <c r="P177" t="inlineStr">
+        <is>
+          <t>Bestaande bron opgehaald; het antwoord staat op de pagina.</t>
+        </is>
+      </c>
+      <c r="R177" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
       <c r="S177" t="inlineStr">
         <is>
           <t>getal gezien op de pagina</t>
@@ -12059,6 +12299,21 @@
         </is>
       </c>
       <c r="N219" s="4" t="n"/>
+      <c r="O219" t="inlineStr">
+        <is>
+          <t>https://www.berlin.de/en/attractions-and-sights/3560266-3104050-brandenburg-gate.en.html</t>
+        </is>
+      </c>
+      <c r="P219" t="inlineStr">
+        <is>
+          <t>Bestaande bron opgehaald; het antwoord staat op de pagina.</t>
+        </is>
+      </c>
+      <c r="R219" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
       <c r="S219" t="inlineStr">
         <is>
           <t>bevestigd</t>
@@ -12304,6 +12559,21 @@
         </is>
       </c>
       <c r="N224" s="4" t="n"/>
+      <c r="O224" t="inlineStr">
+        <is>
+          <t>https://asi.nic.in/taj-mahal/</t>
+        </is>
+      </c>
+      <c r="P224" t="inlineStr">
+        <is>
+          <t>Bestaande bron opgehaald; het antwoord staat op de pagina.</t>
+        </is>
+      </c>
+      <c r="R224" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
       <c r="S224" t="inlineStr">
         <is>
           <t>getal gezien op de pagina</t>
@@ -20076,6 +20346,21 @@
         </is>
       </c>
       <c r="N375" s="4" t="n"/>
+      <c r="O375" t="inlineStr">
+        <is>
+          <t>https://www.ipcc.ch/report/ar6/wg1/chapter/chapter-5/</t>
+        </is>
+      </c>
+      <c r="P375" t="inlineStr">
+        <is>
+          <t>Bestaande bron opgehaald; het antwoord staat op de pagina.</t>
+        </is>
+      </c>
+      <c r="R375" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
       <c r="S375" t="inlineStr">
         <is>
           <t>getal gezien op de pagina</t>
@@ -20331,6 +20616,21 @@
         </is>
       </c>
       <c r="N380" s="4" t="n"/>
+      <c r="O380" t="inlineStr">
+        <is>
+          <t>https://www.usgs.gov/special-topics/water-science-school/science/where-earths-water</t>
+        </is>
+      </c>
+      <c r="P380" t="inlineStr">
+        <is>
+          <t>Bestaande bron opgehaald; het antwoord staat op de pagina.</t>
+        </is>
+      </c>
+      <c r="R380" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
       <c r="S380" t="inlineStr">
         <is>
           <t>bevestigd</t>
@@ -21320,6 +21620,21 @@
         </is>
       </c>
       <c r="N399" s="4" t="n"/>
+      <c r="O399" t="inlineStr">
+        <is>
+          <t>https://www.yamaha.com/en/musical_instrument_guide/piano/structure/</t>
+        </is>
+      </c>
+      <c r="P399" t="inlineStr">
+        <is>
+          <t>Bestaande bron opgehaald; het antwoord staat op de pagina.</t>
+        </is>
+      </c>
+      <c r="R399" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
       <c r="S399" t="inlineStr">
         <is>
           <t>bevestigd</t>
@@ -22760,6 +23075,21 @@
         </is>
       </c>
       <c r="N426" s="4" t="n"/>
+      <c r="O426" t="inlineStr">
+        <is>
+          <t>https://www.conseil-constitutionnel.fr/en/declaration-of-human-and-civic-rights-of-26-august-1789</t>
+        </is>
+      </c>
+      <c r="P426" t="inlineStr">
+        <is>
+          <t>Bestaande bron opgehaald; het antwoord staat op de pagina.</t>
+        </is>
+      </c>
+      <c r="R426" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
       <c r="S426" t="inlineStr">
         <is>
           <t>bevestigd</t>
@@ -22902,6 +23232,21 @@
         </is>
       </c>
       <c r="N429" s="4" t="n"/>
+      <c r="O429" t="inlineStr">
+        <is>
+          <t>https://www.nato.int/cps/en/natohq/topics_52044.htm</t>
+        </is>
+      </c>
+      <c r="P429" t="inlineStr">
+        <is>
+          <t>Bestaande bron opgehaald; het antwoord staat op de pagina.</t>
+        </is>
+      </c>
+      <c r="R429" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
       <c r="S429" t="inlineStr">
         <is>
           <t>getal gezien op de pagina</t>
@@ -23117,6 +23462,21 @@
         </is>
       </c>
       <c r="N433" s="4" t="n"/>
+      <c r="O433" t="inlineStr">
+        <is>
+          <t>https://www.nato.int/cps/en/natolive/topics_52044.htm</t>
+        </is>
+      </c>
+      <c r="P433" t="inlineStr">
+        <is>
+          <t>Bestaande bron opgehaald; het antwoord staat op de pagina.</t>
+        </is>
+      </c>
+      <c r="R433" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
       <c r="S433" t="inlineStr">
         <is>
           <t>getal gezien op de pagina</t>
@@ -24684,6 +25044,21 @@
         </is>
       </c>
       <c r="N463" s="4" t="n"/>
+      <c r="O463" t="inlineStr">
+        <is>
+          <t>https://openstax.org/books/chemistry-2e/pages/7-2-covalent-bonding</t>
+        </is>
+      </c>
+      <c r="P463" t="inlineStr">
+        <is>
+          <t>Bestaande bron opgehaald; het antwoord staat op de pagina.</t>
+        </is>
+      </c>
+      <c r="R463" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
       <c r="S463" t="inlineStr">
         <is>
           <t>bevestigd</t>
@@ -24728,6 +25103,21 @@
         </is>
       </c>
       <c r="N464" s="4" t="n"/>
+      <c r="O464" t="inlineStr">
+        <is>
+          <t>https://openstax.org/books/chemistry-2e/pages/2-3-atomic-structure-and-symbolism</t>
+        </is>
+      </c>
+      <c r="P464" t="inlineStr">
+        <is>
+          <t>Bestaande bron opgehaald; het antwoord staat op de pagina.</t>
+        </is>
+      </c>
+      <c r="R464" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
       <c r="S464" t="inlineStr">
         <is>
           <t>bevestigd</t>
@@ -24860,6 +25250,21 @@
         </is>
       </c>
       <c r="N467" s="4" t="n"/>
+      <c r="O467" t="inlineStr">
+        <is>
+          <t>https://pubchem.ncbi.nlm.nih.gov/compound/Carbon-dioxide</t>
+        </is>
+      </c>
+      <c r="P467" t="inlineStr">
+        <is>
+          <t>Bestaande bron opgehaald; het antwoord staat op de pagina.</t>
+        </is>
+      </c>
+      <c r="R467" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
       <c r="S467" t="inlineStr">
         <is>
           <t>bevestigd</t>
@@ -25100,6 +25505,21 @@
         </is>
       </c>
       <c r="N472" s="4" t="n"/>
+      <c r="O472" t="inlineStr">
+        <is>
+          <t>https://iupac.org/what-we-do/periodic-table-of-elements/</t>
+        </is>
+      </c>
+      <c r="P472" t="inlineStr">
+        <is>
+          <t>Bestaande bron opgehaald; het antwoord staat op de pagina.</t>
+        </is>
+      </c>
+      <c r="R472" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
       <c r="S472" t="inlineStr">
         <is>
           <t>bevestigd</t>
@@ -25144,6 +25564,21 @@
         </is>
       </c>
       <c r="N473" s="4" t="n"/>
+      <c r="O473" t="inlineStr">
+        <is>
+          <t>https://www.ecfr.gov/current/title-21/chapter-I/subchapter-B/part-169</t>
+        </is>
+      </c>
+      <c r="P473" t="inlineStr">
+        <is>
+          <t>Bestaande bron opgehaald; het antwoord staat op de pagina.</t>
+        </is>
+      </c>
+      <c r="R473" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
       <c r="S473" t="inlineStr">
         <is>
           <t>getal gezien op de pagina</t>
@@ -25188,6 +25623,21 @@
         </is>
       </c>
       <c r="N474" s="4" t="n"/>
+      <c r="O474" t="inlineStr">
+        <is>
+          <t>https://www.rsc.org/periodic-table/element/92/uranium</t>
+        </is>
+      </c>
+      <c r="P474" t="inlineStr">
+        <is>
+          <t>Bestaande bron opgehaald; het antwoord staat op de pagina.</t>
+        </is>
+      </c>
+      <c r="R474" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
       <c r="S474" t="inlineStr">
         <is>
           <t>bevestigd</t>
@@ -25232,6 +25682,21 @@
         </is>
       </c>
       <c r="N475" s="4" t="n"/>
+      <c r="O475" t="inlineStr">
+        <is>
+          <t>https://www.rsc.org/periodic-table/element/74/tungsten</t>
+        </is>
+      </c>
+      <c r="P475" t="inlineStr">
+        <is>
+          <t>Bestaande bron opgehaald; het antwoord staat op de pagina.</t>
+        </is>
+      </c>
+      <c r="R475" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
       <c r="S475" t="inlineStr">
         <is>
           <t>bevestigd</t>
@@ -25330,6 +25795,21 @@
         </is>
       </c>
       <c r="N477" s="4" t="n"/>
+      <c r="O477" t="inlineStr">
+        <is>
+          <t>https://www.usgs.gov/special-topics/water-science-school/science/ph-and-water</t>
+        </is>
+      </c>
+      <c r="P477" t="inlineStr">
+        <is>
+          <t>Bestaande bron opgehaald; het antwoord staat op de pagina.</t>
+        </is>
+      </c>
+      <c r="R477" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
       <c r="S477" t="inlineStr">
         <is>
           <t>bevestigd</t>
@@ -26067,6 +26547,21 @@
         </is>
       </c>
       <c r="N491" s="4" t="n"/>
+      <c r="O491" t="inlineStr">
+        <is>
+          <t>https://handbook.fide.com/chapter/E012023</t>
+        </is>
+      </c>
+      <c r="P491" t="inlineStr">
+        <is>
+          <t>Bestaande bron opgehaald; het antwoord staat op de pagina.</t>
+        </is>
+      </c>
+      <c r="R491" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
       <c r="S491" t="inlineStr">
         <is>
           <t>bevestigd</t>
@@ -26530,6 +27025,21 @@
         </is>
       </c>
       <c r="N500" s="4" t="n"/>
+      <c r="O500" t="inlineStr">
+        <is>
+          <t>https://operations.nfl.com/the-rules/nfl-rulebook/</t>
+        </is>
+      </c>
+      <c r="P500" t="inlineStr">
+        <is>
+          <t>Bestaande bron opgehaald; het antwoord staat op de pagina.</t>
+        </is>
+      </c>
+      <c r="R500" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
       <c r="S500" t="inlineStr">
         <is>
           <t>bevestigd</t>
@@ -26716,6 +27226,21 @@
         </is>
       </c>
       <c r="N504" s="4" t="n"/>
+      <c r="O504" t="inlineStr">
+        <is>
+          <t>https://www.theifab.com/laws/latest/the-players/</t>
+        </is>
+      </c>
+      <c r="P504" t="inlineStr">
+        <is>
+          <t>Bestaande bron opgehaald; het antwoord staat op de pagina.</t>
+        </is>
+      </c>
+      <c r="R504" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
       <c r="S504" t="inlineStr">
         <is>
           <t>getal gezien op de pagina</t>
@@ -27015,6 +27540,21 @@
         </is>
       </c>
       <c r="N510" s="4" t="n"/>
+      <c r="O510" t="inlineStr">
+        <is>
+          <t>https://science.nasa.gov/jupiter/facts/</t>
+        </is>
+      </c>
+      <c r="P510" t="inlineStr">
+        <is>
+          <t>Bestaande bron opgehaald; het antwoord staat op de pagina.</t>
+        </is>
+      </c>
+      <c r="R510" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
       <c r="S510" t="inlineStr">
         <is>
           <t>getal gezien op de pagina</t>
@@ -27059,6 +27599,21 @@
         </is>
       </c>
       <c r="N511" s="4" t="n"/>
+      <c r="O511" t="inlineStr">
+        <is>
+          <t>https://science.nasa.gov/venus/venus-facts/</t>
+        </is>
+      </c>
+      <c r="P511" t="inlineStr">
+        <is>
+          <t>Bestaande bron opgehaald; het antwoord staat op de pagina.</t>
+        </is>
+      </c>
+      <c r="R511" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
       <c r="S511" t="inlineStr">
         <is>
           <t>getal gezien op de pagina</t>
@@ -27103,6 +27658,21 @@
         </is>
       </c>
       <c r="N512" s="4" t="n"/>
+      <c r="O512" t="inlineStr">
+        <is>
+          <t>https://science.nasa.gov/neptune/facts/</t>
+        </is>
+      </c>
+      <c r="P512" t="inlineStr">
+        <is>
+          <t>Bestaande bron opgehaald; het antwoord staat op de pagina.</t>
+        </is>
+      </c>
+      <c r="R512" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
       <c r="S512" t="inlineStr">
         <is>
           <t>getal gezien op de pagina</t>
@@ -28345,6 +28915,21 @@
         </is>
       </c>
       <c r="N536" s="4" t="n"/>
+      <c r="O536" t="inlineStr">
+        <is>
+          <t>https://science.nasa.gov/moon/facts/</t>
+        </is>
+      </c>
+      <c r="P536" t="inlineStr">
+        <is>
+          <t>Bestaande bron opgehaald; het antwoord staat op de pagina.</t>
+        </is>
+      </c>
+      <c r="R536" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
       <c r="S536" t="inlineStr">
         <is>
           <t>bevestigd</t>
@@ -30329,6 +30914,21 @@
         </is>
       </c>
       <c r="N574" s="4" t="n"/>
+      <c r="O574" t="inlineStr">
+        <is>
+          <t>https://tfl.gov.uk/corporate/about-tfl/what-we-do/london-underground</t>
+        </is>
+      </c>
+      <c r="P574" t="inlineStr">
+        <is>
+          <t>Bestaande bron opgehaald; het antwoord staat op de pagina.</t>
+        </is>
+      </c>
+      <c r="R574" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
       <c r="S574" t="inlineStr">
         <is>
           <t>bevestigd</t>
@@ -30373,9 +30973,24 @@
         </is>
       </c>
       <c r="N575" s="4" t="n"/>
+      <c r="O575" t="inlineStr">
+        <is>
+          <t>https://www.airbus.com/en/products-services/commercial-aircraft/passenger-aircraft/a380</t>
+        </is>
+      </c>
+      <c r="P575" t="inlineStr">
+        <is>
+          <t>Bestaande bron opgehaald; het antwoord staat op de pagina.</t>
+        </is>
+      </c>
       <c r="Q575" t="inlineStr">
         <is>
           <t>Wikidata: klopt</t>
+        </is>
+      </c>
+      <c r="R575" t="inlineStr">
+        <is>
+          <t>hoog</t>
         </is>
       </c>
       <c r="S575" t="inlineStr">
@@ -32097,6 +32712,21 @@
         </is>
       </c>
       <c r="N609" s="4" t="n"/>
+      <c r="O609" t="inlineStr">
+        <is>
+          <t>https://www.ncbi.nlm.nih.gov/books/NBK470353/</t>
+        </is>
+      </c>
+      <c r="P609" t="inlineStr">
+        <is>
+          <t>Bestaande bron opgehaald; het antwoord staat op de pagina.</t>
+        </is>
+      </c>
+      <c r="R609" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
       <c r="S609" t="inlineStr">
         <is>
           <t>bevestigd</t>
@@ -32141,6 +32771,21 @@
         </is>
       </c>
       <c r="N610" s="4" t="n"/>
+      <c r="O610" t="inlineStr">
+        <is>
+          <t>https://www.usgs.gov/special-topics/water-science-school/science/water-you-water-and-human-body</t>
+        </is>
+      </c>
+      <c r="P610" t="inlineStr">
+        <is>
+          <t>Bestaande bron opgehaald; het antwoord staat op de pagina.</t>
+        </is>
+      </c>
+      <c r="R610" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
       <c r="S610" t="inlineStr">
         <is>
           <t>getal gezien op de pagina</t>
@@ -33631,6 +34276,21 @@
         </is>
       </c>
       <c r="N640" s="4" t="n"/>
+      <c r="O640" t="inlineStr">
+        <is>
+          <t>https://nationalzoo.si.edu/animals/aldabra-tortoise</t>
+        </is>
+      </c>
+      <c r="P640" t="inlineStr">
+        <is>
+          <t>Bestaande bron opgehaald; het antwoord staat op de pagina.</t>
+        </is>
+      </c>
+      <c r="R640" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
       <c r="S640" t="inlineStr">
         <is>
           <t>getal gezien op de pagina</t>
@@ -34986,6 +35646,21 @@
         </is>
       </c>
       <c r="N665" s="4" t="n"/>
+      <c r="O665" t="inlineStr">
+        <is>
+          <t>https://flybase.org/</t>
+        </is>
+      </c>
+      <c r="P665" t="inlineStr">
+        <is>
+          <t>Bestaande bron opgehaald; het antwoord staat op de pagina.</t>
+        </is>
+      </c>
+      <c r="R665" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
       <c r="S665" t="inlineStr">
         <is>
           <t>getal gezien op de pagina</t>
@@ -35133,6 +35808,21 @@
         </is>
       </c>
       <c r="N668" s="4" t="n"/>
+      <c r="O668" t="inlineStr">
+        <is>
+          <t>https://www.fisheries.noaa.gov/species/american-lobster</t>
+        </is>
+      </c>
+      <c r="P668" t="inlineStr">
+        <is>
+          <t>Bestaande bron opgehaald; het antwoord staat op de pagina.</t>
+        </is>
+      </c>
+      <c r="R668" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
       <c r="S668" t="inlineStr">
         <is>
           <t>bevestigd</t>
@@ -39583,6 +40273,21 @@
         </is>
       </c>
       <c r="N752" s="4" t="n"/>
+      <c r="O752" t="inlineStr">
+        <is>
+          <t>https://www.alpconv.org/en/home/</t>
+        </is>
+      </c>
+      <c r="P752" t="inlineStr">
+        <is>
+          <t>Bestaande bron opgehaald; het antwoord staat op de pagina.</t>
+        </is>
+      </c>
+      <c r="R752" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
       <c r="S752" t="inlineStr">
         <is>
           <t>getal gezien op de pagina</t>
@@ -44508,6 +45213,21 @@
           <t>geen EN-vertaling</t>
         </is>
       </c>
+      <c r="O843" t="inlineStr">
+        <is>
+          <t>https://education.nationalgeographic.org/resource/equator/</t>
+        </is>
+      </c>
+      <c r="P843" t="inlineStr">
+        <is>
+          <t>Bestaande bron opgehaald; het antwoord staat op de pagina.</t>
+        </is>
+      </c>
+      <c r="R843" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
       <c r="S843" t="inlineStr">
         <is>
           <t>getal gezien op de pagina</t>
@@ -55216,6 +55936,21 @@
         </is>
       </c>
       <c r="N1044" s="4" t="n"/>
+      <c r="O1044" t="inlineStr">
+        <is>
+          <t>https://www.fao.org/aquastat/en/overview/methodology/water-use</t>
+        </is>
+      </c>
+      <c r="P1044" t="inlineStr">
+        <is>
+          <t>Bestaande bron opgehaald; het antwoord staat op de pagina.</t>
+        </is>
+      </c>
+      <c r="R1044" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
       <c r="S1044" t="inlineStr">
         <is>
           <t>getal gezien op de pagina</t>
@@ -64456,6 +65191,21 @@
         </is>
       </c>
       <c r="N1217" s="4" t="n"/>
+      <c r="O1217" t="inlineStr">
+        <is>
+          <t>https://www.un.org/en/about-us/history-of-the-un</t>
+        </is>
+      </c>
+      <c r="P1217" t="inlineStr">
+        <is>
+          <t>Bestaande bron opgehaald; het antwoord staat op de pagina.</t>
+        </is>
+      </c>
+      <c r="R1217" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
       <c r="S1217" t="inlineStr">
         <is>
           <t>getal gezien op de pagina</t>
@@ -67256,6 +68006,21 @@
         </is>
       </c>
       <c r="N1270" s="4" t="n"/>
+      <c r="O1270" t="inlineStr">
+        <is>
+          <t>https://openstax.org/books/chemistry-2e/pages/2-3-atomic-structure-and-symbolism</t>
+        </is>
+      </c>
+      <c r="P1270" t="inlineStr">
+        <is>
+          <t>Bestaande bron opgehaald; het antwoord staat op de pagina.</t>
+        </is>
+      </c>
+      <c r="R1270" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
       <c r="S1270" t="inlineStr">
         <is>
           <t>bevestigd</t>
@@ -67359,6 +68124,21 @@
         </is>
       </c>
       <c r="N1272" s="4" t="n"/>
+      <c r="O1272" t="inlineStr">
+        <is>
+          <t>https://openstax.org/books/chemistry-2e/pages/7-2-covalent-bonding</t>
+        </is>
+      </c>
+      <c r="P1272" t="inlineStr">
+        <is>
+          <t>Bestaande bron opgehaald; het antwoord staat op de pagina.</t>
+        </is>
+      </c>
+      <c r="R1272" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
       <c r="S1272" t="inlineStr">
         <is>
           <t>bevestigd</t>
@@ -68199,6 +68979,21 @@
         </is>
       </c>
       <c r="N1288" s="4" t="n"/>
+      <c r="O1288" t="inlineStr">
+        <is>
+          <t>https://handbook.fide.com/chapter/E012023</t>
+        </is>
+      </c>
+      <c r="P1288" t="inlineStr">
+        <is>
+          <t>Bestaande bron opgehaald; het antwoord staat op de pagina.</t>
+        </is>
+      </c>
+      <c r="R1288" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
       <c r="S1288" t="inlineStr">
         <is>
           <t>bevestigd</t>
@@ -68792,6 +69587,21 @@
         </is>
       </c>
       <c r="N1299" s="4" t="n"/>
+      <c r="O1299" t="inlineStr">
+        <is>
+          <t>https://www.randa.org/en/rog/the-rules-of-golf</t>
+        </is>
+      </c>
+      <c r="P1299" t="inlineStr">
+        <is>
+          <t>Bestaande bron opgehaald; het antwoord staat op de pagina.</t>
+        </is>
+      </c>
+      <c r="R1299" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
       <c r="S1299" t="inlineStr">
         <is>
           <t>bevestigd</t>
@@ -68880,6 +69690,21 @@
         </is>
       </c>
       <c r="N1301" s="4" t="n"/>
+      <c r="O1301" t="inlineStr">
+        <is>
+          <t>https://www.randa.org/en/rog/the-rules-of-golf</t>
+        </is>
+      </c>
+      <c r="P1301" t="inlineStr">
+        <is>
+          <t>Bestaande bron opgehaald; het antwoord staat op de pagina.</t>
+        </is>
+      </c>
+      <c r="R1301" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
       <c r="S1301" t="inlineStr">
         <is>
           <t>bevestigd</t>
@@ -70272,6 +71097,21 @@
         </is>
       </c>
       <c r="N1327" s="4" t="n"/>
+      <c r="O1327" t="inlineStr">
+        <is>
+          <t>https://www.theifab.com/laws/latest/the-field-of-play/</t>
+        </is>
+      </c>
+      <c r="P1327" t="inlineStr">
+        <is>
+          <t>Bestaande bron opgehaald; het antwoord staat op de pagina.</t>
+        </is>
+      </c>
+      <c r="R1327" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
       <c r="S1327" t="inlineStr">
         <is>
           <t>getal gezien op de pagina</t>
@@ -70472,6 +71312,21 @@
         </is>
       </c>
       <c r="N1331" s="4" t="n"/>
+      <c r="O1331" t="inlineStr">
+        <is>
+          <t>https://www.theifab.com/laws/latest/the-field-of-play/</t>
+        </is>
+      </c>
+      <c r="P1331" t="inlineStr">
+        <is>
+          <t>Bestaande bron opgehaald; het antwoord staat op de pagina.</t>
+        </is>
+      </c>
+      <c r="R1331" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
       <c r="S1331" t="inlineStr">
         <is>
           <t>getal gezien op de pagina</t>
@@ -70727,6 +71582,21 @@
         </is>
       </c>
       <c r="N1336" s="4" t="n"/>
+      <c r="O1336" t="inlineStr">
+        <is>
+          <t>https://operations.nfl.com/the-rules/nfl-rulebook/</t>
+        </is>
+      </c>
+      <c r="P1336" t="inlineStr">
+        <is>
+          <t>Bestaande bron opgehaald; het antwoord staat op de pagina.</t>
+        </is>
+      </c>
+      <c r="R1336" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
       <c r="S1336" t="inlineStr">
         <is>
           <t>bevestigd</t>
@@ -72664,6 +73534,21 @@
         </is>
       </c>
       <c r="N1374" s="4" t="n"/>
+      <c r="O1374" t="inlineStr">
+        <is>
+          <t>https://science.nasa.gov/solar-system/planets/</t>
+        </is>
+      </c>
+      <c r="P1374" t="inlineStr">
+        <is>
+          <t>Bestaande bron opgehaald; het antwoord staat op de pagina.</t>
+        </is>
+      </c>
+      <c r="R1374" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
       <c r="S1374" t="inlineStr">
         <is>
           <t>bevestigd</t>
@@ -73333,6 +74218,21 @@
         </is>
       </c>
       <c r="N1387" s="4" t="n"/>
+      <c r="O1387" t="inlineStr">
+        <is>
+          <t>https://www.nasa.gov/mission/apollo-11/</t>
+        </is>
+      </c>
+      <c r="P1387" t="inlineStr">
+        <is>
+          <t>Bestaande bron opgehaald; het antwoord staat op de pagina.</t>
+        </is>
+      </c>
+      <c r="R1387" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
       <c r="S1387" t="inlineStr">
         <is>
           <t>getal gezien op de pagina</t>
@@ -73677,6 +74577,21 @@
         </is>
       </c>
       <c r="N1394" s="4" t="n"/>
+      <c r="O1394" t="inlineStr">
+        <is>
+          <t>https://science.nasa.gov/sun/facts/</t>
+        </is>
+      </c>
+      <c r="P1394" t="inlineStr">
+        <is>
+          <t>Bestaande bron opgehaald; het antwoord staat op de pagina.</t>
+        </is>
+      </c>
+      <c r="R1394" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
       <c r="S1394" t="inlineStr">
         <is>
           <t>bevestigd</t>
@@ -74314,6 +75229,21 @@
           <t>geen EN-vertaling</t>
         </is>
       </c>
+      <c r="O1406" t="inlineStr">
+        <is>
+          <t>https://physics.nist.gov/cuu/Units/binary.html</t>
+        </is>
+      </c>
+      <c r="P1406" t="inlineStr">
+        <is>
+          <t>Bestaande bron opgehaald; het antwoord staat op de pagina.</t>
+        </is>
+      </c>
+      <c r="R1406" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
       <c r="S1406" t="inlineStr">
         <is>
           <t>bevestigd</t>
@@ -74358,6 +75288,21 @@
         </is>
       </c>
       <c r="N1407" s="4" t="n"/>
+      <c r="O1407" t="inlineStr">
+        <is>
+          <t>https://physics.nist.gov/cuu/Units/binary.html</t>
+        </is>
+      </c>
+      <c r="P1407" t="inlineStr">
+        <is>
+          <t>Bestaande bron opgehaald; het antwoord staat op de pagina.</t>
+        </is>
+      </c>
+      <c r="R1407" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
       <c r="S1407" t="inlineStr">
         <is>
           <t>bevestigd</t>
@@ -75344,6 +76289,21 @@
         </is>
       </c>
       <c r="N1426" s="4" t="n"/>
+      <c r="O1426" t="inlineStr">
+        <is>
+          <t>https://www.ibm.com/history/floppy-disk</t>
+        </is>
+      </c>
+      <c r="P1426" t="inlineStr">
+        <is>
+          <t>Bestaande bron opgehaald; het antwoord staat op de pagina.</t>
+        </is>
+      </c>
+      <c r="R1426" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
       <c r="S1426" t="inlineStr">
         <is>
           <t>getal gezien op de pagina</t>
@@ -76933,6 +77893,21 @@
         </is>
       </c>
       <c r="N1457" s="4" t="n"/>
+      <c r="O1457" t="inlineStr">
+        <is>
+          <t>https://mathworld.wolfram.com/Divisor.html</t>
+        </is>
+      </c>
+      <c r="P1457" t="inlineStr">
+        <is>
+          <t>Bestaande bron opgehaald; het antwoord staat op de pagina.</t>
+        </is>
+      </c>
+      <c r="R1457" t="inlineStr">
+        <is>
+          <t>hoog</t>
+        </is>
+      </c>
       <c r="S1457" t="inlineStr">
         <is>
           <t>bevestigd</t>
